--- a/ComfortDelGro-Equity-Valuation.xlsx
+++ b/ComfortDelGro-Equity-Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChengJing\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4027C114-7BA7-4571-B617-EA2A19242798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE882FB5-321F-4D30-81D7-65E06C1E01BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D93AAA56-1308-4026-9D8F-E913B55E5CC3}"/>
   </bookViews>
@@ -2872,7 +2872,7 @@
     <xf numFmtId="169" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3013,6 +3013,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="44" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3025,7 +3026,7 @@
     <xf numFmtId="0" fontId="19" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="20% - Accent1 2" xfId="21" xr:uid="{7F1DC058-3DA4-4945-98D8-2DC0ECB9F210}"/>
@@ -4807,7 +4808,7 @@
       <c r="B70" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="C70" s="116">
+      <c r="C70" s="112">
         <f ca="1">C68*1000000/C69</f>
         <v>0.9578190953376885</v>
       </c>
@@ -4849,10 +4850,12 @@
         <v>2.8482165008562825</v>
       </c>
       <c r="F79" s="97">
-        <v>3.96</v>
+        <f>E79+1</f>
+        <v>3.8482165008562825</v>
       </c>
       <c r="G79" s="97">
-        <v>3.96</v>
+        <f>F79+1</f>
+        <v>4.8482165008562825</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4986,13 +4989,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -5250,17 +5253,17 @@
       <c r="A1" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115" t="s">
+      <c r="C1" s="116"/>
+      <c r="D1" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -6880,51 +6883,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="113" t="s">
         <v>252</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="I1" s="112" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="I1" s="113" t="s">
         <v>320</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="S1" s="112" t="s">
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="S1" s="113" t="s">
         <v>444</v>
       </c>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="AB1" s="112" t="s">
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="AB1" s="113" t="s">
         <v>504</v>
       </c>
-      <c r="AC1" s="112"/>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="112"/>
-      <c r="AG1" s="112"/>
-      <c r="AH1" s="112"/>
-      <c r="AK1" s="112" t="s">
+      <c r="AC1" s="113"/>
+      <c r="AD1" s="113"/>
+      <c r="AE1" s="113"/>
+      <c r="AF1" s="113"/>
+      <c r="AG1" s="113"/>
+      <c r="AH1" s="113"/>
+      <c r="AK1" s="113" t="s">
         <v>232</v>
       </c>
-      <c r="AL1" s="112"/>
-      <c r="AM1" s="112"/>
-      <c r="AN1" s="112"/>
-      <c r="AO1" s="112"/>
-      <c r="AP1" s="112"/>
-      <c r="AQ1" s="112"/>
+      <c r="AL1" s="113"/>
+      <c r="AM1" s="113"/>
+      <c r="AN1" s="113"/>
+      <c r="AO1" s="113"/>
+      <c r="AP1" s="113"/>
+      <c r="AQ1" s="113"/>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
@@ -13709,14 +13712,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
       <c r="G1" s="104"/>
       <c r="H1" s="104"/>
       <c r="I1" s="104"/>
@@ -16705,13 +16708,13 @@
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
-      <c r="E2" s="114" t="s">
+      <c r="E2" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="41" t="s">
@@ -19581,13 +19584,13 @@
         <v>132</v>
       </c>
       <c r="D1" s="49"/>
-      <c r="E1" s="115" t="s">
+      <c r="E1" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="41" t="s">
@@ -19858,34 +19861,34 @@
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="117">
         <f>'Profit &amp; loss'!C32</f>
         <v>-368.4</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="117">
         <f>'Profit &amp; loss'!D32</f>
         <v>-399.6</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="117">
         <f>E12+E5</f>
         <v>-437.32044448529803</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="117">
         <f t="shared" ref="F14:I14" ca="1" si="5">F12+F5</f>
         <v>-471.88960848717466</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="117">
         <f t="shared" ca="1" si="5"/>
         <v>-502.70316984993144</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="117">
         <f t="shared" ca="1" si="5"/>
         <v>-530.38300837039526</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="117">
         <f t="shared" ca="1" si="5"/>
         <v>-555.55292720866862</v>
       </c>
@@ -19915,13 +19918,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">

--- a/ComfortDelGro-Equity-Valuation.xlsx
+++ b/ComfortDelGro-Equity-Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChengJing\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE882FB5-321F-4D30-81D7-65E06C1E01BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC634B8-E728-4FEE-A5B5-C118D80222AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D93AAA56-1308-4026-9D8F-E913B55E5CC3}"/>
   </bookViews>
@@ -473,7 +473,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="571">
   <si>
     <t>Net income</t>
   </si>
@@ -1210,9 +1210,6 @@
     <t>Implied Share Price</t>
   </si>
   <si>
-    <t>Diluted shares oustanbding</t>
-  </si>
-  <si>
     <t xml:space="preserve">Basic shares oustanding </t>
   </si>
   <si>
@@ -1228,9 +1225,6 @@
     <t>Sensitivity table</t>
   </si>
   <si>
-    <t>Exit multiplier</t>
-  </si>
-  <si>
     <t>STI:</t>
   </si>
   <si>
@@ -2183,6 +2177,15 @@
   </si>
   <si>
     <t>levered historical beta:</t>
+  </si>
+  <si>
+    <t>Diluted shares outstanding</t>
+  </si>
+  <si>
+    <t>Terminal growth</t>
+  </si>
+  <si>
+    <t>Diluted shares oustanding</t>
   </si>
 </sst>
 </file>
@@ -3014,6 +3017,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="44" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3026,7 +3030,6 @@
     <xf numFmtId="0" fontId="19" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="37" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="20% - Accent1 2" xfId="21" xr:uid="{7F1DC058-3DA4-4945-98D8-2DC0ECB9F210}"/>
@@ -3606,18 +3609,23 @@
         <v>-2272</v>
       </c>
       <c r="E11" s="37">
+        <f>'Profit &amp; loss'!E14</f>
         <v>-2353.4732930059699</v>
       </c>
       <c r="F11" s="37">
+        <f>'Profit &amp; loss'!F14</f>
         <v>-2402.8782667141104</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="37">
+        <f>'Profit &amp; loss'!G14</f>
         <v>-2450.9358320483925</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="37">
+        <f>'Profit &amp; loss'!H14</f>
         <v>-2499.9545486893608</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="37">
+        <f>'Profit &amp; loss'!I14</f>
         <v>-2552.4535942118373</v>
       </c>
     </row>
@@ -3634,18 +3642,23 @@
         <v>-644.29999999999995</v>
       </c>
       <c r="E12" s="37">
+        <f>'Profit &amp; loss'!E15</f>
         <v>-667.40442019531088</v>
       </c>
       <c r="F12" s="37">
+        <f>'Profit &amp; loss'!F15</f>
         <v>-681.41481832918191</v>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="37">
+        <f>'Profit &amp; loss'!G15</f>
         <v>-695.04311469576555</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="37">
+        <f>'Profit &amp; loss'!H15</f>
         <v>-708.94397698968089</v>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="37">
+        <f>'Profit &amp; loss'!I15</f>
         <v>-723.83180050646422</v>
       </c>
     </row>
@@ -3662,18 +3675,23 @@
         <v>-350.9</v>
       </c>
       <c r="E13" s="37">
+        <f>'Profit &amp; loss'!E16</f>
         <v>-363.48317716364204</v>
       </c>
       <c r="F13" s="37">
+        <f>'Profit &amp; loss'!F16</f>
         <v>-371.11354920333679</v>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="37">
+        <f>'Profit &amp; loss'!G16</f>
         <v>-378.53582018740354</v>
       </c>
-      <c r="H13" s="75">
+      <c r="H13" s="37">
+        <f>'Profit &amp; loss'!H16</f>
         <v>-386.10653659115167</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="37">
+        <f>'Profit &amp; loss'!I16</f>
         <v>-394.21477385956581</v>
       </c>
     </row>
@@ -3690,19 +3708,24 @@
         <v>-349.3</v>
       </c>
       <c r="E14" s="37">
-        <v>-408.87568412822515</v>
+        <f ca="1">'Profit &amp; loss'!E17</f>
+        <v>-361.82580160518722</v>
       </c>
       <c r="F14" s="37">
-        <v>-417.45895230648944</v>
-      </c>
-      <c r="G14" s="75">
-        <v>-425.80813135261923</v>
-      </c>
-      <c r="H14" s="75">
-        <v>-434.32429397967161</v>
-      </c>
-      <c r="I14" s="75">
-        <v>-443.4451041532447</v>
+        <f ca="1">'Profit &amp; loss'!F17</f>
+        <v>-369.42138140987623</v>
+      </c>
+      <c r="G14" s="37">
+        <f ca="1">'Profit &amp; loss'!G17</f>
+        <v>-376.80980903807375</v>
+      </c>
+      <c r="H14" s="37">
+        <f ca="1">'Profit &amp; loss'!H17</f>
+        <v>-384.34600521883527</v>
+      </c>
+      <c r="I14" s="37">
+        <f ca="1">'Profit &amp; loss'!I17</f>
+        <v>-392.41727132843079</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -3718,19 +3741,24 @@
         <v>-90</v>
       </c>
       <c r="E15" s="37">
-        <v>-105.35016195688596</v>
+        <f>'Profit &amp; loss'!E18</f>
+        <v>-93.227375163088595</v>
       </c>
       <c r="F15" s="37">
-        <v>-107.56171115827097</v>
-      </c>
-      <c r="G15" s="75">
-        <v>-109.71294538143638</v>
-      </c>
-      <c r="H15" s="75">
-        <v>-111.90720428906512</v>
-      </c>
-      <c r="I15" s="75">
-        <v>-114.25725557913547</v>
+        <f>'Profit &amp; loss'!F18</f>
+        <v>-95.184438382161076</v>
+      </c>
+      <c r="G15" s="37">
+        <f>'Profit &amp; loss'!G18</f>
+        <v>-97.088127149804293</v>
+      </c>
+      <c r="H15" s="37">
+        <f>'Profit &amp; loss'!H18</f>
+        <v>-99.029889692800381</v>
+      </c>
+      <c r="I15" s="37">
+        <f>'Profit &amp; loss'!I18</f>
+        <v>-101.10951737634919</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
@@ -3746,19 +3774,24 @@
         <v>-122.6</v>
       </c>
       <c r="E16" s="37">
-        <v>-143.51033173238019</v>
+        <f ca="1">'Profit &amp; loss'!E19</f>
+        <v>-126.99640216660735</v>
       </c>
       <c r="F16" s="37">
-        <v>-146.52295320004467</v>
-      </c>
-      <c r="G16" s="75">
-        <v>-149.45341226404557</v>
-      </c>
-      <c r="H16" s="75">
-        <v>-152.44248050932649</v>
-      </c>
-      <c r="I16" s="75">
-        <v>-155.64377260002234</v>
+        <f ca="1">'Profit &amp; loss'!F19</f>
+        <v>-129.66235717392163</v>
+      </c>
+      <c r="G16" s="37">
+        <f ca="1">'Profit &amp; loss'!G19</f>
+        <v>-132.25560431740007</v>
+      </c>
+      <c r="H16" s="37">
+        <f ca="1">'Profit &amp; loss'!H19</f>
+        <v>-134.90071640374808</v>
+      </c>
+      <c r="I16" s="37">
+        <f ca="1">'Profit &amp; loss'!I19</f>
+        <v>-137.73363144822679</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -3774,18 +3807,23 @@
         <v>-97.5</v>
       </c>
       <c r="E17" s="37">
+        <f>'Profit &amp; loss'!E20</f>
         <v>-100.99632309334598</v>
       </c>
       <c r="F17" s="37">
+        <f>'Profit &amp; loss'!F20</f>
         <v>-103.11647491400781</v>
       </c>
-      <c r="G17" s="75">
+      <c r="G17" s="37">
+        <f>'Profit &amp; loss'!G20</f>
         <v>-105.17880441228797</v>
       </c>
-      <c r="H17" s="75">
+      <c r="H17" s="37">
+        <f>'Profit &amp; loss'!H20</f>
         <v>-107.28238050053375</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="37">
+        <f>'Profit &amp; loss'!I20</f>
         <v>-109.53531049104495</v>
       </c>
     </row>
@@ -3802,18 +3840,23 @@
         <v>-85.7</v>
       </c>
       <c r="E18" s="37">
+        <f>'Profit &amp; loss'!E21</f>
         <v>-88.773178349741031</v>
       </c>
       <c r="F18" s="37">
+        <f>'Profit &amp; loss'!F21</f>
         <v>-90.636737437235595</v>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="37">
+        <f>'Profit &amp; loss'!G21</f>
         <v>-92.449472185980298</v>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="37">
+        <f>'Profit &amp; loss'!H21</f>
         <v>-94.298461629699915</v>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="37">
+        <f>'Profit &amp; loss'!I21</f>
         <v>-96.278729323923628</v>
       </c>
     </row>
@@ -3830,18 +3873,23 @@
         <v>-90.6</v>
       </c>
       <c r="E19" s="37">
+        <f>'Profit &amp; loss'!E22</f>
         <v>-93.848890997509173</v>
       </c>
       <c r="F19" s="37">
+        <f>'Profit &amp; loss'!F22</f>
         <v>-95.819001304708792</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="37">
+        <f>'Profit &amp; loss'!G22</f>
         <v>-97.73538133080298</v>
       </c>
-      <c r="H19" s="75">
+      <c r="H19" s="37">
+        <f>'Profit &amp; loss'!H22</f>
         <v>-99.69008895741905</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="37">
+        <f>'Profit &amp; loss'!I22</f>
         <v>-101.78358082552485</v>
       </c>
     </row>
@@ -3858,18 +3906,23 @@
         <v>-70.400000000000006</v>
       </c>
       <c r="E20" s="37">
+        <f>'Profit &amp; loss'!E23</f>
         <v>-72.924524572015969</v>
       </c>
       <c r="F20" s="37">
+        <f>'Profit &amp; loss'!F23</f>
         <v>-74.45538291226822</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="37">
+        <f>'Profit &amp; loss'!G23</f>
         <v>-75.94449057051358</v>
       </c>
-      <c r="H20" s="75">
+      <c r="H20" s="37">
+        <f>'Profit &amp; loss'!H23</f>
         <v>-77.463380381923855</v>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="37">
+        <f>'Profit &amp; loss'!I23</f>
         <v>-79.090111369944267</v>
       </c>
     </row>
@@ -3886,18 +3939,23 @@
         <v>-36</v>
       </c>
       <c r="E21" s="37">
+        <f>'Profit &amp; loss'!E24</f>
         <v>-37.290950065235435</v>
       </c>
       <c r="F21" s="37">
+        <f>'Profit &amp; loss'!F24</f>
         <v>-38.073775352864423</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="37">
+        <f>'Profit &amp; loss'!G24</f>
         <v>-38.835250859921707</v>
       </c>
-      <c r="H21" s="75">
+      <c r="H21" s="37">
+        <f>'Profit &amp; loss'!H24</f>
         <v>-39.611955877120145</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="37">
+        <f>'Profit &amp; loss'!I24</f>
         <v>-40.443806950539674</v>
       </c>
     </row>
@@ -3914,18 +3972,23 @@
         <v>-30.8</v>
       </c>
       <c r="E22" s="37">
+        <f>'Profit &amp; loss'!E25</f>
         <v>-31.904479500256986</v>
       </c>
       <c r="F22" s="37">
+        <f>'Profit &amp; loss'!F25</f>
         <v>-32.574230024117341</v>
       </c>
-      <c r="G22" s="75">
+      <c r="G22" s="37">
+        <f>'Profit &amp; loss'!G25</f>
         <v>-33.225714624599689</v>
       </c>
-      <c r="H22" s="75">
+      <c r="H22" s="37">
+        <f>'Profit &amp; loss'!H25</f>
         <v>-33.890228917091683</v>
       </c>
-      <c r="I22" s="75">
+      <c r="I22" s="37">
+        <f>'Profit &amp; loss'!I25</f>
         <v>-34.601923724350613</v>
       </c>
     </row>
@@ -3942,18 +4005,23 @@
         <v>-2.1</v>
       </c>
       <c r="E23" s="37">
+        <f>'Profit &amp; loss'!E26</f>
         <v>-2.1753054204720672</v>
       </c>
       <c r="F23" s="37">
+        <f>'Profit &amp; loss'!F26</f>
         <v>-2.2209702289170914</v>
       </c>
-      <c r="G23" s="75">
+      <c r="G23" s="37">
+        <f>'Profit &amp; loss'!G26</f>
         <v>-2.2653896334954333</v>
       </c>
-      <c r="H23" s="75">
+      <c r="H23" s="37">
+        <f>'Profit &amp; loss'!H26</f>
         <v>-2.3106974261653419</v>
       </c>
-      <c r="I23" s="75">
+      <c r="I23" s="37">
+        <f>'Profit &amp; loss'!I26</f>
         <v>-2.3592220721148145</v>
       </c>
     </row>
@@ -3970,19 +4038,24 @@
         <v>25.9</v>
       </c>
       <c r="E24" s="37">
-        <v>26.828766852488826</v>
+        <f>'Profit &amp; loss'!E27</f>
+        <v>0</v>
       </c>
       <c r="F24" s="37">
-        <v>27.391966156644127</v>
-      </c>
-      <c r="G24" s="75">
-        <v>27.939805479777007</v>
-      </c>
-      <c r="H24" s="75">
-        <v>28.498601589372552</v>
-      </c>
-      <c r="I24" s="75">
-        <v>29.097072222749375</v>
+        <f>'Profit &amp; loss'!F27</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="37">
+        <f>'Profit &amp; loss'!G27</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="37">
+        <f>'Profit &amp; loss'!H27</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="37">
+        <f>'Profit &amp; loss'!I27</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -3998,18 +4071,23 @@
         <v>-69.7</v>
       </c>
       <c r="E25" s="37">
+        <f>'Profit &amp; loss'!E28</f>
         <v>-72.19942276519194</v>
       </c>
       <c r="F25" s="37">
+        <f>'Profit &amp; loss'!F28</f>
         <v>-73.715059502629188</v>
       </c>
-      <c r="G25" s="75">
+      <c r="G25" s="37">
+        <f>'Profit &amp; loss'!G28</f>
         <v>-75.18936069268176</v>
       </c>
-      <c r="H25" s="75">
+      <c r="H25" s="37">
+        <f>'Profit &amp; loss'!H28</f>
         <v>-76.693147906535415</v>
       </c>
-      <c r="I25" s="75">
+      <c r="I25" s="37">
+        <f>'Profit &amp; loss'!I28</f>
         <v>-78.303704012572652</v>
       </c>
     </row>
@@ -4017,33 +4095,33 @@
       <c r="B26" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="74">
+      <c r="C26" s="27">
         <f>SUM(C9:C25)</f>
         <v>691.30000000000007</v>
       </c>
-      <c r="D26" s="74">
+      <c r="D26" s="27">
         <f>SUM(D9:D25)</f>
         <v>772.60000000000014</v>
       </c>
-      <c r="E26" s="74">
-        <f>SUM(E9:E25)</f>
-        <v>724.61862390630574</v>
-      </c>
-      <c r="F26" s="74">
-        <f>SUM(F9:F25)</f>
-        <v>739.83008356846176</v>
-      </c>
-      <c r="G26" s="74">
-        <f t="shared" ref="G26:I26" si="2">SUM(G9:G25)</f>
-        <v>754.62668523983098</v>
-      </c>
-      <c r="H26" s="74">
-        <f t="shared" si="2"/>
-        <v>769.71921894462741</v>
-      </c>
-      <c r="I26" s="74">
-        <f t="shared" si="2"/>
-        <v>785.88332254246382</v>
+      <c r="E26" s="27">
+        <f ca="1">SUM(E9:E25)</f>
+        <v>773.47645593642494</v>
+      </c>
+      <c r="F26" s="27">
+        <f ca="1">SUM(F9:F25)</f>
+        <v>789.71355711066383</v>
+      </c>
+      <c r="G26" s="27">
+        <f t="shared" ref="G26:I26" ca="1" si="2">SUM(G9:G25)</f>
+        <v>805.50782825287706</v>
+      </c>
+      <c r="H26" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>821.61798481793437</v>
+      </c>
+      <c r="I26" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>838.87196249911017</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -4092,24 +4170,24 @@
         <v>373.00000000000011</v>
       </c>
       <c r="E28" s="74">
-        <f t="shared" si="3"/>
-        <v>287.29817942100772</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>336.15601145112691</v>
       </c>
       <c r="F28" s="74">
         <f t="shared" ca="1" si="3"/>
-        <v>267.9404750812871</v>
+        <v>317.82394862348917</v>
       </c>
       <c r="G28" s="74">
         <f t="shared" ca="1" si="3"/>
-        <v>251.92351538989953</v>
+        <v>302.80465840294562</v>
       </c>
       <c r="H28" s="74">
         <f t="shared" ca="1" si="3"/>
-        <v>239.33621057423215</v>
+        <v>291.23497644753911</v>
       </c>
       <c r="I28" s="74">
         <f t="shared" ca="1" si="3"/>
-        <v>230.3303953337952</v>
+        <v>283.31903529044155</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
@@ -4126,23 +4204,23 @@
       </c>
       <c r="E29" s="76">
         <f ca="1">'Profit &amp; loss'!E40</f>
-        <v>-42.201054835969309</v>
+        <v>-57.270982889745234</v>
       </c>
       <c r="F29" s="76">
         <f ca="1">'Profit &amp; loss'!F40</f>
-        <v>-38.326400727176406</v>
+        <v>-53.712682232462939</v>
       </c>
       <c r="G29" s="76">
         <f ca="1">'Profit &amp; loss'!G40</f>
-        <v>-35.117475917096655</v>
+        <v>-50.811483052488938</v>
       </c>
       <c r="H29" s="76">
         <f ca="1">'Profit &amp; loss'!H40</f>
-        <v>-32.591032411420535</v>
+        <v>-48.598919689520649</v>
       </c>
       <c r="I29" s="76">
         <f ca="1">'Profit &amp; loss'!I40</f>
-        <v>-30.776264330502514</v>
+        <v>-47.120317241442713</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
@@ -4158,24 +4236,24 @@
         <v>298.73212104857731</v>
       </c>
       <c r="E30" s="29">
-        <f>E28*(1-WACC!$D$6)</f>
-        <v>230.0943552596041</v>
+        <f ca="1">E28*(1-WACC!$D$6)</f>
+        <v>269.22412413947711</v>
       </c>
       <c r="F30" s="29">
         <f ca="1">F28*(1-WACC!$D$6)</f>
-        <v>214.59095559194731</v>
+        <v>254.54215091777198</v>
       </c>
       <c r="G30" s="29">
         <f ca="1">G28*(1-WACC!$D$6)</f>
-        <v>201.76312625854845</v>
+        <v>242.51334549088961</v>
       </c>
       <c r="H30" s="29">
         <f ca="1">H28*(1-WACC!$D$6)</f>
-        <v>191.68207460742437</v>
+        <v>233.2472982244123</v>
       </c>
       <c r="I30" s="29">
         <f ca="1">I28*(1-WACC!$D$6)</f>
-        <v>184.46940359255214</v>
+        <v>226.9074969054968</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -4256,11 +4334,11 @@
       </c>
       <c r="G33" s="75">
         <f t="shared" ref="G33" ca="1" si="6">F34-G34</f>
-        <v>-1.3156604594159944</v>
+        <v>-1.3156604594162218</v>
       </c>
       <c r="H33" s="75">
         <f t="shared" ref="H33" ca="1" si="7">G34-H34</f>
-        <v>-1.341973668603714</v>
+        <v>-1.3419736686034867</v>
       </c>
       <c r="I33" s="75">
         <f t="shared" ref="I33" ca="1" si="8">H34-I34</f>
@@ -4289,7 +4367,7 @@
       </c>
       <c r="G34" s="111">
         <f t="shared" ca="1" si="9"/>
-        <v>-63.001316569802157</v>
+        <v>-63.001316569801929</v>
       </c>
       <c r="H34" s="111">
         <f t="shared" ca="1" si="9"/>
@@ -4322,7 +4400,7 @@
       </c>
       <c r="G35" s="111">
         <f ca="1">'balance sheet'!K11-'balance sheet'!K6</f>
-        <v>1096.4485826117898</v>
+        <v>1096.44858261179</v>
       </c>
       <c r="H35" s="111">
         <f ca="1">'balance sheet'!L11-'balance sheet'!L6</f>
@@ -4377,23 +4455,23 @@
       </c>
       <c r="E37" s="45">
         <f ca="1">E30+E31+E32+E33</f>
-        <v>60.967347880749685</v>
+        <v>100.09711676062273</v>
       </c>
       <c r="F37" s="45">
         <f ca="1">F30+F31+F32+F33</f>
-        <v>68.227094739778749</v>
+        <v>108.17829006560351</v>
       </c>
       <c r="G37" s="45">
         <f t="shared" ref="G37:I37" ca="1" si="10">G30+G31+G32+G33</f>
-        <v>73.911696021498756</v>
+        <v>114.66191525383965</v>
       </c>
       <c r="H37" s="45">
         <f t="shared" ca="1" si="10"/>
-        <v>78.899390889099436</v>
+        <v>120.46461450608751</v>
       </c>
       <c r="I37" s="45">
         <f t="shared" ca="1" si="10"/>
-        <v>83.283060495206996</v>
+        <v>125.72115380815171</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
@@ -4493,23 +4571,23 @@
       </c>
       <c r="E44" s="43">
         <f ca="1">E37</f>
-        <v>60.967347880749685</v>
+        <v>100.09711676062273</v>
       </c>
       <c r="F44" s="43">
         <f ca="1">F37</f>
-        <v>68.227094739778749</v>
+        <v>108.17829006560351</v>
       </c>
       <c r="G44" s="43">
         <f t="shared" ref="G44:I44" ca="1" si="16">G37</f>
-        <v>73.911696021498756</v>
+        <v>114.66191525383965</v>
       </c>
       <c r="H44" s="43">
         <f t="shared" ca="1" si="16"/>
-        <v>78.899390889099436</v>
+        <v>120.46461450608751</v>
       </c>
       <c r="I44" s="43">
         <f t="shared" ca="1" si="16"/>
-        <v>83.283060495206996</v>
+        <v>125.72115380815171</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
@@ -4540,23 +4618,23 @@
       <c r="D46" s="77"/>
       <c r="E46" s="85">
         <f ca="1">E37/(1+WACC!D18)^1</f>
-        <v>58.491650196109937</v>
+        <v>96.032478740151547</v>
       </c>
       <c r="F46" s="85">
         <f ca="1">F44/(1+WACC!$D$18)^'Unlevered cash flow'!F45</f>
-        <v>62.798608388891935</v>
+        <v>99.571088288608905</v>
       </c>
       <c r="G46" s="85">
         <f ca="1">G44/(1+WACC!$D$18)^'Unlevered cash flow'!G45</f>
-        <v>65.268387030951047</v>
+        <v>101.25323413388995</v>
       </c>
       <c r="H46" s="85">
         <f ca="1">H44/(1+WACC!$D$18)^'Unlevered cash flow'!H45</f>
-        <v>66.843615649506717</v>
+        <v>102.05770032786643</v>
       </c>
       <c r="I46" s="85">
         <f ca="1">I44/(1+WACC!$D$18)^'Unlevered cash flow'!I45</f>
-        <v>67.692340442120937</v>
+        <v>102.18595586850981</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
@@ -4565,7 +4643,7 @@
       </c>
       <c r="C48" s="60">
         <f ca="1">SUM(E46:I46)</f>
-        <v>321.09460170758058</v>
+        <v>501.10045735902668</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
@@ -4586,14 +4664,14 @@
       </c>
       <c r="C53" s="43">
         <f ca="1">SUM(E46:I46)</f>
-        <v>321.09460170758058</v>
+        <v>501.10045735902668</v>
       </c>
       <c r="F53" t="s">
         <v>219</v>
       </c>
       <c r="I53" s="43">
         <f ca="1">C48</f>
-        <v>321.09460170758058</v>
+        <v>501.10045735902668</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
@@ -4601,8 +4679,8 @@
         <v>220</v>
       </c>
       <c r="C54" s="1">
-        <f>I26</f>
-        <v>785.88332254246382</v>
+        <f ca="1">I26</f>
+        <v>838.87196249911017</v>
       </c>
       <c r="F54" t="s">
         <v>221</v>
@@ -4640,7 +4718,7 @@
       </c>
       <c r="I56" s="60">
         <f ca="1">I44*(1+I54)</f>
-        <v>84.94872170511114</v>
+        <v>128.23557688431475</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
@@ -4648,15 +4726,15 @@
         <v>225</v>
       </c>
       <c r="C57" s="1">
-        <f>C54*C55</f>
-        <v>2238.3658470132054</v>
+        <f ca="1">C54*C55</f>
+        <v>2389.2889656956581</v>
       </c>
       <c r="F57" t="s">
         <v>225</v>
       </c>
       <c r="I57" s="60">
         <f ca="1">I56/(I55-I54)</f>
-        <v>3804.9814716267506</v>
+        <v>5743.8650547560574</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
@@ -4664,15 +4742,15 @@
         <v>226</v>
       </c>
       <c r="C58" s="1">
-        <f>C57/(1+C56)^$I$45</f>
-        <v>1819.3402361666861</v>
+        <f ca="1">C57/(1+C56)^$I$45</f>
+        <v>1942.0103094047747</v>
       </c>
       <c r="F58" t="s">
         <v>226</v>
       </c>
       <c r="I58" s="1">
         <f ca="1">I57/(1+I55)^I45</f>
-        <v>3092.6829492312372</v>
+        <v>4668.6044728450543</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
@@ -4681,7 +4759,7 @@
       </c>
       <c r="C59" s="87">
         <f ca="1">C58+C53</f>
-        <v>2140.4348378742666</v>
+        <v>2443.1107667638016</v>
       </c>
       <c r="F59" s="30" t="s">
         <v>227</v>
@@ -4690,7 +4768,7 @@
       <c r="H59" s="30"/>
       <c r="I59" s="94">
         <f ca="1">I58+I53</f>
-        <v>3413.777550938818</v>
+        <v>5169.7049302040814</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
@@ -4699,7 +4777,7 @@
       </c>
       <c r="C61" s="78"/>
       <c r="F61" s="42" t="s">
-        <v>245</v>
+        <v>570</v>
       </c>
       <c r="G61" s="78"/>
     </row>
@@ -4709,10 +4787,10 @@
       </c>
       <c r="C62" s="43">
         <f ca="1">I59</f>
-        <v>3413.777550938818</v>
+        <v>5169.7049302040814</v>
       </c>
       <c r="F62" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G62" s="101">
         <v>2166763244</v>
@@ -4727,10 +4805,10 @@
         <v>868.4</v>
       </c>
       <c r="F63" s="95" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G63" s="101">
-        <v>115200</v>
+        <v>684669</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
@@ -4742,7 +4820,7 @@
         <v>1821.5</v>
       </c>
       <c r="F64" s="95" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -4757,7 +4835,7 @@
         <v>385.2</v>
       </c>
       <c r="F65" s="95" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -4771,11 +4849,11 @@
         <v>0</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>240</v>
+        <v>568</v>
       </c>
       <c r="G66" s="51">
         <f>SUM(G62:G65)</f>
-        <v>2166878444</v>
+        <v>2167447913</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4792,7 +4870,7 @@
       </c>
       <c r="C68" s="96">
         <f ca="1">C62+C63-C64-C65</f>
-        <v>2075.4775509388182</v>
+        <v>3831.4049302040812</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4801,7 +4879,7 @@
       </c>
       <c r="C69" s="101">
         <f>G66</f>
-        <v>2166878444</v>
+        <v>2167447913</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4810,12 +4888,12 @@
       </c>
       <c r="C70" s="112">
         <f ca="1">C68*1000000/C69</f>
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B75" s="42" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C75" s="78"/>
       <c r="D75" s="42"/>
@@ -4826,7 +4904,7 @@
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="102"/>
       <c r="D78" s="8" t="s">
-        <v>251</v>
+        <v>569</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4835,7 +4913,7 @@
       </c>
       <c r="B79" s="60">
         <f ca="1">C70</f>
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="C79" s="97">
         <f>D79-1</f>
@@ -4866,19 +4944,19 @@
       </c>
       <c r="C80">
         <f t="dataTable" ref="C80:G84" dt2D="1" dtr="1" r1="C55" r2="C56" ca="1"/>
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="D80">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="E80">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="F80">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="G80">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4888,19 +4966,19 @@
         <v>5.2325659753815534E-2</v>
       </c>
       <c r="C81">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="D81">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="E81">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="F81">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="G81">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4909,61 +4987,61 @@
         <v>4.2325659753815532E-2</v>
       </c>
       <c r="C82">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="D82">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="E82">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="F82">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="G82">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B83" s="98">
-        <f>0.0319-0.01</f>
-        <v>2.1899999999999996E-2</v>
+        <f>B82-0.01</f>
+        <v>3.232565975381553E-2</v>
       </c>
       <c r="C83">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="D83">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="E83">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="F83">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="G83">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B84" s="98">
         <f>B83-0.01</f>
-        <v>1.1899999999999996E-2</v>
+        <v>2.2325659753815529E-2</v>
       </c>
       <c r="C84">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="D84">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="E84">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="F84">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
       <c r="G84">
-        <v>0.9578190953376885</v>
+        <v>1.7677033469750012</v>
       </c>
     </row>
   </sheetData>
@@ -4989,13 +5067,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -5045,19 +5123,19 @@
       </c>
       <c r="E3" s="43">
         <f ca="1">D9</f>
-        <v>384.01382545096317</v>
+        <v>383.59024444848143</v>
       </c>
       <c r="F3" s="43">
         <f t="shared" ref="F3:H3" ca="1" si="4">E9</f>
-        <v>382.93655851354964</v>
+        <v>382.08050454097679</v>
       </c>
       <c r="G3" s="43">
         <f t="shared" ca="1" si="4"/>
-        <v>381.94948706898066</v>
+        <v>380.65231066691484</v>
       </c>
       <c r="H3" s="43">
         <f t="shared" ca="1" si="4"/>
-        <v>381.03342813814288</v>
+        <v>379.2863068579943</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5074,23 +5152,23 @@
       </c>
       <c r="D4" s="6">
         <f ca="1">(C4/'Profit &amp; loss'!D41)*'Profit &amp; loss'!E41</f>
-        <v>25.970979599965688</v>
+        <v>35.245174180618179</v>
       </c>
       <c r="E4" s="6">
         <f ca="1">(D4/'Profit &amp; loss'!E41)*'Profit &amp; loss'!F41</f>
-        <v>23.58647610337027</v>
+        <v>33.05535797483801</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">(E4/'Profit &amp; loss'!F41)*'Profit &amp; loss'!G41</f>
-        <v>21.611669523195111</v>
+        <v>31.269929032092218</v>
       </c>
       <c r="G4" s="6">
         <f ca="1">(F4/'Profit &amp; loss'!G41)*'Profit &amp; loss'!H41</f>
-        <v>20.056869222552976</v>
+        <v>29.908293921628015</v>
       </c>
       <c r="H4" s="6">
         <f ca="1">(G4/'Profit &amp; loss'!H41)*'Profit &amp; loss'!I41</f>
-        <v>18.940041574727942</v>
+        <v>28.998346192483549</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -5131,23 +5209,23 @@
       </c>
       <c r="D6" s="6">
         <f ca="1">(C6/'Profit &amp; loss'!D41)*'Profit &amp; loss'!E41</f>
-        <v>-27.157154149002583</v>
+        <v>-36.854929732136796</v>
       </c>
       <c r="E6" s="6">
         <f ca="1">(D6/'Profit &amp; loss'!E41)*'Profit &amp; loss'!F41</f>
-        <v>-24.663743040783814</v>
+        <v>-34.565097882342627</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">(E6/'Profit &amp; loss'!F41)*'Profit &amp; loss'!G41</f>
-        <v>-22.598740967764119</v>
+        <v>-32.698122906154119</v>
       </c>
       <c r="G6" s="6">
         <f ca="1">(F6/'Profit &amp; loss'!G41)*'Profit &amp; loss'!H41</f>
-        <v>-20.972928153390729</v>
+        <v>-31.274297730548525</v>
       </c>
       <c r="H6" s="6">
         <f ca="1">(G6/'Profit &amp; loss'!H41)*'Profit &amp; loss'!I41</f>
-        <v>-19.805091550496766</v>
+        <v>-30.322789888774864</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -5214,23 +5292,23 @@
       </c>
       <c r="D9" s="62">
         <f t="shared" ref="D9:H9" ca="1" si="5">SUM(D3:D8)</f>
-        <v>384.01382545096317</v>
+        <v>383.59024444848143</v>
       </c>
       <c r="E9" s="62">
         <f t="shared" ca="1" si="5"/>
-        <v>382.93655851354964</v>
+        <v>382.08050454097679</v>
       </c>
       <c r="F9" s="62">
         <f t="shared" ca="1" si="5"/>
-        <v>381.94948706898066</v>
+        <v>380.65231066691484</v>
       </c>
       <c r="G9" s="62">
         <f t="shared" ca="1" si="5"/>
-        <v>381.03342813814288</v>
+        <v>379.2863068579943</v>
       </c>
       <c r="H9" s="62">
         <f t="shared" ca="1" si="5"/>
-        <v>380.1683781623741</v>
+        <v>377.96186316170298</v>
       </c>
     </row>
   </sheetData>
@@ -5253,17 +5331,17 @@
       <c r="A1" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="116" t="s">
+      <c r="B1" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116" t="s">
+      <c r="C1" s="117"/>
+      <c r="D1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -6883,98 +6961,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="I1" s="113" t="s">
-        <v>320</v>
-      </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="S1" s="113" t="s">
-        <v>444</v>
-      </c>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="AB1" s="113" t="s">
-        <v>504</v>
-      </c>
-      <c r="AC1" s="113"/>
-      <c r="AD1" s="113"/>
-      <c r="AE1" s="113"/>
-      <c r="AF1" s="113"/>
-      <c r="AG1" s="113"/>
-      <c r="AH1" s="113"/>
-      <c r="AK1" s="113" t="s">
+      <c r="A1" s="114" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="I1" s="114" t="s">
+        <v>318</v>
+      </c>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="S1" s="114" t="s">
+        <v>442</v>
+      </c>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="AB1" s="114" t="s">
+        <v>502</v>
+      </c>
+      <c r="AC1" s="114"/>
+      <c r="AD1" s="114"/>
+      <c r="AE1" s="114"/>
+      <c r="AF1" s="114"/>
+      <c r="AG1" s="114"/>
+      <c r="AH1" s="114"/>
+      <c r="AK1" s="114" t="s">
         <v>232</v>
       </c>
-      <c r="AL1" s="113"/>
-      <c r="AM1" s="113"/>
-      <c r="AN1" s="113"/>
-      <c r="AO1" s="113"/>
-      <c r="AP1" s="113"/>
-      <c r="AQ1" s="113"/>
+      <c r="AL1" s="114"/>
+      <c r="AM1" s="114"/>
+      <c r="AN1" s="114"/>
+      <c r="AO1" s="114"/>
+      <c r="AP1" s="114"/>
+      <c r="AQ1" s="114"/>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="D2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="E2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="F2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>258</v>
-      </c>
       <c r="G2" s="31" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="K2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="L2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="M2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="N2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="M2" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>258</v>
-      </c>
       <c r="O2" s="31" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P2" s="108" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Q2">
         <f>SLOPE(O3:O63,G3:G63)</f>
@@ -6982,84 +7060,84 @@
       </c>
       <c r="R2" s="2"/>
       <c r="S2" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="T2" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="U2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="T2" s="31" t="s">
+      <c r="V2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="W2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="V2" s="31" t="s">
+      <c r="X2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="W2" s="31" t="s">
+      <c r="Y2" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="X2" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y2" s="31" t="s">
-        <v>259</v>
-      </c>
       <c r="Z2" s="107" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AA2">
         <f>SLOPE(Y3:Y63,G3:G63)</f>
         <v>0.7517124637493322</v>
       </c>
       <c r="AB2" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC2" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="AC2" s="31" t="s">
+      <c r="AE2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="AD2" s="31" t="s">
+      <c r="AF2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="AE2" s="31" t="s">
+      <c r="AG2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AH2" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="AG2" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="AH2" s="31" t="s">
-        <v>259</v>
-      </c>
       <c r="AI2" s="107" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AJ2">
         <f>SLOPE(AH3:AH63,G3:G63)</f>
         <v>0.34260011499870624</v>
       </c>
       <c r="AK2" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="AL2" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="AM2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="AL2" s="31" t="s">
+      <c r="AN2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="AM2" s="31" t="s">
+      <c r="AO2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="AN2" s="31" t="s">
+      <c r="AP2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="AO2" s="31" t="s">
+      <c r="AQ2" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="AP2" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="AQ2" s="31" t="s">
-        <v>259</v>
-      </c>
       <c r="AS2" s="31" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AT2">
         <f>SLOPE(AQ3:AQ63,G3:G63)</f>
@@ -7083,7 +7161,7 @@
         <v>4648.38</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G3" s="106">
         <v>5.57E-2</v>
@@ -7105,7 +7183,7 @@
         <v>1.45</v>
       </c>
       <c r="N3" s="31" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="O3" s="106">
         <v>-6.7999999999999996E-3</v>
@@ -7126,13 +7204,13 @@
         <v>3.86</v>
       </c>
       <c r="X3" s="31" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Y3" s="31">
         <v>-8.2400000000000001E-2</v>
       </c>
       <c r="Z3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AA3">
         <f>AA2/(1+(1-0.2049)*(9838+42313+801903+68873+132694)/(952614))</f>
@@ -7154,13 +7232,13 @@
         <v>180</v>
       </c>
       <c r="AG3" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AH3" s="31">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="AI3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AJ3">
         <f>AJ2/(1+(1-0.238)*(447.1+710.2)/(719.5))</f>
@@ -7182,13 +7260,13 @@
         <v>20.8</v>
       </c>
       <c r="AP3" s="31" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AQ3" s="31">
         <v>8.6999999999999994E-3</v>
       </c>
       <c r="AS3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AT3">
         <f>AT2/(1-(1-0.47759)*(1249+346.3)/(-352.3))</f>
@@ -7212,7 +7290,7 @@
         <v>4492.46</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G4" s="106">
         <v>2.7E-2</v>
@@ -7234,13 +7312,13 @@
         <v>1.42</v>
       </c>
       <c r="N4" s="31" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="O4" s="106">
         <v>2.7799999999999998E-2</v>
       </c>
       <c r="P4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="Q4">
         <f>MEDIAN(AA3,AJ3,AT3)</f>
@@ -7262,7 +7340,7 @@
         <v>4.16</v>
       </c>
       <c r="X4" s="31" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y4" s="31">
         <v>-8.0100000000000005E-2</v>
@@ -7283,7 +7361,7 @@
         <v>173.5</v>
       </c>
       <c r="AG4" s="31" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AH4" s="31">
         <v>7.8700000000000006E-2</v>
@@ -7304,7 +7382,7 @@
         <v>21</v>
       </c>
       <c r="AP4" s="31" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AQ4" s="31">
         <v>5.0099999999999999E-2</v>
@@ -7327,7 +7405,7 @@
         <v>4372.6400000000003</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G5" s="106">
         <v>2.1499999999999998E-2</v>
@@ -7349,13 +7427,13 @@
         <v>1.44</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O5" s="106">
         <v>-1.37E-2</v>
       </c>
       <c r="P5" s="91" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="Q5" s="109">
         <f>Q4*(1+(1-'Profit &amp; loss'!E105)*('debt schedule'!C5+'debt schedule'!C11)/('balance sheet'!H57))</f>
@@ -7377,7 +7455,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="X5" s="31" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Y5" s="31">
         <v>-5.1299999999999998E-2</v>
@@ -7398,7 +7476,7 @@
         <v>171.3</v>
       </c>
       <c r="AG5" s="31" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AH5" s="31">
         <v>-0.15859999999999999</v>
@@ -7419,7 +7497,7 @@
         <v>19</v>
       </c>
       <c r="AP5" s="31" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AQ5" s="31">
         <v>-0.16370000000000001</v>
@@ -7442,7 +7520,7 @@
         <v>4307.76</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G6" s="106">
         <v>2.9899999999999999E-2</v>
@@ -7464,7 +7542,7 @@
         <v>1.44</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="O6" s="106">
         <v>6.8999999999999999E-3</v>
@@ -7485,7 +7563,7 @@
         <v>4.71</v>
       </c>
       <c r="X6" s="31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y6" s="31">
         <v>-8.0999999999999996E-3</v>
@@ -7506,7 +7584,7 @@
         <v>198.8</v>
       </c>
       <c r="AG6" s="31" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AH6" s="31">
         <v>-6.9099999999999995E-2</v>
@@ -7527,7 +7605,7 @@
         <v>25.24</v>
       </c>
       <c r="AP6" s="31" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AQ6" s="31">
         <v>-8.6300000000000002E-2</v>
@@ -7550,7 +7628,7 @@
         <v>4252.2700000000004</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G7" s="106">
         <v>7.1000000000000004E-3</v>
@@ -7572,7 +7650,7 @@
         <v>1.44</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="O7" s="106">
         <v>0</v>
@@ -7593,7 +7671,7 @@
         <v>4.75</v>
       </c>
       <c r="X7" s="31" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Y7" s="31">
         <v>-1.41E-2</v>
@@ -7614,7 +7692,7 @@
         <v>210.2</v>
       </c>
       <c r="AG7" s="31" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AH7" s="31">
         <v>1.8100000000000002E-2</v>
@@ -7635,7 +7713,7 @@
         <v>24.36</v>
       </c>
       <c r="AP7" s="31" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AQ7" s="31">
         <v>-0.12429999999999999</v>
@@ -7658,7 +7736,7 @@
         <v>4144.8900000000003</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G8" s="106">
         <v>2.3E-2</v>
@@ -7680,7 +7758,7 @@
         <v>1.42</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O8" s="106">
         <v>-5.2299999999999999E-2</v>
@@ -7701,7 +7779,7 @@
         <v>3.63</v>
       </c>
       <c r="X8" s="31" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Y8" s="31">
         <v>0.33160000000000001</v>
@@ -7722,7 +7800,7 @@
         <v>215.2</v>
       </c>
       <c r="AG8" s="31" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AH8" s="31">
         <v>-1.2500000000000001E-2</v>
@@ -7743,7 +7821,7 @@
         <v>32.64</v>
       </c>
       <c r="AP8" s="31" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AQ8" s="31">
         <v>-9.64E-2</v>
@@ -7766,7 +7844,7 @@
         <v>3968.57</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G9" s="106">
         <v>5.28E-2</v>
@@ -7788,7 +7866,7 @@
         <v>1.4</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="O9" s="106">
         <v>6.9900000000000004E-2</v>
@@ -7809,7 +7887,7 @@
         <v>3.68</v>
       </c>
       <c r="X9" s="31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="Y9" s="31">
         <v>-1.32E-2</v>
@@ -7830,7 +7908,7 @@
         <v>204.2</v>
       </c>
       <c r="AG9" s="31" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AH9" s="31">
         <v>-2.69E-2</v>
@@ -7851,7 +7929,7 @@
         <v>28</v>
       </c>
       <c r="AP9" s="31" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AQ9" s="31">
         <v>0.23119999999999999</v>
@@ -7874,7 +7952,7 @@
         <v>3845.78</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G10" s="106">
         <v>1.7899999999999999E-2</v>
@@ -7896,7 +7974,7 @@
         <v>1.4</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O10" s="106">
         <v>7.0000000000000001E-3</v>
@@ -7917,7 +7995,7 @@
         <v>3.11</v>
       </c>
       <c r="X10" s="31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Y10" s="31">
         <v>0.16980000000000001</v>
@@ -7938,7 +8016,7 @@
         <v>189.7</v>
       </c>
       <c r="AG10" s="31" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AH10" s="31">
         <v>0.20730000000000001</v>
@@ -7959,7 +8037,7 @@
         <v>25.24</v>
       </c>
       <c r="AP10" s="31" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AQ10" s="31">
         <v>-1.34E-2</v>
@@ -7982,7 +8060,7 @@
         <v>3831.04</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G11" s="106">
         <v>1.6199999999999999E-2</v>
@@ -8004,7 +8082,7 @@
         <v>1.39</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="O11" s="106">
         <v>-7.1900000000000006E-2</v>
@@ -8025,7 +8103,7 @@
         <v>2.68</v>
       </c>
       <c r="X11" s="31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Y11" s="31">
         <v>0.1956</v>
@@ -8046,7 +8124,7 @@
         <v>172.1</v>
       </c>
       <c r="AG11" s="31" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AH11" s="31">
         <v>0.106</v>
@@ -8067,7 +8145,7 @@
         <v>26.92</v>
       </c>
       <c r="AP11" s="31" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AQ11" s="31">
         <v>-3.8600000000000002E-2</v>
@@ -8090,7 +8168,7 @@
         <v>3372.38</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G12" s="106">
         <v>-3.5200000000000002E-2</v>
@@ -8112,7 +8190,7 @@
         <v>1.36</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="O12" s="106">
         <v>4.7899999999999998E-2</v>
@@ -8133,7 +8211,7 @@
         <v>2.19</v>
       </c>
       <c r="X12" s="31" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y12" s="31">
         <v>1.12E-2</v>
@@ -8154,7 +8232,7 @@
         <v>137.80000000000001</v>
       </c>
       <c r="AG12" s="31" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AH12" s="31">
         <v>0.1071</v>
@@ -8175,7 +8253,7 @@
         <v>28.66</v>
       </c>
       <c r="AP12" s="31" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AQ12" s="31">
         <v>-0.4652</v>
@@ -8198,7 +8276,7 @@
         <v>3805.7</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G13" s="106">
         <v>1.9699999999999999E-2</v>
@@ -8220,7 +8298,7 @@
         <v>1.38</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O13" s="106">
         <v>5.04E-2</v>
@@ -8241,7 +8319,7 @@
         <v>2.65</v>
       </c>
       <c r="X13" s="31" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Y13" s="31">
         <v>-0.13550000000000001</v>
@@ -8262,7 +8340,7 @@
         <v>156</v>
       </c>
       <c r="AG13" s="31" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AH13" s="31">
         <v>-2.3199999999999998E-2</v>
@@ -8283,7 +8361,7 @@
         <v>57</v>
       </c>
       <c r="AP13" s="31" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AQ13" s="31">
         <v>-0.1467</v>
@@ -8306,7 +8384,7 @@
         <v>3797.83</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G14" s="106">
         <v>1.03E-2</v>
@@ -8328,7 +8406,7 @@
         <v>1.34</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="O14" s="106">
         <v>-1.4200000000000001E-2</v>
@@ -8349,7 +8427,7 @@
         <v>2.78</v>
       </c>
       <c r="X14" s="31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Y14" s="31">
         <v>-0.1885</v>
@@ -8370,7 +8448,7 @@
         <v>153.6</v>
       </c>
       <c r="AG14" s="31" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AH14" s="31">
         <v>-2.0799999999999999E-2</v>
@@ -8391,7 +8469,7 @@
         <v>67.55</v>
       </c>
       <c r="AP14" s="31" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AQ14" s="31">
         <v>-7.2800000000000004E-2</v>
@@ -8414,7 +8492,7 @@
         <v>3765.41</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G15" s="106">
         <v>1.7999999999999999E-2</v>
@@ -8436,7 +8514,7 @@
         <v>1.38</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="O15" s="106">
         <v>-4.7300000000000002E-2</v>
@@ -8457,7 +8535,7 @@
         <v>3.41</v>
       </c>
       <c r="X15" s="31" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Y15" s="31">
         <v>4.3700000000000003E-2</v>
@@ -8478,7 +8556,7 @@
         <v>149</v>
       </c>
       <c r="AG15" s="31" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AH15" s="31">
         <v>1.49E-2</v>
@@ -8499,7 +8577,7 @@
         <v>71.7</v>
       </c>
       <c r="AP15" s="31" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AQ15" s="31">
         <v>-7.3099999999999998E-2</v>
@@ -8522,7 +8600,7 @@
         <v>3715.52</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G16" s="106">
         <v>1.29E-2</v>
@@ -8544,7 +8622,7 @@
         <v>1.44</v>
       </c>
       <c r="N16" s="31" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="O16" s="106">
         <v>1.37E-2</v>
@@ -8565,7 +8643,7 @@
         <v>3.45</v>
       </c>
       <c r="X16" s="31" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Y16" s="31">
         <v>-6.1499999999999999E-2</v>
@@ -8586,7 +8664,7 @@
         <v>150.19999999999999</v>
       </c>
       <c r="AG16" s="31" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AH16" s="31">
         <v>6.1400000000000003E-2</v>
@@ -8607,7 +8685,7 @@
         <v>74.849999999999994</v>
       </c>
       <c r="AP16" s="31" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AQ16" s="31">
         <v>-8.6900000000000005E-2</v>
@@ -8630,7 +8708,7 @@
         <v>3524.33</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G17" s="106">
         <v>5.0700000000000002E-2</v>
@@ -8652,7 +8730,7 @@
         <v>1.45</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="O17" s="106">
         <v>-6.7999999999999996E-3</v>
@@ -8673,7 +8751,7 @@
         <v>3.69</v>
       </c>
       <c r="X17" s="31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="Y17" s="31">
         <v>-5.1000000000000004E-3</v>
@@ -8694,7 +8772,7 @@
         <v>128.6</v>
       </c>
       <c r="AG17" s="31" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH17" s="31">
         <v>0.1358</v>
@@ -8715,7 +8793,7 @@
         <v>66.75</v>
       </c>
       <c r="AP17" s="31" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AQ17" s="31">
         <v>0.25230000000000002</v>
@@ -8738,7 +8816,7 @@
         <v>3553.85</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G18" s="106">
         <v>-7.4000000000000003E-3</v>
@@ -8760,7 +8838,7 @@
         <v>1.42</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="O18" s="106">
         <v>-2.6499999999999999E-2</v>
@@ -8781,7 +8859,7 @@
         <v>3.79</v>
       </c>
       <c r="X18" s="31" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y18" s="31">
         <v>-5.0799999999999998E-2</v>
@@ -8802,7 +8880,7 @@
         <v>131.5</v>
       </c>
       <c r="AG18" s="31" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AH18" s="31">
         <v>-8.7599999999999997E-2</v>
@@ -8823,7 +8901,7 @@
         <v>67.7</v>
       </c>
       <c r="AP18" s="31" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AQ18" s="31">
         <v>-5.7099999999999998E-2</v>
@@ -8846,7 +8924,7 @@
         <v>3412.47</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G19" s="106">
         <v>4.1300000000000003E-2</v>
@@ -8868,7 +8946,7 @@
         <v>1.4</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O19" s="106">
         <v>6.3399999999999998E-2</v>
@@ -8889,7 +8967,7 @@
         <v>3.69</v>
       </c>
       <c r="X19" s="31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Y19" s="31">
         <v>9.8400000000000001E-2</v>
@@ -8910,7 +8988,7 @@
         <v>141.9</v>
       </c>
       <c r="AG19" s="31" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AH19" s="31">
         <v>-6.9400000000000003E-2</v>
@@ -8931,7 +9009,7 @@
         <v>63.95</v>
       </c>
       <c r="AP19" s="31" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AQ19" s="31">
         <v>7.8399999999999997E-2</v>
@@ -8954,7 +9032,7 @@
         <v>3198.44</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G20" s="106">
         <v>-3.8E-3</v>
@@ -8976,7 +9054,7 @@
         <v>1.35</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="O20" s="106">
         <v>1.43E-2</v>
@@ -8997,7 +9075,7 @@
         <v>3.58</v>
       </c>
       <c r="X20" s="31" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Y20" s="31">
         <v>-0.2838</v>
@@ -9018,7 +9096,7 @@
         <v>154.19999999999999</v>
       </c>
       <c r="AG20" s="31" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AH20" s="31">
         <v>-0.10489999999999999</v>
@@ -9039,7 +9117,7 @@
         <v>50.65</v>
       </c>
       <c r="AP20" s="31" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AQ20" s="31">
         <v>0.2135</v>
@@ -9062,7 +9140,7 @@
         <v>3325.17</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G21" s="106">
         <v>3.6900000000000002E-2</v>
@@ -9084,7 +9162,7 @@
         <v>1.33</v>
       </c>
       <c r="N21" s="31" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O21" s="106">
         <v>4.48E-2</v>
@@ -9105,7 +9183,7 @@
         <v>4.76</v>
       </c>
       <c r="X21" s="31" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Y21" s="31">
         <v>1.9400000000000001E-2</v>
@@ -9126,7 +9204,7 @@
         <v>157.4</v>
       </c>
       <c r="AG21" s="31" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AH21" s="31">
         <v>0.108</v>
@@ -9147,7 +9225,7 @@
         <v>48.08</v>
       </c>
       <c r="AP21" s="31" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AQ21" s="31">
         <v>0.1009</v>
@@ -9170,7 +9248,7 @@
         <v>3288.94</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G22" s="106">
         <v>-1.1000000000000001E-3</v>
@@ -9192,7 +9270,7 @@
         <v>1.32</v>
       </c>
       <c r="N22" s="31" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="O22" s="106">
         <v>-3.5999999999999997E-2</v>
@@ -9213,7 +9291,7 @@
         <v>4.8600000000000003</v>
       </c>
       <c r="X22" s="31" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Y22" s="31">
         <v>-5.7999999999999996E-3</v>
@@ -9234,7 +9312,7 @@
         <v>150</v>
       </c>
       <c r="AG22" s="31" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AH22" s="31">
         <v>-7.2599999999999998E-2</v>
@@ -9255,7 +9333,7 @@
         <v>45.5</v>
       </c>
       <c r="AP22" s="31" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AQ22" s="31">
         <v>-5.11E-2</v>
@@ -9278,7 +9356,7 @@
         <v>3241.13</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G23" s="106">
         <v>1.3299999999999999E-2</v>
@@ -9300,7 +9378,7 @@
         <v>1.36</v>
       </c>
       <c r="N23" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="O23" s="106">
         <v>-6.7100000000000007E-2</v>
@@ -9321,7 +9399,7 @@
         <v>5.0199999999999996</v>
       </c>
       <c r="X23" s="31" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Y23" s="31">
         <v>-6.83E-2</v>
@@ -9342,7 +9420,7 @@
         <v>161.4</v>
       </c>
       <c r="AG23" s="31" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AH23" s="31">
         <v>5.2400000000000002E-2</v>
@@ -9363,7 +9441,7 @@
         <v>53.4</v>
       </c>
       <c r="AP23" s="31" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AQ23" s="31">
         <v>-2.8899999999999999E-2</v>
@@ -9386,7 +9464,7 @@
         <v>3136.44</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G24" s="106">
         <v>2.1299999999999999E-2</v>
@@ -9408,7 +9486,7 @@
         <v>1.4</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="O24" s="106">
         <v>6.4299999999999996E-2</v>
@@ -9429,7 +9507,7 @@
         <v>5.34</v>
       </c>
       <c r="X24" s="31" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Y24" s="31">
         <v>-3.8100000000000002E-2</v>
@@ -9450,7 +9528,7 @@
         <v>155.80000000000001</v>
       </c>
       <c r="AG24" s="31" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AH24" s="31">
         <v>-0.1009</v>
@@ -9471,7 +9549,7 @@
         <v>51.5</v>
       </c>
       <c r="AP24" s="31" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AQ24" s="31">
         <v>-0.20399999999999999</v>
@@ -9494,7 +9572,7 @@
         <v>3101.24</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G25" s="106">
         <v>2.6200000000000001E-2</v>
@@ -9516,7 +9594,7 @@
         <v>1.34</v>
       </c>
       <c r="N25" s="31" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="O25" s="106">
         <v>3.6999999999999998E-2</v>
@@ -9537,7 +9615,7 @@
         <v>5.67</v>
       </c>
       <c r="X25" s="31" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Y25" s="31">
         <v>-4.2999999999999997E-2</v>
@@ -9558,7 +9636,7 @@
         <v>148.1</v>
       </c>
       <c r="AG25" s="31" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AH25" s="31">
         <v>0.14030000000000001</v>
@@ -9579,7 +9657,7 @@
         <v>61.5</v>
       </c>
       <c r="AP25" s="31" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AQ25" s="31">
         <v>-0.1077</v>
@@ -9602,7 +9680,7 @@
         <v>3092.4</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G26" s="106">
         <v>-3.5000000000000001E-3</v>
@@ -9624,7 +9702,7 @@
         <v>1.34</v>
       </c>
       <c r="N26" s="31" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O26" s="106">
         <v>-3.5700000000000003E-2</v>
@@ -9645,7 +9723,7 @@
         <v>5.5</v>
       </c>
       <c r="X26" s="31" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Y26" s="31">
         <v>-0.1588</v>
@@ -9666,7 +9744,7 @@
         <v>148</v>
       </c>
       <c r="AG26" s="31" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AH26" s="31">
         <v>-6.2199999999999998E-2</v>
@@ -9687,7 +9765,7 @@
         <v>63</v>
       </c>
       <c r="AP26" s="31" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AQ26" s="31">
         <v>-9.1399999999999995E-2</v>
@@ -9710,7 +9788,7 @@
         <v>3126.29</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G27" s="106">
         <v>-2.69E-2</v>
@@ -9732,7 +9810,7 @@
         <v>1.37</v>
       </c>
       <c r="N27" s="31" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="O27" s="106">
         <v>0</v>
@@ -9753,7 +9831,7 @@
         <v>6.74</v>
       </c>
       <c r="X27" s="31" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Y27" s="31">
         <v>2.5700000000000001E-2</v>
@@ -9774,7 +9852,7 @@
         <v>158.22999999999999</v>
       </c>
       <c r="AG27" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AH27" s="31">
         <v>-3.5999999999999997E-2</v>
@@ -9795,7 +9873,7 @@
         <v>80</v>
       </c>
       <c r="AP27" s="31" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AQ27" s="31">
         <v>1.4800000000000001E-2</v>
@@ -9818,7 +9896,7 @@
         <v>3052.35</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G28" s="106">
         <v>5.4399999999999997E-2</v>
@@ -9840,7 +9918,7 @@
         <v>1.28</v>
       </c>
       <c r="N28" s="31" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O28" s="106">
         <v>8.5300000000000001E-2</v>
@@ -9861,7 +9939,7 @@
         <v>6.49</v>
       </c>
       <c r="X28" s="31" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Y28" s="31">
         <v>5.5800000000000002E-2</v>
@@ -9882,7 +9960,7 @@
         <v>154</v>
       </c>
       <c r="AG28" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AH28" s="31">
         <v>9.2399999999999996E-2</v>
@@ -9903,7 +9981,7 @@
         <v>64.349999999999994</v>
       </c>
       <c r="AP28" s="31" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AQ28" s="31">
         <v>0.26550000000000001</v>
@@ -9926,7 +10004,7 @@
         <v>3061.6</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G29" s="106">
         <v>1.6999999999999999E-3</v>
@@ -9948,7 +10026,7 @@
         <v>1.28</v>
       </c>
       <c r="N29" s="31" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="O29" s="106">
         <v>-2.2700000000000001E-2</v>
@@ -9969,7 +10047,7 @@
         <v>5.97</v>
       </c>
       <c r="X29" s="31" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Y29" s="31">
         <v>0.1013</v>
@@ -9990,7 +10068,7 @@
         <v>151</v>
       </c>
       <c r="AG29" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AH29" s="31">
         <v>1.46E-2</v>
@@ -10011,7 +10089,7 @@
         <v>59.05</v>
       </c>
       <c r="AP29" s="31" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AQ29" s="31">
         <v>6.9599999999999995E-2</v>
@@ -10034,7 +10112,7 @@
         <v>3041.67</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G30" s="106">
         <v>-4.65E-2</v>
@@ -10056,7 +10134,7 @@
         <v>1.27</v>
       </c>
       <c r="N30" s="31" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="O30" s="106">
         <v>1.54E-2</v>
@@ -10077,7 +10155,7 @@
         <v>5.3</v>
       </c>
       <c r="X30" s="31" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Y30" s="31">
         <v>5.0599999999999999E-2</v>
@@ -10098,7 +10176,7 @@
         <v>139.9</v>
       </c>
       <c r="AG30" s="31" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AH30" s="31">
         <v>4.6399999999999997E-2</v>
@@ -10119,7 +10197,7 @@
         <v>54.55</v>
       </c>
       <c r="AP30" s="31" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AQ30" s="31">
         <v>-0.29620000000000002</v>
@@ -10142,7 +10220,7 @@
         <v>3179.33</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G31" s="106">
         <v>-4.8999999999999998E-3</v>
@@ -10164,7 +10242,7 @@
         <v>1.25</v>
       </c>
       <c r="N31" s="31" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O31" s="106">
         <v>2.3599999999999999E-2</v>
@@ -10185,7 +10263,7 @@
         <v>5.6</v>
       </c>
       <c r="X31" s="31" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="Y31" s="31">
         <v>-9.6199999999999994E-2</v>
@@ -10206,7 +10284,7 @@
         <v>140</v>
       </c>
       <c r="AG31" s="31" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AH31" s="31">
         <v>0.04</v>
@@ -10227,7 +10305,7 @@
         <v>82.2</v>
       </c>
       <c r="AP31" s="31" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AQ31" s="31">
         <v>6.0900000000000003E-2</v>
@@ -10250,7 +10328,7 @@
         <v>3143.9</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G32" s="106">
         <v>-4.1700000000000001E-2</v>
@@ -10272,7 +10350,7 @@
         <v>1.23</v>
       </c>
       <c r="N32" s="31" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="O32" s="106">
         <v>7.9000000000000008E-3</v>
@@ -10293,7 +10371,7 @@
         <v>6.13</v>
       </c>
       <c r="X32" s="31" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y32" s="31">
         <v>-8.5099999999999995E-2</v>
@@ -10314,7 +10392,7 @@
         <v>135</v>
       </c>
       <c r="AG32" s="31" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AH32" s="31">
         <v>-8.2000000000000007E-3</v>
@@ -10335,7 +10413,7 @@
         <v>75.3</v>
       </c>
       <c r="AP32" s="31" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AQ32" s="31">
         <v>-0.10340000000000001</v>
@@ -10358,7 +10436,7 @@
         <v>3128.7</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G33" s="106">
         <v>5.2400000000000002E-2</v>
@@ -10380,7 +10458,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="N33" s="31" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="O33" s="106">
         <v>8.6199999999999999E-2</v>
@@ -10401,7 +10479,7 @@
         <v>6.84</v>
       </c>
       <c r="X33" s="31" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y33" s="31">
         <v>-4.5499999999999999E-2</v>
@@ -10422,7 +10500,7 @@
         <v>134.9</v>
       </c>
       <c r="AG33" s="31" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AH33" s="31">
         <v>2.7000000000000001E-3</v>
@@ -10443,7 +10521,7 @@
         <v>90.5</v>
       </c>
       <c r="AP33" s="31" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AQ33" s="31">
         <v>-4.0099999999999997E-2</v>
@@ -10466,7 +10544,7 @@
         <v>3155.52</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G34" s="106">
         <v>1.49E-2</v>
@@ -10488,7 +10566,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" s="31" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="O34" s="106">
         <v>5.45E-2</v>
@@ -10509,7 +10587,7 @@
         <v>6.68</v>
       </c>
       <c r="X34" s="31" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Y34" s="31">
         <v>6.7599999999999993E-2</v>
@@ -10530,7 +10608,7 @@
         <v>109.9</v>
       </c>
       <c r="AG34" s="31" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AH34" s="31">
         <v>0.27089999999999997</v>
@@ -10551,7 +10629,7 @@
         <v>95.51</v>
       </c>
       <c r="AP34" s="31" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AQ34" s="31">
         <v>-8.8599999999999998E-2</v>
@@ -10574,7 +10652,7 @@
         <v>3156.15</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G35" s="106">
         <v>-3.4200000000000001E-2</v>
@@ -10596,7 +10674,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="N35" s="31" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="O35" s="106">
         <v>-5.6800000000000003E-2</v>
@@ -10617,7 +10695,7 @@
         <v>6</v>
       </c>
       <c r="X35" s="31" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="Y35" s="31">
         <v>0.1148</v>
@@ -10638,7 +10716,7 @@
         <v>109.8</v>
       </c>
       <c r="AG35" s="31" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AH35" s="31">
         <v>2.1399999999999999E-2</v>
@@ -10659,7 +10737,7 @@
         <v>103.7</v>
       </c>
       <c r="AP35" s="31" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AQ35" s="31">
         <v>-0.1211</v>
@@ -10682,7 +10760,7 @@
         <v>3263.36</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G36" s="106">
         <v>3.5999999999999999E-3</v>
@@ -10704,7 +10782,7 @@
         <v>1.1559999999999999</v>
       </c>
       <c r="N36" s="31" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O36" s="106">
         <v>8.5000000000000006E-3</v>
@@ -10725,7 +10803,7 @@
         <v>5.57</v>
       </c>
       <c r="X36" s="31" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Y36" s="31">
         <v>4.2700000000000002E-2</v>
@@ -10746,7 +10824,7 @@
         <v>98.1</v>
       </c>
       <c r="AG36" s="31" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AH36" s="31">
         <v>8.1799999999999998E-2</v>
@@ -10767,7 +10845,7 @@
         <v>115.3</v>
       </c>
       <c r="AP36" s="31" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AQ36" s="31">
         <v>-2.5000000000000001E-3</v>
@@ -10790,7 +10868,7 @@
         <v>3094.28</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G37" s="106">
         <v>-1.1000000000000001E-3</v>
@@ -10812,7 +10890,7 @@
         <v>1.137</v>
       </c>
       <c r="N37" s="31" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="O37" s="106">
         <v>-2.4799999999999999E-2</v>
@@ -10833,7 +10911,7 @@
         <v>5.61</v>
       </c>
       <c r="X37" s="31" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="Y37" s="31">
         <v>-9.6199999999999994E-2</v>
@@ -10854,7 +10932,7 @@
         <v>92.66</v>
       </c>
       <c r="AG37" s="31" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AH37" s="31">
         <v>-1.52E-2</v>
@@ -10875,7 +10953,7 @@
         <v>111.1</v>
       </c>
       <c r="AP37" s="31" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AQ37" s="31">
         <v>-2.2499999999999999E-2</v>
@@ -10898,7 +10976,7 @@
         <v>3260.58</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G38" s="106">
         <v>-3.0599999999999999E-2</v>
@@ -10920,7 +10998,7 @@
         <v>1.127</v>
       </c>
       <c r="N38" s="31" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="O38" s="106">
         <v>8.3000000000000001E-3</v>
@@ -10941,7 +11019,7 @@
         <v>5.63</v>
       </c>
       <c r="X38" s="31" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y38" s="31">
         <v>0.12520000000000001</v>
@@ -10962,7 +11040,7 @@
         <v>99.3</v>
       </c>
       <c r="AG38" s="31" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AH38" s="31">
         <v>-2.6800000000000001E-2</v>
@@ -10983,7 +11061,7 @@
         <v>119</v>
       </c>
       <c r="AP38" s="31" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AQ38" s="31">
         <v>-6.5299999999999997E-2</v>
@@ -11006,7 +11084,7 @@
         <v>3212.63</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G39" s="106">
         <v>3.5200000000000002E-2</v>
@@ -11028,7 +11106,7 @@
         <v>1.107</v>
       </c>
       <c r="N39" s="31" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O39" s="106">
         <v>-2.4400000000000002E-2</v>
@@ -11049,7 +11127,7 @@
         <v>5.53</v>
       </c>
       <c r="X39" s="31" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="Y39" s="31">
         <v>1.3899999999999999E-2</v>
@@ -11070,7 +11148,7 @@
         <v>101</v>
       </c>
       <c r="AG39" s="31" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AH39" s="31">
         <v>7.3300000000000004E-2</v>
@@ -11091,7 +11169,7 @@
         <v>130</v>
       </c>
       <c r="AP39" s="31" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AQ39" s="31">
         <v>2.46E-2</v>
@@ -11114,7 +11192,7 @@
         <v>3225.45</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G40" s="106">
         <v>-1.1900000000000001E-2</v>
@@ -11136,7 +11214,7 @@
         <v>1.1859999999999999</v>
       </c>
       <c r="N40" s="31" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="O40" s="106">
         <v>0</v>
@@ -11157,7 +11235,7 @@
         <v>5.27</v>
       </c>
       <c r="X40" s="31" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Y40" s="31">
         <v>4.9299999999999997E-2</v>
@@ -11178,7 +11256,7 @@
         <v>94.15</v>
       </c>
       <c r="AG40" s="31" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AH40" s="31">
         <v>-1.0800000000000001E-2</v>
@@ -11199,7 +11277,7 @@
         <v>124.7</v>
       </c>
       <c r="AP40" s="31" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AQ40" s="31">
         <v>-0.24640000000000001</v>
@@ -11222,7 +11300,7 @@
         <v>3091.18</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G41" s="106">
         <v>6.3799999999999996E-2</v>
@@ -11244,7 +11322,7 @@
         <v>1.1859999999999999</v>
       </c>
       <c r="N41" s="31" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="O41" s="106">
         <v>-3.15E-2</v>
@@ -11265,7 +11343,7 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="X41" s="31" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="Y41" s="31">
         <v>0.1734</v>
@@ -11286,7 +11364,7 @@
         <v>89.55</v>
       </c>
       <c r="AG41" s="31" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AH41" s="31">
         <v>-2.9499999999999998E-2</v>
@@ -11307,7 +11385,7 @@
         <v>166.1</v>
       </c>
       <c r="AP41" s="31" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AQ41" s="31">
         <v>1.95E-2</v>
@@ -11330,7 +11408,7 @@
         <v>2968.87</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G42" s="106">
         <v>-1.1900000000000001E-2</v>
@@ -11352,7 +11430,7 @@
         <v>1.2050000000000001</v>
       </c>
       <c r="N42" s="31" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="O42" s="106">
         <v>-3.7900000000000003E-2</v>
@@ -11373,7 +11451,7 @@
         <v>4.26</v>
       </c>
       <c r="X42" s="31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Y42" s="31">
         <v>-3.3099999999999997E-2</v>
@@ -11394,7 +11472,7 @@
         <v>100</v>
       </c>
       <c r="AG42" s="31" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AH42" s="31">
         <v>0</v>
@@ -11415,7 +11493,7 @@
         <v>156.5</v>
       </c>
       <c r="AP42" s="31" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AQ42" s="31">
         <v>3.0000000000000001E-3</v>
@@ -11438,7 +11516,7 @@
         <v>3098.24</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G43" s="106">
         <v>-2.8400000000000002E-2</v>
@@ -11460,7 +11538,7 @@
         <v>1.264</v>
       </c>
       <c r="N43" s="31" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O43" s="106">
         <v>-6.3799999999999996E-2</v>
@@ -11481,7 +11559,7 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="X43" s="31" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Y43" s="31">
         <v>-0.1138</v>
@@ -11502,7 +11580,7 @@
         <v>103.1</v>
       </c>
       <c r="AG43" s="31" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AH43" s="31">
         <v>-8.5999999999999993E-2</v>
@@ -11523,7 +11601,7 @@
         <v>156.5</v>
       </c>
       <c r="AP43" s="31" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AQ43" s="31">
         <v>-3.8199999999999998E-2</v>
@@ -11546,7 +11624,7 @@
         <v>3205.58</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G44" s="106">
         <v>3.0999999999999999E-3</v>
@@ -11568,7 +11646,7 @@
         <v>1.3720000000000001</v>
       </c>
       <c r="N44" s="31" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O44" s="106">
         <v>2.5000000000000001E-3</v>
@@ -11589,7 +11667,7 @@
         <v>5.14</v>
       </c>
       <c r="X44" s="31" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Y44" s="31">
         <v>-0.1051</v>
@@ -11610,7 +11688,7 @@
         <v>105.3</v>
       </c>
       <c r="AG44" s="31" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AH44" s="31">
         <v>-0.13780000000000001</v>
@@ -11631,7 +11709,7 @@
         <v>167.3</v>
       </c>
       <c r="AP44" s="31" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AQ44" s="31">
         <v>-4.5699999999999998E-2</v>
@@ -11654,7 +11732,7 @@
         <v>3088.25</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G45" s="106">
         <v>3.5200000000000002E-2</v>
@@ -11676,7 +11754,7 @@
         <v>1.33</v>
       </c>
       <c r="N45" s="31" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="O45" s="106">
         <v>1.43E-2</v>
@@ -11697,7 +11775,7 @@
         <v>5.29</v>
       </c>
       <c r="X45" s="31" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="Y45" s="31">
         <v>6.8400000000000002E-2</v>
@@ -11718,7 +11796,7 @@
         <v>122.2</v>
       </c>
       <c r="AG45" s="31" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AH45" s="31">
         <v>4.7100000000000003E-2</v>
@@ -11739,7 +11817,7 @@
         <v>167.1</v>
       </c>
       <c r="AP45" s="31" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AQ45" s="31">
         <v>-5.45E-2</v>
@@ -11762,7 +11840,7 @@
         <v>3072.34</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G46" s="106">
         <v>-4.0300000000000002E-2</v>
@@ -11784,7 +11862,7 @@
         <v>1.31</v>
       </c>
       <c r="N46" s="31" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O46" s="106">
         <v>-2.7799999999999998E-2</v>
@@ -11805,7 +11883,7 @@
         <v>5.62</v>
       </c>
       <c r="X46" s="31" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Y46" s="31">
         <v>-0.24299999999999999</v>
@@ -11826,7 +11904,7 @@
         <v>121.4</v>
       </c>
       <c r="AG46" s="31" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AH46" s="31">
         <v>-6.59E-2</v>
@@ -11847,7 +11925,7 @@
         <v>189.9</v>
       </c>
       <c r="AP46" s="31" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AQ46" s="31">
         <v>-0.2681</v>
@@ -11870,7 +11948,7 @@
         <v>3165.18</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G47" s="106">
         <v>-3.7100000000000001E-2</v>
@@ -11892,7 +11970,7 @@
         <v>1.34</v>
       </c>
       <c r="N47" s="31" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O47" s="106">
         <v>-2.0400000000000001E-2</v>
@@ -11913,7 +11991,7 @@
         <v>7.26</v>
       </c>
       <c r="X47" s="31" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="Y47" s="31">
         <v>-5.04E-2</v>
@@ -11934,7 +12012,7 @@
         <v>101.95</v>
       </c>
       <c r="AG47" s="31" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AH47" s="31">
         <v>0.21010000000000001</v>
@@ -11955,7 +12033,7 @@
         <v>237.12</v>
       </c>
       <c r="AP47" s="31" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AQ47" s="31">
         <v>6.7500000000000004E-2</v>
@@ -11978,7 +12056,7 @@
         <v>3303.07</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G48" s="106">
         <v>-1.5100000000000001E-2</v>
@@ -12000,7 +12078,7 @@
         <v>1.407</v>
       </c>
       <c r="N48" s="31" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O48" s="106">
         <v>-1.34E-2</v>
@@ -12021,7 +12099,7 @@
         <v>6.81</v>
       </c>
       <c r="X48" s="31" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Y48" s="31">
         <v>0.12479999999999999</v>
@@ -12042,7 +12120,7 @@
         <v>100.8</v>
       </c>
       <c r="AG48" s="31" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AH48" s="31">
         <v>4.4999999999999997E-3</v>
@@ -12063,7 +12141,7 @@
         <v>223</v>
       </c>
       <c r="AP48" s="31" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="AQ48" s="31">
         <v>6.7799999999999999E-2</v>
@@ -12086,7 +12164,7 @@
         <v>3128.06</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G49" s="106">
         <v>5.1299999999999998E-2</v>
@@ -12108,7 +12186,7 @@
         <v>1.2909999999999999</v>
       </c>
       <c r="N49" s="31" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O49" s="106">
         <v>5.67E-2</v>
@@ -12129,7 +12207,7 @@
         <v>6.67</v>
       </c>
       <c r="X49" s="31" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Y49" s="31">
         <v>-2.4899999999999999E-2</v>
@@ -12150,7 +12228,7 @@
         <v>83.75</v>
       </c>
       <c r="AG49" s="31" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AH49" s="31">
         <v>0.1208</v>
@@ -12171,7 +12249,7 @@
         <v>183.7</v>
       </c>
       <c r="AP49" s="31" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AQ49" s="31">
         <v>-2.4299999999999999E-2</v>
@@ -12194,7 +12272,7 @@
         <v>3214.93</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G50" s="106">
         <v>-2.3E-3</v>
@@ -12216,7 +12294,7 @@
         <v>1.32</v>
       </c>
       <c r="N50" s="31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O50" s="106">
         <v>3.6799999999999999E-2</v>
@@ -12237,7 +12315,7 @@
         <v>6.61</v>
       </c>
       <c r="X50" s="31" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Y50" s="31">
         <v>2.8400000000000002E-2</v>
@@ -12258,7 +12336,7 @@
         <v>97.6</v>
       </c>
       <c r="AG50" s="31" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AH50" s="31">
         <v>-8.8999999999999999E-3</v>
@@ -12279,7 +12357,7 @@
         <v>230.8</v>
       </c>
       <c r="AP50" s="31" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AQ50" s="31">
         <v>-4.48E-2</v>
@@ -12302,7 +12380,7 @@
         <v>3127.6</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G51" s="106">
         <v>4.0300000000000002E-2</v>
@@ -12324,7 +12402,7 @@
         <v>1.2909999999999999</v>
       </c>
       <c r="N51" s="31" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O51" s="106">
         <v>-2.86E-2</v>
@@ -12345,7 +12423,7 @@
         <v>6.34</v>
       </c>
       <c r="X51" s="31" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Y51" s="31">
         <v>-4.7399999999999998E-2</v>
@@ -12366,7 +12444,7 @@
         <v>97</v>
       </c>
       <c r="AG51" s="31" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AH51" s="31">
         <v>-1.0800000000000001E-2</v>
@@ -12387,7 +12465,7 @@
         <v>239.8</v>
       </c>
       <c r="AP51" s="31" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AQ51" s="31">
         <v>-2.8000000000000001E-2</v>
@@ -12410,7 +12488,7 @@
         <v>3045.13</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G52" s="106">
         <v>2.7099999999999999E-2</v>
@@ -12432,7 +12510,7 @@
         <v>1.31</v>
       </c>
       <c r="N52" s="31" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="O52" s="106">
         <v>2.1899999999999999E-2</v>
@@ -12453,7 +12531,7 @@
         <v>6.1</v>
       </c>
       <c r="X52" s="31" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Y52" s="31">
         <v>0.14599999999999999</v>
@@ -12474,7 +12552,7 @@
         <v>90.5</v>
       </c>
       <c r="AG52" s="31" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AH52" s="31">
         <v>9.8900000000000002E-2</v>
@@ -12495,7 +12573,7 @@
         <v>214</v>
       </c>
       <c r="AP52" s="31" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AQ52" s="31">
         <v>0.2041</v>
@@ -12518,7 +12596,7 @@
         <v>3041.29</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G53" s="106">
         <v>-4.9099999999999998E-2</v>
@@ -12540,7 +12618,7 @@
         <v>1.33</v>
       </c>
       <c r="N53" s="31" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O53" s="106">
         <v>-0.12180000000000001</v>
@@ -12561,7 +12639,7 @@
         <v>6.11</v>
       </c>
       <c r="X53" s="31" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Y53" s="31">
         <v>-0.1226</v>
@@ -12582,7 +12660,7 @@
         <v>92.7</v>
       </c>
       <c r="AG53" s="31" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AH53" s="31">
         <v>-7.7399999999999997E-2</v>
@@ -12603,7 +12681,7 @@
         <v>207.2</v>
       </c>
       <c r="AP53" s="31" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AQ53" s="31">
         <v>-6.5600000000000006E-2</v>
@@ -12626,7 +12704,7 @@
         <v>3044.73</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G54" s="106">
         <v>3.61E-2</v>
@@ -12648,7 +12726,7 @@
         <v>1.456</v>
       </c>
       <c r="N54" s="31" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="O54" s="106">
         <v>3.3099999999999997E-2</v>
@@ -12669,7 +12747,7 @@
         <v>7.11</v>
       </c>
       <c r="X54" s="31" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Y54" s="31">
         <v>-0.17530000000000001</v>
@@ -12690,7 +12768,7 @@
         <v>84</v>
       </c>
       <c r="AG54" s="31" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AH54" s="31">
         <v>0.13320000000000001</v>
@@ -12711,7 +12789,7 @@
         <v>215.87</v>
       </c>
       <c r="AP54" s="31" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AQ54" s="31">
         <v>-5.2200000000000003E-2</v>
@@ -12734,7 +12812,7 @@
         <v>3037.79</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G55" s="106">
         <v>1.04E-2</v>
@@ -12756,7 +12834,7 @@
         <v>1.446</v>
       </c>
       <c r="N55" s="31" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="O55" s="106">
         <v>-6.7900000000000002E-2</v>
@@ -12777,7 +12855,7 @@
         <v>8.16</v>
       </c>
       <c r="X55" s="31" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Y55" s="31">
         <v>-1.11E-2</v>
@@ -12798,7 +12876,7 @@
         <v>82.15</v>
       </c>
       <c r="AG55" s="31" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AH55" s="31">
         <v>-1.44E-2</v>
@@ -12819,7 +12897,7 @@
         <v>212.2</v>
       </c>
       <c r="AP55" s="31" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="AQ55" s="31">
         <v>-6.0699999999999997E-2</v>
@@ -12842,7 +12920,7 @@
         <v>3050.24</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G56" s="106">
         <v>-3.5299999999999998E-2</v>
@@ -12864,7 +12942,7 @@
         <v>1.5049999999999999</v>
       </c>
       <c r="N56" s="31" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O56" s="106">
         <v>3.1800000000000002E-2</v>
@@ -12885,7 +12963,7 @@
         <v>8.74</v>
       </c>
       <c r="X56" s="31" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Y56" s="31">
         <v>-3.4299999999999997E-2</v>
@@ -12906,7 +12984,7 @@
         <v>82.2</v>
       </c>
       <c r="AG56" s="31" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AH56" s="31">
         <v>8.8700000000000001E-2</v>
@@ -12927,7 +13005,7 @@
         <v>251.8</v>
       </c>
       <c r="AP56" s="31" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AQ56" s="31">
         <v>-5.5899999999999998E-2</v>
@@ -12950,7 +13028,7 @@
         <v>3095.35</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G57" s="106">
         <v>1.17E-2</v>
@@ -12972,7 +13050,7 @@
         <v>1.5049999999999999</v>
       </c>
       <c r="N57" s="31" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="O57" s="106">
         <v>-4.2700000000000002E-2</v>
@@ -12993,7 +13071,7 @@
         <v>8.7899999999999991</v>
       </c>
       <c r="X57" s="31" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Y57" s="31">
         <v>-1.6899999999999998E-2</v>
@@ -13014,7 +13092,7 @@
         <v>72.400000000000006</v>
       </c>
       <c r="AG57" s="31" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AH57" s="31">
         <v>1.2200000000000001E-2</v>
@@ -13035,7 +13113,7 @@
         <v>226.8</v>
       </c>
       <c r="AP57" s="31" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AQ57" s="31">
         <v>2.0299999999999999E-2</v>
@@ -13058,7 +13136,7 @@
         <v>3089.49</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G58" s="106">
         <v>-1.0699999999999999E-2</v>
@@ -13080,7 +13158,7 @@
         <v>1.5629999999999999</v>
       </c>
       <c r="N58" s="31" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="O58" s="106">
         <v>-3.5299999999999998E-2</v>
@@ -13101,7 +13179,7 @@
         <v>8.42</v>
       </c>
       <c r="X58" s="31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Y58" s="31">
         <v>-2.7699999999999999E-2</v>
@@ -13122,7 +13200,7 @@
         <v>77.95</v>
       </c>
       <c r="AG58" s="31" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AH58" s="31">
         <v>4.8999999999999998E-3</v>
@@ -13143,7 +13221,7 @@
         <v>258.2</v>
       </c>
       <c r="AP58" s="31" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AQ58" s="31">
         <v>-0.11840000000000001</v>
@@ -13166,7 +13244,7 @@
         <v>3023.95</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G59" s="106">
         <v>-1.6799999999999999E-2</v>
@@ -13188,7 +13266,7 @@
         <v>1.4950000000000001</v>
       </c>
       <c r="N59" s="31" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O59" s="106">
         <v>-1.1599999999999999E-2</v>
@@ -13209,7 +13287,7 @@
         <v>9.44</v>
       </c>
       <c r="X59" s="31" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Y59" s="31">
         <v>-3.3700000000000001E-2</v>
@@ -13230,7 +13308,7 @@
         <v>72.099999999999994</v>
       </c>
       <c r="AG59" s="31" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AH59" s="31">
         <v>9.69E-2</v>
@@ -13251,7 +13329,7 @@
         <v>276.39999999999998</v>
       </c>
       <c r="AP59" s="31" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AQ59" s="31">
         <v>9.2999999999999992E-3</v>
@@ -13274,7 +13352,7 @@
         <v>3145.28</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G60" s="106">
         <v>1.67E-2</v>
@@ -13296,7 +13374,7 @@
         <v>1.66</v>
       </c>
       <c r="N60" s="31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O60" s="106">
         <v>5.7999999999999996E-3</v>
@@ -13317,7 +13395,7 @@
         <v>8.9</v>
       </c>
       <c r="X60" s="31" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Y60" s="31">
         <v>0.1003</v>
@@ -13338,7 +13416,7 @@
         <v>72.05</v>
       </c>
       <c r="AG60" s="31" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AH60" s="31">
         <v>-0.1928</v>
@@ -13359,7 +13437,7 @@
         <v>295</v>
       </c>
       <c r="AP60" s="31" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AQ60" s="31">
         <v>-2.6599999999999999E-2</v>
@@ -13382,7 +13460,7 @@
         <v>2948.64</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G61" s="106">
         <v>7.3300000000000004E-2</v>
@@ -13404,7 +13482,7 @@
         <v>1.5529999999999999</v>
       </c>
       <c r="N61" s="31" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="O61" s="106">
         <v>6.2100000000000002E-2</v>
@@ -13425,7 +13503,7 @@
         <v>7.7</v>
       </c>
       <c r="X61" s="31" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="Y61" s="31">
         <v>7.2499999999999995E-2</v>
@@ -13446,7 +13524,7 @@
         <v>84.5</v>
       </c>
       <c r="AG61" s="31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AH61" s="31">
         <v>2.2800000000000001E-2</v>
@@ -13467,7 +13545,7 @@
         <v>292.52</v>
       </c>
       <c r="AP61" s="31" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AQ61" s="31">
         <v>2.9399999999999999E-2</v>
@@ -13490,7 +13568,7 @@
         <v>2869.3</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G62" s="106">
         <v>1.6E-2</v>
@@ -13512,7 +13590,7 @@
         <v>1.514</v>
       </c>
       <c r="N62" s="31" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O62" s="106">
         <v>1.9E-2</v>
@@ -13533,7 +13611,7 @@
         <v>6.1</v>
       </c>
       <c r="X62" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Y62" s="31">
         <v>0.3256</v>
@@ -13554,7 +13632,7 @@
         <v>71.13</v>
       </c>
       <c r="AG62" s="31" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AH62" s="31">
         <v>0.25440000000000002</v>
@@ -13575,7 +13653,7 @@
         <v>245.6</v>
       </c>
       <c r="AP62" s="31" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AQ62" s="31">
         <v>0.19500000000000001</v>
@@ -13598,7 +13676,7 @@
         <v>2832.04</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G63" s="106">
         <v>2.06E-2</v>
@@ -13620,7 +13698,7 @@
         <v>1.534</v>
       </c>
       <c r="N63" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="O63" s="106">
         <v>-5.3900000000000003E-2</v>
@@ -13641,7 +13719,7 @@
         <v>5.81</v>
       </c>
       <c r="X63" s="31" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Y63" s="31">
         <v>-3.5900000000000001E-2</v>
@@ -13662,7 +13740,7 @@
         <v>66.5</v>
       </c>
       <c r="AG63" s="31" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AH63" s="31">
         <v>-3.04E-2</v>
@@ -13683,7 +13761,7 @@
         <v>222.81</v>
       </c>
       <c r="AP63" s="31" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AQ63" s="31">
         <v>5.3900000000000003E-2</v>
@@ -13712,14 +13790,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="104"/>
       <c r="H1" s="104"/>
       <c r="I1" s="104"/>
@@ -13953,24 +14031,24 @@
         <v>-349.3</v>
       </c>
       <c r="E17" s="37">
-        <f>-$E68*E$12</f>
-        <v>-408.87568412822515</v>
+        <f ca="1">-$E68*E$12</f>
+        <v>-361.82580160518722</v>
       </c>
       <c r="F17" s="37">
-        <f>-$E68*F$12</f>
-        <v>-417.45895230648944</v>
+        <f ca="1">-$E68*F$12</f>
+        <v>-369.42138140987623</v>
       </c>
       <c r="G17" s="37">
-        <f t="shared" ref="G17:I17" si="5">-$E68*G$12</f>
-        <v>-425.80813135261923</v>
+        <f t="shared" ref="G17:I17" ca="1" si="5">-$E68*G$12</f>
+        <v>-376.80980903807375</v>
       </c>
       <c r="H17" s="37">
-        <f t="shared" si="5"/>
-        <v>-434.32429397967161</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-384.34600521883527</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="5"/>
-        <v>-443.4451041532447</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-392.41727132843079</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
@@ -13987,23 +14065,23 @@
       </c>
       <c r="E18" s="37">
         <f>-$E73*E$12</f>
-        <v>-105.35016195688596</v>
+        <v>-93.227375163088595</v>
       </c>
       <c r="F18" s="37">
         <f>-$E73*F$12</f>
-        <v>-107.56171115827097</v>
+        <v>-95.184438382161076</v>
       </c>
       <c r="G18" s="37">
         <f t="shared" ref="G18:I18" si="6">-$E73*G$12</f>
-        <v>-109.71294538143638</v>
+        <v>-97.088127149804293</v>
       </c>
       <c r="H18" s="37">
         <f t="shared" si="6"/>
-        <v>-111.90720428906512</v>
+        <v>-99.029889692800381</v>
       </c>
       <c r="I18" s="37">
         <f t="shared" si="6"/>
-        <v>-114.25725557913547</v>
+        <v>-101.10951737634919</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
@@ -14019,24 +14097,24 @@
         <v>-122.6</v>
       </c>
       <c r="E19" s="37">
-        <f>-$E78*E$12</f>
-        <v>-143.51033173238019</v>
+        <f ca="1">-$E78*E$12</f>
+        <v>-126.99640216660735</v>
       </c>
       <c r="F19" s="37">
-        <f>-$E78*F$12</f>
-        <v>-146.52295320004467</v>
+        <f ca="1">-$E78*F$12</f>
+        <v>-129.66235717392163</v>
       </c>
       <c r="G19" s="37">
-        <f t="shared" ref="G19:I19" si="7">-$E78*G$12</f>
-        <v>-149.45341226404557</v>
+        <f t="shared" ref="G19:I19" ca="1" si="7">-$E78*G$12</f>
+        <v>-132.25560431740007</v>
       </c>
       <c r="H19" s="37">
-        <f t="shared" si="7"/>
-        <v>-152.44248050932649</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>-134.90071640374808</v>
       </c>
       <c r="I19" s="37">
-        <f t="shared" si="7"/>
-        <v>-155.64377260002234</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>-137.73363144822679</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
@@ -14348,24 +14426,24 @@
         <v>-4286.0000000000009</v>
       </c>
       <c r="E29" s="37">
-        <f>SUM(E14:E28)</f>
-        <v>-4542.2101429461836</v>
+        <f ca="1">SUM(E14:E28)</f>
+        <v>-4466.5235440635752</v>
       </c>
       <c r="F29" s="37">
-        <f>SUM(F14:F28)</f>
-        <v>-4637.5618825881829</v>
+        <f ca="1">SUM(F14:F28)</f>
+        <v>-4560.2864428893372</v>
       </c>
       <c r="G29" s="37">
-        <f t="shared" ref="G29:I29" si="9">SUM(G14:G28)</f>
-        <v>-4730.3131202399436</v>
+        <f t="shared" ref="G29:I29" ca="1" si="9">SUM(G14:G28)</f>
+        <v>-4651.4921717471207</v>
       </c>
       <c r="H29" s="37">
-        <f t="shared" si="9"/>
-        <v>-4824.9193826447454</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>-4744.5220151820658</v>
       </c>
       <c r="I29" s="37">
-        <f t="shared" si="9"/>
-        <v>-4926.2426896802854</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>-4844.1569775008902</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
@@ -14381,24 +14459,24 @@
         <v>772.60000000000014</v>
       </c>
       <c r="E31" s="27">
-        <f>SUM(E12:E28)</f>
-        <v>697.78985705381695</v>
+        <f ca="1">SUM(E12:E28)</f>
+        <v>773.47645593642494</v>
       </c>
       <c r="F31" s="27">
-        <f>SUM(F12:F28)</f>
-        <v>712.43811741181764</v>
+        <f ca="1">SUM(F12:F28)</f>
+        <v>789.71355711066383</v>
       </c>
       <c r="G31" s="27">
-        <f t="shared" ref="G31:I31" si="10">SUM(G12:G28)</f>
-        <v>726.6868797600539</v>
+        <f t="shared" ref="G31:I31" ca="1" si="10">SUM(G12:G28)</f>
+        <v>805.50782825287706</v>
       </c>
       <c r="H31" s="27">
-        <f t="shared" si="10"/>
-        <v>741.22061735525483</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>821.61798481793437</v>
       </c>
       <c r="I31" s="27">
-        <f t="shared" si="10"/>
-        <v>756.78625031971444</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>838.87196249911017</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="12"/>
@@ -14459,24 +14537,24 @@
         <v>373.00000000000011</v>
       </c>
       <c r="E34" s="7">
-        <f>SUM(E31:E32)</f>
-        <v>260.46941256851892</v>
+        <f ca="1">SUM(E31:E32)</f>
+        <v>336.15601145112691</v>
       </c>
       <c r="F34" s="7">
         <f ca="1">SUM(F31:F32)</f>
-        <v>240.54850892464299</v>
+        <v>317.82394862348917</v>
       </c>
       <c r="G34" s="7">
         <f t="shared" ref="G34:I34" ca="1" si="11">SUM(G31:G32)</f>
-        <v>223.98370991012246</v>
+        <v>302.80465840294562</v>
       </c>
       <c r="H34" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>210.83760898485957</v>
+        <v>291.23497644753911</v>
       </c>
       <c r="I34" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>201.23332311104582</v>
+        <v>283.31903529044155</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="8"/>
@@ -14601,23 +14679,23 @@
       </c>
       <c r="E39" s="27">
         <f ca="1">SUM(E34,E36:E38)</f>
-        <v>211.94887582709126</v>
+        <v>287.63547470969922</v>
       </c>
       <c r="F39" s="27">
         <f ca="1">SUM(F34,F36:F38)</f>
-        <v>192.48896929704128</v>
+        <v>269.76440899588744</v>
       </c>
       <c r="G39" s="27">
         <f t="shared" ref="G39:I39" ca="1" si="14">SUM(G34,G36:G38)</f>
-        <v>176.37259474778782</v>
+        <v>255.19354324061098</v>
       </c>
       <c r="H39" s="27">
         <f t="shared" ca="1" si="14"/>
-        <v>163.68388677709737</v>
+        <v>244.08125423977691</v>
       </c>
       <c r="I39" s="27">
         <f t="shared" ca="1" si="14"/>
-        <v>154.56946875763063</v>
+        <v>236.65518093702636</v>
       </c>
       <c r="J39" s="27"/>
       <c r="K39" s="12"/>
@@ -14637,23 +14715,23 @@
       </c>
       <c r="E40" s="37">
         <f ca="1">-E39*E105</f>
-        <v>-42.201054835969309</v>
+        <v>-57.270982889745234</v>
       </c>
       <c r="F40" s="37">
         <f ca="1">-F39*F105</f>
-        <v>-38.326400727176406</v>
+        <v>-53.712682232462939</v>
       </c>
       <c r="G40" s="37">
         <f t="shared" ref="G40:I40" ca="1" si="15">-G39*G105</f>
-        <v>-35.117475917096655</v>
+        <v>-50.811483052488938</v>
       </c>
       <c r="H40" s="37">
         <f t="shared" ca="1" si="15"/>
-        <v>-32.591032411420535</v>
+        <v>-48.598919689520649</v>
       </c>
       <c r="I40" s="37">
         <f t="shared" ca="1" si="15"/>
-        <v>-30.776264330502514</v>
+        <v>-47.120317241442713</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.25">
@@ -14670,23 +14748,23 @@
       </c>
       <c r="E41" s="46">
         <f ca="1">SUM(E39:E40)</f>
-        <v>169.74782099112196</v>
+        <v>230.364491819954</v>
       </c>
       <c r="F41" s="46">
         <f ca="1">SUM(F39:F40)</f>
-        <v>154.16256856986487</v>
+        <v>216.05172676342448</v>
       </c>
       <c r="G41" s="46">
         <f t="shared" ref="G41:I41" ca="1" si="16">SUM(G39:G40)</f>
-        <v>141.25511883069117</v>
+        <v>204.38206018812204</v>
       </c>
       <c r="H41" s="46">
         <f t="shared" ca="1" si="16"/>
-        <v>131.09285436567683</v>
+        <v>195.48233455025627</v>
       </c>
       <c r="I41" s="46">
         <f t="shared" ca="1" si="16"/>
-        <v>123.79320442712812</v>
+        <v>189.53486369558365</v>
       </c>
       <c r="J41" s="30"/>
       <c r="K41" s="30"/>
@@ -15353,27 +15431,27 @@
       </c>
       <c r="D66" s="39">
         <f ca="1">OFFSET(D66,MATCH($C$9,$B67:$B69,0),)</f>
-        <v>7.8029710711493352E-2</v>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="E66" s="39">
         <f ca="1">OFFSET(E66,MATCH($C$9,$B67:$B69,0),)</f>
-        <v>7.8029710711493352E-2</v>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="F66" s="39">
         <f ca="1">OFFSET(F66,MATCH($C$9,$B67:$B69,0),)</f>
-        <v>7.8029710711493352E-2</v>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="G66" s="39">
         <f t="shared" ref="G66:I66" ca="1" si="33">OFFSET(G66,MATCH($C$9,$B67:$B69,0),)</f>
-        <v>7.8029710711493352E-2</v>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="H66" s="39">
         <f t="shared" ca="1" si="33"/>
-        <v>7.8029710711493352E-2</v>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="I66" s="39">
         <f t="shared" ca="1" si="33"/>
-        <v>7.8029710711493352E-2</v>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="J66" s="36"/>
     </row>
@@ -15382,32 +15460,32 @@
         <v>94</v>
       </c>
       <c r="C67" s="34">
-        <f>-C$17/$C$12</f>
+        <f>-C$17/C$12</f>
         <v>7.365129007036747E-2</v>
       </c>
       <c r="D67" s="34">
-        <f>-D$17/$C$12</f>
-        <v>7.8029710711493352E-2</v>
+        <f>-D$17/D$12</f>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="E67" s="36">
-        <f>E$68+$J67</f>
-        <v>6.8029710711493357E-2</v>
+        <f ca="1">E$68+$J67</f>
+        <v>5.9050725497173127E-2</v>
       </c>
       <c r="F67" s="36">
-        <f>F$68+$J67</f>
-        <v>6.8029710711493357E-2</v>
+        <f ca="1">F$68+$J67</f>
+        <v>5.9050725497173127E-2</v>
       </c>
       <c r="G67" s="36">
-        <f t="shared" ref="G67:I67" si="34">G$68+$J67</f>
-        <v>6.8029710711493357E-2</v>
+        <f t="shared" ref="G67:I67" ca="1" si="34">G$68+$J67</f>
+        <v>5.9050725497173127E-2</v>
       </c>
       <c r="H67" s="36">
-        <f t="shared" si="34"/>
-        <v>6.8029710711493357E-2</v>
+        <f t="shared" ca="1" si="34"/>
+        <v>5.9050725497173127E-2</v>
       </c>
       <c r="I67" s="36">
-        <f t="shared" si="34"/>
-        <v>6.8029710711493357E-2</v>
+        <f t="shared" ca="1" si="34"/>
+        <v>5.9050725497173127E-2</v>
       </c>
       <c r="J67" s="36">
         <v>-0.01</v>
@@ -15418,32 +15496,32 @@
         <v>95</v>
       </c>
       <c r="C68" s="34">
-        <f>-C$17/$C$12</f>
+        <f t="shared" ref="C68:I69" si="35">-C$17/C$12</f>
         <v>7.365129007036747E-2</v>
       </c>
       <c r="D68" s="34">
-        <f>-$D$17/$C$12</f>
-        <v>7.8029710711493352E-2</v>
+        <f t="shared" si="35"/>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="E68" s="34">
-        <f>-$D$17/$C$12</f>
-        <v>7.8029710711493352E-2</v>
+        <f t="shared" ca="1" si="35"/>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="F68" s="34">
-        <f>-$D$17/$C$12</f>
-        <v>7.8029710711493352E-2</v>
+        <f t="shared" ca="1" si="35"/>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="G68" s="34">
-        <f t="shared" ref="G68:I68" si="35">-$D$17/$C$12</f>
-        <v>7.8029710711493352E-2</v>
+        <f t="shared" ca="1" si="35"/>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="H68" s="34">
-        <f t="shared" si="35"/>
-        <v>7.8029710711493352E-2</v>
+        <f t="shared" ca="1" si="35"/>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="I68" s="34">
-        <f t="shared" si="35"/>
-        <v>7.8029710711493352E-2</v>
+        <f t="shared" ca="1" si="35"/>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="J68" s="36"/>
     </row>
@@ -15452,32 +15530,32 @@
         <v>96</v>
       </c>
       <c r="C69" s="34">
-        <f>-C$17/$C$12</f>
+        <f t="shared" si="35"/>
         <v>7.365129007036747E-2</v>
       </c>
       <c r="D69" s="34">
-        <f>-D$17/$C$12</f>
-        <v>7.8029710711493352E-2</v>
+        <f t="shared" si="35"/>
+        <v>6.9050725497173129E-2</v>
       </c>
       <c r="E69" s="36">
-        <f>E$68+$J69</f>
-        <v>8.8029710711493347E-2</v>
+        <f ca="1">E$68+$J69</f>
+        <v>7.9050725497173124E-2</v>
       </c>
       <c r="F69" s="36">
-        <f>F$68+$J69</f>
-        <v>8.8029710711493347E-2</v>
+        <f ca="1">F$68+$J69</f>
+        <v>7.9050725497173124E-2</v>
       </c>
       <c r="G69" s="36">
-        <f t="shared" ref="G69:I69" si="36">G$68+$J69</f>
-        <v>8.8029710711493347E-2</v>
+        <f t="shared" ref="G69:I69" ca="1" si="36">G$68+$J69</f>
+        <v>7.9050725497173124E-2</v>
       </c>
       <c r="H69" s="36">
-        <f t="shared" si="36"/>
-        <v>8.8029710711493347E-2</v>
+        <f t="shared" ca="1" si="36"/>
+        <v>7.9050725497173124E-2</v>
       </c>
       <c r="I69" s="36">
-        <f t="shared" si="36"/>
-        <v>8.8029710711493347E-2</v>
+        <f t="shared" ca="1" si="36"/>
+        <v>7.9050725497173124E-2</v>
       </c>
       <c r="J69" s="36">
         <v>0.01</v>
@@ -15507,27 +15585,27 @@
       </c>
       <c r="D71" s="39">
         <f ca="1">OFFSET(D71,MATCH($C$9,$B72:$B74,0),)</f>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="E71" s="39">
         <f ca="1">OFFSET(E71,MATCH($C$9,$B72:$B74,0),)</f>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="F71" s="39">
         <f ca="1">OFFSET(F71,MATCH($C$9,$B72:$B74,0),)</f>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="G71" s="39">
         <f t="shared" ref="G71:I71" ca="1" si="37">OFFSET(G71,MATCH($C$9,$B72:$B74,0),)</f>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="H71" s="39">
         <f t="shared" ca="1" si="37"/>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="I71" s="39">
         <f t="shared" ca="1" si="37"/>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="J71" s="36"/>
     </row>
@@ -15545,23 +15623,23 @@
       </c>
       <c r="E72" s="36">
         <f>E$73+$J72</f>
-        <v>1.0104992739863731E-2</v>
+        <v>7.7914838097497326E-3</v>
       </c>
       <c r="F72" s="36">
         <f>F$73+$J72</f>
-        <v>1.0104992739863731E-2</v>
+        <v>7.7914838097497326E-3</v>
       </c>
       <c r="G72" s="36">
         <f t="shared" ref="G72:I72" si="38">G$73+$J72</f>
-        <v>1.0104992739863731E-2</v>
+        <v>7.7914838097497326E-3</v>
       </c>
       <c r="H72" s="36">
         <f t="shared" si="38"/>
-        <v>1.0104992739863731E-2</v>
+        <v>7.7914838097497326E-3</v>
       </c>
       <c r="I72" s="36">
         <f t="shared" si="38"/>
-        <v>1.0104992739863731E-2</v>
+        <v>7.7914838097497326E-3</v>
       </c>
       <c r="J72" s="36">
         <v>-0.01</v>
@@ -15576,28 +15654,28 @@
         <v>2.3321791578241931E-2</v>
       </c>
       <c r="D73" s="34">
-        <f>-$D$18/$C$12</f>
-        <v>2.0104992739863731E-2</v>
+        <f>-$D$18/$D$12</f>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="E73" s="34">
-        <f>-$D$18/$C$12</f>
-        <v>2.0104992739863731E-2</v>
+        <f t="shared" ref="E73:I73" si="39">-$D$18/$D$12</f>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="F73" s="34">
-        <f>-$D$18/$C$12</f>
-        <v>2.0104992739863731E-2</v>
+        <f t="shared" si="39"/>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="G73" s="34">
-        <f t="shared" ref="G73:I73" si="39">-$D$18/$C$12</f>
-        <v>2.0104992739863731E-2</v>
+        <f t="shared" si="39"/>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="H73" s="34">
         <f t="shared" si="39"/>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="I73" s="34">
         <f t="shared" si="39"/>
-        <v>2.0104992739863731E-2</v>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="J73" s="36"/>
     </row>
@@ -15615,23 +15693,23 @@
       </c>
       <c r="E74" s="36">
         <f>E$73+$J74</f>
-        <v>3.010499273986373E-2</v>
+        <v>2.7791483809749731E-2</v>
       </c>
       <c r="F74" s="36">
         <f>F$73+$J74</f>
-        <v>3.010499273986373E-2</v>
+        <v>2.7791483809749731E-2</v>
       </c>
       <c r="G74" s="36">
         <f t="shared" ref="G74:I74" si="40">G$73+$J74</f>
-        <v>3.010499273986373E-2</v>
+        <v>2.7791483809749731E-2</v>
       </c>
       <c r="H74" s="36">
         <f t="shared" si="40"/>
-        <v>3.010499273986373E-2</v>
+        <v>2.7791483809749731E-2</v>
       </c>
       <c r="I74" s="36">
         <f t="shared" si="40"/>
-        <v>3.010499273986373E-2</v>
+        <v>2.7791483809749731E-2</v>
       </c>
       <c r="J74" s="36">
         <v>0.01</v>
@@ -15661,27 +15739,27 @@
       </c>
       <c r="D76" s="39">
         <f ca="1">OFFSET(D76,MATCH($C$9,$B77:$B79,0),)</f>
-        <v>2.7387467887858816E-2</v>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="E76" s="39">
         <f ca="1">OFFSET(E76,MATCH($C$9,$B77:$B79,0),)</f>
-        <v>2.7387467887858816E-2</v>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="F76" s="39">
         <f ca="1">OFFSET(F76,MATCH($C$9,$B77:$B79,0),)</f>
-        <v>2.7387467887858816E-2</v>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="G76" s="39">
         <f t="shared" ref="G76:I76" ca="1" si="41">OFFSET(G76,MATCH($C$9,$B77:$B79,0),)</f>
-        <v>2.7387467887858816E-2</v>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="H76" s="39">
         <f t="shared" ca="1" si="41"/>
-        <v>2.7387467887858816E-2</v>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="I76" s="39">
         <f t="shared" ca="1" si="41"/>
-        <v>2.7387467887858816E-2</v>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="J76" s="36"/>
     </row>
@@ -15690,32 +15768,32 @@
         <v>94</v>
       </c>
       <c r="C77" s="34">
-        <f>-C$19/$C$12</f>
+        <f>-C$19/C$12</f>
         <v>2.2807997319334299E-2</v>
       </c>
       <c r="D77" s="34">
-        <f>-D$19/$C$12</f>
-        <v>2.7387467887858816E-2</v>
+        <f>-D$19/D$12</f>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="E77" s="36">
-        <f>E$78+$J77</f>
-        <v>1.7387467887858818E-2</v>
+        <f ca="1">E$78+$J77</f>
+        <v>1.4235954611947968E-2</v>
       </c>
       <c r="F77" s="36">
-        <f>F$78+$J77</f>
-        <v>1.7387467887858818E-2</v>
+        <f ca="1">F$78+$J77</f>
+        <v>1.4235954611947968E-2</v>
       </c>
       <c r="G77" s="36">
-        <f t="shared" ref="G77:I77" si="42">G$78+$J77</f>
-        <v>1.7387467887858818E-2</v>
+        <f t="shared" ref="G77:I77" ca="1" si="42">G$78+$J77</f>
+        <v>1.4235954611947968E-2</v>
       </c>
       <c r="H77" s="36">
-        <f t="shared" si="42"/>
-        <v>1.7387467887858818E-2</v>
+        <f t="shared" ca="1" si="42"/>
+        <v>1.4235954611947968E-2</v>
       </c>
       <c r="I77" s="36">
-        <f t="shared" si="42"/>
-        <v>1.7387467887858818E-2</v>
+        <f t="shared" ca="1" si="42"/>
+        <v>1.4235954611947968E-2</v>
       </c>
       <c r="J77" s="36">
         <v>-0.01</v>
@@ -15726,32 +15804,32 @@
         <v>95</v>
       </c>
       <c r="C78" s="34">
-        <f>-C$19/$C$12</f>
+        <f>-C$19/C$12</f>
         <v>2.2807997319334299E-2</v>
       </c>
       <c r="D78" s="34">
-        <f>-$D$19/$C$12</f>
-        <v>2.7387467887858816E-2</v>
+        <f>-D$19/D$12</f>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="E78" s="34">
-        <f>-$D$19/$C$12</f>
-        <v>2.7387467887858816E-2</v>
+        <f t="shared" ref="E78:I78" ca="1" si="43">-E$19/E$12</f>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="F78" s="34">
-        <f>-$D$19/$C$12</f>
-        <v>2.7387467887858816E-2</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="G78" s="34">
-        <f t="shared" ref="G78:I78" si="43">-$D$19/$C$12</f>
-        <v>2.7387467887858816E-2</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="H78" s="34">
-        <f t="shared" si="43"/>
-        <v>2.7387467887858816E-2</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="I78" s="34">
-        <f t="shared" si="43"/>
-        <v>2.7387467887858816E-2</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="J78" s="36"/>
     </row>
@@ -15760,32 +15838,32 @@
         <v>96</v>
       </c>
       <c r="C79" s="34">
-        <f>-C$19/$C$12</f>
+        <f>-C$19/C$12</f>
         <v>2.2807997319334299E-2</v>
       </c>
       <c r="D79" s="34">
-        <f>-D$19/$C$12</f>
-        <v>2.7387467887858816E-2</v>
+        <f>-D$19/D$12</f>
+        <v>2.4235954611947969E-2</v>
       </c>
       <c r="E79" s="36">
-        <f>E$78+$J79</f>
-        <v>3.7387467887858815E-2</v>
+        <f ca="1">E$78+$J79</f>
+        <v>3.423595461194797E-2</v>
       </c>
       <c r="F79" s="36">
-        <f>F$78+$J79</f>
-        <v>3.7387467887858815E-2</v>
+        <f ca="1">F$78+$J79</f>
+        <v>3.423595461194797E-2</v>
       </c>
       <c r="G79" s="36">
-        <f t="shared" ref="G79:I79" si="44">G$78+$J79</f>
-        <v>3.7387467887858815E-2</v>
+        <f t="shared" ref="G79:I79" ca="1" si="44">G$78+$J79</f>
+        <v>3.423595461194797E-2</v>
       </c>
       <c r="H79" s="36">
-        <f t="shared" si="44"/>
-        <v>3.7387467887858815E-2</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>3.423595461194797E-2</v>
       </c>
       <c r="I79" s="36">
-        <f t="shared" si="44"/>
-        <v>3.7387467887858815E-2</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>3.423595461194797E-2</v>
       </c>
       <c r="J79" s="36">
         <v>0.01</v>
@@ -16384,24 +16462,24 @@
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="E99" s="34">
-        <f>$E98+$J$97</f>
-        <v>8.4376705017198423E-3</v>
+        <f>$E98+$J$99</f>
+        <v>1.2437670501719842E-2</v>
       </c>
       <c r="F99" s="34">
-        <f>$E98+$J$97</f>
-        <v>8.4376705017198423E-3</v>
+        <f t="shared" ref="F99:I99" si="60">$E98+$J$99</f>
+        <v>1.2437670501719842E-2</v>
       </c>
       <c r="G99" s="34">
-        <f t="shared" ref="G99:I99" si="60">$E98+$J$97</f>
-        <v>8.4376705017198423E-3</v>
+        <f t="shared" si="60"/>
+        <v>1.2437670501719842E-2</v>
       </c>
       <c r="H99" s="34">
         <f t="shared" si="60"/>
-        <v>8.4376705017198423E-3</v>
+        <v>1.2437670501719842E-2</v>
       </c>
       <c r="I99" s="34">
         <f t="shared" si="60"/>
-        <v>8.4376705017198423E-3</v>
+        <v>1.2437670501719842E-2</v>
       </c>
       <c r="J99" s="36">
         <v>2E-3</v>
@@ -16708,13 +16786,13 @@
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
-      <c r="E2" s="115" t="s">
+      <c r="E2" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="41" t="s">
@@ -16760,23 +16838,23 @@
       </c>
       <c r="E4" s="43">
         <f ca="1">'Profit &amp; loss'!E39</f>
-        <v>211.94887582709126</v>
+        <v>287.63547470969922</v>
       </c>
       <c r="F4" s="43">
         <f ca="1">'Profit &amp; loss'!F39</f>
-        <v>192.48896929704128</v>
+        <v>269.76440899588744</v>
       </c>
       <c r="G4" s="43">
         <f ca="1">'Profit &amp; loss'!G39</f>
-        <v>176.37259474778782</v>
+        <v>255.19354324061098</v>
       </c>
       <c r="H4" s="43">
         <f ca="1">'Profit &amp; loss'!H39</f>
-        <v>163.68388677709737</v>
+        <v>244.08125423977691</v>
       </c>
       <c r="I4" s="43">
         <f ca="1">'Profit &amp; loss'!I39</f>
-        <v>154.56946875763063</v>
+        <v>236.65518093702636</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
@@ -17321,23 +17399,23 @@
       </c>
       <c r="E24" s="43">
         <f ca="1">'Profit &amp; loss'!E40</f>
-        <v>-42.201054835969309</v>
+        <v>-57.270982889745234</v>
       </c>
       <c r="F24" s="43">
         <f ca="1">'Profit &amp; loss'!F40</f>
-        <v>-38.326400727176406</v>
+        <v>-53.712682232462939</v>
       </c>
       <c r="G24" s="43">
         <f ca="1">'Profit &amp; loss'!G40</f>
-        <v>-35.117475917096655</v>
+        <v>-50.811483052488938</v>
       </c>
       <c r="H24" s="43">
         <f ca="1">'Profit &amp; loss'!H40</f>
-        <v>-32.591032411420535</v>
+        <v>-48.598919689520649</v>
       </c>
       <c r="I24" s="43">
         <f ca="1">'Profit &amp; loss'!I40</f>
-        <v>-30.776264330502514</v>
+        <v>-47.120317241442713</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -17411,23 +17489,23 @@
       </c>
       <c r="E27" s="44">
         <f ca="1">SUM(E4:E26)</f>
-        <v>663.72558649947359</v>
+        <v>724.34225732830566</v>
       </c>
       <c r="F27" s="44">
         <f t="shared" ca="1" si="2"/>
-        <v>683.58742477917997</v>
+        <v>745.47658297273949</v>
       </c>
       <c r="G27" s="44">
         <f t="shared" ca="1" si="2"/>
-        <v>701.5304240791952</v>
+        <v>764.65736543662604</v>
       </c>
       <c r="H27" s="44">
         <f t="shared" ca="1" si="2"/>
-        <v>719.02168492545638</v>
+        <v>783.41116511003577</v>
       </c>
       <c r="I27" s="44">
         <f t="shared" ca="1" si="2"/>
-        <v>736.79667369471008</v>
+        <v>802.53833296316554</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -17955,23 +18033,23 @@
       </c>
       <c r="E50" s="37">
         <f ca="1">'retained earnings schedule'!D11</f>
-        <v>-110.37666329985419</v>
+        <v>-149.79199026762726</v>
       </c>
       <c r="F50" s="37">
         <f ca="1">'retained earnings schedule'!E11</f>
-        <v>-100.24252343932365</v>
+        <v>-140.48527139306154</v>
       </c>
       <c r="G50" s="37">
         <f ca="1">'retained earnings schedule'!F11</f>
-        <v>-91.849595473579228</v>
+        <v>-132.89719838639189</v>
       </c>
       <c r="H50" s="37">
         <f ca="1">'retained earnings schedule'!G11</f>
-        <v>-85.241694195850144</v>
+        <v>-127.11024916691905</v>
       </c>
       <c r="I50" s="37">
         <f ca="1">'retained earnings schedule'!H11</f>
-        <v>-80.495176692593759</v>
+        <v>-123.24297131805507</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
@@ -17986,23 +18064,23 @@
       </c>
       <c r="E51" s="6">
         <f ca="1">'non-controlling interests '!D6</f>
-        <v>-27.157154149002583</v>
+        <v>-36.854929732136796</v>
       </c>
       <c r="F51" s="6">
         <f ca="1">'non-controlling interests '!E6</f>
-        <v>-24.663743040783814</v>
+        <v>-34.565097882342627</v>
       </c>
       <c r="G51" s="6">
         <f ca="1">'non-controlling interests '!F6</f>
-        <v>-22.598740967764119</v>
+        <v>-32.698122906154119</v>
       </c>
       <c r="H51" s="6">
         <f ca="1">'non-controlling interests '!G6</f>
-        <v>-20.972928153390729</v>
+        <v>-31.274297730548525</v>
       </c>
       <c r="I51" s="6">
         <f ca="1">'non-controlling interests '!H6</f>
-        <v>-19.805091550496766</v>
+        <v>-30.322789888774864</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
@@ -18076,23 +18154,23 @@
       </c>
       <c r="E54" s="44">
         <f t="shared" ref="E54:I54" ca="1" si="4">SUM(E45:E53)</f>
-        <v>-197.42161330684496</v>
+        <v>-246.53471585775225</v>
       </c>
       <c r="F54" s="44">
         <f t="shared" ca="1" si="4"/>
-        <v>-184.79406233809564</v>
+        <v>-234.93816513339235</v>
       </c>
       <c r="G54" s="44">
         <f t="shared" ca="1" si="4"/>
-        <v>-174.33613229933152</v>
+        <v>-225.48311715053418</v>
       </c>
       <c r="H54" s="44">
         <f t="shared" ca="1" si="4"/>
-        <v>-166.10241820722905</v>
+        <v>-218.27234275545575</v>
       </c>
       <c r="I54" s="44">
         <f t="shared" ca="1" si="4"/>
-        <v>-160.18806410107871</v>
+        <v>-213.45355706481811</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
@@ -18111,19 +18189,19 @@
       </c>
       <c r="F55" s="44">
         <f ca="1">'balance sheet'!I6</f>
-        <v>730.48699616341082</v>
+        <v>741.99056444133555</v>
       </c>
       <c r="G55" s="44">
         <f ca="1">'balance sheet'!J6</f>
-        <v>612.3794374009999</v>
+        <v>635.62806107718745</v>
       </c>
       <c r="H55" s="44">
         <f ca="1">'balance sheet'!K6</f>
-        <v>510.33478955329838</v>
+        <v>545.5633697357141</v>
       </c>
       <c r="I55" s="44">
         <f ca="1">'balance sheet'!L6</f>
-        <v>421.43033785140921</v>
+        <v>468.87847367017764</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
@@ -18140,23 +18218,23 @@
       </c>
       <c r="E56" s="45">
         <f t="shared" ca="1" si="5"/>
-        <v>730.48699616341082</v>
+        <v>741.99056444133555</v>
       </c>
       <c r="F56" s="45">
         <f t="shared" ca="1" si="5"/>
-        <v>612.3794374009999</v>
+        <v>635.62806107718745</v>
       </c>
       <c r="G56" s="45">
         <f t="shared" ca="1" si="5"/>
-        <v>510.33478955329838</v>
+        <v>545.5633697357141</v>
       </c>
       <c r="H56" s="45">
         <f t="shared" ca="1" si="5"/>
-        <v>421.43033785140921</v>
+        <v>468.87847367017764</v>
       </c>
       <c r="I56" s="45">
         <f t="shared" ca="1" si="5"/>
-        <v>342.73693093810164</v>
+        <v>402.66123306158613</v>
       </c>
     </row>
   </sheetData>
@@ -18248,23 +18326,23 @@
       </c>
       <c r="I6" s="37">
         <f ca="1">'cash Flow'!E56</f>
-        <v>730.48699616341082</v>
+        <v>741.99056444133555</v>
       </c>
       <c r="J6" s="37">
         <f ca="1">'cash Flow'!F56</f>
-        <v>612.3794374009999</v>
+        <v>635.62806107718745</v>
       </c>
       <c r="K6" s="37">
         <f ca="1">'cash Flow'!G56</f>
-        <v>510.33478955329838</v>
+        <v>545.5633697357141</v>
       </c>
       <c r="L6" s="37">
         <f ca="1">'cash Flow'!H56</f>
-        <v>421.43033785140921</v>
+        <v>468.87847367017764</v>
       </c>
       <c r="M6" s="37">
         <f ca="1">'cash Flow'!I56</f>
-        <v>342.73693093810164</v>
+        <v>402.66123306158613</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -18397,23 +18475,23 @@
       </c>
       <c r="I11" s="13">
         <f ca="1">SUM(I6:I10)</f>
-        <v>1783.3348196718912</v>
+        <v>1794.838387949816</v>
       </c>
       <c r="J11" s="13">
         <f ca="1">SUM(J6:J10)</f>
-        <v>1687.3290281968721</v>
+        <v>1710.5776518730597</v>
       </c>
       <c r="K11" s="13">
         <f t="shared" ref="K11:M11" ca="1" si="1">SUM(K6:K10)</f>
-        <v>1606.7833721650882</v>
+        <v>1642.0119523475041</v>
       </c>
       <c r="L11" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>1539.8078921154347</v>
+        <v>1587.2560279342031</v>
       </c>
       <c r="M11" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>1484.6004138416715</v>
+        <v>1544.524715965156</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
@@ -18685,23 +18763,23 @@
       </c>
       <c r="I23" s="58">
         <f ca="1">SUM(I21,I11)</f>
-        <v>6204.3313522158114</v>
+        <v>6215.8349204937367</v>
       </c>
       <c r="J23" s="58">
         <f t="shared" ref="J23:M23" ca="1" si="3">SUM(J21,J11)</f>
-        <v>6253.3368734571131</v>
+        <v>6276.585497133301</v>
       </c>
       <c r="K23" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>6299.3269872029632</v>
+        <v>6334.5555673853787</v>
       </c>
       <c r="L23" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>6343.7922172030303</v>
+        <v>6391.2403530217989</v>
       </c>
       <c r="M23" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>6388.3338282275381</v>
+        <v>6448.2581303510224</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
@@ -19423,23 +19501,23 @@
       </c>
       <c r="I54" s="1">
         <f ca="1">'retained earnings schedule'!D12</f>
-        <v>2095.5001780913021</v>
+        <v>2107.4273273717085</v>
       </c>
       <c r="J54" s="1">
         <f ca="1">'retained earnings schedule'!E12</f>
-        <v>2125.8337471184732</v>
+        <v>2149.9384247672338</v>
       </c>
       <c r="K54" s="1">
         <f ca="1">'retained earnings schedule'!F12</f>
-        <v>2153.6276009523904</v>
+        <v>2190.1533575368712</v>
       </c>
       <c r="L54" s="1">
         <f ca="1">'retained earnings schedule'!G12</f>
-        <v>2179.4218918996644</v>
+        <v>2228.6171489985804</v>
       </c>
       <c r="M54" s="1">
         <f ca="1">'retained earnings schedule'!H12</f>
-        <v>2203.7798780594708</v>
+        <v>2265.9106951836256</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.25">
@@ -19469,23 +19547,23 @@
       </c>
       <c r="I56" s="37">
         <f ca="1">'non-controlling interests '!D9</f>
-        <v>384.01382545096317</v>
+        <v>383.59024444848143</v>
       </c>
       <c r="J56" s="37">
         <f ca="1">'non-controlling interests '!E9</f>
-        <v>382.93655851354964</v>
+        <v>382.08050454097679</v>
       </c>
       <c r="K56" s="37">
         <f ca="1">'non-controlling interests '!F9</f>
-        <v>381.94948706898066</v>
+        <v>380.65231066691484</v>
       </c>
       <c r="L56" s="37">
         <f ca="1">'non-controlling interests '!G9</f>
-        <v>381.03342813814288</v>
+        <v>379.2863068579943</v>
       </c>
       <c r="M56" s="37">
         <f ca="1">'non-controlling interests '!H9</f>
-        <v>380.1683781623741</v>
+        <v>377.96186316170298</v>
       </c>
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.25">
@@ -19506,23 +19584,23 @@
       </c>
       <c r="I57" s="64">
         <f t="shared" ref="I57:M57" ca="1" si="7">SUM(I50:I56)</f>
-        <v>3012.9140035422652</v>
+        <v>3024.41757182019</v>
       </c>
       <c r="J57" s="64">
         <f t="shared" ca="1" si="7"/>
-        <v>3042.170305632023</v>
+        <v>3065.4189293082109</v>
       </c>
       <c r="K57" s="64">
         <f t="shared" ca="1" si="7"/>
-        <v>3068.9770880213709</v>
+        <v>3104.205668203786</v>
       </c>
       <c r="L57" s="64">
         <f t="shared" ca="1" si="7"/>
-        <v>3093.8553200378074</v>
+        <v>3141.3034558565751</v>
       </c>
       <c r="M57" s="64">
         <f t="shared" ca="1" si="7"/>
-        <v>3117.3482562218451</v>
+        <v>3177.2725583453289</v>
       </c>
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.25">
@@ -19543,23 +19621,23 @@
       </c>
       <c r="I59" s="58">
         <f t="shared" ref="I59:M59" ca="1" si="8">SUM(I57,I48)</f>
-        <v>6204.3313522158114</v>
+        <v>6215.8349204937367</v>
       </c>
       <c r="J59" s="58">
         <f t="shared" ca="1" si="8"/>
-        <v>6253.3368734571131</v>
+        <v>6276.585497133301</v>
       </c>
       <c r="K59" s="58">
         <f t="shared" ca="1" si="8"/>
-        <v>6299.3269872029632</v>
+        <v>6334.5555673853778</v>
       </c>
       <c r="L59" s="58">
         <f t="shared" ca="1" si="8"/>
-        <v>6343.7922172030312</v>
+        <v>6391.2403530217989</v>
       </c>
       <c r="M59" s="58">
         <f t="shared" ca="1" si="8"/>
-        <v>6388.3338282275381</v>
+        <v>6448.2581303510215</v>
       </c>
     </row>
   </sheetData>
@@ -19584,13 +19662,13 @@
         <v>132</v>
       </c>
       <c r="D1" s="49"/>
-      <c r="E1" s="116" t="s">
+      <c r="E1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="41" t="s">
@@ -19864,31 +19942,31 @@
       <c r="B14" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="117">
+      <c r="C14" s="113">
         <f>'Profit &amp; loss'!C32</f>
         <v>-368.4</v>
       </c>
-      <c r="D14" s="117">
+      <c r="D14" s="113">
         <f>'Profit &amp; loss'!D32</f>
         <v>-399.6</v>
       </c>
-      <c r="E14" s="117">
+      <c r="E14" s="113">
         <f>E12+E5</f>
         <v>-437.32044448529803</v>
       </c>
-      <c r="F14" s="117">
+      <c r="F14" s="113">
         <f t="shared" ref="F14:I14" ca="1" si="5">F12+F5</f>
         <v>-471.88960848717466</v>
       </c>
-      <c r="G14" s="117">
+      <c r="G14" s="113">
         <f t="shared" ca="1" si="5"/>
         <v>-502.70316984993144</v>
       </c>
-      <c r="H14" s="117">
+      <c r="H14" s="113">
         <f t="shared" ca="1" si="5"/>
         <v>-530.38300837039526</v>
       </c>
-      <c r="I14" s="117">
+      <c r="I14" s="113">
         <f t="shared" ca="1" si="5"/>
         <v>-555.55292720866862</v>
       </c>
@@ -19918,13 +19996,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -19974,19 +20052,19 @@
       </c>
       <c r="E3" s="43">
         <f ca="1">D12</f>
-        <v>2095.5001780913021</v>
+        <v>2107.4273273717085</v>
       </c>
       <c r="F3" s="43">
         <f t="shared" ref="F3:H3" ca="1" si="1">E12</f>
-        <v>2125.8337471184732</v>
+        <v>2149.9384247672338</v>
       </c>
       <c r="G3" s="43">
         <f t="shared" ca="1" si="1"/>
-        <v>2153.6276009523904</v>
+        <v>2190.1533575368712</v>
       </c>
       <c r="H3" s="43">
         <f t="shared" ca="1" si="1"/>
-        <v>2179.4218918996644</v>
+        <v>2228.6171489985804</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -20003,23 +20081,23 @@
       </c>
       <c r="D4" s="6">
         <f ca="1">'Profit &amp; loss'!E41</f>
-        <v>169.74782099112196</v>
+        <v>230.364491819954</v>
       </c>
       <c r="E4" s="6">
         <f ca="1">'Profit &amp; loss'!F41</f>
-        <v>154.16256856986487</v>
+        <v>216.05172676342448</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'Profit &amp; loss'!G41</f>
-        <v>141.25511883069117</v>
+        <v>204.38206018812204</v>
       </c>
       <c r="G4" s="6">
         <f ca="1">'Profit &amp; loss'!H41</f>
-        <v>131.09285436567683</v>
+        <v>195.48233455025627</v>
       </c>
       <c r="H4" s="6">
         <f ca="1">'Profit &amp; loss'!I41</f>
-        <v>123.79320442712812</v>
+        <v>189.53486369558365</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -20034,23 +20112,23 @@
       </c>
       <c r="D5" s="6">
         <f ca="1">(C5/C4)*D4</f>
-        <v>-25.970979599965688</v>
+        <v>-35.245174180618179</v>
       </c>
       <c r="E5" s="6">
         <f ca="1">(D5/D4)*E4</f>
-        <v>-23.58647610337027</v>
+        <v>-33.05535797483801</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" ref="F5:H5" ca="1" si="2">(E5/E4)*F4</f>
-        <v>-21.611669523195111</v>
+        <v>-31.269929032092218</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-20.056869222552976</v>
+        <v>-29.908293921628015</v>
       </c>
       <c r="H5" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.940041574727942</v>
+        <v>-28.998346192483549</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -20067,23 +20145,23 @@
       </c>
       <c r="D6" s="6">
         <f t="shared" ref="D6:H6" ca="1" si="3">SUM(D4:D5)</f>
-        <v>143.77684139115627</v>
+        <v>195.1193176393358</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" ca="1" si="3"/>
-        <v>130.5760924664946</v>
+        <v>182.99636878858647</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" ca="1" si="3"/>
-        <v>119.64344930749607</v>
+        <v>173.11213115602982</v>
       </c>
       <c r="G6" s="6">
         <f t="shared" ca="1" si="3"/>
-        <v>111.03598514312385</v>
+        <v>165.57404062862827</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" ca="1" si="3"/>
-        <v>104.85316285240017</v>
+        <v>160.5365175031001</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -20202,23 +20280,23 @@
       </c>
       <c r="D11" s="56">
         <f ca="1">(C11/C4)*D4</f>
-        <v>-110.37666329985419</v>
+        <v>-149.79199026762726</v>
       </c>
       <c r="E11" s="56">
         <f ca="1">(D11/D4)*E4</f>
-        <v>-100.24252343932365</v>
+        <v>-140.48527139306154</v>
       </c>
       <c r="F11" s="56">
         <f t="shared" ref="F11:H11" ca="1" si="4">(E11/E4)*F4</f>
-        <v>-91.849595473579228</v>
+        <v>-132.89719838639189</v>
       </c>
       <c r="G11" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-85.241694195850144</v>
+        <v>-127.11024916691905</v>
       </c>
       <c r="H11" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-80.495176692593759</v>
+        <v>-123.24297131805507</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -20235,23 +20313,23 @@
       </c>
       <c r="D12" s="51">
         <f ca="1">SUM(D3,D6:D11)</f>
-        <v>2095.5001780913021</v>
+        <v>2107.4273273717085</v>
       </c>
       <c r="E12" s="51">
         <f ca="1">SUM(E3,E6:E11)</f>
-        <v>2125.8337471184732</v>
+        <v>2149.9384247672338</v>
       </c>
       <c r="F12" s="51">
         <f t="shared" ref="F12:H12" ca="1" si="5">SUM(F3,F6:F11)</f>
-        <v>2153.6276009523904</v>
+        <v>2190.1533575368712</v>
       </c>
       <c r="G12" s="51">
         <f t="shared" ca="1" si="5"/>
-        <v>2179.4218918996644</v>
+        <v>2228.6171489985804</v>
       </c>
       <c r="H12" s="51">
         <f t="shared" ca="1" si="5"/>
-        <v>2203.7798780594708</v>
+        <v>2265.9106951836256</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">

--- a/ComfortDelGro-Equity-Valuation.xlsx
+++ b/ComfortDelGro-Equity-Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChengJing\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC634B8-E728-4FEE-A5B5-C118D80222AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AAE408-D7E9-44D1-8BCD-8A7DEE8E0C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D93AAA56-1308-4026-9D8F-E913B55E5CC3}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <sheet name="Income Statement - Data" sheetId="2" r:id="rId13"/>
     <sheet name="Balance Sheet - Data" sheetId="3" r:id="rId14"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId15"/>
-  </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1183,9 +1180,6 @@
     <t>EV</t>
   </si>
   <si>
-    <t>Enterprise Value to Equity Value</t>
-  </si>
-  <si>
     <t>+ Cash &amp; Cash Equivalents</t>
   </si>
   <si>
@@ -2186,13 +2180,16 @@
   </si>
   <si>
     <t>Diluted shares oustanding</t>
+  </si>
+  <si>
+    <t>Discounted Cash Flow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="16">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
@@ -2209,7 +2206,6 @@
     <numFmt numFmtId="175" formatCode="#,###.00\x"/>
     <numFmt numFmtId="176" formatCode="#.##\x"/>
     <numFmt numFmtId="177" formatCode="#.###\x"/>
-    <numFmt numFmtId="178" formatCode="General\ \x"/>
   </numFmts>
   <fonts count="32" x14ac:knownFonts="1">
     <font>
@@ -2875,7 +2871,7 @@
     <xf numFmtId="169" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2977,7 +2973,6 @@
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="173" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="174" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2993,9 +2988,7 @@
     <xf numFmtId="43" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="168" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="23" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3030,6 +3023,8 @@
     <xf numFmtId="0" fontId="19" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="20% - Accent1 2" xfId="21" xr:uid="{7F1DC058-3DA4-4945-98D8-2DC0ECB9F210}"/>
@@ -3097,46 +3092,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="UFCF"/>
-      <sheetName val="WACC"/>
-      <sheetName val="Comparable Companies"/>
-      <sheetName val="Shares Outstanding"/>
-      <sheetName val="Income Statement"/>
-      <sheetName val="Cash Flow Statement"/>
-      <sheetName val="Balance Sheet"/>
-      <sheetName val="Revolver"/>
-      <sheetName val="Retained Earnings"/>
-      <sheetName val="Fixed Assets"/>
-      <sheetName val="Data Source --&gt;"/>
-      <sheetName val="Income Statement - Data"/>
-      <sheetName val="Balance Sheet - Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3450,9 +3405,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="65" t="str">
-        <f>"Discounted Cash Flow "&amp;'[1]Income Statement'!C3</f>
-        <v xml:space="preserve">Discounted Cash Flow </v>
+      <c r="B1" s="65" t="s">
+        <v>570</v>
       </c>
       <c r="C1" s="66"/>
       <c r="D1" s="66"/>
@@ -4365,15 +4319,15 @@
         <f t="shared" ca="1" si="9"/>
         <v>-64.316977029218151</v>
       </c>
-      <c r="G34" s="111">
+      <c r="G34" s="108">
         <f t="shared" ca="1" si="9"/>
         <v>-63.001316569801929</v>
       </c>
-      <c r="H34" s="111">
+      <c r="H34" s="108">
         <f t="shared" ca="1" si="9"/>
         <v>-61.659342901198443</v>
       </c>
-      <c r="I34" s="111">
+      <c r="I34" s="108">
         <f t="shared" ca="1" si="9"/>
         <v>-60.222089102123618</v>
       </c>
@@ -4398,15 +4352,15 @@
         <f ca="1">'balance sheet'!J11-'balance sheet'!J6</f>
         <v>1074.9495907958722</v>
       </c>
-      <c r="G35" s="111">
+      <c r="G35" s="108">
         <f ca="1">'balance sheet'!K11-'balance sheet'!K6</f>
         <v>1096.44858261179</v>
       </c>
-      <c r="H35" s="111">
+      <c r="H35" s="108">
         <f ca="1">'balance sheet'!L11-'balance sheet'!L6</f>
         <v>1118.3775542640255</v>
       </c>
-      <c r="I35" s="111">
+      <c r="I35" s="108">
         <f ca="1">'balance sheet'!M11-'balance sheet'!M6</f>
         <v>1141.86348290357</v>
       </c>
@@ -4431,15 +4385,15 @@
         <f ca="1">'balance sheet'!J35-'balance sheet'!J27-'balance sheet'!J28-'balance sheet'!J29</f>
         <v>1139.2665678250903</v>
       </c>
-      <c r="G36" s="111">
+      <c r="G36" s="108">
         <f ca="1">'balance sheet'!K35-'balance sheet'!K27-'balance sheet'!K28-'balance sheet'!K29</f>
         <v>1159.4498991815919</v>
       </c>
-      <c r="H36" s="111">
+      <c r="H36" s="108">
         <f ca="1">'balance sheet'!L35-'balance sheet'!L27-'balance sheet'!L28-'balance sheet'!L29</f>
         <v>1180.036897165224</v>
       </c>
-      <c r="I36" s="111">
+      <c r="I36" s="108">
         <f ca="1">'balance sheet'!M35-'balance sheet'!M27-'balance sheet'!M28-'balance sheet'!M29</f>
         <v>1202.0855720056936</v>
       </c>
@@ -4616,23 +4570,23 @@
       </c>
       <c r="C46" s="77"/>
       <c r="D46" s="77"/>
-      <c r="E46" s="85">
+      <c r="E46" s="84">
         <f ca="1">E37/(1+WACC!D18)^1</f>
         <v>96.032478740151547</v>
       </c>
-      <c r="F46" s="85">
+      <c r="F46" s="84">
         <f ca="1">F44/(1+WACC!$D$18)^'Unlevered cash flow'!F45</f>
         <v>99.571088288608905</v>
       </c>
-      <c r="G46" s="85">
+      <c r="G46" s="84">
         <f ca="1">G44/(1+WACC!$D$18)^'Unlevered cash flow'!G45</f>
         <v>101.25323413388995</v>
       </c>
-      <c r="H46" s="85">
+      <c r="H46" s="84">
         <f ca="1">H44/(1+WACC!$D$18)^'Unlevered cash flow'!H45</f>
         <v>102.05770032786643</v>
       </c>
-      <c r="I46" s="85">
+      <c r="I46" s="84">
         <f ca="1">I44/(1+WACC!$D$18)^'Unlevered cash flow'!I45</f>
         <v>102.18595586850981</v>
       </c>
@@ -4685,7 +4639,7 @@
       <c r="F54" t="s">
         <v>221</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="103">
         <v>0.02</v>
       </c>
     </row>
@@ -4693,7 +4647,7 @@
       <c r="B55" t="s">
         <v>222</v>
       </c>
-      <c r="C55" s="86">
+      <c r="C55" s="85">
         <f>'COMPARABLE COMPANIES'!B6</f>
         <v>2.8482165008562825</v>
       </c>
@@ -4757,7 +4711,7 @@
       <c r="B59" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="C59" s="87">
+      <c r="C59" s="86">
         <f ca="1">C58+C53</f>
         <v>2443.1107667638016</v>
       </c>
@@ -4766,18 +4720,15 @@
       </c>
       <c r="G59" s="30"/>
       <c r="H59" s="30"/>
-      <c r="I59" s="94">
+      <c r="I59" s="93">
         <f ca="1">I58+I53</f>
         <v>5169.7049302040814</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B61" s="42" t="s">
-        <v>236</v>
-      </c>
       <c r="C61" s="78"/>
       <c r="F61" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G61" s="78"/>
     </row>
@@ -4790,66 +4741,66 @@
         <v>5169.7049302040814</v>
       </c>
       <c r="F62" t="s">
-        <v>245</v>
-      </c>
-      <c r="G62" s="101">
+        <v>244</v>
+      </c>
+      <c r="G62" s="98">
         <v>2166763244</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B63" s="95" t="s">
-        <v>237</v>
+      <c r="B63" s="94" t="s">
+        <v>236</v>
       </c>
       <c r="C63" s="1">
         <f>'balance sheet'!H6</f>
         <v>868.4</v>
       </c>
-      <c r="F63" s="95" t="s">
-        <v>248</v>
-      </c>
-      <c r="G63" s="101">
+      <c r="F63" s="94" t="s">
+        <v>247</v>
+      </c>
+      <c r="G63" s="98">
         <v>684669</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B64" s="95" t="s">
-        <v>238</v>
+      <c r="B64" s="94" t="s">
+        <v>237</v>
       </c>
       <c r="C64" s="1">
         <f>SUM('balance sheet'!H27:H29,'balance sheet'!H38:H40)</f>
         <v>1821.5</v>
       </c>
-      <c r="F64" s="95" t="s">
-        <v>246</v>
+      <c r="F64" s="94" t="s">
+        <v>245</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="95" t="s">
-        <v>239</v>
+      <c r="B65" s="94" t="s">
+        <v>238</v>
       </c>
       <c r="C65">
         <f>'balance sheet'!H56</f>
         <v>385.2</v>
       </c>
-      <c r="F65" s="95" t="s">
-        <v>247</v>
+      <c r="F65" s="94" t="s">
+        <v>246</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="95" t="s">
-        <v>240</v>
+      <c r="B66" s="94" t="s">
+        <v>239</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G66" s="51">
         <f>SUM(G62:G65)</f>
@@ -4857,8 +4808,8 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="95" t="s">
-        <v>241</v>
+      <c r="B67" s="94" t="s">
+        <v>240</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -4866,34 +4817,34 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B68" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="C68" s="96">
+        <v>241</v>
+      </c>
+      <c r="C68" s="95">
         <f ca="1">C62+C63-C64-C65</f>
         <v>3831.4049302040812</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>243</v>
-      </c>
-      <c r="C69" s="101">
+        <v>242</v>
+      </c>
+      <c r="C69" s="98">
         <f>G66</f>
         <v>2167447913</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B70" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="C70" s="112">
+        <v>243</v>
+      </c>
+      <c r="C70" s="109">
         <f ca="1">C68*1000000/C69</f>
         <v>1.7677033469750012</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B75" s="42" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C75" s="78"/>
       <c r="D75" s="42"/>
@@ -4902,45 +4853,45 @@
       <c r="G75" s="78"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="102"/>
+      <c r="A78" s="99"/>
       <c r="D78" s="8" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="103" t="s">
+      <c r="A79" s="100" t="s">
         <v>223</v>
       </c>
-      <c r="B79" s="60">
+      <c r="B79" s="116">
         <f ca="1">C70</f>
         <v>1.7677033469750012</v>
       </c>
-      <c r="C79" s="97">
-        <f>D79-1</f>
-        <v>0.84821650085628253</v>
-      </c>
-      <c r="D79" s="97">
-        <f>E79-1</f>
-        <v>1.8482165008562825</v>
-      </c>
-      <c r="E79" s="99">
-        <f>C55</f>
-        <v>2.8482165008562825</v>
-      </c>
-      <c r="F79" s="97">
-        <f>E79+1</f>
-        <v>3.8482165008562825</v>
-      </c>
-      <c r="G79" s="97">
-        <f>F79+1</f>
-        <v>4.8482165008562825</v>
+      <c r="C79" s="2">
+        <f>D79-0.005</f>
+        <v>9.9999999999999985E-3</v>
+      </c>
+      <c r="D79" s="2">
+        <f>E79-0.005</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E79" s="103">
+        <f>I54</f>
+        <v>0.02</v>
+      </c>
+      <c r="F79" s="2">
+        <f>E79+0.005</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G79" s="2">
+        <f>F79+0.005</f>
+        <v>3.0000000000000002E-2</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="102"/>
-      <c r="B80" s="98">
-        <f>B81+0.01</f>
-        <v>6.2325659753815536E-2</v>
+      <c r="A80" s="99"/>
+      <c r="B80" s="96">
+        <f t="shared" ref="B79:B80" si="17">B81+0.0025</f>
+        <v>4.7325659753815537E-2</v>
       </c>
       <c r="C80">
         <f t="dataTable" ref="C80:G84" dt2D="1" dtr="1" r1="C55" r2="C56" ca="1"/>
@@ -4960,10 +4911,10 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="102"/>
-      <c r="B81" s="98">
-        <f>B82+0.01</f>
-        <v>5.2325659753815534E-2</v>
+      <c r="A81" s="99"/>
+      <c r="B81" s="96">
+        <f>B82+0.0025</f>
+        <v>4.4825659753815535E-2</v>
       </c>
       <c r="C81">
         <v>1.7677033469750012</v>
@@ -4982,7 +4933,7 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="100">
+      <c r="B82" s="97">
         <f>I55</f>
         <v>4.2325659753815532E-2</v>
       </c>
@@ -5003,9 +4954,9 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="98">
-        <f>B82-0.01</f>
-        <v>3.232565975381553E-2</v>
+      <c r="B83" s="96">
+        <f>B82-0.0025</f>
+        <v>3.982565975381553E-2</v>
       </c>
       <c r="C83">
         <v>1.7677033469750012</v>
@@ -5024,9 +4975,9 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="98">
-        <f>B83-0.01</f>
-        <v>2.2325659753815529E-2</v>
+      <c r="B84" s="96">
+        <f>B83-0.0025</f>
+        <v>3.7325659753815528E-2</v>
       </c>
       <c r="C84">
         <v>1.7677033469750012</v>
@@ -5067,13 +5018,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="117" t="s">
+      <c r="D1" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -5331,17 +5282,17 @@
       <c r="A1" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="117" t="s">
+      <c r="B1" s="114" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117" t="s">
+      <c r="C1" s="114"/>
+      <c r="D1" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -6654,6 +6605,7 @@
     <col min="4" max="4" width="30.42578125" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
@@ -6708,7 +6660,7 @@
       <c r="F6" t="s">
         <v>205</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="115">
         <f>'beta calculation'!Q5</f>
         <v>0.59520093089099124</v>
       </c>
@@ -6717,7 +6669,7 @@
       <c r="B7" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C7" s="82"/>
+      <c r="C7" s="81"/>
       <c r="D7" s="2">
         <f>D5*(1-D6)</f>
         <v>2.3215489092327905E-2</v>
@@ -6734,7 +6686,7 @@
       <c r="F8" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="G8" s="82"/>
+      <c r="G8" s="81"/>
       <c r="H8" s="2">
         <f>G5+G6*H7</f>
         <v>5.3176999376688933E-2</v>
@@ -6768,7 +6720,7 @@
         <v>213</v>
       </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="83">
+      <c r="D14" s="82">
         <f>SUM(D12:D13)</f>
         <v>5029322911.2399998</v>
       </c>
@@ -6776,7 +6728,7 @@
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="83"/>
+      <c r="D15" s="82"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
@@ -6803,7 +6755,7 @@
         <v>212</v>
       </c>
       <c r="C18" s="61"/>
-      <c r="D18" s="84">
+      <c r="D18" s="83">
         <f>D16*H8+D17*D7</f>
         <v>4.2325659753815532E-2</v>
       </c>
@@ -6835,7 +6787,7 @@
       <c r="A2" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="88">
+      <c r="B2" s="87">
         <f>F4/F3</f>
         <v>2.8482165008562825</v>
       </c>
@@ -6848,14 +6800,14 @@
       <c r="A3" t="s">
         <v>233</v>
       </c>
-      <c r="B3" s="88">
+      <c r="B3" s="87">
         <f>F8/F7</f>
         <v>2.3947860505477307</v>
       </c>
       <c r="E3" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="93">
+      <c r="F3" s="92">
         <f>464.8*1000000</f>
         <v>464800000</v>
       </c>
@@ -6864,14 +6816,14 @@
       <c r="A4" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="89">
+      <c r="B4" s="88">
         <f>F13/F12</f>
         <v>6.6296784378324967</v>
       </c>
       <c r="E4" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="93">
+      <c r="F4" s="92">
         <f>(614086377*17.4/100)+(1249000000+346300000)-425600000+47300000</f>
         <v>1323851029.598</v>
       </c>
@@ -6880,16 +6832,16 @@
       <c r="A5" s="61" t="s">
         <v>230</v>
       </c>
-      <c r="B5" s="90">
+      <c r="B5" s="89">
         <f>AVERAGE(B2:B4)</f>
         <v>3.9575603297455033</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="90" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="92">
+      <c r="B6" s="91">
         <f>MEDIAN(B2:B4)</f>
         <v>2.8482165008562825</v>
       </c>
@@ -6961,98 +6913,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A1" s="114" t="s">
-        <v>250</v>
-      </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="I1" s="114" t="s">
-        <v>318</v>
-      </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="S1" s="114" t="s">
-        <v>442</v>
-      </c>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="AB1" s="114" t="s">
-        <v>502</v>
-      </c>
-      <c r="AC1" s="114"/>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="114"/>
-      <c r="AG1" s="114"/>
-      <c r="AH1" s="114"/>
-      <c r="AK1" s="114" t="s">
+      <c r="A1" s="111" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="I1" s="111" t="s">
+        <v>317</v>
+      </c>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="S1" s="111" t="s">
+        <v>441</v>
+      </c>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="111"/>
+      <c r="Y1" s="111"/>
+      <c r="AB1" s="111" t="s">
+        <v>501</v>
+      </c>
+      <c r="AC1" s="111"/>
+      <c r="AD1" s="111"/>
+      <c r="AE1" s="111"/>
+      <c r="AF1" s="111"/>
+      <c r="AG1" s="111"/>
+      <c r="AH1" s="111"/>
+      <c r="AK1" s="111" t="s">
         <v>232</v>
       </c>
-      <c r="AL1" s="114"/>
-      <c r="AM1" s="114"/>
-      <c r="AN1" s="114"/>
-      <c r="AO1" s="114"/>
-      <c r="AP1" s="114"/>
-      <c r="AQ1" s="114"/>
+      <c r="AL1" s="111"/>
+      <c r="AM1" s="111"/>
+      <c r="AN1" s="111"/>
+      <c r="AO1" s="111"/>
+      <c r="AP1" s="111"/>
+      <c r="AQ1" s="111"/>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="C2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="D2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="E2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="F2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="31" t="s">
-        <v>256</v>
-      </c>
       <c r="G2" s="31" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="J2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="K2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="L2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="M2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="M2" s="31" t="s">
+      <c r="N2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="N2" s="31" t="s">
-        <v>256</v>
-      </c>
       <c r="O2" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="P2" s="108" t="s">
-        <v>567</v>
+        <v>379</v>
+      </c>
+      <c r="P2" s="105" t="s">
+        <v>566</v>
       </c>
       <c r="Q2">
         <f>SLOPE(O3:O63,G3:G63)</f>
@@ -7060,84 +7012,84 @@
       </c>
       <c r="R2" s="2"/>
       <c r="S2" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="T2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="T2" s="31" t="s">
+      <c r="U2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="V2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="V2" s="31" t="s">
+      <c r="W2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="W2" s="31" t="s">
+      <c r="X2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="X2" s="31" t="s">
+      <c r="Y2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="Y2" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z2" s="107" t="s">
-        <v>381</v>
+      <c r="Z2" s="104" t="s">
+        <v>380</v>
       </c>
       <c r="AA2">
         <f>SLOPE(Y3:Y63,G3:G63)</f>
         <v>0.7517124637493322</v>
       </c>
       <c r="AB2" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="AC2" s="31" t="s">
+      <c r="AD2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="AD2" s="31" t="s">
+      <c r="AE2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="AE2" s="31" t="s">
+      <c r="AF2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AG2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="AG2" s="31" t="s">
+      <c r="AH2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="AH2" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="AI2" s="107" t="s">
-        <v>563</v>
+      <c r="AI2" s="104" t="s">
+        <v>562</v>
       </c>
       <c r="AJ2">
         <f>SLOPE(AH3:AH63,G3:G63)</f>
         <v>0.34260011499870624</v>
       </c>
       <c r="AK2" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="AL2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="AL2" s="31" t="s">
+      <c r="AM2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="AM2" s="31" t="s">
+      <c r="AN2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="AN2" s="31" t="s">
+      <c r="AO2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="AO2" s="31" t="s">
+      <c r="AP2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="AP2" s="31" t="s">
+      <c r="AQ2" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="AQ2" s="31" t="s">
-        <v>257</v>
-      </c>
       <c r="AS2" s="31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AT2">
         <f>SLOPE(AQ3:AQ63,G3:G63)</f>
@@ -7145,29 +7097,29 @@
       </c>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A3" s="105">
+      <c r="A3" s="102">
         <v>46023</v>
       </c>
-      <c r="B3" s="93">
+      <c r="B3" s="92">
         <v>4905.13</v>
       </c>
-      <c r="C3" s="93">
+      <c r="C3" s="92">
         <v>4652.34</v>
       </c>
-      <c r="D3" s="93">
+      <c r="D3" s="92">
         <v>4933.88</v>
       </c>
-      <c r="E3" s="93">
+      <c r="E3" s="92">
         <v>4648.38</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="G3" s="106">
+        <v>257</v>
+      </c>
+      <c r="G3" s="103">
         <v>5.57E-2</v>
       </c>
       <c r="H3" s="31"/>
-      <c r="I3" s="105">
+      <c r="I3" s="102">
         <v>46023</v>
       </c>
       <c r="J3" s="31">
@@ -7183,12 +7135,12 @@
         <v>1.45</v>
       </c>
       <c r="N3" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="O3" s="106">
+        <v>318</v>
+      </c>
+      <c r="O3" s="103">
         <v>-6.7999999999999996E-3</v>
       </c>
-      <c r="S3" s="105">
+      <c r="S3" s="102">
         <v>46023</v>
       </c>
       <c r="T3" s="31">
@@ -7204,19 +7156,19 @@
         <v>3.86</v>
       </c>
       <c r="X3" s="31" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y3" s="31">
         <v>-8.2400000000000001E-2</v>
       </c>
       <c r="Z3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AA3">
         <f>AA2/(1+(1-0.2049)*(9838+42313+801903+68873+132694)/(952614))</f>
         <v>0.39961857731694406</v>
       </c>
-      <c r="AB3" s="105">
+      <c r="AB3" s="102">
         <v>46023</v>
       </c>
       <c r="AC3" s="31">
@@ -7232,19 +7184,19 @@
         <v>180</v>
       </c>
       <c r="AG3" s="31" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AH3" s="31">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="AI3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AJ3">
         <f>AJ2/(1+(1-0.238)*(447.1+710.2)/(719.5))</f>
         <v>0.15393189696173068</v>
       </c>
-      <c r="AK3" s="105">
+      <c r="AK3" s="102">
         <v>46023</v>
       </c>
       <c r="AL3" s="31">
@@ -7260,43 +7212,43 @@
         <v>20.8</v>
       </c>
       <c r="AP3" s="31" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AQ3" s="31">
         <v>8.6999999999999994E-3</v>
       </c>
       <c r="AS3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AT3">
-        <f>AT2/(1-(1-0.47759)*(1249+346.3)/(-352.3))</f>
-        <v>0.56648431580189518</v>
+        <f>AT2/(1+(1-0.47759)*(1249+346.3)/(18.57*667949082))</f>
+        <v>1.9065591523152106</v>
       </c>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A4" s="105">
+      <c r="A4" s="102">
         <v>45669</v>
       </c>
-      <c r="B4" s="93">
+      <c r="B4" s="92">
         <v>4646.21</v>
       </c>
-      <c r="C4" s="93">
+      <c r="C4" s="92">
         <v>4531.55</v>
       </c>
-      <c r="D4" s="93">
+      <c r="D4" s="92">
         <v>4665.12</v>
       </c>
-      <c r="E4" s="93">
+      <c r="E4" s="92">
         <v>4492.46</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="G4" s="106">
+        <v>258</v>
+      </c>
+      <c r="G4" s="103">
         <v>2.7E-2</v>
       </c>
       <c r="H4" s="31"/>
-      <c r="I4" s="105">
+      <c r="I4" s="102">
         <v>45669</v>
       </c>
       <c r="J4" s="31">
@@ -7312,19 +7264,19 @@
         <v>1.42</v>
       </c>
       <c r="N4" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="O4" s="106">
+        <v>319</v>
+      </c>
+      <c r="O4" s="103">
         <v>2.7799999999999998E-2</v>
       </c>
       <c r="P4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Q4">
         <f>MEDIAN(AA3,AJ3,AT3)</f>
         <v>0.39961857731694406</v>
       </c>
-      <c r="S4" s="105">
+      <c r="S4" s="102">
         <v>45669</v>
       </c>
       <c r="T4" s="31">
@@ -7340,12 +7292,12 @@
         <v>4.16</v>
       </c>
       <c r="X4" s="31" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Y4" s="31">
         <v>-8.0100000000000005E-2</v>
       </c>
-      <c r="AB4" s="105">
+      <c r="AB4" s="102">
         <v>45669</v>
       </c>
       <c r="AC4" s="31">
@@ -7361,12 +7313,12 @@
         <v>173.5</v>
       </c>
       <c r="AG4" s="31" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AH4" s="31">
         <v>7.8700000000000006E-2</v>
       </c>
-      <c r="AK4" s="105">
+      <c r="AK4" s="102">
         <v>45669</v>
       </c>
       <c r="AL4" s="31">
@@ -7382,36 +7334,36 @@
         <v>21</v>
       </c>
       <c r="AP4" s="31" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AQ4" s="31">
         <v>5.0099999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A5" s="105">
+      <c r="A5" s="102">
         <v>45668</v>
       </c>
-      <c r="B5" s="93">
+      <c r="B5" s="92">
         <v>4523.96</v>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="92">
         <v>4437.38</v>
       </c>
-      <c r="D5" s="93">
+      <c r="D5" s="92">
         <v>4575.91</v>
       </c>
-      <c r="E5" s="93">
+      <c r="E5" s="92">
         <v>4372.6400000000003</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="G5" s="106">
+        <v>259</v>
+      </c>
+      <c r="G5" s="103">
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="H5" s="31"/>
-      <c r="I5" s="105">
+      <c r="I5" s="102">
         <v>45668</v>
       </c>
       <c r="J5" s="31">
@@ -7427,19 +7379,19 @@
         <v>1.44</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="O5" s="106">
+        <v>320</v>
+      </c>
+      <c r="O5" s="103">
         <v>-1.37E-2</v>
       </c>
-      <c r="P5" s="91" t="s">
-        <v>566</v>
-      </c>
-      <c r="Q5" s="109">
+      <c r="P5" s="90" t="s">
+        <v>565</v>
+      </c>
+      <c r="Q5" s="106">
         <f>Q4*(1+(1-'Profit &amp; loss'!E105)*('debt schedule'!C5+'debt schedule'!C11)/('balance sheet'!H57))</f>
         <v>0.59520093089099124</v>
       </c>
-      <c r="S5" s="105">
+      <c r="S5" s="102">
         <v>45668</v>
       </c>
       <c r="T5" s="31">
@@ -7455,12 +7407,12 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="X5" s="31" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y5" s="31">
         <v>-5.1299999999999998E-2</v>
       </c>
-      <c r="AB5" s="105">
+      <c r="AB5" s="102">
         <v>45668</v>
       </c>
       <c r="AC5" s="31">
@@ -7476,12 +7428,12 @@
         <v>171.3</v>
       </c>
       <c r="AG5" s="31" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AH5" s="31">
         <v>-0.15859999999999999</v>
       </c>
-      <c r="AK5" s="105">
+      <c r="AK5" s="102">
         <v>45668</v>
       </c>
       <c r="AL5" s="31">
@@ -7497,36 +7449,36 @@
         <v>19</v>
       </c>
       <c r="AP5" s="31" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AQ5" s="31">
         <v>-0.16370000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A6" s="105">
+      <c r="A6" s="102">
         <v>45667</v>
       </c>
-      <c r="B6" s="93">
+      <c r="B6" s="92">
         <v>4428.62</v>
       </c>
-      <c r="C6" s="93">
+      <c r="C6" s="92">
         <v>4307.76</v>
       </c>
-      <c r="D6" s="93">
+      <c r="D6" s="92">
         <v>4478.1499999999996</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="92">
         <v>4307.76</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="G6" s="106">
+        <v>260</v>
+      </c>
+      <c r="G6" s="103">
         <v>2.9899999999999999E-2</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="105">
+      <c r="I6" s="102">
         <v>45667</v>
       </c>
       <c r="J6" s="31">
@@ -7542,12 +7494,12 @@
         <v>1.44</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="O6" s="106">
+        <v>321</v>
+      </c>
+      <c r="O6" s="103">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="S6" s="105">
+      <c r="S6" s="102">
         <v>45667</v>
       </c>
       <c r="T6" s="31">
@@ -7563,12 +7515,12 @@
         <v>4.71</v>
       </c>
       <c r="X6" s="31" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y6" s="31">
         <v>-8.0999999999999996E-3</v>
       </c>
-      <c r="AB6" s="105">
+      <c r="AB6" s="102">
         <v>45667</v>
       </c>
       <c r="AC6" s="31">
@@ -7584,12 +7536,12 @@
         <v>198.8</v>
       </c>
       <c r="AG6" s="31" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AH6" s="31">
         <v>-6.9099999999999995E-2</v>
       </c>
-      <c r="AK6" s="105">
+      <c r="AK6" s="102">
         <v>45667</v>
       </c>
       <c r="AL6" s="31">
@@ -7605,36 +7557,36 @@
         <v>25.24</v>
       </c>
       <c r="AP6" s="31" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AQ6" s="31">
         <v>-8.6300000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A7" s="105">
+      <c r="A7" s="102">
         <v>45666</v>
       </c>
-      <c r="B7" s="93">
+      <c r="B7" s="92">
         <v>4300.16</v>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="92">
         <v>4270.8599999999997</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="92">
         <v>4375.33</v>
       </c>
-      <c r="E7" s="93">
+      <c r="E7" s="92">
         <v>4252.2700000000004</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="G7" s="106">
+        <v>261</v>
+      </c>
+      <c r="G7" s="103">
         <v>7.1000000000000004E-3</v>
       </c>
       <c r="H7" s="31"/>
-      <c r="I7" s="105">
+      <c r="I7" s="102">
         <v>45666</v>
       </c>
       <c r="J7" s="31">
@@ -7650,12 +7602,12 @@
         <v>1.44</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>323</v>
-      </c>
-      <c r="O7" s="106">
-        <v>0</v>
-      </c>
-      <c r="S7" s="105">
+        <v>322</v>
+      </c>
+      <c r="O7" s="103">
+        <v>0</v>
+      </c>
+      <c r="S7" s="102">
         <v>45666</v>
       </c>
       <c r="T7" s="31">
@@ -7671,12 +7623,12 @@
         <v>4.75</v>
       </c>
       <c r="X7" s="31" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Y7" s="31">
         <v>-1.41E-2</v>
       </c>
-      <c r="AB7" s="105">
+      <c r="AB7" s="102">
         <v>45666</v>
       </c>
       <c r="AC7" s="31">
@@ -7692,12 +7644,12 @@
         <v>210.2</v>
       </c>
       <c r="AG7" s="31" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AH7" s="31">
         <v>1.8100000000000002E-2</v>
       </c>
-      <c r="AK7" s="105">
+      <c r="AK7" s="102">
         <v>45666</v>
       </c>
       <c r="AL7" s="31">
@@ -7713,36 +7665,36 @@
         <v>24.36</v>
       </c>
       <c r="AP7" s="31" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AQ7" s="31">
         <v>-0.12429999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A8" s="105">
+      <c r="A8" s="102">
         <v>45665</v>
       </c>
-      <c r="B8" s="93">
+      <c r="B8" s="92">
         <v>4269.7</v>
       </c>
-      <c r="C8" s="93">
+      <c r="C8" s="92">
         <v>4169.28</v>
       </c>
-      <c r="D8" s="93">
+      <c r="D8" s="92">
         <v>4282.8</v>
       </c>
-      <c r="E8" s="93">
+      <c r="E8" s="92">
         <v>4144.8900000000003</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="G8" s="106">
+        <v>262</v>
+      </c>
+      <c r="G8" s="103">
         <v>2.3E-2</v>
       </c>
       <c r="H8" s="31"/>
-      <c r="I8" s="105">
+      <c r="I8" s="102">
         <v>45665</v>
       </c>
       <c r="J8" s="31">
@@ -7758,12 +7710,12 @@
         <v>1.42</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="O8" s="106">
+        <v>323</v>
+      </c>
+      <c r="O8" s="103">
         <v>-5.2299999999999999E-2</v>
       </c>
-      <c r="S8" s="105">
+      <c r="S8" s="102">
         <v>45665</v>
       </c>
       <c r="T8" s="31">
@@ -7779,12 +7731,12 @@
         <v>3.63</v>
       </c>
       <c r="X8" s="31" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y8" s="31">
         <v>0.33160000000000001</v>
       </c>
-      <c r="AB8" s="105">
+      <c r="AB8" s="102">
         <v>45665</v>
       </c>
       <c r="AC8" s="31">
@@ -7800,12 +7752,12 @@
         <v>215.2</v>
       </c>
       <c r="AG8" s="31" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AH8" s="31">
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="AK8" s="105">
+      <c r="AK8" s="102">
         <v>45665</v>
       </c>
       <c r="AL8" s="31">
@@ -7821,36 +7773,36 @@
         <v>32.64</v>
       </c>
       <c r="AP8" s="31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AQ8" s="31">
         <v>-9.64E-2</v>
       </c>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A9" s="105">
+      <c r="A9" s="102">
         <v>45664</v>
       </c>
-      <c r="B9" s="93">
+      <c r="B9" s="92">
         <v>4173.7700000000004</v>
       </c>
-      <c r="C9" s="93">
+      <c r="C9" s="92">
         <v>3972.18</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="92">
         <v>4274.32</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="92">
         <v>3968.57</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="G9" s="106">
+        <v>263</v>
+      </c>
+      <c r="G9" s="103">
         <v>5.28E-2</v>
       </c>
       <c r="H9" s="31"/>
-      <c r="I9" s="105">
+      <c r="I9" s="102">
         <v>45664</v>
       </c>
       <c r="J9" s="31">
@@ -7866,12 +7818,12 @@
         <v>1.4</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="O9" s="106">
+        <v>324</v>
+      </c>
+      <c r="O9" s="103">
         <v>6.9900000000000004E-2</v>
       </c>
-      <c r="S9" s="105">
+      <c r="S9" s="102">
         <v>45664</v>
       </c>
       <c r="T9" s="31">
@@ -7887,12 +7839,12 @@
         <v>3.68</v>
       </c>
       <c r="X9" s="31" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y9" s="31">
         <v>-1.32E-2</v>
       </c>
-      <c r="AB9" s="105">
+      <c r="AB9" s="102">
         <v>45664</v>
       </c>
       <c r="AC9" s="31">
@@ -7908,12 +7860,12 @@
         <v>204.2</v>
       </c>
       <c r="AG9" s="31" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AH9" s="31">
         <v>-2.69E-2</v>
       </c>
-      <c r="AK9" s="105">
+      <c r="AK9" s="102">
         <v>45664</v>
       </c>
       <c r="AL9" s="31">
@@ -7929,36 +7881,36 @@
         <v>28</v>
       </c>
       <c r="AP9" s="31" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AQ9" s="31">
         <v>0.23119999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A10" s="105">
+      <c r="A10" s="102">
         <v>45663</v>
       </c>
-      <c r="B10" s="93">
+      <c r="B10" s="92">
         <v>3964.29</v>
       </c>
-      <c r="C10" s="93">
+      <c r="C10" s="92">
         <v>3904.42</v>
       </c>
-      <c r="D10" s="93">
+      <c r="D10" s="92">
         <v>3971.7</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="92">
         <v>3845.78</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="G10" s="106">
+        <v>264</v>
+      </c>
+      <c r="G10" s="103">
         <v>1.7899999999999999E-2</v>
       </c>
       <c r="H10" s="31"/>
-      <c r="I10" s="105">
+      <c r="I10" s="102">
         <v>45663</v>
       </c>
       <c r="J10" s="31">
@@ -7974,12 +7926,12 @@
         <v>1.4</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="O10" s="106">
+        <v>325</v>
+      </c>
+      <c r="O10" s="103">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="102">
         <v>45663</v>
       </c>
       <c r="T10" s="31">
@@ -7995,12 +7947,12 @@
         <v>3.11</v>
       </c>
       <c r="X10" s="31" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y10" s="31">
         <v>0.16980000000000001</v>
       </c>
-      <c r="AB10" s="105">
+      <c r="AB10" s="102">
         <v>45663</v>
       </c>
       <c r="AC10" s="31">
@@ -8016,12 +7968,12 @@
         <v>189.7</v>
       </c>
       <c r="AG10" s="31" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AH10" s="31">
         <v>0.20730000000000001</v>
       </c>
-      <c r="AK10" s="105">
+      <c r="AK10" s="102">
         <v>45663</v>
       </c>
       <c r="AL10" s="31">
@@ -8037,36 +7989,36 @@
         <v>25.24</v>
       </c>
       <c r="AP10" s="31" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AQ10" s="31">
         <v>-1.34E-2</v>
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A11" s="105">
+      <c r="A11" s="102">
         <v>45662</v>
       </c>
-      <c r="B11" s="93">
+      <c r="B11" s="92">
         <v>3894.61</v>
       </c>
-      <c r="C11" s="93">
+      <c r="C11" s="92">
         <v>3842.38</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="92">
         <v>3956.26</v>
       </c>
-      <c r="E11" s="93">
+      <c r="E11" s="92">
         <v>3831.04</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="G11" s="106">
+        <v>265</v>
+      </c>
+      <c r="G11" s="103">
         <v>1.6199999999999999E-2</v>
       </c>
       <c r="H11" s="31"/>
-      <c r="I11" s="105">
+      <c r="I11" s="102">
         <v>45662</v>
       </c>
       <c r="J11" s="31">
@@ -8082,12 +8034,12 @@
         <v>1.39</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="O11" s="106">
+        <v>326</v>
+      </c>
+      <c r="O11" s="103">
         <v>-7.1900000000000006E-2</v>
       </c>
-      <c r="S11" s="105">
+      <c r="S11" s="102">
         <v>45662</v>
       </c>
       <c r="T11" s="31">
@@ -8103,12 +8055,12 @@
         <v>2.68</v>
       </c>
       <c r="X11" s="31" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Y11" s="31">
         <v>0.1956</v>
       </c>
-      <c r="AB11" s="105">
+      <c r="AB11" s="102">
         <v>45662</v>
       </c>
       <c r="AC11" s="31">
@@ -8124,12 +8076,12 @@
         <v>172.1</v>
       </c>
       <c r="AG11" s="31" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AH11" s="31">
         <v>0.106</v>
       </c>
-      <c r="AK11" s="105">
+      <c r="AK11" s="102">
         <v>45662</v>
       </c>
       <c r="AL11" s="31">
@@ -8145,36 +8097,36 @@
         <v>26.92</v>
       </c>
       <c r="AP11" s="31" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AQ11" s="31">
         <v>-3.8600000000000002E-2</v>
       </c>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A12" s="105">
+      <c r="A12" s="102">
         <v>45661</v>
       </c>
-      <c r="B12" s="93">
+      <c r="B12" s="92">
         <v>3832.51</v>
       </c>
-      <c r="C12" s="93">
+      <c r="C12" s="92">
         <v>3950.77</v>
       </c>
-      <c r="D12" s="93">
+      <c r="D12" s="92">
         <v>3980.28</v>
       </c>
-      <c r="E12" s="93">
+      <c r="E12" s="92">
         <v>3372.38</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="G12" s="106">
+        <v>266</v>
+      </c>
+      <c r="G12" s="103">
         <v>-3.5200000000000002E-2</v>
       </c>
       <c r="H12" s="31"/>
-      <c r="I12" s="105">
+      <c r="I12" s="102">
         <v>45661</v>
       </c>
       <c r="J12" s="31">
@@ -8190,12 +8142,12 @@
         <v>1.36</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="O12" s="106">
+        <v>327</v>
+      </c>
+      <c r="O12" s="103">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="S12" s="105">
+      <c r="S12" s="102">
         <v>45661</v>
       </c>
       <c r="T12" s="31">
@@ -8211,12 +8163,12 @@
         <v>2.19</v>
       </c>
       <c r="X12" s="31" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y12" s="31">
         <v>1.12E-2</v>
       </c>
-      <c r="AB12" s="105">
+      <c r="AB12" s="102">
         <v>45661</v>
       </c>
       <c r="AC12" s="31">
@@ -8232,12 +8184,12 @@
         <v>137.80000000000001</v>
       </c>
       <c r="AG12" s="31" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AH12" s="31">
         <v>0.1071</v>
       </c>
-      <c r="AK12" s="105">
+      <c r="AK12" s="102">
         <v>45661</v>
       </c>
       <c r="AL12" s="31">
@@ -8253,36 +8205,36 @@
         <v>28.66</v>
       </c>
       <c r="AP12" s="31" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AQ12" s="31">
         <v>-0.4652</v>
       </c>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A13" s="105">
+      <c r="A13" s="102">
         <v>45660</v>
       </c>
-      <c r="B13" s="93">
+      <c r="B13" s="92">
         <v>3972.43</v>
       </c>
-      <c r="C13" s="93">
+      <c r="C13" s="92">
         <v>3895.37</v>
       </c>
-      <c r="D13" s="93">
+      <c r="D13" s="92">
         <v>4005.18</v>
       </c>
-      <c r="E13" s="93">
+      <c r="E13" s="92">
         <v>3805.7</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="G13" s="106">
+        <v>267</v>
+      </c>
+      <c r="G13" s="103">
         <v>1.9699999999999999E-2</v>
       </c>
       <c r="H13" s="31"/>
-      <c r="I13" s="105">
+      <c r="I13" s="102">
         <v>45660</v>
       </c>
       <c r="J13" s="31">
@@ -8298,12 +8250,12 @@
         <v>1.38</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="O13" s="106">
+        <v>328</v>
+      </c>
+      <c r="O13" s="103">
         <v>5.04E-2</v>
       </c>
-      <c r="S13" s="105">
+      <c r="S13" s="102">
         <v>45660</v>
       </c>
       <c r="T13" s="31">
@@ -8319,12 +8271,12 @@
         <v>2.65</v>
       </c>
       <c r="X13" s="31" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Y13" s="31">
         <v>-0.13550000000000001</v>
       </c>
-      <c r="AB13" s="105">
+      <c r="AB13" s="102">
         <v>45660</v>
       </c>
       <c r="AC13" s="31">
@@ -8340,12 +8292,12 @@
         <v>156</v>
       </c>
       <c r="AG13" s="31" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AH13" s="31">
         <v>-2.3199999999999998E-2</v>
       </c>
-      <c r="AK13" s="105">
+      <c r="AK13" s="102">
         <v>45660</v>
       </c>
       <c r="AL13" s="31">
@@ -8361,36 +8313,36 @@
         <v>57</v>
       </c>
       <c r="AP13" s="31" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AQ13" s="31">
         <v>-0.1467</v>
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A14" s="105">
+      <c r="A14" s="102">
         <v>45659</v>
       </c>
-      <c r="B14" s="93">
+      <c r="B14" s="92">
         <v>3895.7</v>
       </c>
-      <c r="C14" s="93">
+      <c r="C14" s="92">
         <v>3802.42</v>
       </c>
-      <c r="D14" s="93">
+      <c r="D14" s="92">
         <v>3951.64</v>
       </c>
-      <c r="E14" s="93">
+      <c r="E14" s="92">
         <v>3797.83</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="G14" s="106">
+        <v>268</v>
+      </c>
+      <c r="G14" s="103">
         <v>1.03E-2</v>
       </c>
       <c r="H14" s="31"/>
-      <c r="I14" s="105">
+      <c r="I14" s="102">
         <v>45659</v>
       </c>
       <c r="J14" s="31">
@@ -8406,12 +8358,12 @@
         <v>1.34</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="O14" s="106">
+        <v>329</v>
+      </c>
+      <c r="O14" s="103">
         <v>-1.4200000000000001E-2</v>
       </c>
-      <c r="S14" s="105">
+      <c r="S14" s="102">
         <v>45659</v>
       </c>
       <c r="T14" s="31">
@@ -8427,12 +8379,12 @@
         <v>2.78</v>
       </c>
       <c r="X14" s="31" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y14" s="31">
         <v>-0.1885</v>
       </c>
-      <c r="AB14" s="105">
+      <c r="AB14" s="102">
         <v>45659</v>
       </c>
       <c r="AC14" s="31">
@@ -8448,12 +8400,12 @@
         <v>153.6</v>
       </c>
       <c r="AG14" s="31" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AH14" s="31">
         <v>-2.0799999999999999E-2</v>
       </c>
-      <c r="AK14" s="105">
+      <c r="AK14" s="102">
         <v>45659</v>
       </c>
       <c r="AL14" s="31">
@@ -8469,36 +8421,36 @@
         <v>67.55</v>
       </c>
       <c r="AP14" s="31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AQ14" s="31">
         <v>-7.2800000000000004E-2</v>
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A15" s="105">
+      <c r="A15" s="102">
         <v>45658</v>
       </c>
-      <c r="B15" s="93">
+      <c r="B15" s="92">
         <v>3855.82</v>
       </c>
-      <c r="C15" s="93">
+      <c r="C15" s="92">
         <v>3790.36</v>
       </c>
-      <c r="D15" s="93">
+      <c r="D15" s="92">
         <v>3886.98</v>
       </c>
-      <c r="E15" s="93">
+      <c r="E15" s="92">
         <v>3765.41</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="G15" s="106">
+        <v>269</v>
+      </c>
+      <c r="G15" s="103">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="H15" s="31"/>
-      <c r="I15" s="105">
+      <c r="I15" s="102">
         <v>45658</v>
       </c>
       <c r="J15" s="31">
@@ -8514,12 +8466,12 @@
         <v>1.38</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="O15" s="106">
+        <v>330</v>
+      </c>
+      <c r="O15" s="103">
         <v>-4.7300000000000002E-2</v>
       </c>
-      <c r="S15" s="105">
+      <c r="S15" s="102">
         <v>45658</v>
       </c>
       <c r="T15" s="31">
@@ -8535,7 +8487,7 @@
         <v>3.41</v>
       </c>
       <c r="X15" s="31" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y15" s="31">
         <v>4.3700000000000003E-2</v>
@@ -8556,7 +8508,7 @@
         <v>149</v>
       </c>
       <c r="AG15" s="31" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH15" s="31">
         <v>1.49E-2</v>
@@ -8577,36 +8529,36 @@
         <v>71.7</v>
       </c>
       <c r="AP15" s="31" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AQ15" s="31">
         <v>-7.3099999999999998E-2</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A16" s="105">
+      <c r="A16" s="102">
         <v>45303</v>
       </c>
-      <c r="B16" s="93">
+      <c r="B16" s="92">
         <v>3787.6</v>
       </c>
-      <c r="C16" s="93">
+      <c r="C16" s="92">
         <v>3760.39</v>
       </c>
-      <c r="D16" s="93">
+      <c r="D16" s="92">
         <v>3842.71</v>
       </c>
-      <c r="E16" s="93">
+      <c r="E16" s="92">
         <v>3715.52</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="G16" s="106">
+        <v>270</v>
+      </c>
+      <c r="G16" s="103">
         <v>1.29E-2</v>
       </c>
       <c r="H16" s="31"/>
-      <c r="I16" s="105">
+      <c r="I16" s="102">
         <v>45303</v>
       </c>
       <c r="J16" s="31">
@@ -8622,12 +8574,12 @@
         <v>1.44</v>
       </c>
       <c r="N16" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="O16" s="106">
+        <v>331</v>
+      </c>
+      <c r="O16" s="103">
         <v>1.37E-2</v>
       </c>
-      <c r="S16" s="105">
+      <c r="S16" s="102">
         <v>45303</v>
       </c>
       <c r="T16" s="31">
@@ -8643,12 +8595,12 @@
         <v>3.45</v>
       </c>
       <c r="X16" s="31" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Y16" s="31">
         <v>-6.1499999999999999E-2</v>
       </c>
-      <c r="AB16" s="105">
+      <c r="AB16" s="102">
         <v>45303</v>
       </c>
       <c r="AC16" s="31">
@@ -8664,12 +8616,12 @@
         <v>150.19999999999999</v>
       </c>
       <c r="AG16" s="31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH16" s="31">
         <v>6.1400000000000003E-2</v>
       </c>
-      <c r="AK16" s="105">
+      <c r="AK16" s="102">
         <v>45303</v>
       </c>
       <c r="AL16" s="31">
@@ -8685,36 +8637,36 @@
         <v>74.849999999999994</v>
       </c>
       <c r="AP16" s="31" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AQ16" s="31">
         <v>-8.6900000000000005E-2</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A17" s="105">
+      <c r="A17" s="102">
         <v>45302</v>
       </c>
-      <c r="B17" s="93">
+      <c r="B17" s="92">
         <v>3739.29</v>
       </c>
-      <c r="C17" s="93">
+      <c r="C17" s="92">
         <v>3527.13</v>
       </c>
-      <c r="D17" s="93">
+      <c r="D17" s="92">
         <v>3766.93</v>
       </c>
-      <c r="E17" s="93">
+      <c r="E17" s="92">
         <v>3524.33</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="G17" s="106">
+        <v>271</v>
+      </c>
+      <c r="G17" s="103">
         <v>5.0700000000000002E-2</v>
       </c>
       <c r="H17" s="31"/>
-      <c r="I17" s="105">
+      <c r="I17" s="102">
         <v>45302</v>
       </c>
       <c r="J17" s="31">
@@ -8730,12 +8682,12 @@
         <v>1.45</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="O17" s="106">
+        <v>332</v>
+      </c>
+      <c r="O17" s="103">
         <v>-6.7999999999999996E-3</v>
       </c>
-      <c r="S17" s="105">
+      <c r="S17" s="102">
         <v>45302</v>
       </c>
       <c r="T17" s="31">
@@ -8751,12 +8703,12 @@
         <v>3.69</v>
       </c>
       <c r="X17" s="31" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y17" s="31">
         <v>-5.1000000000000004E-3</v>
       </c>
-      <c r="AB17" s="105">
+      <c r="AB17" s="102">
         <v>45302</v>
       </c>
       <c r="AC17" s="31">
@@ -8772,12 +8724,12 @@
         <v>128.6</v>
       </c>
       <c r="AG17" s="31" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AH17" s="31">
         <v>0.1358</v>
       </c>
-      <c r="AK17" s="105">
+      <c r="AK17" s="102">
         <v>45302</v>
       </c>
       <c r="AL17" s="31">
@@ -8793,36 +8745,36 @@
         <v>66.75</v>
       </c>
       <c r="AP17" s="31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AQ17" s="31">
         <v>0.25230000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A18" s="105">
+      <c r="A18" s="102">
         <v>45301</v>
       </c>
-      <c r="B18" s="93">
+      <c r="B18" s="92">
         <v>3558.88</v>
       </c>
-      <c r="C18" s="93">
+      <c r="C18" s="92">
         <v>3593.42</v>
       </c>
-      <c r="D18" s="93">
+      <c r="D18" s="92">
         <v>3644.18</v>
       </c>
-      <c r="E18" s="93">
+      <c r="E18" s="92">
         <v>3553.85</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="G18" s="106">
+        <v>272</v>
+      </c>
+      <c r="G18" s="103">
         <v>-7.4000000000000003E-3</v>
       </c>
       <c r="H18" s="31"/>
-      <c r="I18" s="105">
+      <c r="I18" s="102">
         <v>45301</v>
       </c>
       <c r="J18" s="31">
@@ -8838,12 +8790,12 @@
         <v>1.42</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="O18" s="106">
+        <v>333</v>
+      </c>
+      <c r="O18" s="103">
         <v>-2.6499999999999999E-2</v>
       </c>
-      <c r="S18" s="105">
+      <c r="S18" s="102">
         <v>45301</v>
       </c>
       <c r="T18" s="31">
@@ -8859,12 +8811,12 @@
         <v>3.79</v>
       </c>
       <c r="X18" s="31" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y18" s="31">
         <v>-5.0799999999999998E-2</v>
       </c>
-      <c r="AB18" s="105">
+      <c r="AB18" s="102">
         <v>45301</v>
       </c>
       <c r="AC18" s="31">
@@ -8880,12 +8832,12 @@
         <v>131.5</v>
       </c>
       <c r="AG18" s="31" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH18" s="31">
         <v>-8.7599999999999997E-2</v>
       </c>
-      <c r="AK18" s="105">
+      <c r="AK18" s="102">
         <v>45301</v>
       </c>
       <c r="AL18" s="31">
@@ -8901,36 +8853,36 @@
         <v>67.7</v>
       </c>
       <c r="AP18" s="31" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AQ18" s="31">
         <v>-5.7099999999999998E-2</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A19" s="105">
+      <c r="A19" s="102">
         <v>45300</v>
       </c>
-      <c r="B19" s="93">
+      <c r="B19" s="92">
         <v>3585.29</v>
       </c>
-      <c r="C19" s="93">
+      <c r="C19" s="92">
         <v>3442.71</v>
       </c>
-      <c r="D19" s="93">
+      <c r="D19" s="92">
         <v>3652.62</v>
       </c>
-      <c r="E19" s="93">
+      <c r="E19" s="92">
         <v>3412.47</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="G19" s="106">
+        <v>273</v>
+      </c>
+      <c r="G19" s="103">
         <v>4.1300000000000003E-2</v>
       </c>
       <c r="H19" s="31"/>
-      <c r="I19" s="105">
+      <c r="I19" s="102">
         <v>45300</v>
       </c>
       <c r="J19" s="31">
@@ -8946,12 +8898,12 @@
         <v>1.4</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="O19" s="106">
+        <v>334</v>
+      </c>
+      <c r="O19" s="103">
         <v>6.3399999999999998E-2</v>
       </c>
-      <c r="S19" s="105">
+      <c r="S19" s="102">
         <v>45300</v>
       </c>
       <c r="T19" s="31">
@@ -8967,12 +8919,12 @@
         <v>3.69</v>
       </c>
       <c r="X19" s="31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y19" s="31">
         <v>9.8400000000000001E-2</v>
       </c>
-      <c r="AB19" s="105">
+      <c r="AB19" s="102">
         <v>45300</v>
       </c>
       <c r="AC19" s="31">
@@ -8988,12 +8940,12 @@
         <v>141.9</v>
       </c>
       <c r="AG19" s="31" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AH19" s="31">
         <v>-6.9400000000000003E-2</v>
       </c>
-      <c r="AK19" s="105">
+      <c r="AK19" s="102">
         <v>45300</v>
       </c>
       <c r="AL19" s="31">
@@ -9009,36 +8961,36 @@
         <v>63.95</v>
       </c>
       <c r="AP19" s="31" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AQ19" s="31">
         <v>7.8399999999999997E-2</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A20" s="105">
+      <c r="A20" s="102">
         <v>45299</v>
       </c>
-      <c r="B20" s="93">
+      <c r="B20" s="92">
         <v>3442.93</v>
       </c>
-      <c r="C20" s="93">
+      <c r="C20" s="92">
         <v>3453.24</v>
       </c>
-      <c r="D20" s="93">
+      <c r="D20" s="92">
         <v>3454.53</v>
       </c>
-      <c r="E20" s="93">
+      <c r="E20" s="92">
         <v>3198.44</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="G20" s="106">
+        <v>274</v>
+      </c>
+      <c r="G20" s="103">
         <v>-3.8E-3</v>
       </c>
       <c r="H20" s="31"/>
-      <c r="I20" s="105">
+      <c r="I20" s="102">
         <v>45299</v>
       </c>
       <c r="J20" s="31">
@@ -9054,12 +9006,12 @@
         <v>1.35</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="O20" s="106">
+        <v>335</v>
+      </c>
+      <c r="O20" s="103">
         <v>1.43E-2</v>
       </c>
-      <c r="S20" s="105">
+      <c r="S20" s="102">
         <v>45299</v>
       </c>
       <c r="T20" s="31">
@@ -9075,12 +9027,12 @@
         <v>3.58</v>
       </c>
       <c r="X20" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y20" s="31">
         <v>-0.2838</v>
       </c>
-      <c r="AB20" s="105">
+      <c r="AB20" s="102">
         <v>45299</v>
       </c>
       <c r="AC20" s="31">
@@ -9096,12 +9048,12 @@
         <v>154.19999999999999</v>
       </c>
       <c r="AG20" s="31" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH20" s="31">
         <v>-0.10489999999999999</v>
       </c>
-      <c r="AK20" s="105">
+      <c r="AK20" s="102">
         <v>45299</v>
       </c>
       <c r="AL20" s="31">
@@ -9117,36 +9069,36 @@
         <v>50.65</v>
       </c>
       <c r="AP20" s="31" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AQ20" s="31">
         <v>0.2135</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A21" s="105">
+      <c r="A21" s="102">
         <v>45298</v>
       </c>
-      <c r="B21" s="93">
+      <c r="B21" s="92">
         <v>3455.94</v>
       </c>
-      <c r="C21" s="93">
+      <c r="C21" s="92">
         <v>3334.71</v>
       </c>
-      <c r="D21" s="93">
+      <c r="D21" s="92">
         <v>3509.2</v>
       </c>
-      <c r="E21" s="93">
+      <c r="E21" s="92">
         <v>3325.17</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="G21" s="106">
+        <v>275</v>
+      </c>
+      <c r="G21" s="103">
         <v>3.6900000000000002E-2</v>
       </c>
       <c r="H21" s="31"/>
-      <c r="I21" s="105">
+      <c r="I21" s="102">
         <v>45298</v>
       </c>
       <c r="J21" s="31">
@@ -9162,12 +9114,12 @@
         <v>1.33</v>
       </c>
       <c r="N21" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="O21" s="106">
+        <v>336</v>
+      </c>
+      <c r="O21" s="103">
         <v>4.48E-2</v>
       </c>
-      <c r="S21" s="105">
+      <c r="S21" s="102">
         <v>45298</v>
       </c>
       <c r="T21" s="31">
@@ -9183,12 +9135,12 @@
         <v>4.76</v>
       </c>
       <c r="X21" s="31" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Y21" s="31">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="AB21" s="105">
+      <c r="AB21" s="102">
         <v>45298</v>
       </c>
       <c r="AC21" s="31">
@@ -9204,12 +9156,12 @@
         <v>157.4</v>
       </c>
       <c r="AG21" s="31" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AH21" s="31">
         <v>0.108</v>
       </c>
-      <c r="AK21" s="105">
+      <c r="AK21" s="102">
         <v>45298</v>
       </c>
       <c r="AL21" s="31">
@@ -9225,36 +9177,36 @@
         <v>48.08</v>
       </c>
       <c r="AP21" s="31" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AQ21" s="31">
         <v>0.1009</v>
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A22" s="105">
+      <c r="A22" s="102">
         <v>45297</v>
       </c>
-      <c r="B22" s="93">
+      <c r="B22" s="92">
         <v>3332.8</v>
       </c>
-      <c r="C22" s="93">
+      <c r="C22" s="92">
         <v>3347.22</v>
       </c>
-      <c r="D22" s="93">
+      <c r="D22" s="92">
         <v>3355.63</v>
       </c>
-      <c r="E22" s="93">
+      <c r="E22" s="92">
         <v>3288.94</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="G22" s="106">
+        <v>276</v>
+      </c>
+      <c r="G22" s="103">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="H22" s="31"/>
-      <c r="I22" s="105">
+      <c r="I22" s="102">
         <v>45297</v>
       </c>
       <c r="J22" s="31">
@@ -9270,12 +9222,12 @@
         <v>1.32</v>
       </c>
       <c r="N22" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="O22" s="106">
+        <v>337</v>
+      </c>
+      <c r="O22" s="103">
         <v>-3.5999999999999997E-2</v>
       </c>
-      <c r="S22" s="105">
+      <c r="S22" s="102">
         <v>45297</v>
       </c>
       <c r="T22" s="31">
@@ -9291,12 +9243,12 @@
         <v>4.8600000000000003</v>
       </c>
       <c r="X22" s="31" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Y22" s="31">
         <v>-5.7999999999999996E-3</v>
       </c>
-      <c r="AB22" s="105">
+      <c r="AB22" s="102">
         <v>45297</v>
       </c>
       <c r="AC22" s="31">
@@ -9312,12 +9264,12 @@
         <v>150</v>
       </c>
       <c r="AG22" s="31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AH22" s="31">
         <v>-7.2599999999999998E-2</v>
       </c>
-      <c r="AK22" s="105">
+      <c r="AK22" s="102">
         <v>45297</v>
       </c>
       <c r="AL22" s="31">
@@ -9333,36 +9285,36 @@
         <v>45.5</v>
       </c>
       <c r="AP22" s="31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AQ22" s="31">
         <v>-5.11E-2</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A23" s="105">
+      <c r="A23" s="102">
         <v>45296</v>
       </c>
-      <c r="B23" s="93">
+      <c r="B23" s="92">
         <v>3336.59</v>
       </c>
-      <c r="C23" s="93">
+      <c r="C23" s="92">
         <v>3309.78</v>
       </c>
-      <c r="D23" s="93">
+      <c r="D23" s="92">
         <v>3336.59</v>
       </c>
-      <c r="E23" s="93">
+      <c r="E23" s="92">
         <v>3241.13</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="G23" s="106">
+        <v>277</v>
+      </c>
+      <c r="G23" s="103">
         <v>1.3299999999999999E-2</v>
       </c>
       <c r="H23" s="31"/>
-      <c r="I23" s="105">
+      <c r="I23" s="102">
         <v>45296</v>
       </c>
       <c r="J23" s="31">
@@ -9378,12 +9330,12 @@
         <v>1.36</v>
       </c>
       <c r="N23" s="31" t="s">
-        <v>339</v>
-      </c>
-      <c r="O23" s="106">
+        <v>338</v>
+      </c>
+      <c r="O23" s="103">
         <v>-6.7100000000000007E-2</v>
       </c>
-      <c r="S23" s="105">
+      <c r="S23" s="102">
         <v>45296</v>
       </c>
       <c r="T23" s="31">
@@ -9399,12 +9351,12 @@
         <v>5.0199999999999996</v>
       </c>
       <c r="X23" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Y23" s="31">
         <v>-6.83E-2</v>
       </c>
-      <c r="AB23" s="105">
+      <c r="AB23" s="102">
         <v>45296</v>
       </c>
       <c r="AC23" s="31">
@@ -9420,12 +9372,12 @@
         <v>161.4</v>
       </c>
       <c r="AG23" s="31" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AH23" s="31">
         <v>5.2400000000000002E-2</v>
       </c>
-      <c r="AK23" s="105">
+      <c r="AK23" s="102">
         <v>45296</v>
       </c>
       <c r="AL23" s="31">
@@ -9441,36 +9393,36 @@
         <v>53.4</v>
       </c>
       <c r="AP23" s="31" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AQ23" s="31">
         <v>-2.8899999999999999E-2</v>
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A24" s="105">
+      <c r="A24" s="102">
         <v>45295</v>
       </c>
-      <c r="B24" s="93">
+      <c r="B24" s="92">
         <v>3292.69</v>
       </c>
-      <c r="C24" s="93">
+      <c r="C24" s="92">
         <v>3231.48</v>
       </c>
-      <c r="D24" s="93">
+      <c r="D24" s="92">
         <v>3308.12</v>
       </c>
-      <c r="E24" s="93">
+      <c r="E24" s="92">
         <v>3136.44</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="G24" s="106">
+        <v>278</v>
+      </c>
+      <c r="G24" s="103">
         <v>2.1299999999999999E-2</v>
       </c>
       <c r="H24" s="31"/>
-      <c r="I24" s="105">
+      <c r="I24" s="102">
         <v>45295</v>
       </c>
       <c r="J24" s="31">
@@ -9486,12 +9438,12 @@
         <v>1.4</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="O24" s="106">
+        <v>339</v>
+      </c>
+      <c r="O24" s="103">
         <v>6.4299999999999996E-2</v>
       </c>
-      <c r="S24" s="105">
+      <c r="S24" s="102">
         <v>45295</v>
       </c>
       <c r="T24" s="31">
@@ -9507,12 +9459,12 @@
         <v>5.34</v>
       </c>
       <c r="X24" s="31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Y24" s="31">
         <v>-3.8100000000000002E-2</v>
       </c>
-      <c r="AB24" s="105">
+      <c r="AB24" s="102">
         <v>45295</v>
       </c>
       <c r="AC24" s="31">
@@ -9528,12 +9480,12 @@
         <v>155.80000000000001</v>
       </c>
       <c r="AG24" s="31" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AH24" s="31">
         <v>-0.1009</v>
       </c>
-      <c r="AK24" s="105">
+      <c r="AK24" s="102">
         <v>45295</v>
       </c>
       <c r="AL24" s="31">
@@ -9549,36 +9501,36 @@
         <v>51.5</v>
       </c>
       <c r="AP24" s="31" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AQ24" s="31">
         <v>-0.20399999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A25" s="105">
+      <c r="A25" s="102">
         <v>45294</v>
       </c>
-      <c r="B25" s="93">
+      <c r="B25" s="92">
         <v>3224.01</v>
       </c>
-      <c r="C25" s="93">
+      <c r="C25" s="92">
         <v>3151.07</v>
       </c>
-      <c r="D25" s="93">
+      <c r="D25" s="92">
         <v>3262.52</v>
       </c>
-      <c r="E25" s="93">
+      <c r="E25" s="92">
         <v>3101.24</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="G25" s="106">
+        <v>279</v>
+      </c>
+      <c r="G25" s="103">
         <v>2.6200000000000001E-2</v>
       </c>
       <c r="H25" s="31"/>
-      <c r="I25" s="105">
+      <c r="I25" s="102">
         <v>45294</v>
       </c>
       <c r="J25" s="31">
@@ -9594,12 +9546,12 @@
         <v>1.34</v>
       </c>
       <c r="N25" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="O25" s="106">
+        <v>340</v>
+      </c>
+      <c r="O25" s="103">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="S25" s="105">
+      <c r="S25" s="102">
         <v>45294</v>
       </c>
       <c r="T25" s="31">
@@ -9615,12 +9567,12 @@
         <v>5.67</v>
       </c>
       <c r="X25" s="31" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Y25" s="31">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="AB25" s="105">
+      <c r="AB25" s="102">
         <v>45294</v>
       </c>
       <c r="AC25" s="31">
@@ -9636,12 +9588,12 @@
         <v>148.1</v>
       </c>
       <c r="AG25" s="31" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AH25" s="31">
         <v>0.14030000000000001</v>
       </c>
-      <c r="AK25" s="105">
+      <c r="AK25" s="102">
         <v>45294</v>
       </c>
       <c r="AL25" s="31">
@@ -9657,36 +9609,36 @@
         <v>61.5</v>
       </c>
       <c r="AP25" s="31" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AQ25" s="31">
         <v>-0.1077</v>
       </c>
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A26" s="105">
+      <c r="A26" s="102">
         <v>45293</v>
       </c>
-      <c r="B26" s="93">
+      <c r="B26" s="92">
         <v>3141.85</v>
       </c>
-      <c r="C26" s="93">
+      <c r="C26" s="92">
         <v>3144.18</v>
       </c>
-      <c r="D26" s="93">
+      <c r="D26" s="92">
         <v>3247.63</v>
       </c>
-      <c r="E26" s="93">
+      <c r="E26" s="92">
         <v>3092.4</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="G26" s="106">
+        <v>280</v>
+      </c>
+      <c r="G26" s="103">
         <v>-3.5000000000000001E-3</v>
       </c>
       <c r="H26" s="31"/>
-      <c r="I26" s="105">
+      <c r="I26" s="102">
         <v>45293</v>
       </c>
       <c r="J26" s="31">
@@ -9702,12 +9654,12 @@
         <v>1.34</v>
       </c>
       <c r="N26" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="O26" s="106">
+        <v>341</v>
+      </c>
+      <c r="O26" s="103">
         <v>-3.5700000000000003E-2</v>
       </c>
-      <c r="S26" s="105">
+      <c r="S26" s="102">
         <v>45293</v>
       </c>
       <c r="T26" s="31">
@@ -9723,12 +9675,12 @@
         <v>5.5</v>
       </c>
       <c r="X26" s="31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Y26" s="31">
         <v>-0.1588</v>
       </c>
-      <c r="AB26" s="105">
+      <c r="AB26" s="102">
         <v>45293</v>
       </c>
       <c r="AC26" s="31">
@@ -9744,12 +9696,12 @@
         <v>148</v>
       </c>
       <c r="AG26" s="31" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AH26" s="31">
         <v>-6.2199999999999998E-2</v>
       </c>
-      <c r="AK26" s="105">
+      <c r="AK26" s="102">
         <v>45293</v>
       </c>
       <c r="AL26" s="31">
@@ -9765,36 +9717,36 @@
         <v>63</v>
       </c>
       <c r="AP26" s="31" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AQ26" s="31">
         <v>-9.1399999999999995E-2</v>
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A27" s="105">
+      <c r="A27" s="102">
         <v>45292</v>
       </c>
-      <c r="B27" s="93">
+      <c r="B27" s="92">
         <v>3153.01</v>
       </c>
-      <c r="C27" s="93">
+      <c r="C27" s="92">
         <v>3240.83</v>
       </c>
-      <c r="D27" s="93">
+      <c r="D27" s="92">
         <v>3259.28</v>
       </c>
-      <c r="E27" s="93">
+      <c r="E27" s="92">
         <v>3126.29</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="G27" s="106">
+        <v>281</v>
+      </c>
+      <c r="G27" s="103">
         <v>-2.69E-2</v>
       </c>
       <c r="H27" s="31"/>
-      <c r="I27" s="105">
+      <c r="I27" s="102">
         <v>45292</v>
       </c>
       <c r="J27" s="31">
@@ -9810,12 +9762,12 @@
         <v>1.37</v>
       </c>
       <c r="N27" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="O27" s="106">
-        <v>0</v>
-      </c>
-      <c r="S27" s="105">
+        <v>342</v>
+      </c>
+      <c r="O27" s="103">
+        <v>0</v>
+      </c>
+      <c r="S27" s="102">
         <v>45292</v>
       </c>
       <c r="T27" s="31">
@@ -9831,12 +9783,12 @@
         <v>6.74</v>
       </c>
       <c r="X27" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y27" s="31">
         <v>2.5700000000000001E-2</v>
       </c>
-      <c r="AB27" s="105">
+      <c r="AB27" s="102">
         <v>45292</v>
       </c>
       <c r="AC27" s="31">
@@ -9852,12 +9804,12 @@
         <v>158.22999999999999</v>
       </c>
       <c r="AG27" s="31" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AH27" s="31">
         <v>-3.5999999999999997E-2</v>
       </c>
-      <c r="AK27" s="105">
+      <c r="AK27" s="102">
         <v>45292</v>
       </c>
       <c r="AL27" s="31">
@@ -9873,36 +9825,36 @@
         <v>80</v>
       </c>
       <c r="AP27" s="31" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AQ27" s="31">
         <v>1.4800000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A28" s="105">
+      <c r="A28" s="102">
         <v>44938</v>
       </c>
-      <c r="B28" s="93">
+      <c r="B28" s="92">
         <v>3240.27</v>
       </c>
-      <c r="C28" s="93">
+      <c r="C28" s="92">
         <v>3081.25</v>
       </c>
-      <c r="D28" s="93">
+      <c r="D28" s="92">
         <v>3250.05</v>
       </c>
-      <c r="E28" s="93">
+      <c r="E28" s="92">
         <v>3052.35</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="G28" s="106">
+        <v>282</v>
+      </c>
+      <c r="G28" s="103">
         <v>5.4399999999999997E-2</v>
       </c>
       <c r="H28" s="31"/>
-      <c r="I28" s="105">
+      <c r="I28" s="102">
         <v>44938</v>
       </c>
       <c r="J28" s="31">
@@ -9918,12 +9870,12 @@
         <v>1.28</v>
       </c>
       <c r="N28" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="O28" s="106">
+        <v>343</v>
+      </c>
+      <c r="O28" s="103">
         <v>8.5300000000000001E-2</v>
       </c>
-      <c r="S28" s="105">
+      <c r="S28" s="102">
         <v>44938</v>
       </c>
       <c r="T28" s="31">
@@ -9939,7 +9891,7 @@
         <v>6.49</v>
       </c>
       <c r="X28" s="31" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y28" s="31">
         <v>5.5800000000000002E-2</v>
@@ -9960,7 +9912,7 @@
         <v>154</v>
       </c>
       <c r="AG28" s="31" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AH28" s="31">
         <v>9.2399999999999996E-2</v>
@@ -9981,36 +9933,36 @@
         <v>64.349999999999994</v>
       </c>
       <c r="AP28" s="31" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AQ28" s="31">
         <v>0.26550000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A29" s="105">
+      <c r="A29" s="102">
         <v>44937</v>
       </c>
-      <c r="B29" s="93">
+      <c r="B29" s="92">
         <v>3072.99</v>
       </c>
-      <c r="C29" s="93">
+      <c r="C29" s="92">
         <v>3071.74</v>
       </c>
-      <c r="D29" s="93">
+      <c r="D29" s="92">
         <v>3180.53</v>
       </c>
-      <c r="E29" s="93">
+      <c r="E29" s="92">
         <v>3061.6</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="G29" s="106">
+        <v>283</v>
+      </c>
+      <c r="G29" s="103">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="H29" s="31"/>
-      <c r="I29" s="105">
+      <c r="I29" s="102">
         <v>44937</v>
       </c>
       <c r="J29" s="31">
@@ -10026,12 +9978,12 @@
         <v>1.28</v>
       </c>
       <c r="N29" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="O29" s="106">
+        <v>344</v>
+      </c>
+      <c r="O29" s="103">
         <v>-2.2700000000000001E-2</v>
       </c>
-      <c r="S29" s="105">
+      <c r="S29" s="102">
         <v>44937</v>
       </c>
       <c r="T29" s="31">
@@ -10047,12 +9999,12 @@
         <v>5.97</v>
       </c>
       <c r="X29" s="31" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y29" s="31">
         <v>0.1013</v>
       </c>
-      <c r="AB29" s="105">
+      <c r="AB29" s="102">
         <v>44937</v>
       </c>
       <c r="AC29" s="31">
@@ -10068,12 +10020,12 @@
         <v>151</v>
       </c>
       <c r="AG29" s="31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AH29" s="31">
         <v>1.46E-2</v>
       </c>
-      <c r="AK29" s="105">
+      <c r="AK29" s="102">
         <v>44937</v>
       </c>
       <c r="AL29" s="31">
@@ -10089,36 +10041,36 @@
         <v>59.05</v>
       </c>
       <c r="AP29" s="31" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AQ29" s="31">
         <v>6.9599999999999995E-2</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A30" s="105">
+      <c r="A30" s="102">
         <v>44936</v>
       </c>
-      <c r="B30" s="93">
+      <c r="B30" s="92">
         <v>3067.74</v>
       </c>
-      <c r="C30" s="93">
+      <c r="C30" s="92">
         <v>3226.53</v>
       </c>
-      <c r="D30" s="93">
+      <c r="D30" s="92">
         <v>3232.09</v>
       </c>
-      <c r="E30" s="93">
+      <c r="E30" s="92">
         <v>3041.67</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="G30" s="106">
+        <v>284</v>
+      </c>
+      <c r="G30" s="103">
         <v>-4.65E-2</v>
       </c>
       <c r="H30" s="31"/>
-      <c r="I30" s="105">
+      <c r="I30" s="102">
         <v>44936</v>
       </c>
       <c r="J30" s="31">
@@ -10134,12 +10086,12 @@
         <v>1.27</v>
       </c>
       <c r="N30" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="O30" s="106">
+        <v>345</v>
+      </c>
+      <c r="O30" s="103">
         <v>1.54E-2</v>
       </c>
-      <c r="S30" s="105">
+      <c r="S30" s="102">
         <v>44936</v>
       </c>
       <c r="T30" s="31">
@@ -10155,12 +10107,12 @@
         <v>5.3</v>
       </c>
       <c r="X30" s="31" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y30" s="31">
         <v>5.0599999999999999E-2</v>
       </c>
-      <c r="AB30" s="105">
+      <c r="AB30" s="102">
         <v>44936</v>
       </c>
       <c r="AC30" s="31">
@@ -10176,12 +10128,12 @@
         <v>139.9</v>
       </c>
       <c r="AG30" s="31" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AH30" s="31">
         <v>4.6399999999999997E-2</v>
       </c>
-      <c r="AK30" s="105">
+      <c r="AK30" s="102">
         <v>44936</v>
       </c>
       <c r="AL30" s="31">
@@ -10197,36 +10149,36 @@
         <v>54.55</v>
       </c>
       <c r="AP30" s="31" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AQ30" s="31">
         <v>-0.29620000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A31" s="105">
+      <c r="A31" s="102">
         <v>44935</v>
       </c>
-      <c r="B31" s="93">
+      <c r="B31" s="92">
         <v>3217.41</v>
       </c>
-      <c r="C31" s="93">
+      <c r="C31" s="92">
         <v>3240.53</v>
       </c>
-      <c r="D31" s="93">
+      <c r="D31" s="92">
         <v>3289.07</v>
       </c>
-      <c r="E31" s="93">
+      <c r="E31" s="92">
         <v>3179.33</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="G31" s="106">
+        <v>285</v>
+      </c>
+      <c r="G31" s="103">
         <v>-4.8999999999999998E-3</v>
       </c>
       <c r="H31" s="31"/>
-      <c r="I31" s="105">
+      <c r="I31" s="102">
         <v>44935</v>
       </c>
       <c r="J31" s="31">
@@ -10242,12 +10194,12 @@
         <v>1.25</v>
       </c>
       <c r="N31" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="O31" s="106">
+        <v>346</v>
+      </c>
+      <c r="O31" s="103">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="S31" s="105">
+      <c r="S31" s="102">
         <v>44935</v>
       </c>
       <c r="T31" s="31">
@@ -10263,12 +10215,12 @@
         <v>5.6</v>
       </c>
       <c r="X31" s="31" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y31" s="31">
         <v>-9.6199999999999994E-2</v>
       </c>
-      <c r="AB31" s="105">
+      <c r="AB31" s="102">
         <v>44935</v>
       </c>
       <c r="AC31" s="31">
@@ -10284,12 +10236,12 @@
         <v>140</v>
       </c>
       <c r="AG31" s="31" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AH31" s="31">
         <v>0.04</v>
       </c>
-      <c r="AK31" s="105">
+      <c r="AK31" s="102">
         <v>44935</v>
       </c>
       <c r="AL31" s="31">
@@ -10305,36 +10257,36 @@
         <v>82.2</v>
       </c>
       <c r="AP31" s="31" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AQ31" s="31">
         <v>6.0900000000000003E-2</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A32" s="105">
+      <c r="A32" s="102">
         <v>44934</v>
       </c>
-      <c r="B32" s="93">
+      <c r="B32" s="92">
         <v>3233.3</v>
       </c>
-      <c r="C32" s="93">
+      <c r="C32" s="92">
         <v>3383.07</v>
       </c>
-      <c r="D32" s="93">
+      <c r="D32" s="92">
         <v>3385.68</v>
       </c>
-      <c r="E32" s="93">
+      <c r="E32" s="92">
         <v>3143.9</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="G32" s="106">
+        <v>286</v>
+      </c>
+      <c r="G32" s="103">
         <v>-4.1700000000000001E-2</v>
       </c>
       <c r="H32" s="31"/>
-      <c r="I32" s="105">
+      <c r="I32" s="102">
         <v>44934</v>
       </c>
       <c r="J32" s="31">
@@ -10350,12 +10302,12 @@
         <v>1.23</v>
       </c>
       <c r="N32" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="O32" s="106">
+        <v>347</v>
+      </c>
+      <c r="O32" s="103">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="S32" s="105">
+      <c r="S32" s="102">
         <v>44934</v>
       </c>
       <c r="T32" s="31">
@@ -10371,12 +10323,12 @@
         <v>6.13</v>
       </c>
       <c r="X32" s="31" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Y32" s="31">
         <v>-8.5099999999999995E-2</v>
       </c>
-      <c r="AB32" s="105">
+      <c r="AB32" s="102">
         <v>44934</v>
       </c>
       <c r="AC32" s="31">
@@ -10392,12 +10344,12 @@
         <v>135</v>
       </c>
       <c r="AG32" s="31" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH32" s="31">
         <v>-8.2000000000000007E-3</v>
       </c>
-      <c r="AK32" s="105">
+      <c r="AK32" s="102">
         <v>44934</v>
       </c>
       <c r="AL32" s="31">
@@ -10413,36 +10365,36 @@
         <v>75.3</v>
       </c>
       <c r="AP32" s="31" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AQ32" s="31">
         <v>-0.10340000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A33" s="105">
+      <c r="A33" s="102">
         <v>44933</v>
       </c>
-      <c r="B33" s="93">
+      <c r="B33" s="92">
         <v>3373.98</v>
       </c>
-      <c r="C33" s="93">
+      <c r="C33" s="92">
         <v>3215.56</v>
       </c>
-      <c r="D33" s="93">
+      <c r="D33" s="92">
         <v>3392.63</v>
       </c>
-      <c r="E33" s="93">
+      <c r="E33" s="92">
         <v>3128.7</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="G33" s="106">
+        <v>287</v>
+      </c>
+      <c r="G33" s="103">
         <v>5.2400000000000002E-2</v>
       </c>
       <c r="H33" s="31"/>
-      <c r="I33" s="105">
+      <c r="I33" s="102">
         <v>44933</v>
       </c>
       <c r="J33" s="31">
@@ -10458,12 +10410,12 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="N33" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="O33" s="106">
+        <v>348</v>
+      </c>
+      <c r="O33" s="103">
         <v>8.6199999999999999E-2</v>
       </c>
-      <c r="S33" s="105">
+      <c r="S33" s="102">
         <v>44933</v>
       </c>
       <c r="T33" s="31">
@@ -10479,12 +10431,12 @@
         <v>6.84</v>
       </c>
       <c r="X33" s="31" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Y33" s="31">
         <v>-4.5499999999999999E-2</v>
       </c>
-      <c r="AB33" s="105">
+      <c r="AB33" s="102">
         <v>44933</v>
       </c>
       <c r="AC33" s="31">
@@ -10500,12 +10452,12 @@
         <v>134.9</v>
       </c>
       <c r="AG33" s="31" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH33" s="31">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="AK33" s="105">
+      <c r="AK33" s="102">
         <v>44933</v>
       </c>
       <c r="AL33" s="31">
@@ -10521,36 +10473,36 @@
         <v>90.5</v>
       </c>
       <c r="AP33" s="31" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AQ33" s="31">
         <v>-4.0099999999999997E-2</v>
       </c>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A34" s="105">
+      <c r="A34" s="102">
         <v>44932</v>
       </c>
-      <c r="B34" s="93">
+      <c r="B34" s="92">
         <v>3205.91</v>
       </c>
-      <c r="C34" s="93">
+      <c r="C34" s="92">
         <v>3162.52</v>
       </c>
-      <c r="D34" s="93">
+      <c r="D34" s="92">
         <v>3277.51</v>
       </c>
-      <c r="E34" s="93">
+      <c r="E34" s="92">
         <v>3155.52</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="G34" s="106">
+        <v>288</v>
+      </c>
+      <c r="G34" s="103">
         <v>1.49E-2</v>
       </c>
       <c r="H34" s="31"/>
-      <c r="I34" s="105">
+      <c r="I34" s="102">
         <v>44932</v>
       </c>
       <c r="J34" s="31">
@@ -10566,12 +10518,12 @@
         <v>1.01</v>
       </c>
       <c r="N34" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="O34" s="106">
+        <v>349</v>
+      </c>
+      <c r="O34" s="103">
         <v>5.45E-2</v>
       </c>
-      <c r="S34" s="105">
+      <c r="S34" s="102">
         <v>44932</v>
       </c>
       <c r="T34" s="31">
@@ -10587,12 +10539,12 @@
         <v>6.68</v>
       </c>
       <c r="X34" s="31" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y34" s="31">
         <v>6.7599999999999993E-2</v>
       </c>
-      <c r="AB34" s="105">
+      <c r="AB34" s="102">
         <v>44932</v>
       </c>
       <c r="AC34" s="31">
@@ -10608,12 +10560,12 @@
         <v>109.9</v>
       </c>
       <c r="AG34" s="31" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AH34" s="31">
         <v>0.27089999999999997</v>
       </c>
-      <c r="AK34" s="105">
+      <c r="AK34" s="102">
         <v>44932</v>
       </c>
       <c r="AL34" s="31">
@@ -10629,36 +10581,36 @@
         <v>95.51</v>
       </c>
       <c r="AP34" s="31" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AQ34" s="31">
         <v>-8.8599999999999998E-2</v>
       </c>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A35" s="105">
+      <c r="A35" s="102">
         <v>44931</v>
       </c>
-      <c r="B35" s="93">
+      <c r="B35" s="92">
         <v>3158.8</v>
       </c>
-      <c r="C35" s="93">
+      <c r="C35" s="92">
         <v>3291.43</v>
       </c>
-      <c r="D35" s="93">
+      <c r="D35" s="92">
         <v>3309.68</v>
       </c>
-      <c r="E35" s="93">
+      <c r="E35" s="92">
         <v>3156.15</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="G35" s="106">
+        <v>289</v>
+      </c>
+      <c r="G35" s="103">
         <v>-3.4200000000000001E-2</v>
       </c>
       <c r="H35" s="31"/>
-      <c r="I35" s="105">
+      <c r="I35" s="102">
         <v>44931</v>
       </c>
       <c r="J35" s="31">
@@ -10674,12 +10626,12 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="N35" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="O35" s="106">
+        <v>350</v>
+      </c>
+      <c r="O35" s="103">
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="S35" s="105">
+      <c r="S35" s="102">
         <v>44931</v>
       </c>
       <c r="T35" s="31">
@@ -10695,12 +10647,12 @@
         <v>6</v>
       </c>
       <c r="X35" s="31" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y35" s="31">
         <v>0.1148</v>
       </c>
-      <c r="AB35" s="105">
+      <c r="AB35" s="102">
         <v>44931</v>
       </c>
       <c r="AC35" s="31">
@@ -10716,12 +10668,12 @@
         <v>109.8</v>
       </c>
       <c r="AG35" s="31" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AH35" s="31">
         <v>2.1399999999999999E-2</v>
       </c>
-      <c r="AK35" s="105">
+      <c r="AK35" s="102">
         <v>44931</v>
       </c>
       <c r="AL35" s="31">
@@ -10737,36 +10689,36 @@
         <v>103.7</v>
       </c>
       <c r="AP35" s="31" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AQ35" s="31">
         <v>-0.1211</v>
       </c>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A36" s="105">
+      <c r="A36" s="102">
         <v>44930</v>
       </c>
-      <c r="B36" s="93">
+      <c r="B36" s="92">
         <v>3270.51</v>
       </c>
-      <c r="C36" s="93">
+      <c r="C36" s="92">
         <v>3272.48</v>
       </c>
-      <c r="D36" s="93">
+      <c r="D36" s="92">
         <v>3331.66</v>
       </c>
-      <c r="E36" s="93">
+      <c r="E36" s="92">
         <v>3263.36</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="G36" s="106">
+        <v>290</v>
+      </c>
+      <c r="G36" s="103">
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="H36" s="31"/>
-      <c r="I36" s="105">
+      <c r="I36" s="102">
         <v>44930</v>
       </c>
       <c r="J36" s="31">
@@ -10782,12 +10734,12 @@
         <v>1.1559999999999999</v>
       </c>
       <c r="N36" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="O36" s="106">
+        <v>351</v>
+      </c>
+      <c r="O36" s="103">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="S36" s="105">
+      <c r="S36" s="102">
         <v>44930</v>
       </c>
       <c r="T36" s="31">
@@ -10803,12 +10755,12 @@
         <v>5.57</v>
       </c>
       <c r="X36" s="31" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y36" s="31">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="AB36" s="105">
+      <c r="AB36" s="102">
         <v>44930</v>
       </c>
       <c r="AC36" s="31">
@@ -10824,12 +10776,12 @@
         <v>98.1</v>
       </c>
       <c r="AG36" s="31" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AH36" s="31">
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="AK36" s="105">
+      <c r="AK36" s="102">
         <v>44930</v>
       </c>
       <c r="AL36" s="31">
@@ -10845,36 +10797,36 @@
         <v>115.3</v>
       </c>
       <c r="AP36" s="31" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AQ36" s="31">
         <v>-2.5000000000000001E-3</v>
       </c>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A37" s="105">
+      <c r="A37" s="102">
         <v>44929</v>
       </c>
-      <c r="B37" s="93">
+      <c r="B37" s="92">
         <v>3258.9</v>
       </c>
-      <c r="C37" s="93">
+      <c r="C37" s="92">
         <v>3265.5</v>
       </c>
-      <c r="D37" s="93">
+      <c r="D37" s="92">
         <v>3275.1</v>
       </c>
-      <c r="E37" s="93">
+      <c r="E37" s="92">
         <v>3094.28</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="G37" s="106">
+        <v>291</v>
+      </c>
+      <c r="G37" s="103">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="H37" s="31"/>
-      <c r="I37" s="105">
+      <c r="I37" s="102">
         <v>44929</v>
       </c>
       <c r="J37" s="31">
@@ -10890,12 +10842,12 @@
         <v>1.137</v>
       </c>
       <c r="N37" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="O37" s="106">
+        <v>352</v>
+      </c>
+      <c r="O37" s="103">
         <v>-2.4799999999999999E-2</v>
       </c>
-      <c r="S37" s="105">
+      <c r="S37" s="102">
         <v>44929</v>
       </c>
       <c r="T37" s="31">
@@ -10911,12 +10863,12 @@
         <v>5.61</v>
       </c>
       <c r="X37" s="31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y37" s="31">
         <v>-9.6199999999999994E-2</v>
       </c>
-      <c r="AB37" s="105">
+      <c r="AB37" s="102">
         <v>44929</v>
       </c>
       <c r="AC37" s="31">
@@ -10932,12 +10884,12 @@
         <v>92.66</v>
       </c>
       <c r="AG37" s="31" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AH37" s="31">
         <v>-1.52E-2</v>
       </c>
-      <c r="AK37" s="105">
+      <c r="AK37" s="102">
         <v>44929</v>
       </c>
       <c r="AL37" s="31">
@@ -10953,36 +10905,36 @@
         <v>111.1</v>
       </c>
       <c r="AP37" s="31" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AQ37" s="31">
         <v>-2.2499999999999999E-2</v>
       </c>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A38" s="105">
+      <c r="A38" s="102">
         <v>44928</v>
       </c>
-      <c r="B38" s="93">
+      <c r="B38" s="92">
         <v>3262.63</v>
       </c>
-      <c r="C38" s="93">
+      <c r="C38" s="92">
         <v>3385.36</v>
       </c>
-      <c r="D38" s="93">
+      <c r="D38" s="92">
         <v>3397.32</v>
       </c>
-      <c r="E38" s="93">
+      <c r="E38" s="92">
         <v>3260.58</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="G38" s="106">
+        <v>292</v>
+      </c>
+      <c r="G38" s="103">
         <v>-3.0599999999999999E-2</v>
       </c>
       <c r="H38" s="31"/>
-      <c r="I38" s="105">
+      <c r="I38" s="102">
         <v>44928</v>
       </c>
       <c r="J38" s="31">
@@ -10998,12 +10950,12 @@
         <v>1.127</v>
       </c>
       <c r="N38" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="O38" s="106">
+        <v>353</v>
+      </c>
+      <c r="O38" s="103">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="S38" s="105">
+      <c r="S38" s="102">
         <v>44928</v>
       </c>
       <c r="T38" s="31">
@@ -11019,12 +10971,12 @@
         <v>5.63</v>
       </c>
       <c r="X38" s="31" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y38" s="31">
         <v>0.12520000000000001</v>
       </c>
-      <c r="AB38" s="105">
+      <c r="AB38" s="102">
         <v>44928</v>
       </c>
       <c r="AC38" s="31">
@@ -11040,12 +10992,12 @@
         <v>99.3</v>
       </c>
       <c r="AG38" s="31" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AH38" s="31">
         <v>-2.6800000000000001E-2</v>
       </c>
-      <c r="AK38" s="105">
+      <c r="AK38" s="102">
         <v>44928</v>
       </c>
       <c r="AL38" s="31">
@@ -11061,36 +11013,36 @@
         <v>119</v>
       </c>
       <c r="AP38" s="31" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AQ38" s="31">
         <v>-6.5299999999999997E-2</v>
       </c>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A39" s="105">
+      <c r="A39" s="102">
         <v>44927</v>
       </c>
-      <c r="B39" s="93">
+      <c r="B39" s="92">
         <v>3365.67</v>
       </c>
-      <c r="C39" s="93">
+      <c r="C39" s="92">
         <v>3243.99</v>
       </c>
-      <c r="D39" s="93">
+      <c r="D39" s="92">
         <v>3408.19</v>
       </c>
-      <c r="E39" s="93">
+      <c r="E39" s="92">
         <v>3212.63</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>294</v>
-      </c>
-      <c r="G39" s="106">
+        <v>293</v>
+      </c>
+      <c r="G39" s="103">
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="H39" s="31"/>
-      <c r="I39" s="105">
+      <c r="I39" s="102">
         <v>44927</v>
       </c>
       <c r="J39" s="31">
@@ -11106,12 +11058,12 @@
         <v>1.107</v>
       </c>
       <c r="N39" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="O39" s="106">
+        <v>354</v>
+      </c>
+      <c r="O39" s="103">
         <v>-2.4400000000000002E-2</v>
       </c>
-      <c r="S39" s="105">
+      <c r="S39" s="102">
         <v>44927</v>
       </c>
       <c r="T39" s="31">
@@ -11127,12 +11079,12 @@
         <v>5.53</v>
       </c>
       <c r="X39" s="31" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Y39" s="31">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="AB39" s="105">
+      <c r="AB39" s="102">
         <v>44927</v>
       </c>
       <c r="AC39" s="31">
@@ -11148,12 +11100,12 @@
         <v>101</v>
       </c>
       <c r="AG39" s="31" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AH39" s="31">
         <v>7.3300000000000004E-2</v>
       </c>
-      <c r="AK39" s="105">
+      <c r="AK39" s="102">
         <v>44927</v>
       </c>
       <c r="AL39" s="31">
@@ -11169,36 +11121,36 @@
         <v>130</v>
       </c>
       <c r="AP39" s="31" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AQ39" s="31">
         <v>2.46E-2</v>
       </c>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A40" s="105">
+      <c r="A40" s="102">
         <v>44573</v>
       </c>
-      <c r="B40" s="93">
+      <c r="B40" s="92">
         <v>3251.32</v>
       </c>
-      <c r="C40" s="93">
+      <c r="C40" s="92">
         <v>3306.49</v>
       </c>
-      <c r="D40" s="93">
+      <c r="D40" s="92">
         <v>3313.8</v>
       </c>
-      <c r="E40" s="93">
+      <c r="E40" s="92">
         <v>3225.45</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="G40" s="106">
+        <v>294</v>
+      </c>
+      <c r="G40" s="103">
         <v>-1.1900000000000001E-2</v>
       </c>
       <c r="H40" s="31"/>
-      <c r="I40" s="105">
+      <c r="I40" s="102">
         <v>44573</v>
       </c>
       <c r="J40" s="31">
@@ -11214,12 +11166,12 @@
         <v>1.1859999999999999</v>
       </c>
       <c r="N40" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="O40" s="106">
-        <v>0</v>
-      </c>
-      <c r="S40" s="105">
+        <v>355</v>
+      </c>
+      <c r="O40" s="103">
+        <v>0</v>
+      </c>
+      <c r="S40" s="102">
         <v>44573</v>
       </c>
       <c r="T40" s="31">
@@ -11235,12 +11187,12 @@
         <v>5.27</v>
       </c>
       <c r="X40" s="31" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y40" s="31">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="AB40" s="105">
+      <c r="AB40" s="102">
         <v>44573</v>
       </c>
       <c r="AC40" s="31">
@@ -11256,12 +11208,12 @@
         <v>94.15</v>
       </c>
       <c r="AG40" s="31" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AH40" s="31">
         <v>-1.0800000000000001E-2</v>
       </c>
-      <c r="AK40" s="105">
+      <c r="AK40" s="102">
         <v>44573</v>
       </c>
       <c r="AL40" s="31">
@@ -11277,36 +11229,36 @@
         <v>124.7</v>
       </c>
       <c r="AP40" s="31" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AQ40" s="31">
         <v>-0.24640000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A41" s="105">
+      <c r="A41" s="102">
         <v>44572</v>
       </c>
-      <c r="B41" s="93">
+      <c r="B41" s="92">
         <v>3290.49</v>
       </c>
-      <c r="C41" s="93">
+      <c r="C41" s="92">
         <v>3107</v>
       </c>
-      <c r="D41" s="93">
+      <c r="D41" s="92">
         <v>3308.3</v>
       </c>
-      <c r="E41" s="93">
+      <c r="E41" s="92">
         <v>3091.18</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="G41" s="106">
+        <v>295</v>
+      </c>
+      <c r="G41" s="103">
         <v>6.3799999999999996E-2</v>
       </c>
       <c r="H41" s="31"/>
-      <c r="I41" s="105">
+      <c r="I41" s="102">
         <v>44572</v>
       </c>
       <c r="J41" s="31">
@@ -11322,12 +11274,12 @@
         <v>1.1859999999999999</v>
       </c>
       <c r="N41" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="O41" s="106">
+        <v>356</v>
+      </c>
+      <c r="O41" s="103">
         <v>-3.15E-2</v>
       </c>
-      <c r="S41" s="105">
+      <c r="S41" s="102">
         <v>44572</v>
       </c>
       <c r="T41" s="31">
@@ -11343,7 +11295,7 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="X41" s="31" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y41" s="31">
         <v>0.1734</v>
@@ -11364,7 +11316,7 @@
         <v>89.55</v>
       </c>
       <c r="AG41" s="31" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AH41" s="31">
         <v>-2.9499999999999998E-2</v>
@@ -11385,36 +11337,36 @@
         <v>166.1</v>
       </c>
       <c r="AP41" s="31" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AQ41" s="31">
         <v>1.95E-2</v>
       </c>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A42" s="105">
+      <c r="A42" s="102">
         <v>44571</v>
       </c>
-      <c r="B42" s="93">
+      <c r="B42" s="92">
         <v>3093.11</v>
       </c>
-      <c r="C42" s="93">
+      <c r="C42" s="92">
         <v>3113</v>
       </c>
-      <c r="D42" s="93">
+      <c r="D42" s="92">
         <v>3168.4</v>
       </c>
-      <c r="E42" s="93">
+      <c r="E42" s="92">
         <v>2968.87</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="G42" s="106">
+        <v>264</v>
+      </c>
+      <c r="G42" s="103">
         <v>-1.1900000000000001E-2</v>
       </c>
       <c r="H42" s="31"/>
-      <c r="I42" s="105">
+      <c r="I42" s="102">
         <v>44571</v>
       </c>
       <c r="J42" s="31">
@@ -11430,12 +11382,12 @@
         <v>1.2050000000000001</v>
       </c>
       <c r="N42" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="O42" s="106">
+        <v>357</v>
+      </c>
+      <c r="O42" s="103">
         <v>-3.7900000000000003E-2</v>
       </c>
-      <c r="S42" s="105">
+      <c r="S42" s="102">
         <v>44571</v>
       </c>
       <c r="T42" s="31">
@@ -11451,12 +11403,12 @@
         <v>4.26</v>
       </c>
       <c r="X42" s="31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Y42" s="31">
         <v>-3.3099999999999997E-2</v>
       </c>
-      <c r="AB42" s="105">
+      <c r="AB42" s="102">
         <v>44571</v>
       </c>
       <c r="AC42" s="31">
@@ -11472,12 +11424,12 @@
         <v>100</v>
       </c>
       <c r="AG42" s="31" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AH42" s="31">
         <v>0</v>
       </c>
-      <c r="AK42" s="105">
+      <c r="AK42" s="102">
         <v>44571</v>
       </c>
       <c r="AL42" s="31">
@@ -11493,36 +11445,36 @@
         <v>156.5</v>
       </c>
       <c r="AP42" s="31" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AQ42" s="31">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A43" s="105">
+      <c r="A43" s="102">
         <v>44570</v>
       </c>
-      <c r="B43" s="93">
+      <c r="B43" s="92">
         <v>3130.24</v>
       </c>
-      <c r="C43" s="93">
+      <c r="C43" s="92">
         <v>3211.56</v>
       </c>
-      <c r="D43" s="93">
+      <c r="D43" s="92">
         <v>3297.59</v>
       </c>
-      <c r="E43" s="93">
+      <c r="E43" s="92">
         <v>3098.24</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="G43" s="106">
+        <v>296</v>
+      </c>
+      <c r="G43" s="103">
         <v>-2.8400000000000002E-2</v>
       </c>
       <c r="H43" s="31"/>
-      <c r="I43" s="105">
+      <c r="I43" s="102">
         <v>44570</v>
       </c>
       <c r="J43" s="31">
@@ -11538,12 +11490,12 @@
         <v>1.264</v>
       </c>
       <c r="N43" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="O43" s="106">
+        <v>358</v>
+      </c>
+      <c r="O43" s="103">
         <v>-6.3799999999999996E-2</v>
       </c>
-      <c r="S43" s="105">
+      <c r="S43" s="102">
         <v>44570</v>
       </c>
       <c r="T43" s="31">
@@ -11559,12 +11511,12 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="X43" s="31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y43" s="31">
         <v>-0.1138</v>
       </c>
-      <c r="AB43" s="105">
+      <c r="AB43" s="102">
         <v>44570</v>
       </c>
       <c r="AC43" s="31">
@@ -11580,12 +11532,12 @@
         <v>103.1</v>
       </c>
       <c r="AG43" s="31" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AH43" s="31">
         <v>-8.5999999999999993E-2</v>
       </c>
-      <c r="AK43" s="105">
+      <c r="AK43" s="102">
         <v>44570</v>
       </c>
       <c r="AL43" s="31">
@@ -11601,36 +11553,36 @@
         <v>156.5</v>
       </c>
       <c r="AP43" s="31" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AQ43" s="31">
         <v>-3.8199999999999998E-2</v>
       </c>
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A44" s="105">
+      <c r="A44" s="102">
         <v>44569</v>
       </c>
-      <c r="B44" s="93">
+      <c r="B44" s="92">
         <v>3221.67</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="92">
         <v>3238.18</v>
       </c>
-      <c r="D44" s="93">
+      <c r="D44" s="92">
         <v>3307.29</v>
       </c>
-      <c r="E44" s="93">
+      <c r="E44" s="92">
         <v>3205.58</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="G44" s="106">
+        <v>297</v>
+      </c>
+      <c r="G44" s="103">
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="H44" s="31"/>
-      <c r="I44" s="105">
+      <c r="I44" s="102">
         <v>44569</v>
       </c>
       <c r="J44" s="31">
@@ -11646,12 +11598,12 @@
         <v>1.3720000000000001</v>
       </c>
       <c r="N44" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="O44" s="106">
+        <v>359</v>
+      </c>
+      <c r="O44" s="103">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="S44" s="105">
+      <c r="S44" s="102">
         <v>44569</v>
       </c>
       <c r="T44" s="31">
@@ -11667,12 +11619,12 @@
         <v>5.14</v>
       </c>
       <c r="X44" s="31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y44" s="31">
         <v>-0.1051</v>
       </c>
-      <c r="AB44" s="105">
+      <c r="AB44" s="102">
         <v>44569</v>
       </c>
       <c r="AC44" s="31">
@@ -11688,12 +11640,12 @@
         <v>105.3</v>
       </c>
       <c r="AG44" s="31" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AH44" s="31">
         <v>-0.13780000000000001</v>
       </c>
-      <c r="AK44" s="105">
+      <c r="AK44" s="102">
         <v>44569</v>
       </c>
       <c r="AL44" s="31">
@@ -11709,36 +11661,36 @@
         <v>167.3</v>
       </c>
       <c r="AP44" s="31" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AQ44" s="31">
         <v>-4.5699999999999998E-2</v>
       </c>
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A45" s="105">
+      <c r="A45" s="102">
         <v>44568</v>
       </c>
-      <c r="B45" s="93">
+      <c r="B45" s="92">
         <v>3211.56</v>
       </c>
-      <c r="C45" s="93">
+      <c r="C45" s="92">
         <v>3104.25</v>
       </c>
-      <c r="D45" s="93">
+      <c r="D45" s="92">
         <v>3244.29</v>
       </c>
-      <c r="E45" s="93">
+      <c r="E45" s="92">
         <v>3088.25</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="G45" s="106">
+        <v>298</v>
+      </c>
+      <c r="G45" s="103">
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="H45" s="31"/>
-      <c r="I45" s="105">
+      <c r="I45" s="102">
         <v>44568</v>
       </c>
       <c r="J45" s="31">
@@ -11754,12 +11706,12 @@
         <v>1.33</v>
       </c>
       <c r="N45" s="31" t="s">
-        <v>361</v>
-      </c>
-      <c r="O45" s="106">
+        <v>360</v>
+      </c>
+      <c r="O45" s="103">
         <v>1.43E-2</v>
       </c>
-      <c r="S45" s="105">
+      <c r="S45" s="102">
         <v>44568</v>
       </c>
       <c r="T45" s="31">
@@ -11775,12 +11727,12 @@
         <v>5.29</v>
       </c>
       <c r="X45" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y45" s="31">
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="AB45" s="105">
+      <c r="AB45" s="102">
         <v>44568</v>
       </c>
       <c r="AC45" s="31">
@@ -11796,12 +11748,12 @@
         <v>122.2</v>
       </c>
       <c r="AG45" s="31" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AH45" s="31">
         <v>4.7100000000000003E-2</v>
       </c>
-      <c r="AK45" s="105">
+      <c r="AK45" s="102">
         <v>44568</v>
       </c>
       <c r="AL45" s="31">
@@ -11817,36 +11769,36 @@
         <v>167.1</v>
       </c>
       <c r="AP45" s="31" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AQ45" s="31">
         <v>-5.45E-2</v>
       </c>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A46" s="105">
+      <c r="A46" s="102">
         <v>44567</v>
       </c>
-      <c r="B46" s="93">
+      <c r="B46" s="92">
         <v>3102.21</v>
       </c>
-      <c r="C46" s="93">
+      <c r="C46" s="92">
         <v>3242.92</v>
       </c>
-      <c r="D46" s="93">
+      <c r="D46" s="92">
         <v>3253.15</v>
       </c>
-      <c r="E46" s="93">
+      <c r="E46" s="92">
         <v>3072.34</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="G46" s="106">
+        <v>299</v>
+      </c>
+      <c r="G46" s="103">
         <v>-4.0300000000000002E-2</v>
       </c>
       <c r="H46" s="31"/>
-      <c r="I46" s="105">
+      <c r="I46" s="102">
         <v>44567</v>
       </c>
       <c r="J46" s="31">
@@ -11862,12 +11814,12 @@
         <v>1.31</v>
       </c>
       <c r="N46" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="O46" s="106">
+        <v>361</v>
+      </c>
+      <c r="O46" s="103">
         <v>-2.7799999999999998E-2</v>
       </c>
-      <c r="S46" s="105">
+      <c r="S46" s="102">
         <v>44567</v>
       </c>
       <c r="T46" s="31">
@@ -11883,12 +11835,12 @@
         <v>5.62</v>
       </c>
       <c r="X46" s="31" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Y46" s="31">
         <v>-0.24299999999999999</v>
       </c>
-      <c r="AB46" s="105">
+      <c r="AB46" s="102">
         <v>44567</v>
       </c>
       <c r="AC46" s="31">
@@ -11904,12 +11856,12 @@
         <v>121.4</v>
       </c>
       <c r="AG46" s="31" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AH46" s="31">
         <v>-6.59E-2</v>
       </c>
-      <c r="AK46" s="105">
+      <c r="AK46" s="102">
         <v>44567</v>
       </c>
       <c r="AL46" s="31">
@@ -11925,36 +11877,36 @@
         <v>189.9</v>
       </c>
       <c r="AP46" s="31" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AQ46" s="31">
         <v>-0.2681</v>
       </c>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A47" s="105">
+      <c r="A47" s="102">
         <v>44566</v>
       </c>
-      <c r="B47" s="93">
+      <c r="B47" s="92">
         <v>3232.49</v>
       </c>
-      <c r="C47" s="93">
+      <c r="C47" s="92">
         <v>3365.43</v>
       </c>
-      <c r="D47" s="93">
+      <c r="D47" s="92">
         <v>3373.15</v>
       </c>
-      <c r="E47" s="93">
+      <c r="E47" s="92">
         <v>3165.18</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="G47" s="106">
+        <v>300</v>
+      </c>
+      <c r="G47" s="103">
         <v>-3.7100000000000001E-2</v>
       </c>
       <c r="H47" s="31"/>
-      <c r="I47" s="105">
+      <c r="I47" s="102">
         <v>44566</v>
       </c>
       <c r="J47" s="31">
@@ -11970,12 +11922,12 @@
         <v>1.34</v>
       </c>
       <c r="N47" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="O47" s="106">
+        <v>362</v>
+      </c>
+      <c r="O47" s="103">
         <v>-2.0400000000000001E-2</v>
       </c>
-      <c r="S47" s="105">
+      <c r="S47" s="102">
         <v>44566</v>
       </c>
       <c r="T47" s="31">
@@ -11991,12 +11943,12 @@
         <v>7.26</v>
       </c>
       <c r="X47" s="31" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y47" s="31">
         <v>-5.04E-2</v>
       </c>
-      <c r="AB47" s="105">
+      <c r="AB47" s="102">
         <v>44566</v>
       </c>
       <c r="AC47" s="31">
@@ -12012,12 +11964,12 @@
         <v>101.95</v>
       </c>
       <c r="AG47" s="31" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AH47" s="31">
         <v>0.21010000000000001</v>
       </c>
-      <c r="AK47" s="105">
+      <c r="AK47" s="102">
         <v>44566</v>
       </c>
       <c r="AL47" s="31">
@@ -12033,36 +11985,36 @@
         <v>237.12</v>
       </c>
       <c r="AP47" s="31" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AQ47" s="31">
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A48" s="105">
+      <c r="A48" s="102">
         <v>44565</v>
       </c>
-      <c r="B48" s="93">
+      <c r="B48" s="92">
         <v>3356.9</v>
       </c>
-      <c r="C48" s="93">
+      <c r="C48" s="92">
         <v>3403.93</v>
       </c>
-      <c r="D48" s="93">
+      <c r="D48" s="92">
         <v>3445.9</v>
       </c>
-      <c r="E48" s="93">
+      <c r="E48" s="92">
         <v>3303.07</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="G48" s="106">
+        <v>301</v>
+      </c>
+      <c r="G48" s="103">
         <v>-1.5100000000000001E-2</v>
       </c>
       <c r="H48" s="31"/>
-      <c r="I48" s="105">
+      <c r="I48" s="102">
         <v>44565</v>
       </c>
       <c r="J48" s="31">
@@ -12078,12 +12030,12 @@
         <v>1.407</v>
       </c>
       <c r="N48" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="O48" s="106">
+        <v>363</v>
+      </c>
+      <c r="O48" s="103">
         <v>-1.34E-2</v>
       </c>
-      <c r="S48" s="105">
+      <c r="S48" s="102">
         <v>44565</v>
       </c>
       <c r="T48" s="31">
@@ -12099,12 +12051,12 @@
         <v>6.81</v>
       </c>
       <c r="X48" s="31" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Y48" s="31">
         <v>0.12479999999999999</v>
       </c>
-      <c r="AB48" s="105">
+      <c r="AB48" s="102">
         <v>44565</v>
       </c>
       <c r="AC48" s="31">
@@ -12120,12 +12072,12 @@
         <v>100.8</v>
       </c>
       <c r="AG48" s="31" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AH48" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="AK48" s="105">
+      <c r="AK48" s="102">
         <v>44565</v>
       </c>
       <c r="AL48" s="31">
@@ -12141,36 +12093,36 @@
         <v>223</v>
       </c>
       <c r="AP48" s="31" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AQ48" s="31">
         <v>6.7799999999999999E-2</v>
       </c>
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A49" s="105">
+      <c r="A49" s="102">
         <v>44564</v>
       </c>
-      <c r="B49" s="93">
+      <c r="B49" s="92">
         <v>3408.52</v>
       </c>
-      <c r="C49" s="93">
+      <c r="C49" s="92">
         <v>3262.49</v>
       </c>
-      <c r="D49" s="93">
+      <c r="D49" s="92">
         <v>3456.09</v>
       </c>
-      <c r="E49" s="93">
+      <c r="E49" s="92">
         <v>3128.06</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="G49" s="106">
+        <v>302</v>
+      </c>
+      <c r="G49" s="103">
         <v>5.1299999999999998E-2</v>
       </c>
       <c r="H49" s="31"/>
-      <c r="I49" s="105">
+      <c r="I49" s="102">
         <v>44564</v>
       </c>
       <c r="J49" s="31">
@@ -12186,12 +12138,12 @@
         <v>1.2909999999999999</v>
       </c>
       <c r="N49" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="O49" s="106">
+        <v>364</v>
+      </c>
+      <c r="O49" s="103">
         <v>5.67E-2</v>
       </c>
-      <c r="S49" s="105">
+      <c r="S49" s="102">
         <v>44564</v>
       </c>
       <c r="T49" s="31">
@@ -12207,12 +12159,12 @@
         <v>6.67</v>
       </c>
       <c r="X49" s="31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Y49" s="31">
         <v>-2.4899999999999999E-2</v>
       </c>
-      <c r="AB49" s="105">
+      <c r="AB49" s="102">
         <v>44564</v>
       </c>
       <c r="AC49" s="31">
@@ -12228,12 +12180,12 @@
         <v>83.75</v>
       </c>
       <c r="AG49" s="31" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AH49" s="31">
         <v>0.1208</v>
       </c>
-      <c r="AK49" s="105">
+      <c r="AK49" s="102">
         <v>44564</v>
       </c>
       <c r="AL49" s="31">
@@ -12249,36 +12201,36 @@
         <v>183.7</v>
       </c>
       <c r="AP49" s="31" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AQ49" s="31">
         <v>-2.4299999999999999E-2</v>
       </c>
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A50" s="105">
+      <c r="A50" s="102">
         <v>44563</v>
       </c>
-      <c r="B50" s="93">
+      <c r="B50" s="92">
         <v>3242.24</v>
       </c>
-      <c r="C50" s="93">
+      <c r="C50" s="92">
         <v>3302.23</v>
       </c>
-      <c r="D50" s="93">
+      <c r="D50" s="92">
         <v>3466.23</v>
       </c>
-      <c r="E50" s="93">
+      <c r="E50" s="92">
         <v>3214.93</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="G50" s="106">
+        <v>303</v>
+      </c>
+      <c r="G50" s="103">
         <v>-2.3E-3</v>
       </c>
       <c r="H50" s="31"/>
-      <c r="I50" s="105">
+      <c r="I50" s="102">
         <v>44563</v>
       </c>
       <c r="J50" s="31">
@@ -12294,12 +12246,12 @@
         <v>1.32</v>
       </c>
       <c r="N50" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="O50" s="106">
+        <v>365</v>
+      </c>
+      <c r="O50" s="103">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="S50" s="105">
+      <c r="S50" s="102">
         <v>44563</v>
       </c>
       <c r="T50" s="31">
@@ -12315,12 +12267,12 @@
         <v>6.61</v>
       </c>
       <c r="X50" s="31" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y50" s="31">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="AB50" s="105">
+      <c r="AB50" s="102">
         <v>44563</v>
       </c>
       <c r="AC50" s="31">
@@ -12336,12 +12288,12 @@
         <v>97.6</v>
       </c>
       <c r="AG50" s="31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH50" s="31">
         <v>-8.8999999999999999E-3</v>
       </c>
-      <c r="AK50" s="105">
+      <c r="AK50" s="102">
         <v>44563</v>
       </c>
       <c r="AL50" s="31">
@@ -12357,36 +12309,36 @@
         <v>230.8</v>
       </c>
       <c r="AP50" s="31" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AQ50" s="31">
         <v>-4.48E-2</v>
       </c>
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A51" s="105">
+      <c r="A51" s="102">
         <v>44562</v>
       </c>
-      <c r="B51" s="93">
+      <c r="B51" s="92">
         <v>3249.59</v>
       </c>
-      <c r="C51" s="93">
+      <c r="C51" s="92">
         <v>3130.48</v>
       </c>
-      <c r="D51" s="93">
+      <c r="D51" s="92">
         <v>3299.64</v>
       </c>
-      <c r="E51" s="93">
+      <c r="E51" s="92">
         <v>3127.6</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="G51" s="106">
+        <v>304</v>
+      </c>
+      <c r="G51" s="103">
         <v>4.0300000000000002E-2</v>
       </c>
       <c r="H51" s="31"/>
-      <c r="I51" s="105">
+      <c r="I51" s="102">
         <v>44562</v>
       </c>
       <c r="J51" s="31">
@@ -12402,12 +12354,12 @@
         <v>1.2909999999999999</v>
       </c>
       <c r="N51" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="O51" s="106">
+        <v>366</v>
+      </c>
+      <c r="O51" s="103">
         <v>-2.86E-2</v>
       </c>
-      <c r="S51" s="105">
+      <c r="S51" s="102">
         <v>44562</v>
       </c>
       <c r="T51" s="31">
@@ -12423,12 +12375,12 @@
         <v>6.34</v>
       </c>
       <c r="X51" s="31" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y51" s="31">
         <v>-4.7399999999999998E-2</v>
       </c>
-      <c r="AB51" s="105">
+      <c r="AB51" s="102">
         <v>44562</v>
       </c>
       <c r="AC51" s="31">
@@ -12444,12 +12396,12 @@
         <v>97</v>
       </c>
       <c r="AG51" s="31" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AH51" s="31">
         <v>-1.0800000000000001E-2</v>
       </c>
-      <c r="AK51" s="105">
+      <c r="AK51" s="102">
         <v>44562</v>
       </c>
       <c r="AL51" s="31">
@@ -12465,36 +12417,36 @@
         <v>239.8</v>
       </c>
       <c r="AP51" s="31" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AQ51" s="31">
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A52" s="105">
+      <c r="A52" s="102">
         <v>44208</v>
       </c>
-      <c r="B52" s="93">
+      <c r="B52" s="92">
         <v>3123.68</v>
       </c>
-      <c r="C52" s="93">
+      <c r="C52" s="92">
         <v>3052.4</v>
       </c>
-      <c r="D52" s="93">
+      <c r="D52" s="92">
         <v>3161.95</v>
       </c>
-      <c r="E52" s="93">
+      <c r="E52" s="92">
         <v>3045.13</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="G52" s="106">
+        <v>305</v>
+      </c>
+      <c r="G52" s="103">
         <v>2.7099999999999999E-2</v>
       </c>
       <c r="H52" s="31"/>
-      <c r="I52" s="105">
+      <c r="I52" s="102">
         <v>44208</v>
       </c>
       <c r="J52" s="31">
@@ -12510,12 +12462,12 @@
         <v>1.31</v>
       </c>
       <c r="N52" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="O52" s="106">
+        <v>367</v>
+      </c>
+      <c r="O52" s="103">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="S52" s="105">
+      <c r="S52" s="102">
         <v>44208</v>
       </c>
       <c r="T52" s="31">
@@ -12531,12 +12483,12 @@
         <v>6.1</v>
       </c>
       <c r="X52" s="31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y52" s="31">
         <v>0.14599999999999999</v>
       </c>
-      <c r="AB52" s="105">
+      <c r="AB52" s="102">
         <v>44208</v>
       </c>
       <c r="AC52" s="31">
@@ -12552,12 +12504,12 @@
         <v>90.5</v>
       </c>
       <c r="AG52" s="31" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AH52" s="31">
         <v>9.8900000000000002E-2</v>
       </c>
-      <c r="AK52" s="105">
+      <c r="AK52" s="102">
         <v>44208</v>
       </c>
       <c r="AL52" s="31">
@@ -12573,36 +12525,36 @@
         <v>214</v>
       </c>
       <c r="AP52" s="31" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AQ52" s="31">
         <v>0.2041</v>
       </c>
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A53" s="105">
+      <c r="A53" s="102">
         <v>44207</v>
       </c>
-      <c r="B53" s="93">
+      <c r="B53" s="92">
         <v>3041.29</v>
       </c>
-      <c r="C53" s="93">
+      <c r="C53" s="92">
         <v>3226.23</v>
       </c>
-      <c r="D53" s="93">
+      <c r="D53" s="92">
         <v>3273.54</v>
       </c>
-      <c r="E53" s="93">
+      <c r="E53" s="92">
         <v>3041.29</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="G53" s="106">
+        <v>306</v>
+      </c>
+      <c r="G53" s="103">
         <v>-4.9099999999999998E-2</v>
       </c>
       <c r="H53" s="31"/>
-      <c r="I53" s="105">
+      <c r="I53" s="102">
         <v>44207</v>
       </c>
       <c r="J53" s="31">
@@ -12618,12 +12570,12 @@
         <v>1.33</v>
       </c>
       <c r="N53" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="O53" s="106">
+        <v>368</v>
+      </c>
+      <c r="O53" s="103">
         <v>-0.12180000000000001</v>
       </c>
-      <c r="S53" s="105">
+      <c r="S53" s="102">
         <v>44207</v>
       </c>
       <c r="T53" s="31">
@@ -12639,12 +12591,12 @@
         <v>6.11</v>
       </c>
       <c r="X53" s="31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y53" s="31">
         <v>-0.1226</v>
       </c>
-      <c r="AB53" s="105">
+      <c r="AB53" s="102">
         <v>44207</v>
       </c>
       <c r="AC53" s="31">
@@ -12660,12 +12612,12 @@
         <v>92.7</v>
       </c>
       <c r="AG53" s="31" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AH53" s="31">
         <v>-7.7399999999999997E-2</v>
       </c>
-      <c r="AK53" s="105">
+      <c r="AK53" s="102">
         <v>44207</v>
       </c>
       <c r="AL53" s="31">
@@ -12681,36 +12633,36 @@
         <v>207.2</v>
       </c>
       <c r="AP53" s="31" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AQ53" s="31">
         <v>-6.5600000000000006E-2</v>
       </c>
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A54" s="105">
+      <c r="A54" s="102">
         <v>44206</v>
       </c>
-      <c r="B54" s="93">
+      <c r="B54" s="92">
         <v>3198.17</v>
       </c>
-      <c r="C54" s="93">
+      <c r="C54" s="92">
         <v>3072.54</v>
       </c>
-      <c r="D54" s="93">
+      <c r="D54" s="92">
         <v>3228.05</v>
       </c>
-      <c r="E54" s="93">
+      <c r="E54" s="92">
         <v>3044.73</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="G54" s="106">
+        <v>307</v>
+      </c>
+      <c r="G54" s="103">
         <v>3.61E-2</v>
       </c>
       <c r="H54" s="31"/>
-      <c r="I54" s="105">
+      <c r="I54" s="102">
         <v>44206</v>
       </c>
       <c r="J54" s="31">
@@ -12726,12 +12678,12 @@
         <v>1.456</v>
       </c>
       <c r="N54" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="O54" s="106">
+        <v>369</v>
+      </c>
+      <c r="O54" s="103">
         <v>3.3099999999999997E-2</v>
       </c>
-      <c r="S54" s="105">
+      <c r="S54" s="102">
         <v>44206</v>
       </c>
       <c r="T54" s="31">
@@ -12747,7 +12699,7 @@
         <v>7.11</v>
       </c>
       <c r="X54" s="31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y54" s="31">
         <v>-0.17530000000000001</v>
@@ -12768,7 +12720,7 @@
         <v>84</v>
       </c>
       <c r="AG54" s="31" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AH54" s="31">
         <v>0.13320000000000001</v>
@@ -12789,36 +12741,36 @@
         <v>215.87</v>
       </c>
       <c r="AP54" s="31" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AQ54" s="31">
         <v>-5.2200000000000003E-2</v>
       </c>
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A55" s="105">
+      <c r="A55" s="102">
         <v>44205</v>
       </c>
-      <c r="B55" s="93">
+      <c r="B55" s="92">
         <v>3086.7</v>
       </c>
-      <c r="C55" s="93">
+      <c r="C55" s="92">
         <v>3055.71</v>
       </c>
-      <c r="D55" s="93">
+      <c r="D55" s="92">
         <v>3108.53</v>
       </c>
-      <c r="E55" s="93">
+      <c r="E55" s="92">
         <v>3037.79</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="G55" s="106">
+        <v>308</v>
+      </c>
+      <c r="G55" s="103">
         <v>1.04E-2</v>
       </c>
       <c r="H55" s="31"/>
-      <c r="I55" s="105">
+      <c r="I55" s="102">
         <v>44205</v>
       </c>
       <c r="J55" s="31">
@@ -12834,12 +12786,12 @@
         <v>1.446</v>
       </c>
       <c r="N55" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="O55" s="106">
+        <v>370</v>
+      </c>
+      <c r="O55" s="103">
         <v>-6.7900000000000002E-2</v>
       </c>
-      <c r="S55" s="105">
+      <c r="S55" s="102">
         <v>44205</v>
       </c>
       <c r="T55" s="31">
@@ -12855,12 +12807,12 @@
         <v>8.16</v>
       </c>
       <c r="X55" s="31" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y55" s="31">
         <v>-1.11E-2</v>
       </c>
-      <c r="AB55" s="105">
+      <c r="AB55" s="102">
         <v>44205</v>
       </c>
       <c r="AC55" s="31">
@@ -12876,12 +12828,12 @@
         <v>82.15</v>
       </c>
       <c r="AG55" s="31" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AH55" s="31">
         <v>-1.44E-2</v>
       </c>
-      <c r="AK55" s="105">
+      <c r="AK55" s="102">
         <v>44205</v>
       </c>
       <c r="AL55" s="31">
@@ -12897,36 +12849,36 @@
         <v>212.2</v>
       </c>
       <c r="AP55" s="31" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AQ55" s="31">
         <v>-6.0699999999999997E-2</v>
       </c>
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A56" s="105">
+      <c r="A56" s="102">
         <v>44204</v>
       </c>
-      <c r="B56" s="93">
+      <c r="B56" s="92">
         <v>3055.05</v>
       </c>
-      <c r="C56" s="93">
+      <c r="C56" s="92">
         <v>3176.42</v>
       </c>
-      <c r="D56" s="93">
+      <c r="D56" s="92">
         <v>3207.99</v>
       </c>
-      <c r="E56" s="93">
+      <c r="E56" s="92">
         <v>3050.24</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="G56" s="106">
+        <v>309</v>
+      </c>
+      <c r="G56" s="103">
         <v>-3.5299999999999998E-2</v>
       </c>
       <c r="H56" s="31"/>
-      <c r="I56" s="105">
+      <c r="I56" s="102">
         <v>44204</v>
       </c>
       <c r="J56" s="31">
@@ -12942,12 +12894,12 @@
         <v>1.5049999999999999</v>
       </c>
       <c r="N56" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="O56" s="106">
+        <v>371</v>
+      </c>
+      <c r="O56" s="103">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="S56" s="105">
+      <c r="S56" s="102">
         <v>44204</v>
       </c>
       <c r="T56" s="31">
@@ -12963,12 +12915,12 @@
         <v>8.74</v>
       </c>
       <c r="X56" s="31" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Y56" s="31">
         <v>-3.4299999999999997E-2</v>
       </c>
-      <c r="AB56" s="105">
+      <c r="AB56" s="102">
         <v>44204</v>
       </c>
       <c r="AC56" s="31">
@@ -12984,12 +12936,12 @@
         <v>82.2</v>
       </c>
       <c r="AG56" s="31" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH56" s="31">
         <v>8.8700000000000001E-2</v>
       </c>
-      <c r="AK56" s="105">
+      <c r="AK56" s="102">
         <v>44204</v>
       </c>
       <c r="AL56" s="31">
@@ -13005,36 +12957,36 @@
         <v>251.8</v>
       </c>
       <c r="AP56" s="31" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AQ56" s="31">
         <v>-5.5899999999999998E-2</v>
       </c>
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A57" s="105">
+      <c r="A57" s="102">
         <v>44203</v>
       </c>
-      <c r="B57" s="93">
+      <c r="B57" s="92">
         <v>3166.94</v>
       </c>
-      <c r="C57" s="93">
+      <c r="C57" s="92">
         <v>3140.25</v>
       </c>
-      <c r="D57" s="93">
+      <c r="D57" s="92">
         <v>3195.25</v>
       </c>
-      <c r="E57" s="93">
+      <c r="E57" s="92">
         <v>3095.35</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="G57" s="106">
+        <v>310</v>
+      </c>
+      <c r="G57" s="103">
         <v>1.17E-2</v>
       </c>
       <c r="H57" s="31"/>
-      <c r="I57" s="105">
+      <c r="I57" s="102">
         <v>44203</v>
       </c>
       <c r="J57" s="31">
@@ -13050,12 +13002,12 @@
         <v>1.5049999999999999</v>
       </c>
       <c r="N57" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="O57" s="106">
+        <v>372</v>
+      </c>
+      <c r="O57" s="103">
         <v>-4.2700000000000002E-2</v>
       </c>
-      <c r="S57" s="105">
+      <c r="S57" s="102">
         <v>44203</v>
       </c>
       <c r="T57" s="31">
@@ -13071,12 +13023,12 @@
         <v>8.7899999999999991</v>
       </c>
       <c r="X57" s="31" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Y57" s="31">
         <v>-1.6899999999999998E-2</v>
       </c>
-      <c r="AB57" s="105">
+      <c r="AB57" s="102">
         <v>44203</v>
       </c>
       <c r="AC57" s="31">
@@ -13092,12 +13044,12 @@
         <v>72.400000000000006</v>
       </c>
       <c r="AG57" s="31" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AH57" s="31">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="AK57" s="105">
+      <c r="AK57" s="102">
         <v>44203</v>
       </c>
       <c r="AL57" s="31">
@@ -13113,36 +13065,36 @@
         <v>226.8</v>
       </c>
       <c r="AP57" s="31" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AQ57" s="31">
         <v>2.0299999999999999E-2</v>
       </c>
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A58" s="105">
+      <c r="A58" s="102">
         <v>44202</v>
       </c>
-      <c r="B58" s="93">
+      <c r="B58" s="92">
         <v>3130.46</v>
       </c>
-      <c r="C58" s="93">
+      <c r="C58" s="92">
         <v>3176.71</v>
       </c>
-      <c r="D58" s="93">
+      <c r="D58" s="92">
         <v>3188</v>
       </c>
-      <c r="E58" s="93">
+      <c r="E58" s="92">
         <v>3089.49</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="G58" s="106">
+        <v>311</v>
+      </c>
+      <c r="G58" s="103">
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="H58" s="31"/>
-      <c r="I58" s="105">
+      <c r="I58" s="102">
         <v>44202</v>
       </c>
       <c r="J58" s="31">
@@ -13158,12 +13110,12 @@
         <v>1.5629999999999999</v>
       </c>
       <c r="N58" s="31" t="s">
-        <v>374</v>
-      </c>
-      <c r="O58" s="106">
+        <v>373</v>
+      </c>
+      <c r="O58" s="103">
         <v>-3.5299999999999998E-2</v>
       </c>
-      <c r="S58" s="105">
+      <c r="S58" s="102">
         <v>44202</v>
       </c>
       <c r="T58" s="31">
@@ -13179,12 +13131,12 @@
         <v>8.42</v>
       </c>
       <c r="X58" s="31" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Y58" s="31">
         <v>-2.7699999999999999E-2</v>
       </c>
-      <c r="AB58" s="105">
+      <c r="AB58" s="102">
         <v>44202</v>
       </c>
       <c r="AC58" s="31">
@@ -13200,12 +13152,12 @@
         <v>77.95</v>
       </c>
       <c r="AG58" s="31" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AH58" s="31">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="AK58" s="105">
+      <c r="AK58" s="102">
         <v>44202</v>
       </c>
       <c r="AL58" s="31">
@@ -13221,36 +13173,36 @@
         <v>258.2</v>
       </c>
       <c r="AP58" s="31" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AQ58" s="31">
         <v>-0.11840000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A59" s="105">
+      <c r="A59" s="102">
         <v>44201</v>
       </c>
-      <c r="B59" s="93">
+      <c r="B59" s="92">
         <v>3164.28</v>
       </c>
-      <c r="C59" s="93">
+      <c r="C59" s="92">
         <v>3221.79</v>
       </c>
-      <c r="D59" s="93">
+      <c r="D59" s="92">
         <v>3221.94</v>
       </c>
-      <c r="E59" s="93">
+      <c r="E59" s="92">
         <v>3023.95</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="G59" s="106">
+        <v>312</v>
+      </c>
+      <c r="G59" s="103">
         <v>-1.6799999999999999E-2</v>
       </c>
       <c r="H59" s="31"/>
-      <c r="I59" s="105">
+      <c r="I59" s="102">
         <v>44201</v>
       </c>
       <c r="J59" s="31">
@@ -13266,12 +13218,12 @@
         <v>1.4950000000000001</v>
       </c>
       <c r="N59" s="31" t="s">
-        <v>375</v>
-      </c>
-      <c r="O59" s="106">
+        <v>374</v>
+      </c>
+      <c r="O59" s="103">
         <v>-1.1599999999999999E-2</v>
       </c>
-      <c r="S59" s="105">
+      <c r="S59" s="102">
         <v>44201</v>
       </c>
       <c r="T59" s="31">
@@ -13287,12 +13239,12 @@
         <v>9.44</v>
       </c>
       <c r="X59" s="31" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Y59" s="31">
         <v>-3.3700000000000001E-2</v>
       </c>
-      <c r="AB59" s="105">
+      <c r="AB59" s="102">
         <v>44201</v>
       </c>
       <c r="AC59" s="31">
@@ -13308,12 +13260,12 @@
         <v>72.099999999999994</v>
       </c>
       <c r="AG59" s="31" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AH59" s="31">
         <v>9.69E-2</v>
       </c>
-      <c r="AK59" s="105">
+      <c r="AK59" s="102">
         <v>44201</v>
       </c>
       <c r="AL59" s="31">
@@ -13329,36 +13281,36 @@
         <v>276.39999999999998</v>
       </c>
       <c r="AP59" s="31" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AQ59" s="31">
         <v>9.2999999999999992E-3</v>
       </c>
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A60" s="105">
+      <c r="A60" s="102">
         <v>44200</v>
       </c>
-      <c r="B60" s="93">
+      <c r="B60" s="92">
         <v>3218.27</v>
       </c>
-      <c r="C60" s="93">
+      <c r="C60" s="92">
         <v>3187.17</v>
       </c>
-      <c r="D60" s="93">
+      <c r="D60" s="92">
         <v>3237.23</v>
       </c>
-      <c r="E60" s="93">
+      <c r="E60" s="92">
         <v>3145.28</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="G60" s="106">
+        <v>313</v>
+      </c>
+      <c r="G60" s="103">
         <v>1.67E-2</v>
       </c>
       <c r="H60" s="31"/>
-      <c r="I60" s="105">
+      <c r="I60" s="102">
         <v>44200</v>
       </c>
       <c r="J60" s="31">
@@ -13374,12 +13326,12 @@
         <v>1.66</v>
       </c>
       <c r="N60" s="31" t="s">
-        <v>376</v>
-      </c>
-      <c r="O60" s="106">
+        <v>375</v>
+      </c>
+      <c r="O60" s="103">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="S60" s="105">
+      <c r="S60" s="102">
         <v>44200</v>
       </c>
       <c r="T60" s="31">
@@ -13395,12 +13347,12 @@
         <v>8.9</v>
       </c>
       <c r="X60" s="31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Y60" s="31">
         <v>0.1003</v>
       </c>
-      <c r="AB60" s="105">
+      <c r="AB60" s="102">
         <v>44200</v>
       </c>
       <c r="AC60" s="31">
@@ -13416,12 +13368,12 @@
         <v>72.05</v>
       </c>
       <c r="AG60" s="31" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AH60" s="31">
         <v>-0.1928</v>
       </c>
-      <c r="AK60" s="105">
+      <c r="AK60" s="102">
         <v>44200</v>
       </c>
       <c r="AL60" s="31">
@@ -13437,36 +13389,36 @@
         <v>295</v>
       </c>
       <c r="AP60" s="31" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AQ60" s="31">
         <v>-2.6599999999999999E-2</v>
       </c>
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A61" s="105">
+      <c r="A61" s="102">
         <v>44199</v>
       </c>
-      <c r="B61" s="93">
+      <c r="B61" s="92">
         <v>3165.34</v>
       </c>
-      <c r="C61" s="93">
+      <c r="C61" s="92">
         <v>2948.69</v>
       </c>
-      <c r="D61" s="93">
+      <c r="D61" s="92">
         <v>3204.24</v>
       </c>
-      <c r="E61" s="93">
+      <c r="E61" s="92">
         <v>2948.64</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="G61" s="106">
+        <v>314</v>
+      </c>
+      <c r="G61" s="103">
         <v>7.3300000000000004E-2</v>
       </c>
       <c r="H61" s="31"/>
-      <c r="I61" s="105">
+      <c r="I61" s="102">
         <v>44199</v>
       </c>
       <c r="J61" s="31">
@@ -13482,12 +13434,12 @@
         <v>1.5529999999999999</v>
       </c>
       <c r="N61" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="O61" s="106">
+        <v>376</v>
+      </c>
+      <c r="O61" s="103">
         <v>6.2100000000000002E-2</v>
       </c>
-      <c r="S61" s="105">
+      <c r="S61" s="102">
         <v>44199</v>
       </c>
       <c r="T61" s="31">
@@ -13503,12 +13455,12 @@
         <v>7.7</v>
       </c>
       <c r="X61" s="31" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y61" s="31">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="AB61" s="105">
+      <c r="AB61" s="102">
         <v>44199</v>
       </c>
       <c r="AC61" s="31">
@@ -13524,12 +13476,12 @@
         <v>84.5</v>
       </c>
       <c r="AG61" s="31" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AH61" s="31">
         <v>2.2800000000000001E-2</v>
       </c>
-      <c r="AK61" s="105">
+      <c r="AK61" s="102">
         <v>44199</v>
       </c>
       <c r="AL61" s="31">
@@ -13545,36 +13497,36 @@
         <v>292.52</v>
       </c>
       <c r="AP61" s="31" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AQ61" s="31">
         <v>2.9399999999999999E-2</v>
       </c>
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A62" s="105">
+      <c r="A62" s="102">
         <v>44198</v>
       </c>
-      <c r="B62" s="93">
+      <c r="B62" s="92">
         <v>2949.04</v>
       </c>
-      <c r="C62" s="93">
+      <c r="C62" s="92">
         <v>2888.75</v>
       </c>
-      <c r="D62" s="93">
+      <c r="D62" s="92">
         <v>2976.36</v>
       </c>
-      <c r="E62" s="93">
+      <c r="E62" s="92">
         <v>2869.3</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="G62" s="106">
+        <v>315</v>
+      </c>
+      <c r="G62" s="103">
         <v>1.6E-2</v>
       </c>
       <c r="H62" s="31"/>
-      <c r="I62" s="105">
+      <c r="I62" s="102">
         <v>44198</v>
       </c>
       <c r="J62" s="31">
@@ -13590,12 +13542,12 @@
         <v>1.514</v>
       </c>
       <c r="N62" s="31" t="s">
-        <v>378</v>
-      </c>
-      <c r="O62" s="106">
+        <v>377</v>
+      </c>
+      <c r="O62" s="103">
         <v>1.9E-2</v>
       </c>
-      <c r="S62" s="105">
+      <c r="S62" s="102">
         <v>44198</v>
       </c>
       <c r="T62" s="31">
@@ -13611,12 +13563,12 @@
         <v>6.1</v>
       </c>
       <c r="X62" s="31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y62" s="31">
         <v>0.3256</v>
       </c>
-      <c r="AB62" s="105">
+      <c r="AB62" s="102">
         <v>44198</v>
       </c>
       <c r="AC62" s="31">
@@ -13632,12 +13584,12 @@
         <v>71.13</v>
       </c>
       <c r="AG62" s="31" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH62" s="31">
         <v>0.25440000000000002</v>
       </c>
-      <c r="AK62" s="105">
+      <c r="AK62" s="102">
         <v>44198</v>
       </c>
       <c r="AL62" s="31">
@@ -13653,36 +13605,36 @@
         <v>245.6</v>
       </c>
       <c r="AP62" s="31" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AQ62" s="31">
         <v>0.19500000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A63" s="105">
+      <c r="A63" s="102">
         <v>44197</v>
       </c>
-      <c r="B63" s="93">
+      <c r="B63" s="92">
         <v>2902.52</v>
       </c>
-      <c r="C63" s="93">
+      <c r="C63" s="92">
         <v>2846.2</v>
       </c>
-      <c r="D63" s="93">
+      <c r="D63" s="92">
         <v>3017.15</v>
       </c>
-      <c r="E63" s="93">
+      <c r="E63" s="92">
         <v>2832.04</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="G63" s="106">
+        <v>316</v>
+      </c>
+      <c r="G63" s="103">
         <v>2.06E-2</v>
       </c>
       <c r="H63" s="31"/>
-      <c r="I63" s="105">
+      <c r="I63" s="102">
         <v>44197</v>
       </c>
       <c r="J63" s="31">
@@ -13698,12 +13650,12 @@
         <v>1.534</v>
       </c>
       <c r="N63" s="31" t="s">
-        <v>379</v>
-      </c>
-      <c r="O63" s="106">
+        <v>378</v>
+      </c>
+      <c r="O63" s="103">
         <v>-5.3900000000000003E-2</v>
       </c>
-      <c r="S63" s="105">
+      <c r="S63" s="102">
         <v>44197</v>
       </c>
       <c r="T63" s="31">
@@ -13719,12 +13671,12 @@
         <v>5.81</v>
       </c>
       <c r="X63" s="31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y63" s="31">
         <v>-3.5900000000000001E-2</v>
       </c>
-      <c r="AB63" s="105">
+      <c r="AB63" s="102">
         <v>44197</v>
       </c>
       <c r="AC63" s="31">
@@ -13740,12 +13692,12 @@
         <v>66.5</v>
       </c>
       <c r="AG63" s="31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AH63" s="31">
         <v>-3.04E-2</v>
       </c>
-      <c r="AK63" s="105">
+      <c r="AK63" s="102">
         <v>44197</v>
       </c>
       <c r="AL63" s="31">
@@ -13761,7 +13713,7 @@
         <v>222.81</v>
       </c>
       <c r="AP63" s="31" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AQ63" s="31">
         <v>5.3900000000000003E-2</v>
@@ -13790,17 +13742,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
@@ -13905,11 +13857,11 @@
         <f>F12*(1+G48)</f>
         <v>5457</v>
       </c>
-      <c r="H12" s="110">
+      <c r="H12" s="107">
         <f t="shared" ref="H12:I12" si="1">G12*(1+H48)</f>
         <v>5566.14</v>
       </c>
-      <c r="I12" s="110">
+      <c r="I12" s="107">
         <f t="shared" si="1"/>
         <v>5683.0289400000001</v>
       </c>
@@ -16786,13 +16738,13 @@
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
-      <c r="E2" s="116" t="s">
+      <c r="E2" s="113" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="41" t="s">
@@ -19662,13 +19614,13 @@
         <v>132</v>
       </c>
       <c r="D1" s="49"/>
-      <c r="E1" s="117" t="s">
+      <c r="E1" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="41" t="s">
@@ -19942,31 +19894,31 @@
       <c r="B14" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="113">
+      <c r="C14" s="110">
         <f>'Profit &amp; loss'!C32</f>
         <v>-368.4</v>
       </c>
-      <c r="D14" s="113">
+      <c r="D14" s="110">
         <f>'Profit &amp; loss'!D32</f>
         <v>-399.6</v>
       </c>
-      <c r="E14" s="113">
+      <c r="E14" s="110">
         <f>E12+E5</f>
         <v>-437.32044448529803</v>
       </c>
-      <c r="F14" s="113">
+      <c r="F14" s="110">
         <f t="shared" ref="F14:I14" ca="1" si="5">F12+F5</f>
         <v>-471.88960848717466</v>
       </c>
-      <c r="G14" s="113">
+      <c r="G14" s="110">
         <f t="shared" ca="1" si="5"/>
         <v>-502.70316984993144</v>
       </c>
-      <c r="H14" s="113">
+      <c r="H14" s="110">
         <f t="shared" ca="1" si="5"/>
         <v>-530.38300837039526</v>
       </c>
-      <c r="I14" s="113">
+      <c r="I14" s="110">
         <f t="shared" ca="1" si="5"/>
         <v>-555.55292720866862</v>
       </c>
@@ -19996,13 +19948,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="117" t="s">
+      <c r="D1" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">

--- a/ComfortDelGro-Equity-Valuation.xlsx
+++ b/ComfortDelGro-Equity-Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChengJing\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AAE408-D7E9-44D1-8BCD-8A7DEE8E0C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE86053-7615-4E0A-B55E-DAD99D5505BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D93AAA56-1308-4026-9D8F-E913B55E5CC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{D93AAA56-1308-4026-9D8F-E913B55E5CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Unlevered cash flow" sheetId="14" r:id="rId1"/>
@@ -1198,9 +1198,6 @@
     <t>Equity Value</t>
   </si>
   <si>
-    <t>Shares Outstanding</t>
-  </si>
-  <si>
     <t>Implied Share Price</t>
   </si>
   <si>
@@ -1213,9 +1210,6 @@
     <t>convertibles</t>
   </si>
   <si>
-    <t>treasury shares</t>
-  </si>
-  <si>
     <t>Sensitivity table</t>
   </si>
   <si>
@@ -2179,17 +2173,23 @@
     <t>Terminal growth</t>
   </si>
   <si>
-    <t>Diluted shares oustanding</t>
-  </si>
-  <si>
     <t>Discounted Cash Flow</t>
+  </si>
+  <si>
+    <t>Preferred shares</t>
+  </si>
+  <si>
+    <t>Diluted  shares oustanding</t>
+  </si>
+  <si>
+    <t>Diluted Shares Outstanding</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="15">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
@@ -2202,7 +2202,6 @@
     <numFmt numFmtId="171" formatCode="#\E"/>
     <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="173" formatCode="#,##0_ ;\-#,##0\ "/>
-    <numFmt numFmtId="174" formatCode="0.0000000000000000%"/>
     <numFmt numFmtId="175" formatCode="#,###.00\x"/>
     <numFmt numFmtId="176" formatCode="#.##\x"/>
     <numFmt numFmtId="177" formatCode="#.###\x"/>
@@ -2871,7 +2870,7 @@
     <xf numFmtId="169" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2975,7 +2974,6 @@
     <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="173" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3011,6 +3009,8 @@
     </xf>
     <xf numFmtId="44" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3023,8 +3023,9 @@
     <xf numFmtId="0" fontId="19" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="20% - Accent1 2" xfId="21" xr:uid="{7F1DC058-3DA4-4945-98D8-2DC0ECB9F210}"/>
@@ -3391,7 +3392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CCF159-3CA6-4D47-A7FD-3D774C4FA464}">
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -3406,7 +3407,7 @@
   <sheetData>
     <row r="1" spans="2:9" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B1" s="65" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C1" s="66"/>
       <c r="D1" s="66"/>
@@ -4319,15 +4320,15 @@
         <f t="shared" ca="1" si="9"/>
         <v>-64.316977029218151</v>
       </c>
-      <c r="G34" s="108">
+      <c r="G34" s="107">
         <f t="shared" ca="1" si="9"/>
         <v>-63.001316569801929</v>
       </c>
-      <c r="H34" s="108">
+      <c r="H34" s="107">
         <f t="shared" ca="1" si="9"/>
         <v>-61.659342901198443</v>
       </c>
-      <c r="I34" s="108">
+      <c r="I34" s="107">
         <f t="shared" ca="1" si="9"/>
         <v>-60.222089102123618</v>
       </c>
@@ -4352,15 +4353,15 @@
         <f ca="1">'balance sheet'!J11-'balance sheet'!J6</f>
         <v>1074.9495907958722</v>
       </c>
-      <c r="G35" s="108">
+      <c r="G35" s="107">
         <f ca="1">'balance sheet'!K11-'balance sheet'!K6</f>
         <v>1096.44858261179</v>
       </c>
-      <c r="H35" s="108">
+      <c r="H35" s="107">
         <f ca="1">'balance sheet'!L11-'balance sheet'!L6</f>
         <v>1118.3775542640255</v>
       </c>
-      <c r="I35" s="108">
+      <c r="I35" s="107">
         <f ca="1">'balance sheet'!M11-'balance sheet'!M6</f>
         <v>1141.86348290357</v>
       </c>
@@ -4385,15 +4386,15 @@
         <f ca="1">'balance sheet'!J35-'balance sheet'!J27-'balance sheet'!J28-'balance sheet'!J29</f>
         <v>1139.2665678250903</v>
       </c>
-      <c r="G36" s="108">
+      <c r="G36" s="107">
         <f ca="1">'balance sheet'!K35-'balance sheet'!K27-'balance sheet'!K28-'balance sheet'!K29</f>
         <v>1159.4498991815919</v>
       </c>
-      <c r="H36" s="108">
+      <c r="H36" s="107">
         <f ca="1">'balance sheet'!L35-'balance sheet'!L27-'balance sheet'!L28-'balance sheet'!L29</f>
         <v>1180.036897165224</v>
       </c>
-      <c r="I36" s="108">
+      <c r="I36" s="107">
         <f ca="1">'balance sheet'!M35-'balance sheet'!M27-'balance sheet'!M28-'balance sheet'!M29</f>
         <v>1202.0855720056936</v>
       </c>
@@ -4570,25 +4571,25 @@
       </c>
       <c r="C46" s="77"/>
       <c r="D46" s="77"/>
-      <c r="E46" s="84">
-        <f ca="1">E37/(1+WACC!D18)^1</f>
-        <v>96.032478740151547</v>
-      </c>
-      <c r="F46" s="84">
-        <f ca="1">F44/(1+WACC!$D$18)^'Unlevered cash flow'!F45</f>
-        <v>99.571088288608905</v>
-      </c>
-      <c r="G46" s="84">
-        <f ca="1">G44/(1+WACC!$D$18)^'Unlevered cash flow'!G45</f>
-        <v>101.25323413388995</v>
-      </c>
-      <c r="H46" s="84">
-        <f ca="1">H44/(1+WACC!$D$18)^'Unlevered cash flow'!H45</f>
-        <v>102.05770032786643</v>
-      </c>
-      <c r="I46" s="84">
-        <f ca="1">I44/(1+WACC!$D$18)^'Unlevered cash flow'!I45</f>
-        <v>102.18595586850981</v>
+      <c r="E46" s="83">
+        <f ca="1">E44/(1+$I$55)^E45</f>
+        <v>96.066970066434294</v>
+      </c>
+      <c r="F46" s="83">
+        <f t="shared" ref="F46:I46" ca="1" si="17">F44/(1+$I$55)^F45</f>
+        <v>99.642625661870909</v>
+      </c>
+      <c r="G46" s="83">
+        <f t="shared" ca="1" si="17"/>
+        <v>101.3623726105201</v>
+      </c>
+      <c r="H46" s="83">
+        <f t="shared" ca="1" si="17"/>
+        <v>102.20440079338292</v>
+      </c>
+      <c r="I46" s="83">
+        <f t="shared" ca="1" si="17"/>
+        <v>102.36959487601078</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
@@ -4597,7 +4598,7 @@
       </c>
       <c r="C48" s="60">
         <f ca="1">SUM(E46:I46)</f>
-        <v>501.10045735902668</v>
+        <v>501.64596400821893</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
@@ -4618,14 +4619,14 @@
       </c>
       <c r="C53" s="43">
         <f ca="1">SUM(E46:I46)</f>
-        <v>501.10045735902668</v>
+        <v>501.64596400821893</v>
       </c>
       <c r="F53" t="s">
         <v>219</v>
       </c>
       <c r="I53" s="43">
         <f ca="1">C48</f>
-        <v>501.10045735902668</v>
+        <v>501.64596400821893</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
@@ -4639,7 +4640,7 @@
       <c r="F54" t="s">
         <v>221</v>
       </c>
-      <c r="I54" s="103">
+      <c r="I54" s="102">
         <v>0.02</v>
       </c>
     </row>
@@ -4647,16 +4648,16 @@
       <c r="B55" t="s">
         <v>222</v>
       </c>
-      <c r="C55" s="85">
+      <c r="C55" s="84">
         <f>'COMPARABLE COMPANIES'!B6</f>
         <v>2.8482165008562825</v>
       </c>
       <c r="F55" t="s">
         <v>223</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="2">
         <f>WACC!D18</f>
-        <v>4.2325659753815532E-2</v>
+        <v>4.1951429210283407E-2</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
@@ -4665,7 +4666,7 @@
       </c>
       <c r="C56" s="2">
         <f>WACC!D18</f>
-        <v>4.2325659753815532E-2</v>
+        <v>4.1951429210283407E-2</v>
       </c>
       <c r="F56" t="s">
         <v>224</v>
@@ -4688,7 +4689,7 @@
       </c>
       <c r="I57" s="60">
         <f ca="1">I56/(I55-I54)</f>
-        <v>5743.8650547560574</v>
+        <v>5841.7871408683168</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
@@ -4697,36 +4698,36 @@
       </c>
       <c r="C58" s="1">
         <f ca="1">C57/(1+C56)^$I$45</f>
-        <v>1942.0103094047747</v>
+        <v>1945.5003080327137</v>
       </c>
       <c r="F58" t="s">
         <v>226</v>
       </c>
       <c r="I58" s="1">
         <f ca="1">I57/(1+I55)^I45</f>
-        <v>4668.6044728450543</v>
+        <v>4756.7284012931441</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="C59" s="86">
+      <c r="C59" s="85">
         <f ca="1">C58+C53</f>
-        <v>2443.1107667638016</v>
+        <v>2447.1462720409327</v>
       </c>
       <c r="F59" s="30" t="s">
         <v>227</v>
       </c>
       <c r="G59" s="30"/>
       <c r="H59" s="30"/>
-      <c r="I59" s="93">
+      <c r="I59" s="92">
         <f ca="1">I58+I53</f>
-        <v>5169.7049302040814</v>
+        <v>5258.3743653013626</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C61" s="78"/>
+      <c r="C61" s="117"/>
       <c r="F61" s="42" t="s">
         <v>569</v>
       </c>
@@ -4738,77 +4739,77 @@
       </c>
       <c r="C62" s="43">
         <f ca="1">I59</f>
-        <v>5169.7049302040814</v>
+        <v>5258.3743653013626</v>
       </c>
       <c r="F62" t="s">
-        <v>244</v>
-      </c>
-      <c r="G62" s="98">
+        <v>243</v>
+      </c>
+      <c r="G62" s="97">
         <v>2166763244</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B63" s="94" t="s">
+      <c r="B63" s="93" t="s">
         <v>236</v>
       </c>
       <c r="C63" s="1">
         <f>'balance sheet'!H6</f>
         <v>868.4</v>
       </c>
-      <c r="F63" s="94" t="s">
-        <v>247</v>
-      </c>
-      <c r="G63" s="98">
-        <v>684669</v>
+      <c r="F63" s="93" t="s">
+        <v>568</v>
+      </c>
+      <c r="G63" s="97">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B64" s="94" t="s">
+      <c r="B64" s="93" t="s">
         <v>237</v>
       </c>
       <c r="C64" s="1">
         <f>SUM('balance sheet'!H27:H29,'balance sheet'!H38:H40)</f>
         <v>1821.5</v>
       </c>
-      <c r="F64" s="94" t="s">
-        <v>245</v>
+      <c r="F64" s="93" t="s">
+        <v>244</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="94" t="s">
+      <c r="B65" s="93" t="s">
         <v>238</v>
       </c>
       <c r="C65">
         <f>'balance sheet'!H56</f>
         <v>385.2</v>
       </c>
-      <c r="F65" s="94" t="s">
-        <v>246</v>
+      <c r="F65" s="93" t="s">
+        <v>245</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="94" t="s">
+      <c r="B66" s="93" t="s">
         <v>239</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G66" s="51">
         <f>SUM(G62:G65)</f>
-        <v>2167447913</v>
+        <v>2166763244</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="94" t="s">
+      <c r="B67" s="93" t="s">
         <v>240</v>
       </c>
       <c r="C67">
@@ -4819,32 +4820,35 @@
       <c r="B68" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C68" s="95">
+      <c r="C68" s="94">
         <f ca="1">C62+C63-C64-C65</f>
-        <v>3831.4049302040812</v>
+        <v>3920.0743653013624</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>242</v>
-      </c>
-      <c r="C69" s="98">
+        <v>570</v>
+      </c>
+      <c r="C69" s="97">
         <f>G66</f>
-        <v>2167447913</v>
+        <v>2166763244</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B70" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="C70" s="109">
+        <v>242</v>
+      </c>
+      <c r="C70" s="108">
         <f ca="1">C68*1000000/C69</f>
-        <v>1.7677033469750012</v>
-      </c>
+        <v>1.8091844488115945</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E71" s="2"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B75" s="42" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C75" s="78"/>
       <c r="D75" s="42"/>
@@ -4853,147 +4857,145 @@
       <c r="G75" s="78"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="99"/>
+      <c r="A78" s="98"/>
       <c r="D78" s="8" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="100" t="s">
+      <c r="A79" s="99" t="s">
         <v>223</v>
       </c>
-      <c r="B79" s="116">
+      <c r="B79" s="111">
         <f ca="1">C70</f>
-        <v>1.7677033469750012</v>
+        <v>1.8091844488115945</v>
       </c>
       <c r="C79" s="2">
-        <f>D79-0.005</f>
-        <v>9.9999999999999985E-3</v>
+        <f>0.01</f>
+        <v>0.01</v>
       </c>
       <c r="D79" s="2">
-        <f>E79-0.005</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E79" s="103">
-        <f>I54</f>
+      <c r="E79" s="102">
         <v>0.02</v>
       </c>
       <c r="F79" s="2">
-        <f>E79+0.005</f>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G79" s="2">
-        <f>F79+0.005</f>
-        <v>3.0000000000000002E-2</v>
+        <f>0.03</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="99"/>
-      <c r="B80" s="96">
-        <f t="shared" ref="B79:B80" si="17">B81+0.0025</f>
-        <v>4.7325659753815537E-2</v>
+      <c r="A80" s="98"/>
+      <c r="B80" s="2">
+        <v>4.6951429210283405E-2</v>
       </c>
       <c r="C80">
-        <f t="dataTable" ref="C80:G84" dt2D="1" dtr="1" r1="C55" r2="C56" ca="1"/>
-        <v>1.7677033469750012</v>
+        <f t="dataTable" ref="C80:G84" dt2D="1" dtr="1" r1="I54" r2="I55" ca="1"/>
+        <v>0.87136382120104172</v>
       </c>
       <c r="D80">
-        <v>1.7677033469750012</v>
+        <v>1.075885446946568</v>
       </c>
       <c r="E80">
-        <v>1.7677033469750012</v>
+        <v>1.3562923343417781</v>
       </c>
       <c r="F80">
-        <v>1.7677033469750012</v>
+        <v>1.7644389168197343</v>
       </c>
       <c r="G80">
-        <v>1.7677033469750012</v>
+        <v>2.4133596413566729</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="99"/>
-      <c r="B81" s="96">
-        <f>B82+0.0025</f>
-        <v>4.4825659753815535E-2</v>
+      <c r="A81" s="98"/>
+      <c r="B81" s="2">
+        <v>4.4451429210283409E-2</v>
       </c>
       <c r="C81">
-        <v>1.7677033469750012</v>
+        <v>0.98077406754290863</v>
       </c>
       <c r="D81">
-        <v>1.7677033469750012</v>
+        <v>1.2210444780641108</v>
       </c>
       <c r="E81">
-        <v>1.7677033469750012</v>
+        <v>1.55957925115278</v>
       </c>
       <c r="F81">
-        <v>1.7677033469750012</v>
+        <v>2.0721551033975731</v>
       </c>
       <c r="G81">
-        <v>1.7677033469750012</v>
+        <v>2.9394196475262482</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="97">
-        <f>I55</f>
-        <v>4.2325659753815532E-2</v>
+      <c r="B82" s="96">
+        <v>4.1951429210283407E-2</v>
       </c>
       <c r="C82">
-        <v>1.7677033469750012</v>
+        <v>1.1073189270492059</v>
       </c>
       <c r="D82">
-        <v>1.7677033469750012</v>
-      </c>
-      <c r="E82">
-        <v>1.7677033469750012</v>
+        <v>1.3931470216540573</v>
+      </c>
+      <c r="E82" s="116">
+        <v>1.8091844488115945</v>
       </c>
       <c r="F82">
-        <v>1.7677033469750012</v>
+        <v>2.470650991117223</v>
       </c>
       <c r="G82">
-        <v>1.7677033469750012</v>
+        <v>3.685579827067599</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B83" s="96">
-        <f>B82-0.0025</f>
-        <v>3.982565975381553E-2</v>
+        <v>3.9451429210283405E-2</v>
       </c>
       <c r="C83">
-        <v>1.7677033469750012</v>
+        <v>1.2553620176675206</v>
       </c>
       <c r="D83">
-        <v>1.7677033469750012</v>
+        <v>1.6004576602881659</v>
       </c>
       <c r="E83">
-        <v>1.7677033469750012</v>
+        <v>2.122967331919186</v>
       </c>
       <c r="F83">
-        <v>1.7677033469750012</v>
+        <v>3.0070396310439702</v>
       </c>
       <c r="G83">
-        <v>1.7677033469750012</v>
+        <v>4.8264967057991823</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="96">
-        <f>B83-0.0025</f>
-        <v>3.7325659753815528E-2</v>
+      <c r="B84" s="2">
+        <v>3.695142921028341E-2</v>
       </c>
       <c r="C84">
-        <v>1.7677033469750012</v>
+        <v>1.4308860276217881</v>
       </c>
       <c r="D84">
-        <v>1.7677033469750012</v>
+        <v>1.8550059201754288</v>
       </c>
       <c r="E84">
-        <v>1.7677033469750012</v>
+        <v>2.5293229420049621</v>
       </c>
       <c r="F84">
-        <v>1.7677033469750012</v>
+        <v>3.7678545108690278</v>
       </c>
       <c r="G84">
-        <v>1.7677033469750012</v>
-      </c>
+        <v>6.7880795004642955</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="95"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="96"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5018,13 +5020,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="114" t="s">
+      <c r="D1" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -5282,17 +5284,17 @@
       <c r="A1" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="114" t="s">
+      <c r="B1" s="115" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114" t="s">
+      <c r="C1" s="115"/>
+      <c r="D1" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -6660,9 +6662,9 @@
       <c r="F6" t="s">
         <v>205</v>
       </c>
-      <c r="G6" s="115">
+      <c r="G6" s="110">
         <f>'beta calculation'!Q5</f>
-        <v>0.59520093089099124</v>
+        <v>0.58140971666986763</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
@@ -6689,7 +6691,7 @@
       <c r="G8" s="81"/>
       <c r="H8" s="2">
         <f>G5+G6*H7</f>
-        <v>5.3176999376688933E-2</v>
+        <v>5.2593631015135395E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -6702,8 +6704,8 @@
         <v>210</v>
       </c>
       <c r="D12" s="1">
-        <f>2167447913*'Unlevered cash flow'!C3</f>
-        <v>3207822911.2399998</v>
+        <f>'Unlevered cash flow'!G62*'Unlevered cash flow'!C3</f>
+        <v>3206809601.1199999</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -6722,7 +6724,7 @@
       <c r="C14" s="8"/>
       <c r="D14" s="82">
         <f>SUM(D12:D13)</f>
-        <v>5029322911.2399998</v>
+        <v>5028309601.1199999</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -6737,7 +6739,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="2">
         <f>D12/D14</f>
-        <v>0.63782401087646567</v>
+        <v>0.63775102479881485</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
@@ -6747,7 +6749,7 @@
       <c r="C17" s="8"/>
       <c r="D17" s="2">
         <f>D13/D14</f>
-        <v>0.36217598912353427</v>
+        <v>0.3622489752011851</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
@@ -6755,9 +6757,9 @@
         <v>212</v>
       </c>
       <c r="C18" s="61"/>
-      <c r="D18" s="83">
+      <c r="D18" s="118">
         <f>D16*H8+D17*D7</f>
-        <v>4.2325659753815532E-2</v>
+        <v>4.1951429210283407E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6787,7 +6789,7 @@
       <c r="A2" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="87">
+      <c r="B2" s="86">
         <f>F4/F3</f>
         <v>2.8482165008562825</v>
       </c>
@@ -6800,14 +6802,14 @@
       <c r="A3" t="s">
         <v>233</v>
       </c>
-      <c r="B3" s="87">
+      <c r="B3" s="86">
         <f>F8/F7</f>
         <v>2.3947860505477307</v>
       </c>
       <c r="E3" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="92">
+      <c r="F3" s="91">
         <f>464.8*1000000</f>
         <v>464800000</v>
       </c>
@@ -6816,14 +6818,14 @@
       <c r="A4" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="88">
+      <c r="B4" s="87">
         <f>F13/F12</f>
         <v>6.6296784378324967</v>
       </c>
       <c r="E4" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="92">
+      <c r="F4" s="91">
         <f>(614086377*17.4/100)+(1249000000+346300000)-425600000+47300000</f>
         <v>1323851029.598</v>
       </c>
@@ -6832,16 +6834,16 @@
       <c r="A5" s="61" t="s">
         <v>230</v>
       </c>
-      <c r="B5" s="89">
+      <c r="B5" s="88">
         <f>AVERAGE(B2:B4)</f>
         <v>3.9575603297455033</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="89" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="91">
+      <c r="B6" s="90">
         <f>MEDIAN(B2:B4)</f>
         <v>2.8482165008562825</v>
       </c>
@@ -6913,98 +6915,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A1" s="111" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="I1" s="111" t="s">
-        <v>317</v>
-      </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="S1" s="111" t="s">
-        <v>441</v>
-      </c>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="AB1" s="111" t="s">
-        <v>501</v>
-      </c>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="111"/>
-      <c r="AG1" s="111"/>
-      <c r="AH1" s="111"/>
-      <c r="AK1" s="111" t="s">
+      <c r="A1" s="112" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="I1" s="112" t="s">
+        <v>315</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="S1" s="112" t="s">
+        <v>439</v>
+      </c>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="112"/>
+      <c r="X1" s="112"/>
+      <c r="Y1" s="112"/>
+      <c r="AB1" s="112" t="s">
+        <v>499</v>
+      </c>
+      <c r="AC1" s="112"/>
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="112"/>
+      <c r="AG1" s="112"/>
+      <c r="AH1" s="112"/>
+      <c r="AK1" s="112" t="s">
         <v>232</v>
       </c>
-      <c r="AL1" s="111"/>
-      <c r="AM1" s="111"/>
-      <c r="AN1" s="111"/>
-      <c r="AO1" s="111"/>
-      <c r="AP1" s="111"/>
-      <c r="AQ1" s="111"/>
+      <c r="AL1" s="112"/>
+      <c r="AM1" s="112"/>
+      <c r="AN1" s="112"/>
+      <c r="AO1" s="112"/>
+      <c r="AP1" s="112"/>
+      <c r="AQ1" s="112"/>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="D2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="E2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="F2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>255</v>
-      </c>
       <c r="G2" s="31" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K2" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="L2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="M2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="N2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="M2" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>255</v>
-      </c>
       <c r="O2" s="31" t="s">
-        <v>379</v>
-      </c>
-      <c r="P2" s="105" t="s">
-        <v>566</v>
+        <v>377</v>
+      </c>
+      <c r="P2" s="104" t="s">
+        <v>564</v>
       </c>
       <c r="Q2">
         <f>SLOPE(O3:O63,G3:G63)</f>
@@ -7012,84 +7014,84 @@
       </c>
       <c r="R2" s="2"/>
       <c r="S2" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="T2" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="U2" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="T2" s="31" t="s">
+      <c r="V2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="W2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="V2" s="31" t="s">
+      <c r="X2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="W2" s="31" t="s">
+      <c r="Y2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="X2" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="Y2" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z2" s="104" t="s">
-        <v>380</v>
+      <c r="Z2" s="103" t="s">
+        <v>378</v>
       </c>
       <c r="AA2">
         <f>SLOPE(Y3:Y63,G3:G63)</f>
         <v>0.7517124637493322</v>
       </c>
       <c r="AB2" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC2" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="AD2" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="AC2" s="31" t="s">
+      <c r="AE2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="AD2" s="31" t="s">
+      <c r="AF2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="AE2" s="31" t="s">
+      <c r="AG2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AH2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="AG2" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH2" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="AI2" s="104" t="s">
-        <v>562</v>
+      <c r="AI2" s="103" t="s">
+        <v>560</v>
       </c>
       <c r="AJ2">
         <f>SLOPE(AH3:AH63,G3:G63)</f>
         <v>0.34260011499870624</v>
       </c>
       <c r="AK2" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL2" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM2" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="AL2" s="31" t="s">
+      <c r="AN2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="AM2" s="31" t="s">
+      <c r="AO2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="AN2" s="31" t="s">
+      <c r="AP2" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="AO2" s="31" t="s">
+      <c r="AQ2" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="AP2" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="AQ2" s="31" t="s">
-        <v>256</v>
-      </c>
       <c r="AS2" s="31" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AT2">
         <f>SLOPE(AQ3:AQ63,G3:G63)</f>
@@ -7097,29 +7099,29 @@
       </c>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A3" s="102">
+      <c r="A3" s="101">
         <v>46023</v>
       </c>
-      <c r="B3" s="92">
+      <c r="B3" s="91">
         <v>4905.13</v>
       </c>
-      <c r="C3" s="92">
+      <c r="C3" s="91">
         <v>4652.34</v>
       </c>
-      <c r="D3" s="92">
+      <c r="D3" s="91">
         <v>4933.88</v>
       </c>
-      <c r="E3" s="92">
+      <c r="E3" s="91">
         <v>4648.38</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="G3" s="103">
+        <v>255</v>
+      </c>
+      <c r="G3" s="102">
         <v>5.57E-2</v>
       </c>
       <c r="H3" s="31"/>
-      <c r="I3" s="102">
+      <c r="I3" s="101">
         <v>46023</v>
       </c>
       <c r="J3" s="31">
@@ -7135,12 +7137,12 @@
         <v>1.45</v>
       </c>
       <c r="N3" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="O3" s="103">
+        <v>316</v>
+      </c>
+      <c r="O3" s="102">
         <v>-6.7999999999999996E-3</v>
       </c>
-      <c r="S3" s="102">
+      <c r="S3" s="101">
         <v>46023</v>
       </c>
       <c r="T3" s="31">
@@ -7156,19 +7158,19 @@
         <v>3.86</v>
       </c>
       <c r="X3" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y3" s="31">
         <v>-8.2400000000000001E-2</v>
       </c>
       <c r="Z3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AA3">
-        <f>AA2/(1+(1-0.2049)*(9838+42313+801903+68873+132694)/(952614))</f>
-        <v>0.39961857731694406</v>
-      </c>
-      <c r="AB3" s="102">
+        <f>AA2/(1+(1-0.2049)*(9838+42313+801903+68873+132694)/(952611))</f>
+        <v>0.39961798785275715</v>
+      </c>
+      <c r="AB3" s="101">
         <v>46023</v>
       </c>
       <c r="AC3" s="31">
@@ -7184,19 +7186,19 @@
         <v>180</v>
       </c>
       <c r="AG3" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AH3" s="31">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="AI3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AJ3">
         <f>AJ2/(1+(1-0.238)*(447.1+710.2)/(719.5))</f>
         <v>0.15393189696173068</v>
       </c>
-      <c r="AK3" s="102">
+      <c r="AK3" s="101">
         <v>46023</v>
       </c>
       <c r="AL3" s="31">
@@ -7212,13 +7214,13 @@
         <v>20.8</v>
       </c>
       <c r="AP3" s="31" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AQ3" s="31">
         <v>8.6999999999999994E-3</v>
       </c>
       <c r="AS3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AT3">
         <f>AT2/(1+(1-0.47759)*(1249+346.3)/(18.57*667949082))</f>
@@ -7226,29 +7228,29 @@
       </c>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A4" s="102">
+      <c r="A4" s="101">
         <v>45669</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="91">
         <v>4646.21</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="91">
         <v>4531.55</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="91">
         <v>4665.12</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="91">
         <v>4492.46</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="G4" s="103">
+        <v>256</v>
+      </c>
+      <c r="G4" s="102">
         <v>2.7E-2</v>
       </c>
       <c r="H4" s="31"/>
-      <c r="I4" s="102">
+      <c r="I4" s="101">
         <v>45669</v>
       </c>
       <c r="J4" s="31">
@@ -7264,19 +7266,19 @@
         <v>1.42</v>
       </c>
       <c r="N4" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="O4" s="103">
+        <v>317</v>
+      </c>
+      <c r="O4" s="102">
         <v>2.7799999999999998E-2</v>
       </c>
       <c r="P4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="Q4">
         <f>MEDIAN(AA3,AJ3,AT3)</f>
-        <v>0.39961857731694406</v>
-      </c>
-      <c r="S4" s="102">
+        <v>0.39961798785275715</v>
+      </c>
+      <c r="S4" s="101">
         <v>45669</v>
       </c>
       <c r="T4" s="31">
@@ -7292,12 +7294,12 @@
         <v>4.16</v>
       </c>
       <c r="X4" s="31" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="Y4" s="31">
         <v>-8.0100000000000005E-2</v>
       </c>
-      <c r="AB4" s="102">
+      <c r="AB4" s="101">
         <v>45669</v>
       </c>
       <c r="AC4" s="31">
@@ -7313,12 +7315,12 @@
         <v>173.5</v>
       </c>
       <c r="AG4" s="31" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AH4" s="31">
         <v>7.8700000000000006E-2</v>
       </c>
-      <c r="AK4" s="102">
+      <c r="AK4" s="101">
         <v>45669</v>
       </c>
       <c r="AL4" s="31">
@@ -7334,36 +7336,36 @@
         <v>21</v>
       </c>
       <c r="AP4" s="31" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AQ4" s="31">
         <v>5.0099999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A5" s="102">
+      <c r="A5" s="101">
         <v>45668</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="91">
         <v>4523.96</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="91">
         <v>4437.38</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="91">
         <v>4575.91</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="91">
         <v>4372.6400000000003</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="G5" s="103">
+        <v>257</v>
+      </c>
+      <c r="G5" s="102">
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="H5" s="31"/>
-      <c r="I5" s="102">
+      <c r="I5" s="101">
         <v>45668</v>
       </c>
       <c r="J5" s="31">
@@ -7379,19 +7381,19 @@
         <v>1.44</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="O5" s="103">
+        <v>318</v>
+      </c>
+      <c r="O5" s="102">
         <v>-1.37E-2</v>
       </c>
-      <c r="P5" s="90" t="s">
-        <v>565</v>
-      </c>
-      <c r="Q5" s="106">
-        <f>Q4*(1+(1-'Profit &amp; loss'!E105)*('debt schedule'!C5+'debt schedule'!C11)/('balance sheet'!H57))</f>
-        <v>0.59520093089099124</v>
-      </c>
-      <c r="S5" s="102">
+      <c r="P5" s="89" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q5" s="105">
+        <f>Q4*(1+(1-'Profit &amp; loss'!E105)*(('debt schedule'!C5+'debt schedule'!C11)/(WACC!D12/1000000)))</f>
+        <v>0.58140971666986763</v>
+      </c>
+      <c r="S5" s="101">
         <v>45668</v>
       </c>
       <c r="T5" s="31">
@@ -7407,12 +7409,12 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="X5" s="31" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Y5" s="31">
         <v>-5.1299999999999998E-2</v>
       </c>
-      <c r="AB5" s="102">
+      <c r="AB5" s="101">
         <v>45668</v>
       </c>
       <c r="AC5" s="31">
@@ -7428,12 +7430,12 @@
         <v>171.3</v>
       </c>
       <c r="AG5" s="31" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AH5" s="31">
         <v>-0.15859999999999999</v>
       </c>
-      <c r="AK5" s="102">
+      <c r="AK5" s="101">
         <v>45668</v>
       </c>
       <c r="AL5" s="31">
@@ -7449,36 +7451,36 @@
         <v>19</v>
       </c>
       <c r="AP5" s="31" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AQ5" s="31">
         <v>-0.16370000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A6" s="102">
+      <c r="A6" s="101">
         <v>45667</v>
       </c>
-      <c r="B6" s="92">
+      <c r="B6" s="91">
         <v>4428.62</v>
       </c>
-      <c r="C6" s="92">
+      <c r="C6" s="91">
         <v>4307.76</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="91">
         <v>4478.1499999999996</v>
       </c>
-      <c r="E6" s="92">
+      <c r="E6" s="91">
         <v>4307.76</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="G6" s="103">
+        <v>258</v>
+      </c>
+      <c r="G6" s="102">
         <v>2.9899999999999999E-2</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="102">
+      <c r="I6" s="101">
         <v>45667</v>
       </c>
       <c r="J6" s="31">
@@ -7494,12 +7496,12 @@
         <v>1.44</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="O6" s="103">
+        <v>319</v>
+      </c>
+      <c r="O6" s="102">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="S6" s="102">
+      <c r="S6" s="101">
         <v>45667</v>
       </c>
       <c r="T6" s="31">
@@ -7515,12 +7517,12 @@
         <v>4.71</v>
       </c>
       <c r="X6" s="31" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Y6" s="31">
         <v>-8.0999999999999996E-3</v>
       </c>
-      <c r="AB6" s="102">
+      <c r="AB6" s="101">
         <v>45667</v>
       </c>
       <c r="AC6" s="31">
@@ -7536,12 +7538,12 @@
         <v>198.8</v>
       </c>
       <c r="AG6" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AH6" s="31">
         <v>-6.9099999999999995E-2</v>
       </c>
-      <c r="AK6" s="102">
+      <c r="AK6" s="101">
         <v>45667</v>
       </c>
       <c r="AL6" s="31">
@@ -7557,36 +7559,36 @@
         <v>25.24</v>
       </c>
       <c r="AP6" s="31" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AQ6" s="31">
         <v>-8.6300000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A7" s="102">
+      <c r="A7" s="101">
         <v>45666</v>
       </c>
-      <c r="B7" s="92">
+      <c r="B7" s="91">
         <v>4300.16</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="91">
         <v>4270.8599999999997</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="91">
         <v>4375.33</v>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="91">
         <v>4252.2700000000004</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="G7" s="103">
+        <v>259</v>
+      </c>
+      <c r="G7" s="102">
         <v>7.1000000000000004E-3</v>
       </c>
       <c r="H7" s="31"/>
-      <c r="I7" s="102">
+      <c r="I7" s="101">
         <v>45666</v>
       </c>
       <c r="J7" s="31">
@@ -7602,12 +7604,12 @@
         <v>1.44</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="O7" s="103">
-        <v>0</v>
-      </c>
-      <c r="S7" s="102">
+        <v>320</v>
+      </c>
+      <c r="O7" s="102">
+        <v>0</v>
+      </c>
+      <c r="S7" s="101">
         <v>45666</v>
       </c>
       <c r="T7" s="31">
@@ -7623,12 +7625,12 @@
         <v>4.75</v>
       </c>
       <c r="X7" s="31" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y7" s="31">
         <v>-1.41E-2</v>
       </c>
-      <c r="AB7" s="102">
+      <c r="AB7" s="101">
         <v>45666</v>
       </c>
       <c r="AC7" s="31">
@@ -7644,12 +7646,12 @@
         <v>210.2</v>
       </c>
       <c r="AG7" s="31" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AH7" s="31">
         <v>1.8100000000000002E-2</v>
       </c>
-      <c r="AK7" s="102">
+      <c r="AK7" s="101">
         <v>45666</v>
       </c>
       <c r="AL7" s="31">
@@ -7665,36 +7667,36 @@
         <v>24.36</v>
       </c>
       <c r="AP7" s="31" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AQ7" s="31">
         <v>-0.12429999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A8" s="102">
+      <c r="A8" s="101">
         <v>45665</v>
       </c>
-      <c r="B8" s="92">
+      <c r="B8" s="91">
         <v>4269.7</v>
       </c>
-      <c r="C8" s="92">
+      <c r="C8" s="91">
         <v>4169.28</v>
       </c>
-      <c r="D8" s="92">
+      <c r="D8" s="91">
         <v>4282.8</v>
       </c>
-      <c r="E8" s="92">
+      <c r="E8" s="91">
         <v>4144.8900000000003</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="G8" s="103">
+        <v>260</v>
+      </c>
+      <c r="G8" s="102">
         <v>2.3E-2</v>
       </c>
       <c r="H8" s="31"/>
-      <c r="I8" s="102">
+      <c r="I8" s="101">
         <v>45665</v>
       </c>
       <c r="J8" s="31">
@@ -7710,12 +7712,12 @@
         <v>1.42</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>323</v>
-      </c>
-      <c r="O8" s="103">
+        <v>321</v>
+      </c>
+      <c r="O8" s="102">
         <v>-5.2299999999999999E-2</v>
       </c>
-      <c r="S8" s="102">
+      <c r="S8" s="101">
         <v>45665</v>
       </c>
       <c r="T8" s="31">
@@ -7731,12 +7733,12 @@
         <v>3.63</v>
       </c>
       <c r="X8" s="31" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Y8" s="31">
         <v>0.33160000000000001</v>
       </c>
-      <c r="AB8" s="102">
+      <c r="AB8" s="101">
         <v>45665</v>
       </c>
       <c r="AC8" s="31">
@@ -7752,12 +7754,12 @@
         <v>215.2</v>
       </c>
       <c r="AG8" s="31" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AH8" s="31">
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="AK8" s="102">
+      <c r="AK8" s="101">
         <v>45665</v>
       </c>
       <c r="AL8" s="31">
@@ -7773,36 +7775,36 @@
         <v>32.64</v>
       </c>
       <c r="AP8" s="31" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AQ8" s="31">
         <v>-9.64E-2</v>
       </c>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A9" s="102">
+      <c r="A9" s="101">
         <v>45664</v>
       </c>
-      <c r="B9" s="92">
+      <c r="B9" s="91">
         <v>4173.7700000000004</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="91">
         <v>3972.18</v>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="91">
         <v>4274.32</v>
       </c>
-      <c r="E9" s="92">
+      <c r="E9" s="91">
         <v>3968.57</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="G9" s="103">
+        <v>261</v>
+      </c>
+      <c r="G9" s="102">
         <v>5.28E-2</v>
       </c>
       <c r="H9" s="31"/>
-      <c r="I9" s="102">
+      <c r="I9" s="101">
         <v>45664</v>
       </c>
       <c r="J9" s="31">
@@ -7818,12 +7820,12 @@
         <v>1.4</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="O9" s="103">
+        <v>322</v>
+      </c>
+      <c r="O9" s="102">
         <v>6.9900000000000004E-2</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="101">
         <v>45664</v>
       </c>
       <c r="T9" s="31">
@@ -7839,12 +7841,12 @@
         <v>3.68</v>
       </c>
       <c r="X9" s="31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y9" s="31">
         <v>-1.32E-2</v>
       </c>
-      <c r="AB9" s="102">
+      <c r="AB9" s="101">
         <v>45664</v>
       </c>
       <c r="AC9" s="31">
@@ -7860,12 +7862,12 @@
         <v>204.2</v>
       </c>
       <c r="AG9" s="31" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AH9" s="31">
         <v>-2.69E-2</v>
       </c>
-      <c r="AK9" s="102">
+      <c r="AK9" s="101">
         <v>45664</v>
       </c>
       <c r="AL9" s="31">
@@ -7881,36 +7883,36 @@
         <v>28</v>
       </c>
       <c r="AP9" s="31" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AQ9" s="31">
         <v>0.23119999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A10" s="102">
+      <c r="A10" s="101">
         <v>45663</v>
       </c>
-      <c r="B10" s="92">
+      <c r="B10" s="91">
         <v>3964.29</v>
       </c>
-      <c r="C10" s="92">
+      <c r="C10" s="91">
         <v>3904.42</v>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="91">
         <v>3971.7</v>
       </c>
-      <c r="E10" s="92">
+      <c r="E10" s="91">
         <v>3845.78</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="G10" s="103">
+        <v>262</v>
+      </c>
+      <c r="G10" s="102">
         <v>1.7899999999999999E-2</v>
       </c>
       <c r="H10" s="31"/>
-      <c r="I10" s="102">
+      <c r="I10" s="101">
         <v>45663</v>
       </c>
       <c r="J10" s="31">
@@ -7926,12 +7928,12 @@
         <v>1.4</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="O10" s="103">
+        <v>323</v>
+      </c>
+      <c r="O10" s="102">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="S10" s="102">
+      <c r="S10" s="101">
         <v>45663</v>
       </c>
       <c r="T10" s="31">
@@ -7947,12 +7949,12 @@
         <v>3.11</v>
       </c>
       <c r="X10" s="31" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Y10" s="31">
         <v>0.16980000000000001</v>
       </c>
-      <c r="AB10" s="102">
+      <c r="AB10" s="101">
         <v>45663</v>
       </c>
       <c r="AC10" s="31">
@@ -7968,12 +7970,12 @@
         <v>189.7</v>
       </c>
       <c r="AG10" s="31" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AH10" s="31">
         <v>0.20730000000000001</v>
       </c>
-      <c r="AK10" s="102">
+      <c r="AK10" s="101">
         <v>45663</v>
       </c>
       <c r="AL10" s="31">
@@ -7989,36 +7991,36 @@
         <v>25.24</v>
       </c>
       <c r="AP10" s="31" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AQ10" s="31">
         <v>-1.34E-2</v>
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A11" s="102">
+      <c r="A11" s="101">
         <v>45662</v>
       </c>
-      <c r="B11" s="92">
+      <c r="B11" s="91">
         <v>3894.61</v>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="91">
         <v>3842.38</v>
       </c>
-      <c r="D11" s="92">
+      <c r="D11" s="91">
         <v>3956.26</v>
       </c>
-      <c r="E11" s="92">
+      <c r="E11" s="91">
         <v>3831.04</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="G11" s="103">
+        <v>263</v>
+      </c>
+      <c r="G11" s="102">
         <v>1.6199999999999999E-2</v>
       </c>
       <c r="H11" s="31"/>
-      <c r="I11" s="102">
+      <c r="I11" s="101">
         <v>45662</v>
       </c>
       <c r="J11" s="31">
@@ -8034,12 +8036,12 @@
         <v>1.39</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="O11" s="103">
+        <v>324</v>
+      </c>
+      <c r="O11" s="102">
         <v>-7.1900000000000006E-2</v>
       </c>
-      <c r="S11" s="102">
+      <c r="S11" s="101">
         <v>45662</v>
       </c>
       <c r="T11" s="31">
@@ -8055,12 +8057,12 @@
         <v>2.68</v>
       </c>
       <c r="X11" s="31" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Y11" s="31">
         <v>0.1956</v>
       </c>
-      <c r="AB11" s="102">
+      <c r="AB11" s="101">
         <v>45662</v>
       </c>
       <c r="AC11" s="31">
@@ -8076,12 +8078,12 @@
         <v>172.1</v>
       </c>
       <c r="AG11" s="31" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AH11" s="31">
         <v>0.106</v>
       </c>
-      <c r="AK11" s="102">
+      <c r="AK11" s="101">
         <v>45662</v>
       </c>
       <c r="AL11" s="31">
@@ -8097,36 +8099,36 @@
         <v>26.92</v>
       </c>
       <c r="AP11" s="31" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AQ11" s="31">
         <v>-3.8600000000000002E-2</v>
       </c>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A12" s="102">
+      <c r="A12" s="101">
         <v>45661</v>
       </c>
-      <c r="B12" s="92">
+      <c r="B12" s="91">
         <v>3832.51</v>
       </c>
-      <c r="C12" s="92">
+      <c r="C12" s="91">
         <v>3950.77</v>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="91">
         <v>3980.28</v>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="91">
         <v>3372.38</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="G12" s="103">
+        <v>264</v>
+      </c>
+      <c r="G12" s="102">
         <v>-3.5200000000000002E-2</v>
       </c>
       <c r="H12" s="31"/>
-      <c r="I12" s="102">
+      <c r="I12" s="101">
         <v>45661</v>
       </c>
       <c r="J12" s="31">
@@ -8142,12 +8144,12 @@
         <v>1.36</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="O12" s="103">
+        <v>325</v>
+      </c>
+      <c r="O12" s="102">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="S12" s="102">
+      <c r="S12" s="101">
         <v>45661</v>
       </c>
       <c r="T12" s="31">
@@ -8163,12 +8165,12 @@
         <v>2.19</v>
       </c>
       <c r="X12" s="31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="Y12" s="31">
         <v>1.12E-2</v>
       </c>
-      <c r="AB12" s="102">
+      <c r="AB12" s="101">
         <v>45661</v>
       </c>
       <c r="AC12" s="31">
@@ -8184,12 +8186,12 @@
         <v>137.80000000000001</v>
       </c>
       <c r="AG12" s="31" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AH12" s="31">
         <v>0.1071</v>
       </c>
-      <c r="AK12" s="102">
+      <c r="AK12" s="101">
         <v>45661</v>
       </c>
       <c r="AL12" s="31">
@@ -8205,36 +8207,36 @@
         <v>28.66</v>
       </c>
       <c r="AP12" s="31" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AQ12" s="31">
         <v>-0.4652</v>
       </c>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A13" s="102">
+      <c r="A13" s="101">
         <v>45660</v>
       </c>
-      <c r="B13" s="92">
+      <c r="B13" s="91">
         <v>3972.43</v>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="91">
         <v>3895.37</v>
       </c>
-      <c r="D13" s="92">
+      <c r="D13" s="91">
         <v>4005.18</v>
       </c>
-      <c r="E13" s="92">
+      <c r="E13" s="91">
         <v>3805.7</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="G13" s="103">
+        <v>265</v>
+      </c>
+      <c r="G13" s="102">
         <v>1.9699999999999999E-2</v>
       </c>
       <c r="H13" s="31"/>
-      <c r="I13" s="102">
+      <c r="I13" s="101">
         <v>45660</v>
       </c>
       <c r="J13" s="31">
@@ -8250,12 +8252,12 @@
         <v>1.38</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="O13" s="103">
+        <v>326</v>
+      </c>
+      <c r="O13" s="102">
         <v>5.04E-2</v>
       </c>
-      <c r="S13" s="102">
+      <c r="S13" s="101">
         <v>45660</v>
       </c>
       <c r="T13" s="31">
@@ -8271,12 +8273,12 @@
         <v>2.65</v>
       </c>
       <c r="X13" s="31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Y13" s="31">
         <v>-0.13550000000000001</v>
       </c>
-      <c r="AB13" s="102">
+      <c r="AB13" s="101">
         <v>45660</v>
       </c>
       <c r="AC13" s="31">
@@ -8292,12 +8294,12 @@
         <v>156</v>
       </c>
       <c r="AG13" s="31" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AH13" s="31">
         <v>-2.3199999999999998E-2</v>
       </c>
-      <c r="AK13" s="102">
+      <c r="AK13" s="101">
         <v>45660</v>
       </c>
       <c r="AL13" s="31">
@@ -8313,36 +8315,36 @@
         <v>57</v>
       </c>
       <c r="AP13" s="31" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AQ13" s="31">
         <v>-0.1467</v>
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A14" s="102">
+      <c r="A14" s="101">
         <v>45659</v>
       </c>
-      <c r="B14" s="92">
+      <c r="B14" s="91">
         <v>3895.7</v>
       </c>
-      <c r="C14" s="92">
+      <c r="C14" s="91">
         <v>3802.42</v>
       </c>
-      <c r="D14" s="92">
+      <c r="D14" s="91">
         <v>3951.64</v>
       </c>
-      <c r="E14" s="92">
+      <c r="E14" s="91">
         <v>3797.83</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="G14" s="103">
+        <v>266</v>
+      </c>
+      <c r="G14" s="102">
         <v>1.03E-2</v>
       </c>
       <c r="H14" s="31"/>
-      <c r="I14" s="102">
+      <c r="I14" s="101">
         <v>45659</v>
       </c>
       <c r="J14" s="31">
@@ -8358,12 +8360,12 @@
         <v>1.34</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="O14" s="103">
+        <v>327</v>
+      </c>
+      <c r="O14" s="102">
         <v>-1.4200000000000001E-2</v>
       </c>
-      <c r="S14" s="102">
+      <c r="S14" s="101">
         <v>45659</v>
       </c>
       <c r="T14" s="31">
@@ -8379,12 +8381,12 @@
         <v>2.78</v>
       </c>
       <c r="X14" s="31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Y14" s="31">
         <v>-0.1885</v>
       </c>
-      <c r="AB14" s="102">
+      <c r="AB14" s="101">
         <v>45659</v>
       </c>
       <c r="AC14" s="31">
@@ -8400,12 +8402,12 @@
         <v>153.6</v>
       </c>
       <c r="AG14" s="31" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AH14" s="31">
         <v>-2.0799999999999999E-2</v>
       </c>
-      <c r="AK14" s="102">
+      <c r="AK14" s="101">
         <v>45659</v>
       </c>
       <c r="AL14" s="31">
@@ -8421,36 +8423,36 @@
         <v>67.55</v>
       </c>
       <c r="AP14" s="31" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AQ14" s="31">
         <v>-7.2800000000000004E-2</v>
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A15" s="102">
+      <c r="A15" s="101">
         <v>45658</v>
       </c>
-      <c r="B15" s="92">
+      <c r="B15" s="91">
         <v>3855.82</v>
       </c>
-      <c r="C15" s="92">
+      <c r="C15" s="91">
         <v>3790.36</v>
       </c>
-      <c r="D15" s="92">
+      <c r="D15" s="91">
         <v>3886.98</v>
       </c>
-      <c r="E15" s="92">
+      <c r="E15" s="91">
         <v>3765.41</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="G15" s="103">
+        <v>267</v>
+      </c>
+      <c r="G15" s="102">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="H15" s="31"/>
-      <c r="I15" s="102">
+      <c r="I15" s="101">
         <v>45658</v>
       </c>
       <c r="J15" s="31">
@@ -8466,12 +8468,12 @@
         <v>1.38</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="O15" s="103">
+        <v>328</v>
+      </c>
+      <c r="O15" s="102">
         <v>-4.7300000000000002E-2</v>
       </c>
-      <c r="S15" s="102">
+      <c r="S15" s="101">
         <v>45658</v>
       </c>
       <c r="T15" s="31">
@@ -8487,7 +8489,7 @@
         <v>3.41</v>
       </c>
       <c r="X15" s="31" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y15" s="31">
         <v>4.3700000000000003E-2</v>
@@ -8508,7 +8510,7 @@
         <v>149</v>
       </c>
       <c r="AG15" s="31" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AH15" s="31">
         <v>1.49E-2</v>
@@ -8529,36 +8531,36 @@
         <v>71.7</v>
       </c>
       <c r="AP15" s="31" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AQ15" s="31">
         <v>-7.3099999999999998E-2</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A16" s="102">
+      <c r="A16" s="101">
         <v>45303</v>
       </c>
-      <c r="B16" s="92">
+      <c r="B16" s="91">
         <v>3787.6</v>
       </c>
-      <c r="C16" s="92">
+      <c r="C16" s="91">
         <v>3760.39</v>
       </c>
-      <c r="D16" s="92">
+      <c r="D16" s="91">
         <v>3842.71</v>
       </c>
-      <c r="E16" s="92">
+      <c r="E16" s="91">
         <v>3715.52</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="G16" s="103">
+        <v>268</v>
+      </c>
+      <c r="G16" s="102">
         <v>1.29E-2</v>
       </c>
       <c r="H16" s="31"/>
-      <c r="I16" s="102">
+      <c r="I16" s="101">
         <v>45303</v>
       </c>
       <c r="J16" s="31">
@@ -8574,12 +8576,12 @@
         <v>1.44</v>
       </c>
       <c r="N16" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="O16" s="103">
+        <v>329</v>
+      </c>
+      <c r="O16" s="102">
         <v>1.37E-2</v>
       </c>
-      <c r="S16" s="102">
+      <c r="S16" s="101">
         <v>45303</v>
       </c>
       <c r="T16" s="31">
@@ -8595,12 +8597,12 @@
         <v>3.45</v>
       </c>
       <c r="X16" s="31" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Y16" s="31">
         <v>-6.1499999999999999E-2</v>
       </c>
-      <c r="AB16" s="102">
+      <c r="AB16" s="101">
         <v>45303</v>
       </c>
       <c r="AC16" s="31">
@@ -8616,12 +8618,12 @@
         <v>150.19999999999999</v>
       </c>
       <c r="AG16" s="31" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AH16" s="31">
         <v>6.1400000000000003E-2</v>
       </c>
-      <c r="AK16" s="102">
+      <c r="AK16" s="101">
         <v>45303</v>
       </c>
       <c r="AL16" s="31">
@@ -8637,36 +8639,36 @@
         <v>74.849999999999994</v>
       </c>
       <c r="AP16" s="31" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AQ16" s="31">
         <v>-8.6900000000000005E-2</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A17" s="102">
+      <c r="A17" s="101">
         <v>45302</v>
       </c>
-      <c r="B17" s="92">
+      <c r="B17" s="91">
         <v>3739.29</v>
       </c>
-      <c r="C17" s="92">
+      <c r="C17" s="91">
         <v>3527.13</v>
       </c>
-      <c r="D17" s="92">
+      <c r="D17" s="91">
         <v>3766.93</v>
       </c>
-      <c r="E17" s="92">
+      <c r="E17" s="91">
         <v>3524.33</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="G17" s="103">
+        <v>269</v>
+      </c>
+      <c r="G17" s="102">
         <v>5.0700000000000002E-2</v>
       </c>
       <c r="H17" s="31"/>
-      <c r="I17" s="102">
+      <c r="I17" s="101">
         <v>45302</v>
       </c>
       <c r="J17" s="31">
@@ -8682,12 +8684,12 @@
         <v>1.45</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="O17" s="103">
+        <v>330</v>
+      </c>
+      <c r="O17" s="102">
         <v>-6.7999999999999996E-3</v>
       </c>
-      <c r="S17" s="102">
+      <c r="S17" s="101">
         <v>45302</v>
       </c>
       <c r="T17" s="31">
@@ -8703,12 +8705,12 @@
         <v>3.69</v>
       </c>
       <c r="X17" s="31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Y17" s="31">
         <v>-5.1000000000000004E-3</v>
       </c>
-      <c r="AB17" s="102">
+      <c r="AB17" s="101">
         <v>45302</v>
       </c>
       <c r="AC17" s="31">
@@ -8724,12 +8726,12 @@
         <v>128.6</v>
       </c>
       <c r="AG17" s="31" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AH17" s="31">
         <v>0.1358</v>
       </c>
-      <c r="AK17" s="102">
+      <c r="AK17" s="101">
         <v>45302</v>
       </c>
       <c r="AL17" s="31">
@@ -8745,36 +8747,36 @@
         <v>66.75</v>
       </c>
       <c r="AP17" s="31" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AQ17" s="31">
         <v>0.25230000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A18" s="102">
+      <c r="A18" s="101">
         <v>45301</v>
       </c>
-      <c r="B18" s="92">
+      <c r="B18" s="91">
         <v>3558.88</v>
       </c>
-      <c r="C18" s="92">
+      <c r="C18" s="91">
         <v>3593.42</v>
       </c>
-      <c r="D18" s="92">
+      <c r="D18" s="91">
         <v>3644.18</v>
       </c>
-      <c r="E18" s="92">
+      <c r="E18" s="91">
         <v>3553.85</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="G18" s="103">
+        <v>270</v>
+      </c>
+      <c r="G18" s="102">
         <v>-7.4000000000000003E-3</v>
       </c>
       <c r="H18" s="31"/>
-      <c r="I18" s="102">
+      <c r="I18" s="101">
         <v>45301</v>
       </c>
       <c r="J18" s="31">
@@ -8790,12 +8792,12 @@
         <v>1.42</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="O18" s="103">
+        <v>331</v>
+      </c>
+      <c r="O18" s="102">
         <v>-2.6499999999999999E-2</v>
       </c>
-      <c r="S18" s="102">
+      <c r="S18" s="101">
         <v>45301</v>
       </c>
       <c r="T18" s="31">
@@ -8811,12 +8813,12 @@
         <v>3.79</v>
       </c>
       <c r="X18" s="31" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Y18" s="31">
         <v>-5.0799999999999998E-2</v>
       </c>
-      <c r="AB18" s="102">
+      <c r="AB18" s="101">
         <v>45301</v>
       </c>
       <c r="AC18" s="31">
@@ -8832,12 +8834,12 @@
         <v>131.5</v>
       </c>
       <c r="AG18" s="31" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AH18" s="31">
         <v>-8.7599999999999997E-2</v>
       </c>
-      <c r="AK18" s="102">
+      <c r="AK18" s="101">
         <v>45301</v>
       </c>
       <c r="AL18" s="31">
@@ -8853,36 +8855,36 @@
         <v>67.7</v>
       </c>
       <c r="AP18" s="31" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AQ18" s="31">
         <v>-5.7099999999999998E-2</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A19" s="102">
+      <c r="A19" s="101">
         <v>45300</v>
       </c>
-      <c r="B19" s="92">
+      <c r="B19" s="91">
         <v>3585.29</v>
       </c>
-      <c r="C19" s="92">
+      <c r="C19" s="91">
         <v>3442.71</v>
       </c>
-      <c r="D19" s="92">
+      <c r="D19" s="91">
         <v>3652.62</v>
       </c>
-      <c r="E19" s="92">
+      <c r="E19" s="91">
         <v>3412.47</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="G19" s="103">
+        <v>271</v>
+      </c>
+      <c r="G19" s="102">
         <v>4.1300000000000003E-2</v>
       </c>
       <c r="H19" s="31"/>
-      <c r="I19" s="102">
+      <c r="I19" s="101">
         <v>45300</v>
       </c>
       <c r="J19" s="31">
@@ -8898,12 +8900,12 @@
         <v>1.4</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="O19" s="103">
+        <v>332</v>
+      </c>
+      <c r="O19" s="102">
         <v>6.3399999999999998E-2</v>
       </c>
-      <c r="S19" s="102">
+      <c r="S19" s="101">
         <v>45300</v>
       </c>
       <c r="T19" s="31">
@@ -8919,12 +8921,12 @@
         <v>3.69</v>
       </c>
       <c r="X19" s="31" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Y19" s="31">
         <v>9.8400000000000001E-2</v>
       </c>
-      <c r="AB19" s="102">
+      <c r="AB19" s="101">
         <v>45300</v>
       </c>
       <c r="AC19" s="31">
@@ -8940,12 +8942,12 @@
         <v>141.9</v>
       </c>
       <c r="AG19" s="31" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AH19" s="31">
         <v>-6.9400000000000003E-2</v>
       </c>
-      <c r="AK19" s="102">
+      <c r="AK19" s="101">
         <v>45300</v>
       </c>
       <c r="AL19" s="31">
@@ -8961,36 +8963,36 @@
         <v>63.95</v>
       </c>
       <c r="AP19" s="31" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AQ19" s="31">
         <v>7.8399999999999997E-2</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A20" s="102">
+      <c r="A20" s="101">
         <v>45299</v>
       </c>
-      <c r="B20" s="92">
+      <c r="B20" s="91">
         <v>3442.93</v>
       </c>
-      <c r="C20" s="92">
+      <c r="C20" s="91">
         <v>3453.24</v>
       </c>
-      <c r="D20" s="92">
+      <c r="D20" s="91">
         <v>3454.53</v>
       </c>
-      <c r="E20" s="92">
+      <c r="E20" s="91">
         <v>3198.44</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="G20" s="103">
+        <v>272</v>
+      </c>
+      <c r="G20" s="102">
         <v>-3.8E-3</v>
       </c>
       <c r="H20" s="31"/>
-      <c r="I20" s="102">
+      <c r="I20" s="101">
         <v>45299</v>
       </c>
       <c r="J20" s="31">
@@ -9006,12 +9008,12 @@
         <v>1.35</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="O20" s="103">
+        <v>333</v>
+      </c>
+      <c r="O20" s="102">
         <v>1.43E-2</v>
       </c>
-      <c r="S20" s="102">
+      <c r="S20" s="101">
         <v>45299</v>
       </c>
       <c r="T20" s="31">
@@ -9027,12 +9029,12 @@
         <v>3.58</v>
       </c>
       <c r="X20" s="31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="Y20" s="31">
         <v>-0.2838</v>
       </c>
-      <c r="AB20" s="102">
+      <c r="AB20" s="101">
         <v>45299</v>
       </c>
       <c r="AC20" s="31">
@@ -9048,12 +9050,12 @@
         <v>154.19999999999999</v>
       </c>
       <c r="AG20" s="31" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AH20" s="31">
         <v>-0.10489999999999999</v>
       </c>
-      <c r="AK20" s="102">
+      <c r="AK20" s="101">
         <v>45299</v>
       </c>
       <c r="AL20" s="31">
@@ -9069,36 +9071,36 @@
         <v>50.65</v>
       </c>
       <c r="AP20" s="31" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AQ20" s="31">
         <v>0.2135</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A21" s="102">
+      <c r="A21" s="101">
         <v>45298</v>
       </c>
-      <c r="B21" s="92">
+      <c r="B21" s="91">
         <v>3455.94</v>
       </c>
-      <c r="C21" s="92">
+      <c r="C21" s="91">
         <v>3334.71</v>
       </c>
-      <c r="D21" s="92">
+      <c r="D21" s="91">
         <v>3509.2</v>
       </c>
-      <c r="E21" s="92">
+      <c r="E21" s="91">
         <v>3325.17</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="G21" s="103">
+        <v>273</v>
+      </c>
+      <c r="G21" s="102">
         <v>3.6900000000000002E-2</v>
       </c>
       <c r="H21" s="31"/>
-      <c r="I21" s="102">
+      <c r="I21" s="101">
         <v>45298</v>
       </c>
       <c r="J21" s="31">
@@ -9114,12 +9116,12 @@
         <v>1.33</v>
       </c>
       <c r="N21" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="O21" s="103">
+        <v>334</v>
+      </c>
+      <c r="O21" s="102">
         <v>4.48E-2</v>
       </c>
-      <c r="S21" s="102">
+      <c r="S21" s="101">
         <v>45298</v>
       </c>
       <c r="T21" s="31">
@@ -9135,12 +9137,12 @@
         <v>4.76</v>
       </c>
       <c r="X21" s="31" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y21" s="31">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="AB21" s="102">
+      <c r="AB21" s="101">
         <v>45298</v>
       </c>
       <c r="AC21" s="31">
@@ -9156,12 +9158,12 @@
         <v>157.4</v>
       </c>
       <c r="AG21" s="31" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH21" s="31">
         <v>0.108</v>
       </c>
-      <c r="AK21" s="102">
+      <c r="AK21" s="101">
         <v>45298</v>
       </c>
       <c r="AL21" s="31">
@@ -9177,36 +9179,36 @@
         <v>48.08</v>
       </c>
       <c r="AP21" s="31" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AQ21" s="31">
         <v>0.1009</v>
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A22" s="102">
+      <c r="A22" s="101">
         <v>45297</v>
       </c>
-      <c r="B22" s="92">
+      <c r="B22" s="91">
         <v>3332.8</v>
       </c>
-      <c r="C22" s="92">
+      <c r="C22" s="91">
         <v>3347.22</v>
       </c>
-      <c r="D22" s="92">
+      <c r="D22" s="91">
         <v>3355.63</v>
       </c>
-      <c r="E22" s="92">
+      <c r="E22" s="91">
         <v>3288.94</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="G22" s="103">
+        <v>274</v>
+      </c>
+      <c r="G22" s="102">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="H22" s="31"/>
-      <c r="I22" s="102">
+      <c r="I22" s="101">
         <v>45297</v>
       </c>
       <c r="J22" s="31">
@@ -9222,12 +9224,12 @@
         <v>1.32</v>
       </c>
       <c r="N22" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="O22" s="103">
+        <v>335</v>
+      </c>
+      <c r="O22" s="102">
         <v>-3.5999999999999997E-2</v>
       </c>
-      <c r="S22" s="102">
+      <c r="S22" s="101">
         <v>45297</v>
       </c>
       <c r="T22" s="31">
@@ -9243,12 +9245,12 @@
         <v>4.8600000000000003</v>
       </c>
       <c r="X22" s="31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Y22" s="31">
         <v>-5.7999999999999996E-3</v>
       </c>
-      <c r="AB22" s="102">
+      <c r="AB22" s="101">
         <v>45297</v>
       </c>
       <c r="AC22" s="31">
@@ -9264,12 +9266,12 @@
         <v>150</v>
       </c>
       <c r="AG22" s="31" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AH22" s="31">
         <v>-7.2599999999999998E-2</v>
       </c>
-      <c r="AK22" s="102">
+      <c r="AK22" s="101">
         <v>45297</v>
       </c>
       <c r="AL22" s="31">
@@ -9285,36 +9287,36 @@
         <v>45.5</v>
       </c>
       <c r="AP22" s="31" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AQ22" s="31">
         <v>-5.11E-2</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A23" s="102">
+      <c r="A23" s="101">
         <v>45296</v>
       </c>
-      <c r="B23" s="92">
+      <c r="B23" s="91">
         <v>3336.59</v>
       </c>
-      <c r="C23" s="92">
+      <c r="C23" s="91">
         <v>3309.78</v>
       </c>
-      <c r="D23" s="92">
+      <c r="D23" s="91">
         <v>3336.59</v>
       </c>
-      <c r="E23" s="92">
+      <c r="E23" s="91">
         <v>3241.13</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="G23" s="103">
+        <v>275</v>
+      </c>
+      <c r="G23" s="102">
         <v>1.3299999999999999E-2</v>
       </c>
       <c r="H23" s="31"/>
-      <c r="I23" s="102">
+      <c r="I23" s="101">
         <v>45296</v>
       </c>
       <c r="J23" s="31">
@@ -9330,12 +9332,12 @@
         <v>1.36</v>
       </c>
       <c r="N23" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="O23" s="103">
+        <v>336</v>
+      </c>
+      <c r="O23" s="102">
         <v>-6.7100000000000007E-2</v>
       </c>
-      <c r="S23" s="102">
+      <c r="S23" s="101">
         <v>45296</v>
       </c>
       <c r="T23" s="31">
@@ -9351,12 +9353,12 @@
         <v>5.0199999999999996</v>
       </c>
       <c r="X23" s="31" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Y23" s="31">
         <v>-6.83E-2</v>
       </c>
-      <c r="AB23" s="102">
+      <c r="AB23" s="101">
         <v>45296</v>
       </c>
       <c r="AC23" s="31">
@@ -9372,12 +9374,12 @@
         <v>161.4</v>
       </c>
       <c r="AG23" s="31" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AH23" s="31">
         <v>5.2400000000000002E-2</v>
       </c>
-      <c r="AK23" s="102">
+      <c r="AK23" s="101">
         <v>45296</v>
       </c>
       <c r="AL23" s="31">
@@ -9393,36 +9395,36 @@
         <v>53.4</v>
       </c>
       <c r="AP23" s="31" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AQ23" s="31">
         <v>-2.8899999999999999E-2</v>
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A24" s="102">
+      <c r="A24" s="101">
         <v>45295</v>
       </c>
-      <c r="B24" s="92">
+      <c r="B24" s="91">
         <v>3292.69</v>
       </c>
-      <c r="C24" s="92">
+      <c r="C24" s="91">
         <v>3231.48</v>
       </c>
-      <c r="D24" s="92">
+      <c r="D24" s="91">
         <v>3308.12</v>
       </c>
-      <c r="E24" s="92">
+      <c r="E24" s="91">
         <v>3136.44</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" s="103">
+        <v>276</v>
+      </c>
+      <c r="G24" s="102">
         <v>2.1299999999999999E-2</v>
       </c>
       <c r="H24" s="31"/>
-      <c r="I24" s="102">
+      <c r="I24" s="101">
         <v>45295</v>
       </c>
       <c r="J24" s="31">
@@ -9438,12 +9440,12 @@
         <v>1.4</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>339</v>
-      </c>
-      <c r="O24" s="103">
+        <v>337</v>
+      </c>
+      <c r="O24" s="102">
         <v>6.4299999999999996E-2</v>
       </c>
-      <c r="S24" s="102">
+      <c r="S24" s="101">
         <v>45295</v>
       </c>
       <c r="T24" s="31">
@@ -9459,12 +9461,12 @@
         <v>5.34</v>
       </c>
       <c r="X24" s="31" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Y24" s="31">
         <v>-3.8100000000000002E-2</v>
       </c>
-      <c r="AB24" s="102">
+      <c r="AB24" s="101">
         <v>45295</v>
       </c>
       <c r="AC24" s="31">
@@ -9480,12 +9482,12 @@
         <v>155.80000000000001</v>
       </c>
       <c r="AG24" s="31" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AH24" s="31">
         <v>-0.1009</v>
       </c>
-      <c r="AK24" s="102">
+      <c r="AK24" s="101">
         <v>45295</v>
       </c>
       <c r="AL24" s="31">
@@ -9501,36 +9503,36 @@
         <v>51.5</v>
       </c>
       <c r="AP24" s="31" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AQ24" s="31">
         <v>-0.20399999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A25" s="102">
+      <c r="A25" s="101">
         <v>45294</v>
       </c>
-      <c r="B25" s="92">
+      <c r="B25" s="91">
         <v>3224.01</v>
       </c>
-      <c r="C25" s="92">
+      <c r="C25" s="91">
         <v>3151.07</v>
       </c>
-      <c r="D25" s="92">
+      <c r="D25" s="91">
         <v>3262.52</v>
       </c>
-      <c r="E25" s="92">
+      <c r="E25" s="91">
         <v>3101.24</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="G25" s="103">
+        <v>277</v>
+      </c>
+      <c r="G25" s="102">
         <v>2.6200000000000001E-2</v>
       </c>
       <c r="H25" s="31"/>
-      <c r="I25" s="102">
+      <c r="I25" s="101">
         <v>45294</v>
       </c>
       <c r="J25" s="31">
@@ -9546,12 +9548,12 @@
         <v>1.34</v>
       </c>
       <c r="N25" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="O25" s="103">
+        <v>338</v>
+      </c>
+      <c r="O25" s="102">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="S25" s="102">
+      <c r="S25" s="101">
         <v>45294</v>
       </c>
       <c r="T25" s="31">
@@ -9567,12 +9569,12 @@
         <v>5.67</v>
       </c>
       <c r="X25" s="31" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Y25" s="31">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="AB25" s="102">
+      <c r="AB25" s="101">
         <v>45294</v>
       </c>
       <c r="AC25" s="31">
@@ -9588,12 +9590,12 @@
         <v>148.1</v>
       </c>
       <c r="AG25" s="31" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AH25" s="31">
         <v>0.14030000000000001</v>
       </c>
-      <c r="AK25" s="102">
+      <c r="AK25" s="101">
         <v>45294</v>
       </c>
       <c r="AL25" s="31">
@@ -9609,36 +9611,36 @@
         <v>61.5</v>
       </c>
       <c r="AP25" s="31" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AQ25" s="31">
         <v>-0.1077</v>
       </c>
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A26" s="102">
+      <c r="A26" s="101">
         <v>45293</v>
       </c>
-      <c r="B26" s="92">
+      <c r="B26" s="91">
         <v>3141.85</v>
       </c>
-      <c r="C26" s="92">
+      <c r="C26" s="91">
         <v>3144.18</v>
       </c>
-      <c r="D26" s="92">
+      <c r="D26" s="91">
         <v>3247.63</v>
       </c>
-      <c r="E26" s="92">
+      <c r="E26" s="91">
         <v>3092.4</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="G26" s="103">
+        <v>278</v>
+      </c>
+      <c r="G26" s="102">
         <v>-3.5000000000000001E-3</v>
       </c>
       <c r="H26" s="31"/>
-      <c r="I26" s="102">
+      <c r="I26" s="101">
         <v>45293</v>
       </c>
       <c r="J26" s="31">
@@ -9654,12 +9656,12 @@
         <v>1.34</v>
       </c>
       <c r="N26" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="O26" s="103">
+        <v>339</v>
+      </c>
+      <c r="O26" s="102">
         <v>-3.5700000000000003E-2</v>
       </c>
-      <c r="S26" s="102">
+      <c r="S26" s="101">
         <v>45293</v>
       </c>
       <c r="T26" s="31">
@@ -9675,12 +9677,12 @@
         <v>5.5</v>
       </c>
       <c r="X26" s="31" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Y26" s="31">
         <v>-0.1588</v>
       </c>
-      <c r="AB26" s="102">
+      <c r="AB26" s="101">
         <v>45293</v>
       </c>
       <c r="AC26" s="31">
@@ -9696,12 +9698,12 @@
         <v>148</v>
       </c>
       <c r="AG26" s="31" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AH26" s="31">
         <v>-6.2199999999999998E-2</v>
       </c>
-      <c r="AK26" s="102">
+      <c r="AK26" s="101">
         <v>45293</v>
       </c>
       <c r="AL26" s="31">
@@ -9717,36 +9719,36 @@
         <v>63</v>
       </c>
       <c r="AP26" s="31" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AQ26" s="31">
         <v>-9.1399999999999995E-2</v>
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A27" s="102">
+      <c r="A27" s="101">
         <v>45292</v>
       </c>
-      <c r="B27" s="92">
+      <c r="B27" s="91">
         <v>3153.01</v>
       </c>
-      <c r="C27" s="92">
+      <c r="C27" s="91">
         <v>3240.83</v>
       </c>
-      <c r="D27" s="92">
+      <c r="D27" s="91">
         <v>3259.28</v>
       </c>
-      <c r="E27" s="92">
+      <c r="E27" s="91">
         <v>3126.29</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="G27" s="103">
+        <v>279</v>
+      </c>
+      <c r="G27" s="102">
         <v>-2.69E-2</v>
       </c>
       <c r="H27" s="31"/>
-      <c r="I27" s="102">
+      <c r="I27" s="101">
         <v>45292</v>
       </c>
       <c r="J27" s="31">
@@ -9762,12 +9764,12 @@
         <v>1.37</v>
       </c>
       <c r="N27" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="O27" s="103">
-        <v>0</v>
-      </c>
-      <c r="S27" s="102">
+        <v>340</v>
+      </c>
+      <c r="O27" s="102">
+        <v>0</v>
+      </c>
+      <c r="S27" s="101">
         <v>45292</v>
       </c>
       <c r="T27" s="31">
@@ -9783,12 +9785,12 @@
         <v>6.74</v>
       </c>
       <c r="X27" s="31" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Y27" s="31">
         <v>2.5700000000000001E-2</v>
       </c>
-      <c r="AB27" s="102">
+      <c r="AB27" s="101">
         <v>45292</v>
       </c>
       <c r="AC27" s="31">
@@ -9804,12 +9806,12 @@
         <v>158.22999999999999</v>
       </c>
       <c r="AG27" s="31" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AH27" s="31">
         <v>-3.5999999999999997E-2</v>
       </c>
-      <c r="AK27" s="102">
+      <c r="AK27" s="101">
         <v>45292</v>
       </c>
       <c r="AL27" s="31">
@@ -9825,36 +9827,36 @@
         <v>80</v>
       </c>
       <c r="AP27" s="31" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AQ27" s="31">
         <v>1.4800000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A28" s="102">
+      <c r="A28" s="101">
         <v>44938</v>
       </c>
-      <c r="B28" s="92">
+      <c r="B28" s="91">
         <v>3240.27</v>
       </c>
-      <c r="C28" s="92">
+      <c r="C28" s="91">
         <v>3081.25</v>
       </c>
-      <c r="D28" s="92">
+      <c r="D28" s="91">
         <v>3250.05</v>
       </c>
-      <c r="E28" s="92">
+      <c r="E28" s="91">
         <v>3052.35</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="G28" s="103">
+        <v>280</v>
+      </c>
+      <c r="G28" s="102">
         <v>5.4399999999999997E-2</v>
       </c>
       <c r="H28" s="31"/>
-      <c r="I28" s="102">
+      <c r="I28" s="101">
         <v>44938</v>
       </c>
       <c r="J28" s="31">
@@ -9870,12 +9872,12 @@
         <v>1.28</v>
       </c>
       <c r="N28" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="O28" s="103">
+        <v>341</v>
+      </c>
+      <c r="O28" s="102">
         <v>8.5300000000000001E-2</v>
       </c>
-      <c r="S28" s="102">
+      <c r="S28" s="101">
         <v>44938</v>
       </c>
       <c r="T28" s="31">
@@ -9891,7 +9893,7 @@
         <v>6.49</v>
       </c>
       <c r="X28" s="31" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Y28" s="31">
         <v>5.5800000000000002E-2</v>
@@ -9912,7 +9914,7 @@
         <v>154</v>
       </c>
       <c r="AG28" s="31" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AH28" s="31">
         <v>9.2399999999999996E-2</v>
@@ -9933,36 +9935,36 @@
         <v>64.349999999999994</v>
       </c>
       <c r="AP28" s="31" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AQ28" s="31">
         <v>0.26550000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A29" s="102">
+      <c r="A29" s="101">
         <v>44937</v>
       </c>
-      <c r="B29" s="92">
+      <c r="B29" s="91">
         <v>3072.99</v>
       </c>
-      <c r="C29" s="92">
+      <c r="C29" s="91">
         <v>3071.74</v>
       </c>
-      <c r="D29" s="92">
+      <c r="D29" s="91">
         <v>3180.53</v>
       </c>
-      <c r="E29" s="92">
+      <c r="E29" s="91">
         <v>3061.6</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="G29" s="103">
+        <v>281</v>
+      </c>
+      <c r="G29" s="102">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="H29" s="31"/>
-      <c r="I29" s="102">
+      <c r="I29" s="101">
         <v>44937</v>
       </c>
       <c r="J29" s="31">
@@ -9978,12 +9980,12 @@
         <v>1.28</v>
       </c>
       <c r="N29" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="O29" s="103">
+        <v>342</v>
+      </c>
+      <c r="O29" s="102">
         <v>-2.2700000000000001E-2</v>
       </c>
-      <c r="S29" s="102">
+      <c r="S29" s="101">
         <v>44937</v>
       </c>
       <c r="T29" s="31">
@@ -9999,12 +10001,12 @@
         <v>5.97</v>
       </c>
       <c r="X29" s="31" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Y29" s="31">
         <v>0.1013</v>
       </c>
-      <c r="AB29" s="102">
+      <c r="AB29" s="101">
         <v>44937</v>
       </c>
       <c r="AC29" s="31">
@@ -10020,12 +10022,12 @@
         <v>151</v>
       </c>
       <c r="AG29" s="31" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AH29" s="31">
         <v>1.46E-2</v>
       </c>
-      <c r="AK29" s="102">
+      <c r="AK29" s="101">
         <v>44937</v>
       </c>
       <c r="AL29" s="31">
@@ -10041,36 +10043,36 @@
         <v>59.05</v>
       </c>
       <c r="AP29" s="31" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AQ29" s="31">
         <v>6.9599999999999995E-2</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A30" s="102">
+      <c r="A30" s="101">
         <v>44936</v>
       </c>
-      <c r="B30" s="92">
+      <c r="B30" s="91">
         <v>3067.74</v>
       </c>
-      <c r="C30" s="92">
+      <c r="C30" s="91">
         <v>3226.53</v>
       </c>
-      <c r="D30" s="92">
+      <c r="D30" s="91">
         <v>3232.09</v>
       </c>
-      <c r="E30" s="92">
+      <c r="E30" s="91">
         <v>3041.67</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="G30" s="103">
+        <v>282</v>
+      </c>
+      <c r="G30" s="102">
         <v>-4.65E-2</v>
       </c>
       <c r="H30" s="31"/>
-      <c r="I30" s="102">
+      <c r="I30" s="101">
         <v>44936</v>
       </c>
       <c r="J30" s="31">
@@ -10086,12 +10088,12 @@
         <v>1.27</v>
       </c>
       <c r="N30" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="O30" s="103">
+        <v>343</v>
+      </c>
+      <c r="O30" s="102">
         <v>1.54E-2</v>
       </c>
-      <c r="S30" s="102">
+      <c r="S30" s="101">
         <v>44936</v>
       </c>
       <c r="T30" s="31">
@@ -10107,12 +10109,12 @@
         <v>5.3</v>
       </c>
       <c r="X30" s="31" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Y30" s="31">
         <v>5.0599999999999999E-2</v>
       </c>
-      <c r="AB30" s="102">
+      <c r="AB30" s="101">
         <v>44936</v>
       </c>
       <c r="AC30" s="31">
@@ -10128,12 +10130,12 @@
         <v>139.9</v>
       </c>
       <c r="AG30" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AH30" s="31">
         <v>4.6399999999999997E-2</v>
       </c>
-      <c r="AK30" s="102">
+      <c r="AK30" s="101">
         <v>44936</v>
       </c>
       <c r="AL30" s="31">
@@ -10149,36 +10151,36 @@
         <v>54.55</v>
       </c>
       <c r="AP30" s="31" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AQ30" s="31">
         <v>-0.29620000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A31" s="102">
+      <c r="A31" s="101">
         <v>44935</v>
       </c>
-      <c r="B31" s="92">
+      <c r="B31" s="91">
         <v>3217.41</v>
       </c>
-      <c r="C31" s="92">
+      <c r="C31" s="91">
         <v>3240.53</v>
       </c>
-      <c r="D31" s="92">
+      <c r="D31" s="91">
         <v>3289.07</v>
       </c>
-      <c r="E31" s="92">
+      <c r="E31" s="91">
         <v>3179.33</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="G31" s="103">
+        <v>283</v>
+      </c>
+      <c r="G31" s="102">
         <v>-4.8999999999999998E-3</v>
       </c>
       <c r="H31" s="31"/>
-      <c r="I31" s="102">
+      <c r="I31" s="101">
         <v>44935</v>
       </c>
       <c r="J31" s="31">
@@ -10194,12 +10196,12 @@
         <v>1.25</v>
       </c>
       <c r="N31" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="O31" s="103">
+        <v>344</v>
+      </c>
+      <c r="O31" s="102">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="S31" s="102">
+      <c r="S31" s="101">
         <v>44935</v>
       </c>
       <c r="T31" s="31">
@@ -10215,12 +10217,12 @@
         <v>5.6</v>
       </c>
       <c r="X31" s="31" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="Y31" s="31">
         <v>-9.6199999999999994E-2</v>
       </c>
-      <c r="AB31" s="102">
+      <c r="AB31" s="101">
         <v>44935</v>
       </c>
       <c r="AC31" s="31">
@@ -10236,12 +10238,12 @@
         <v>140</v>
       </c>
       <c r="AG31" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AH31" s="31">
         <v>0.04</v>
       </c>
-      <c r="AK31" s="102">
+      <c r="AK31" s="101">
         <v>44935</v>
       </c>
       <c r="AL31" s="31">
@@ -10257,36 +10259,36 @@
         <v>82.2</v>
       </c>
       <c r="AP31" s="31" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AQ31" s="31">
         <v>6.0900000000000003E-2</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A32" s="102">
+      <c r="A32" s="101">
         <v>44934</v>
       </c>
-      <c r="B32" s="92">
+      <c r="B32" s="91">
         <v>3233.3</v>
       </c>
-      <c r="C32" s="92">
+      <c r="C32" s="91">
         <v>3383.07</v>
       </c>
-      <c r="D32" s="92">
+      <c r="D32" s="91">
         <v>3385.68</v>
       </c>
-      <c r="E32" s="92">
+      <c r="E32" s="91">
         <v>3143.9</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="G32" s="103">
+        <v>284</v>
+      </c>
+      <c r="G32" s="102">
         <v>-4.1700000000000001E-2</v>
       </c>
       <c r="H32" s="31"/>
-      <c r="I32" s="102">
+      <c r="I32" s="101">
         <v>44934</v>
       </c>
       <c r="J32" s="31">
@@ -10302,12 +10304,12 @@
         <v>1.23</v>
       </c>
       <c r="N32" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="O32" s="103">
+        <v>345</v>
+      </c>
+      <c r="O32" s="102">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="S32" s="102">
+      <c r="S32" s="101">
         <v>44934</v>
       </c>
       <c r="T32" s="31">
@@ -10323,12 +10325,12 @@
         <v>6.13</v>
       </c>
       <c r="X32" s="31" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Y32" s="31">
         <v>-8.5099999999999995E-2</v>
       </c>
-      <c r="AB32" s="102">
+      <c r="AB32" s="101">
         <v>44934</v>
       </c>
       <c r="AC32" s="31">
@@ -10344,12 +10346,12 @@
         <v>135</v>
       </c>
       <c r="AG32" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AH32" s="31">
         <v>-8.2000000000000007E-3</v>
       </c>
-      <c r="AK32" s="102">
+      <c r="AK32" s="101">
         <v>44934</v>
       </c>
       <c r="AL32" s="31">
@@ -10365,36 +10367,36 @@
         <v>75.3</v>
       </c>
       <c r="AP32" s="31" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AQ32" s="31">
         <v>-0.10340000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A33" s="102">
+      <c r="A33" s="101">
         <v>44933</v>
       </c>
-      <c r="B33" s="92">
+      <c r="B33" s="91">
         <v>3373.98</v>
       </c>
-      <c r="C33" s="92">
+      <c r="C33" s="91">
         <v>3215.56</v>
       </c>
-      <c r="D33" s="92">
+      <c r="D33" s="91">
         <v>3392.63</v>
       </c>
-      <c r="E33" s="92">
+      <c r="E33" s="91">
         <v>3128.7</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="G33" s="103">
+        <v>285</v>
+      </c>
+      <c r="G33" s="102">
         <v>5.2400000000000002E-2</v>
       </c>
       <c r="H33" s="31"/>
-      <c r="I33" s="102">
+      <c r="I33" s="101">
         <v>44933</v>
       </c>
       <c r="J33" s="31">
@@ -10410,12 +10412,12 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="N33" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="O33" s="103">
+        <v>346</v>
+      </c>
+      <c r="O33" s="102">
         <v>8.6199999999999999E-2</v>
       </c>
-      <c r="S33" s="102">
+      <c r="S33" s="101">
         <v>44933</v>
       </c>
       <c r="T33" s="31">
@@ -10431,12 +10433,12 @@
         <v>6.84</v>
       </c>
       <c r="X33" s="31" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Y33" s="31">
         <v>-4.5499999999999999E-2</v>
       </c>
-      <c r="AB33" s="102">
+      <c r="AB33" s="101">
         <v>44933</v>
       </c>
       <c r="AC33" s="31">
@@ -10452,12 +10454,12 @@
         <v>134.9</v>
       </c>
       <c r="AG33" s="31" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AH33" s="31">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="AK33" s="102">
+      <c r="AK33" s="101">
         <v>44933</v>
       </c>
       <c r="AL33" s="31">
@@ -10473,36 +10475,36 @@
         <v>90.5</v>
       </c>
       <c r="AP33" s="31" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AQ33" s="31">
         <v>-4.0099999999999997E-2</v>
       </c>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A34" s="102">
+      <c r="A34" s="101">
         <v>44932</v>
       </c>
-      <c r="B34" s="92">
+      <c r="B34" s="91">
         <v>3205.91</v>
       </c>
-      <c r="C34" s="92">
+      <c r="C34" s="91">
         <v>3162.52</v>
       </c>
-      <c r="D34" s="92">
+      <c r="D34" s="91">
         <v>3277.51</v>
       </c>
-      <c r="E34" s="92">
+      <c r="E34" s="91">
         <v>3155.52</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="G34" s="103">
+        <v>286</v>
+      </c>
+      <c r="G34" s="102">
         <v>1.49E-2</v>
       </c>
       <c r="H34" s="31"/>
-      <c r="I34" s="102">
+      <c r="I34" s="101">
         <v>44932</v>
       </c>
       <c r="J34" s="31">
@@ -10518,12 +10520,12 @@
         <v>1.01</v>
       </c>
       <c r="N34" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="O34" s="103">
+        <v>347</v>
+      </c>
+      <c r="O34" s="102">
         <v>5.45E-2</v>
       </c>
-      <c r="S34" s="102">
+      <c r="S34" s="101">
         <v>44932</v>
       </c>
       <c r="T34" s="31">
@@ -10539,12 +10541,12 @@
         <v>6.68</v>
       </c>
       <c r="X34" s="31" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="Y34" s="31">
         <v>6.7599999999999993E-2</v>
       </c>
-      <c r="AB34" s="102">
+      <c r="AB34" s="101">
         <v>44932</v>
       </c>
       <c r="AC34" s="31">
@@ -10560,12 +10562,12 @@
         <v>109.9</v>
       </c>
       <c r="AG34" s="31" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AH34" s="31">
         <v>0.27089999999999997</v>
       </c>
-      <c r="AK34" s="102">
+      <c r="AK34" s="101">
         <v>44932</v>
       </c>
       <c r="AL34" s="31">
@@ -10581,36 +10583,36 @@
         <v>95.51</v>
       </c>
       <c r="AP34" s="31" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AQ34" s="31">
         <v>-8.8599999999999998E-2</v>
       </c>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A35" s="102">
+      <c r="A35" s="101">
         <v>44931</v>
       </c>
-      <c r="B35" s="92">
+      <c r="B35" s="91">
         <v>3158.8</v>
       </c>
-      <c r="C35" s="92">
+      <c r="C35" s="91">
         <v>3291.43</v>
       </c>
-      <c r="D35" s="92">
+      <c r="D35" s="91">
         <v>3309.68</v>
       </c>
-      <c r="E35" s="92">
+      <c r="E35" s="91">
         <v>3156.15</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="G35" s="103">
+        <v>287</v>
+      </c>
+      <c r="G35" s="102">
         <v>-3.4200000000000001E-2</v>
       </c>
       <c r="H35" s="31"/>
-      <c r="I35" s="102">
+      <c r="I35" s="101">
         <v>44931</v>
       </c>
       <c r="J35" s="31">
@@ -10626,12 +10628,12 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="N35" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="O35" s="103">
+        <v>348</v>
+      </c>
+      <c r="O35" s="102">
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="S35" s="102">
+      <c r="S35" s="101">
         <v>44931</v>
       </c>
       <c r="T35" s="31">
@@ -10647,12 +10649,12 @@
         <v>6</v>
       </c>
       <c r="X35" s="31" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y35" s="31">
         <v>0.1148</v>
       </c>
-      <c r="AB35" s="102">
+      <c r="AB35" s="101">
         <v>44931</v>
       </c>
       <c r="AC35" s="31">
@@ -10668,12 +10670,12 @@
         <v>109.8</v>
       </c>
       <c r="AG35" s="31" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AH35" s="31">
         <v>2.1399999999999999E-2</v>
       </c>
-      <c r="AK35" s="102">
+      <c r="AK35" s="101">
         <v>44931</v>
       </c>
       <c r="AL35" s="31">
@@ -10689,36 +10691,36 @@
         <v>103.7</v>
       </c>
       <c r="AP35" s="31" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AQ35" s="31">
         <v>-0.1211</v>
       </c>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A36" s="102">
+      <c r="A36" s="101">
         <v>44930</v>
       </c>
-      <c r="B36" s="92">
+      <c r="B36" s="91">
         <v>3270.51</v>
       </c>
-      <c r="C36" s="92">
+      <c r="C36" s="91">
         <v>3272.48</v>
       </c>
-      <c r="D36" s="92">
+      <c r="D36" s="91">
         <v>3331.66</v>
       </c>
-      <c r="E36" s="92">
+      <c r="E36" s="91">
         <v>3263.36</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="G36" s="103">
+        <v>288</v>
+      </c>
+      <c r="G36" s="102">
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="H36" s="31"/>
-      <c r="I36" s="102">
+      <c r="I36" s="101">
         <v>44930</v>
       </c>
       <c r="J36" s="31">
@@ -10734,12 +10736,12 @@
         <v>1.1559999999999999</v>
       </c>
       <c r="N36" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="O36" s="103">
+        <v>349</v>
+      </c>
+      <c r="O36" s="102">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="S36" s="102">
+      <c r="S36" s="101">
         <v>44930</v>
       </c>
       <c r="T36" s="31">
@@ -10755,12 +10757,12 @@
         <v>5.57</v>
       </c>
       <c r="X36" s="31" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y36" s="31">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="AB36" s="102">
+      <c r="AB36" s="101">
         <v>44930</v>
       </c>
       <c r="AC36" s="31">
@@ -10776,12 +10778,12 @@
         <v>98.1</v>
       </c>
       <c r="AG36" s="31" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AH36" s="31">
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="AK36" s="102">
+      <c r="AK36" s="101">
         <v>44930</v>
       </c>
       <c r="AL36" s="31">
@@ -10797,36 +10799,36 @@
         <v>115.3</v>
       </c>
       <c r="AP36" s="31" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AQ36" s="31">
         <v>-2.5000000000000001E-3</v>
       </c>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A37" s="102">
+      <c r="A37" s="101">
         <v>44929</v>
       </c>
-      <c r="B37" s="92">
+      <c r="B37" s="91">
         <v>3258.9</v>
       </c>
-      <c r="C37" s="92">
+      <c r="C37" s="91">
         <v>3265.5</v>
       </c>
-      <c r="D37" s="92">
+      <c r="D37" s="91">
         <v>3275.1</v>
       </c>
-      <c r="E37" s="92">
+      <c r="E37" s="91">
         <v>3094.28</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="G37" s="103">
+        <v>289</v>
+      </c>
+      <c r="G37" s="102">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="H37" s="31"/>
-      <c r="I37" s="102">
+      <c r="I37" s="101">
         <v>44929</v>
       </c>
       <c r="J37" s="31">
@@ -10842,12 +10844,12 @@
         <v>1.137</v>
       </c>
       <c r="N37" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="O37" s="103">
+        <v>350</v>
+      </c>
+      <c r="O37" s="102">
         <v>-2.4799999999999999E-2</v>
       </c>
-      <c r="S37" s="102">
+      <c r="S37" s="101">
         <v>44929</v>
       </c>
       <c r="T37" s="31">
@@ -10863,12 +10865,12 @@
         <v>5.61</v>
       </c>
       <c r="X37" s="31" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Y37" s="31">
         <v>-9.6199999999999994E-2</v>
       </c>
-      <c r="AB37" s="102">
+      <c r="AB37" s="101">
         <v>44929</v>
       </c>
       <c r="AC37" s="31">
@@ -10884,12 +10886,12 @@
         <v>92.66</v>
       </c>
       <c r="AG37" s="31" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AH37" s="31">
         <v>-1.52E-2</v>
       </c>
-      <c r="AK37" s="102">
+      <c r="AK37" s="101">
         <v>44929</v>
       </c>
       <c r="AL37" s="31">
@@ -10905,36 +10907,36 @@
         <v>111.1</v>
       </c>
       <c r="AP37" s="31" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AQ37" s="31">
         <v>-2.2499999999999999E-2</v>
       </c>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A38" s="102">
+      <c r="A38" s="101">
         <v>44928</v>
       </c>
-      <c r="B38" s="92">
+      <c r="B38" s="91">
         <v>3262.63</v>
       </c>
-      <c r="C38" s="92">
+      <c r="C38" s="91">
         <v>3385.36</v>
       </c>
-      <c r="D38" s="92">
+      <c r="D38" s="91">
         <v>3397.32</v>
       </c>
-      <c r="E38" s="92">
+      <c r="E38" s="91">
         <v>3260.58</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="G38" s="103">
+        <v>290</v>
+      </c>
+      <c r="G38" s="102">
         <v>-3.0599999999999999E-2</v>
       </c>
       <c r="H38" s="31"/>
-      <c r="I38" s="102">
+      <c r="I38" s="101">
         <v>44928</v>
       </c>
       <c r="J38" s="31">
@@ -10950,12 +10952,12 @@
         <v>1.127</v>
       </c>
       <c r="N38" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="O38" s="103">
+        <v>351</v>
+      </c>
+      <c r="O38" s="102">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="S38" s="102">
+      <c r="S38" s="101">
         <v>44928</v>
       </c>
       <c r="T38" s="31">
@@ -10971,12 +10973,12 @@
         <v>5.63</v>
       </c>
       <c r="X38" s="31" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="Y38" s="31">
         <v>0.12520000000000001</v>
       </c>
-      <c r="AB38" s="102">
+      <c r="AB38" s="101">
         <v>44928</v>
       </c>
       <c r="AC38" s="31">
@@ -10992,12 +10994,12 @@
         <v>99.3</v>
       </c>
       <c r="AG38" s="31" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AH38" s="31">
         <v>-2.6800000000000001E-2</v>
       </c>
-      <c r="AK38" s="102">
+      <c r="AK38" s="101">
         <v>44928</v>
       </c>
       <c r="AL38" s="31">
@@ -11013,36 +11015,36 @@
         <v>119</v>
       </c>
       <c r="AP38" s="31" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AQ38" s="31">
         <v>-6.5299999999999997E-2</v>
       </c>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A39" s="102">
+      <c r="A39" s="101">
         <v>44927</v>
       </c>
-      <c r="B39" s="92">
+      <c r="B39" s="91">
         <v>3365.67</v>
       </c>
-      <c r="C39" s="92">
+      <c r="C39" s="91">
         <v>3243.99</v>
       </c>
-      <c r="D39" s="92">
+      <c r="D39" s="91">
         <v>3408.19</v>
       </c>
-      <c r="E39" s="92">
+      <c r="E39" s="91">
         <v>3212.63</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="G39" s="103">
+        <v>291</v>
+      </c>
+      <c r="G39" s="102">
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="H39" s="31"/>
-      <c r="I39" s="102">
+      <c r="I39" s="101">
         <v>44927</v>
       </c>
       <c r="J39" s="31">
@@ -11058,12 +11060,12 @@
         <v>1.107</v>
       </c>
       <c r="N39" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="O39" s="103">
+        <v>352</v>
+      </c>
+      <c r="O39" s="102">
         <v>-2.4400000000000002E-2</v>
       </c>
-      <c r="S39" s="102">
+      <c r="S39" s="101">
         <v>44927</v>
       </c>
       <c r="T39" s="31">
@@ -11079,12 +11081,12 @@
         <v>5.53</v>
       </c>
       <c r="X39" s="31" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Y39" s="31">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="AB39" s="102">
+      <c r="AB39" s="101">
         <v>44927</v>
       </c>
       <c r="AC39" s="31">
@@ -11100,12 +11102,12 @@
         <v>101</v>
       </c>
       <c r="AG39" s="31" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AH39" s="31">
         <v>7.3300000000000004E-2</v>
       </c>
-      <c r="AK39" s="102">
+      <c r="AK39" s="101">
         <v>44927</v>
       </c>
       <c r="AL39" s="31">
@@ -11121,36 +11123,36 @@
         <v>130</v>
       </c>
       <c r="AP39" s="31" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AQ39" s="31">
         <v>2.46E-2</v>
       </c>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A40" s="102">
+      <c r="A40" s="101">
         <v>44573</v>
       </c>
-      <c r="B40" s="92">
+      <c r="B40" s="91">
         <v>3251.32</v>
       </c>
-      <c r="C40" s="92">
+      <c r="C40" s="91">
         <v>3306.49</v>
       </c>
-      <c r="D40" s="92">
+      <c r="D40" s="91">
         <v>3313.8</v>
       </c>
-      <c r="E40" s="92">
+      <c r="E40" s="91">
         <v>3225.45</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>294</v>
-      </c>
-      <c r="G40" s="103">
+        <v>292</v>
+      </c>
+      <c r="G40" s="102">
         <v>-1.1900000000000001E-2</v>
       </c>
       <c r="H40" s="31"/>
-      <c r="I40" s="102">
+      <c r="I40" s="101">
         <v>44573</v>
       </c>
       <c r="J40" s="31">
@@ -11166,12 +11168,12 @@
         <v>1.1859999999999999</v>
       </c>
       <c r="N40" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="O40" s="103">
-        <v>0</v>
-      </c>
-      <c r="S40" s="102">
+        <v>353</v>
+      </c>
+      <c r="O40" s="102">
+        <v>0</v>
+      </c>
+      <c r="S40" s="101">
         <v>44573</v>
       </c>
       <c r="T40" s="31">
@@ -11187,12 +11189,12 @@
         <v>5.27</v>
       </c>
       <c r="X40" s="31" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="Y40" s="31">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="AB40" s="102">
+      <c r="AB40" s="101">
         <v>44573</v>
       </c>
       <c r="AC40" s="31">
@@ -11208,12 +11210,12 @@
         <v>94.15</v>
       </c>
       <c r="AG40" s="31" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AH40" s="31">
         <v>-1.0800000000000001E-2</v>
       </c>
-      <c r="AK40" s="102">
+      <c r="AK40" s="101">
         <v>44573</v>
       </c>
       <c r="AL40" s="31">
@@ -11229,36 +11231,36 @@
         <v>124.7</v>
       </c>
       <c r="AP40" s="31" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AQ40" s="31">
         <v>-0.24640000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A41" s="102">
+      <c r="A41" s="101">
         <v>44572</v>
       </c>
-      <c r="B41" s="92">
+      <c r="B41" s="91">
         <v>3290.49</v>
       </c>
-      <c r="C41" s="92">
+      <c r="C41" s="91">
         <v>3107</v>
       </c>
-      <c r="D41" s="92">
+      <c r="D41" s="91">
         <v>3308.3</v>
       </c>
-      <c r="E41" s="92">
+      <c r="E41" s="91">
         <v>3091.18</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="G41" s="103">
+        <v>293</v>
+      </c>
+      <c r="G41" s="102">
         <v>6.3799999999999996E-2</v>
       </c>
       <c r="H41" s="31"/>
-      <c r="I41" s="102">
+      <c r="I41" s="101">
         <v>44572</v>
       </c>
       <c r="J41" s="31">
@@ -11274,12 +11276,12 @@
         <v>1.1859999999999999</v>
       </c>
       <c r="N41" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="O41" s="103">
+        <v>354</v>
+      </c>
+      <c r="O41" s="102">
         <v>-3.15E-2</v>
       </c>
-      <c r="S41" s="102">
+      <c r="S41" s="101">
         <v>44572</v>
       </c>
       <c r="T41" s="31">
@@ -11295,7 +11297,7 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="X41" s="31" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y41" s="31">
         <v>0.1734</v>
@@ -11316,7 +11318,7 @@
         <v>89.55</v>
       </c>
       <c r="AG41" s="31" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AH41" s="31">
         <v>-2.9499999999999998E-2</v>
@@ -11337,36 +11339,36 @@
         <v>166.1</v>
       </c>
       <c r="AP41" s="31" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AQ41" s="31">
         <v>1.95E-2</v>
       </c>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A42" s="102">
+      <c r="A42" s="101">
         <v>44571</v>
       </c>
-      <c r="B42" s="92">
+      <c r="B42" s="91">
         <v>3093.11</v>
       </c>
-      <c r="C42" s="92">
+      <c r="C42" s="91">
         <v>3113</v>
       </c>
-      <c r="D42" s="92">
+      <c r="D42" s="91">
         <v>3168.4</v>
       </c>
-      <c r="E42" s="92">
+      <c r="E42" s="91">
         <v>2968.87</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="G42" s="103">
+        <v>262</v>
+      </c>
+      <c r="G42" s="102">
         <v>-1.1900000000000001E-2</v>
       </c>
       <c r="H42" s="31"/>
-      <c r="I42" s="102">
+      <c r="I42" s="101">
         <v>44571</v>
       </c>
       <c r="J42" s="31">
@@ -11382,12 +11384,12 @@
         <v>1.2050000000000001</v>
       </c>
       <c r="N42" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="O42" s="103">
+        <v>355</v>
+      </c>
+      <c r="O42" s="102">
         <v>-3.7900000000000003E-2</v>
       </c>
-      <c r="S42" s="102">
+      <c r="S42" s="101">
         <v>44571</v>
       </c>
       <c r="T42" s="31">
@@ -11403,12 +11405,12 @@
         <v>4.26</v>
       </c>
       <c r="X42" s="31" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="Y42" s="31">
         <v>-3.3099999999999997E-2</v>
       </c>
-      <c r="AB42" s="102">
+      <c r="AB42" s="101">
         <v>44571</v>
       </c>
       <c r="AC42" s="31">
@@ -11424,12 +11426,12 @@
         <v>100</v>
       </c>
       <c r="AG42" s="31" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AH42" s="31">
         <v>0</v>
       </c>
-      <c r="AK42" s="102">
+      <c r="AK42" s="101">
         <v>44571</v>
       </c>
       <c r="AL42" s="31">
@@ -11445,36 +11447,36 @@
         <v>156.5</v>
       </c>
       <c r="AP42" s="31" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AQ42" s="31">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A43" s="102">
+      <c r="A43" s="101">
         <v>44570</v>
       </c>
-      <c r="B43" s="92">
+      <c r="B43" s="91">
         <v>3130.24</v>
       </c>
-      <c r="C43" s="92">
+      <c r="C43" s="91">
         <v>3211.56</v>
       </c>
-      <c r="D43" s="92">
+      <c r="D43" s="91">
         <v>3297.59</v>
       </c>
-      <c r="E43" s="92">
+      <c r="E43" s="91">
         <v>3098.24</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="G43" s="103">
+        <v>294</v>
+      </c>
+      <c r="G43" s="102">
         <v>-2.8400000000000002E-2</v>
       </c>
       <c r="H43" s="31"/>
-      <c r="I43" s="102">
+      <c r="I43" s="101">
         <v>44570</v>
       </c>
       <c r="J43" s="31">
@@ -11490,12 +11492,12 @@
         <v>1.264</v>
       </c>
       <c r="N43" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="O43" s="103">
+        <v>356</v>
+      </c>
+      <c r="O43" s="102">
         <v>-6.3799999999999996E-2</v>
       </c>
-      <c r="S43" s="102">
+      <c r="S43" s="101">
         <v>44570</v>
       </c>
       <c r="T43" s="31">
@@ -11511,12 +11513,12 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="X43" s="31" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Y43" s="31">
         <v>-0.1138</v>
       </c>
-      <c r="AB43" s="102">
+      <c r="AB43" s="101">
         <v>44570</v>
       </c>
       <c r="AC43" s="31">
@@ -11532,12 +11534,12 @@
         <v>103.1</v>
       </c>
       <c r="AG43" s="31" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AH43" s="31">
         <v>-8.5999999999999993E-2</v>
       </c>
-      <c r="AK43" s="102">
+      <c r="AK43" s="101">
         <v>44570</v>
       </c>
       <c r="AL43" s="31">
@@ -11553,36 +11555,36 @@
         <v>156.5</v>
       </c>
       <c r="AP43" s="31" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AQ43" s="31">
         <v>-3.8199999999999998E-2</v>
       </c>
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A44" s="102">
+      <c r="A44" s="101">
         <v>44569</v>
       </c>
-      <c r="B44" s="92">
+      <c r="B44" s="91">
         <v>3221.67</v>
       </c>
-      <c r="C44" s="92">
+      <c r="C44" s="91">
         <v>3238.18</v>
       </c>
-      <c r="D44" s="92">
+      <c r="D44" s="91">
         <v>3307.29</v>
       </c>
-      <c r="E44" s="92">
+      <c r="E44" s="91">
         <v>3205.58</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="G44" s="103">
+        <v>295</v>
+      </c>
+      <c r="G44" s="102">
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="H44" s="31"/>
-      <c r="I44" s="102">
+      <c r="I44" s="101">
         <v>44569</v>
       </c>
       <c r="J44" s="31">
@@ -11598,12 +11600,12 @@
         <v>1.3720000000000001</v>
       </c>
       <c r="N44" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="O44" s="103">
+        <v>357</v>
+      </c>
+      <c r="O44" s="102">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="S44" s="102">
+      <c r="S44" s="101">
         <v>44569</v>
       </c>
       <c r="T44" s="31">
@@ -11619,12 +11621,12 @@
         <v>5.14</v>
       </c>
       <c r="X44" s="31" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="Y44" s="31">
         <v>-0.1051</v>
       </c>
-      <c r="AB44" s="102">
+      <c r="AB44" s="101">
         <v>44569</v>
       </c>
       <c r="AC44" s="31">
@@ -11640,12 +11642,12 @@
         <v>105.3</v>
       </c>
       <c r="AG44" s="31" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AH44" s="31">
         <v>-0.13780000000000001</v>
       </c>
-      <c r="AK44" s="102">
+      <c r="AK44" s="101">
         <v>44569</v>
       </c>
       <c r="AL44" s="31">
@@ -11661,36 +11663,36 @@
         <v>167.3</v>
       </c>
       <c r="AP44" s="31" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AQ44" s="31">
         <v>-4.5699999999999998E-2</v>
       </c>
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A45" s="102">
+      <c r="A45" s="101">
         <v>44568</v>
       </c>
-      <c r="B45" s="92">
+      <c r="B45" s="91">
         <v>3211.56</v>
       </c>
-      <c r="C45" s="92">
+      <c r="C45" s="91">
         <v>3104.25</v>
       </c>
-      <c r="D45" s="92">
+      <c r="D45" s="91">
         <v>3244.29</v>
       </c>
-      <c r="E45" s="92">
+      <c r="E45" s="91">
         <v>3088.25</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="G45" s="103">
+        <v>296</v>
+      </c>
+      <c r="G45" s="102">
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="H45" s="31"/>
-      <c r="I45" s="102">
+      <c r="I45" s="101">
         <v>44568</v>
       </c>
       <c r="J45" s="31">
@@ -11706,12 +11708,12 @@
         <v>1.33</v>
       </c>
       <c r="N45" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="O45" s="103">
+        <v>358</v>
+      </c>
+      <c r="O45" s="102">
         <v>1.43E-2</v>
       </c>
-      <c r="S45" s="102">
+      <c r="S45" s="101">
         <v>44568</v>
       </c>
       <c r="T45" s="31">
@@ -11727,12 +11729,12 @@
         <v>5.29</v>
       </c>
       <c r="X45" s="31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Y45" s="31">
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="AB45" s="102">
+      <c r="AB45" s="101">
         <v>44568</v>
       </c>
       <c r="AC45" s="31">
@@ -11748,12 +11750,12 @@
         <v>122.2</v>
       </c>
       <c r="AG45" s="31" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AH45" s="31">
         <v>4.7100000000000003E-2</v>
       </c>
-      <c r="AK45" s="102">
+      <c r="AK45" s="101">
         <v>44568</v>
       </c>
       <c r="AL45" s="31">
@@ -11769,36 +11771,36 @@
         <v>167.1</v>
       </c>
       <c r="AP45" s="31" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AQ45" s="31">
         <v>-5.45E-2</v>
       </c>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A46" s="102">
+      <c r="A46" s="101">
         <v>44567</v>
       </c>
-      <c r="B46" s="92">
+      <c r="B46" s="91">
         <v>3102.21</v>
       </c>
-      <c r="C46" s="92">
+      <c r="C46" s="91">
         <v>3242.92</v>
       </c>
-      <c r="D46" s="92">
+      <c r="D46" s="91">
         <v>3253.15</v>
       </c>
-      <c r="E46" s="92">
+      <c r="E46" s="91">
         <v>3072.34</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="G46" s="103">
+        <v>297</v>
+      </c>
+      <c r="G46" s="102">
         <v>-4.0300000000000002E-2</v>
       </c>
       <c r="H46" s="31"/>
-      <c r="I46" s="102">
+      <c r="I46" s="101">
         <v>44567</v>
       </c>
       <c r="J46" s="31">
@@ -11814,12 +11816,12 @@
         <v>1.31</v>
       </c>
       <c r="N46" s="31" t="s">
-        <v>361</v>
-      </c>
-      <c r="O46" s="103">
+        <v>359</v>
+      </c>
+      <c r="O46" s="102">
         <v>-2.7799999999999998E-2</v>
       </c>
-      <c r="S46" s="102">
+      <c r="S46" s="101">
         <v>44567</v>
       </c>
       <c r="T46" s="31">
@@ -11835,12 +11837,12 @@
         <v>5.62</v>
       </c>
       <c r="X46" s="31" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Y46" s="31">
         <v>-0.24299999999999999</v>
       </c>
-      <c r="AB46" s="102">
+      <c r="AB46" s="101">
         <v>44567</v>
       </c>
       <c r="AC46" s="31">
@@ -11856,12 +11858,12 @@
         <v>121.4</v>
       </c>
       <c r="AG46" s="31" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AH46" s="31">
         <v>-6.59E-2</v>
       </c>
-      <c r="AK46" s="102">
+      <c r="AK46" s="101">
         <v>44567</v>
       </c>
       <c r="AL46" s="31">
@@ -11877,36 +11879,36 @@
         <v>189.9</v>
       </c>
       <c r="AP46" s="31" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AQ46" s="31">
         <v>-0.2681</v>
       </c>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A47" s="102">
+      <c r="A47" s="101">
         <v>44566</v>
       </c>
-      <c r="B47" s="92">
+      <c r="B47" s="91">
         <v>3232.49</v>
       </c>
-      <c r="C47" s="92">
+      <c r="C47" s="91">
         <v>3365.43</v>
       </c>
-      <c r="D47" s="92">
+      <c r="D47" s="91">
         <v>3373.15</v>
       </c>
-      <c r="E47" s="92">
+      <c r="E47" s="91">
         <v>3165.18</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="G47" s="103">
+        <v>298</v>
+      </c>
+      <c r="G47" s="102">
         <v>-3.7100000000000001E-2</v>
       </c>
       <c r="H47" s="31"/>
-      <c r="I47" s="102">
+      <c r="I47" s="101">
         <v>44566</v>
       </c>
       <c r="J47" s="31">
@@ -11922,12 +11924,12 @@
         <v>1.34</v>
       </c>
       <c r="N47" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="O47" s="103">
+        <v>360</v>
+      </c>
+      <c r="O47" s="102">
         <v>-2.0400000000000001E-2</v>
       </c>
-      <c r="S47" s="102">
+      <c r="S47" s="101">
         <v>44566</v>
       </c>
       <c r="T47" s="31">
@@ -11943,12 +11945,12 @@
         <v>7.26</v>
       </c>
       <c r="X47" s="31" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Y47" s="31">
         <v>-5.04E-2</v>
       </c>
-      <c r="AB47" s="102">
+      <c r="AB47" s="101">
         <v>44566</v>
       </c>
       <c r="AC47" s="31">
@@ -11964,12 +11966,12 @@
         <v>101.95</v>
       </c>
       <c r="AG47" s="31" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AH47" s="31">
         <v>0.21010000000000001</v>
       </c>
-      <c r="AK47" s="102">
+      <c r="AK47" s="101">
         <v>44566</v>
       </c>
       <c r="AL47" s="31">
@@ -11985,36 +11987,36 @@
         <v>237.12</v>
       </c>
       <c r="AP47" s="31" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AQ47" s="31">
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A48" s="102">
+      <c r="A48" s="101">
         <v>44565</v>
       </c>
-      <c r="B48" s="92">
+      <c r="B48" s="91">
         <v>3356.9</v>
       </c>
-      <c r="C48" s="92">
+      <c r="C48" s="91">
         <v>3403.93</v>
       </c>
-      <c r="D48" s="92">
+      <c r="D48" s="91">
         <v>3445.9</v>
       </c>
-      <c r="E48" s="92">
+      <c r="E48" s="91">
         <v>3303.07</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="G48" s="103">
+        <v>299</v>
+      </c>
+      <c r="G48" s="102">
         <v>-1.5100000000000001E-2</v>
       </c>
       <c r="H48" s="31"/>
-      <c r="I48" s="102">
+      <c r="I48" s="101">
         <v>44565</v>
       </c>
       <c r="J48" s="31">
@@ -12030,12 +12032,12 @@
         <v>1.407</v>
       </c>
       <c r="N48" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="O48" s="103">
+        <v>361</v>
+      </c>
+      <c r="O48" s="102">
         <v>-1.34E-2</v>
       </c>
-      <c r="S48" s="102">
+      <c r="S48" s="101">
         <v>44565</v>
       </c>
       <c r="T48" s="31">
@@ -12051,12 +12053,12 @@
         <v>6.81</v>
       </c>
       <c r="X48" s="31" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="Y48" s="31">
         <v>0.12479999999999999</v>
       </c>
-      <c r="AB48" s="102">
+      <c r="AB48" s="101">
         <v>44565</v>
       </c>
       <c r="AC48" s="31">
@@ -12072,12 +12074,12 @@
         <v>100.8</v>
       </c>
       <c r="AG48" s="31" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AH48" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="AK48" s="102">
+      <c r="AK48" s="101">
         <v>44565</v>
       </c>
       <c r="AL48" s="31">
@@ -12093,36 +12095,36 @@
         <v>223</v>
       </c>
       <c r="AP48" s="31" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AQ48" s="31">
         <v>6.7799999999999999E-2</v>
       </c>
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A49" s="102">
+      <c r="A49" s="101">
         <v>44564</v>
       </c>
-      <c r="B49" s="92">
+      <c r="B49" s="91">
         <v>3408.52</v>
       </c>
-      <c r="C49" s="92">
+      <c r="C49" s="91">
         <v>3262.49</v>
       </c>
-      <c r="D49" s="92">
+      <c r="D49" s="91">
         <v>3456.09</v>
       </c>
-      <c r="E49" s="92">
+      <c r="E49" s="91">
         <v>3128.06</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="G49" s="103">
+        <v>300</v>
+      </c>
+      <c r="G49" s="102">
         <v>5.1299999999999998E-2</v>
       </c>
       <c r="H49" s="31"/>
-      <c r="I49" s="102">
+      <c r="I49" s="101">
         <v>44564</v>
       </c>
       <c r="J49" s="31">
@@ -12138,12 +12140,12 @@
         <v>1.2909999999999999</v>
       </c>
       <c r="N49" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="O49" s="103">
+        <v>362</v>
+      </c>
+      <c r="O49" s="102">
         <v>5.67E-2</v>
       </c>
-      <c r="S49" s="102">
+      <c r="S49" s="101">
         <v>44564</v>
       </c>
       <c r="T49" s="31">
@@ -12159,12 +12161,12 @@
         <v>6.67</v>
       </c>
       <c r="X49" s="31" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Y49" s="31">
         <v>-2.4899999999999999E-2</v>
       </c>
-      <c r="AB49" s="102">
+      <c r="AB49" s="101">
         <v>44564</v>
       </c>
       <c r="AC49" s="31">
@@ -12180,12 +12182,12 @@
         <v>83.75</v>
       </c>
       <c r="AG49" s="31" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AH49" s="31">
         <v>0.1208</v>
       </c>
-      <c r="AK49" s="102">
+      <c r="AK49" s="101">
         <v>44564</v>
       </c>
       <c r="AL49" s="31">
@@ -12201,36 +12203,36 @@
         <v>183.7</v>
       </c>
       <c r="AP49" s="31" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AQ49" s="31">
         <v>-2.4299999999999999E-2</v>
       </c>
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A50" s="102">
+      <c r="A50" s="101">
         <v>44563</v>
       </c>
-      <c r="B50" s="92">
+      <c r="B50" s="91">
         <v>3242.24</v>
       </c>
-      <c r="C50" s="92">
+      <c r="C50" s="91">
         <v>3302.23</v>
       </c>
-      <c r="D50" s="92">
+      <c r="D50" s="91">
         <v>3466.23</v>
       </c>
-      <c r="E50" s="92">
+      <c r="E50" s="91">
         <v>3214.93</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="G50" s="103">
+        <v>301</v>
+      </c>
+      <c r="G50" s="102">
         <v>-2.3E-3</v>
       </c>
       <c r="H50" s="31"/>
-      <c r="I50" s="102">
+      <c r="I50" s="101">
         <v>44563</v>
       </c>
       <c r="J50" s="31">
@@ -12246,12 +12248,12 @@
         <v>1.32</v>
       </c>
       <c r="N50" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="O50" s="103">
+        <v>363</v>
+      </c>
+      <c r="O50" s="102">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="S50" s="102">
+      <c r="S50" s="101">
         <v>44563</v>
       </c>
       <c r="T50" s="31">
@@ -12267,12 +12269,12 @@
         <v>6.61</v>
       </c>
       <c r="X50" s="31" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="Y50" s="31">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="AB50" s="102">
+      <c r="AB50" s="101">
         <v>44563</v>
       </c>
       <c r="AC50" s="31">
@@ -12288,12 +12290,12 @@
         <v>97.6</v>
       </c>
       <c r="AG50" s="31" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AH50" s="31">
         <v>-8.8999999999999999E-3</v>
       </c>
-      <c r="AK50" s="102">
+      <c r="AK50" s="101">
         <v>44563</v>
       </c>
       <c r="AL50" s="31">
@@ -12309,36 +12311,36 @@
         <v>230.8</v>
       </c>
       <c r="AP50" s="31" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AQ50" s="31">
         <v>-4.48E-2</v>
       </c>
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A51" s="102">
+      <c r="A51" s="101">
         <v>44562</v>
       </c>
-      <c r="B51" s="92">
+      <c r="B51" s="91">
         <v>3249.59</v>
       </c>
-      <c r="C51" s="92">
+      <c r="C51" s="91">
         <v>3130.48</v>
       </c>
-      <c r="D51" s="92">
+      <c r="D51" s="91">
         <v>3299.64</v>
       </c>
-      <c r="E51" s="92">
+      <c r="E51" s="91">
         <v>3127.6</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="G51" s="103">
+        <v>302</v>
+      </c>
+      <c r="G51" s="102">
         <v>4.0300000000000002E-2</v>
       </c>
       <c r="H51" s="31"/>
-      <c r="I51" s="102">
+      <c r="I51" s="101">
         <v>44562</v>
       </c>
       <c r="J51" s="31">
@@ -12354,12 +12356,12 @@
         <v>1.2909999999999999</v>
       </c>
       <c r="N51" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="O51" s="103">
+        <v>364</v>
+      </c>
+      <c r="O51" s="102">
         <v>-2.86E-2</v>
       </c>
-      <c r="S51" s="102">
+      <c r="S51" s="101">
         <v>44562</v>
       </c>
       <c r="T51" s="31">
@@ -12375,12 +12377,12 @@
         <v>6.34</v>
       </c>
       <c r="X51" s="31" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Y51" s="31">
         <v>-4.7399999999999998E-2</v>
       </c>
-      <c r="AB51" s="102">
+      <c r="AB51" s="101">
         <v>44562</v>
       </c>
       <c r="AC51" s="31">
@@ -12396,12 +12398,12 @@
         <v>97</v>
       </c>
       <c r="AG51" s="31" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AH51" s="31">
         <v>-1.0800000000000001E-2</v>
       </c>
-      <c r="AK51" s="102">
+      <c r="AK51" s="101">
         <v>44562</v>
       </c>
       <c r="AL51" s="31">
@@ -12417,36 +12419,36 @@
         <v>239.8</v>
       </c>
       <c r="AP51" s="31" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="AQ51" s="31">
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A52" s="102">
+      <c r="A52" s="101">
         <v>44208</v>
       </c>
-      <c r="B52" s="92">
+      <c r="B52" s="91">
         <v>3123.68</v>
       </c>
-      <c r="C52" s="92">
+      <c r="C52" s="91">
         <v>3052.4</v>
       </c>
-      <c r="D52" s="92">
+      <c r="D52" s="91">
         <v>3161.95</v>
       </c>
-      <c r="E52" s="92">
+      <c r="E52" s="91">
         <v>3045.13</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="G52" s="103">
+        <v>303</v>
+      </c>
+      <c r="G52" s="102">
         <v>2.7099999999999999E-2</v>
       </c>
       <c r="H52" s="31"/>
-      <c r="I52" s="102">
+      <c r="I52" s="101">
         <v>44208</v>
       </c>
       <c r="J52" s="31">
@@ -12462,12 +12464,12 @@
         <v>1.31</v>
       </c>
       <c r="N52" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="O52" s="103">
+        <v>365</v>
+      </c>
+      <c r="O52" s="102">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="S52" s="102">
+      <c r="S52" s="101">
         <v>44208</v>
       </c>
       <c r="T52" s="31">
@@ -12483,12 +12485,12 @@
         <v>6.1</v>
       </c>
       <c r="X52" s="31" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Y52" s="31">
         <v>0.14599999999999999</v>
       </c>
-      <c r="AB52" s="102">
+      <c r="AB52" s="101">
         <v>44208</v>
       </c>
       <c r="AC52" s="31">
@@ -12504,12 +12506,12 @@
         <v>90.5</v>
       </c>
       <c r="AG52" s="31" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AH52" s="31">
         <v>9.8900000000000002E-2</v>
       </c>
-      <c r="AK52" s="102">
+      <c r="AK52" s="101">
         <v>44208</v>
       </c>
       <c r="AL52" s="31">
@@ -12525,36 +12527,36 @@
         <v>214</v>
       </c>
       <c r="AP52" s="31" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AQ52" s="31">
         <v>0.2041</v>
       </c>
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A53" s="102">
+      <c r="A53" s="101">
         <v>44207</v>
       </c>
-      <c r="B53" s="92">
+      <c r="B53" s="91">
         <v>3041.29</v>
       </c>
-      <c r="C53" s="92">
+      <c r="C53" s="91">
         <v>3226.23</v>
       </c>
-      <c r="D53" s="92">
+      <c r="D53" s="91">
         <v>3273.54</v>
       </c>
-      <c r="E53" s="92">
+      <c r="E53" s="91">
         <v>3041.29</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="G53" s="103">
+        <v>304</v>
+      </c>
+      <c r="G53" s="102">
         <v>-4.9099999999999998E-2</v>
       </c>
       <c r="H53" s="31"/>
-      <c r="I53" s="102">
+      <c r="I53" s="101">
         <v>44207</v>
       </c>
       <c r="J53" s="31">
@@ -12570,12 +12572,12 @@
         <v>1.33</v>
       </c>
       <c r="N53" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="O53" s="103">
+        <v>366</v>
+      </c>
+      <c r="O53" s="102">
         <v>-0.12180000000000001</v>
       </c>
-      <c r="S53" s="102">
+      <c r="S53" s="101">
         <v>44207</v>
       </c>
       <c r="T53" s="31">
@@ -12591,12 +12593,12 @@
         <v>6.11</v>
       </c>
       <c r="X53" s="31" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Y53" s="31">
         <v>-0.1226</v>
       </c>
-      <c r="AB53" s="102">
+      <c r="AB53" s="101">
         <v>44207</v>
       </c>
       <c r="AC53" s="31">
@@ -12612,12 +12614,12 @@
         <v>92.7</v>
       </c>
       <c r="AG53" s="31" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AH53" s="31">
         <v>-7.7399999999999997E-2</v>
       </c>
-      <c r="AK53" s="102">
+      <c r="AK53" s="101">
         <v>44207</v>
       </c>
       <c r="AL53" s="31">
@@ -12633,36 +12635,36 @@
         <v>207.2</v>
       </c>
       <c r="AP53" s="31" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AQ53" s="31">
         <v>-6.5600000000000006E-2</v>
       </c>
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A54" s="102">
+      <c r="A54" s="101">
         <v>44206</v>
       </c>
-      <c r="B54" s="92">
+      <c r="B54" s="91">
         <v>3198.17</v>
       </c>
-      <c r="C54" s="92">
+      <c r="C54" s="91">
         <v>3072.54</v>
       </c>
-      <c r="D54" s="92">
+      <c r="D54" s="91">
         <v>3228.05</v>
       </c>
-      <c r="E54" s="92">
+      <c r="E54" s="91">
         <v>3044.73</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="G54" s="103">
+        <v>305</v>
+      </c>
+      <c r="G54" s="102">
         <v>3.61E-2</v>
       </c>
       <c r="H54" s="31"/>
-      <c r="I54" s="102">
+      <c r="I54" s="101">
         <v>44206</v>
       </c>
       <c r="J54" s="31">
@@ -12678,12 +12680,12 @@
         <v>1.456</v>
       </c>
       <c r="N54" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="O54" s="103">
+        <v>367</v>
+      </c>
+      <c r="O54" s="102">
         <v>3.3099999999999997E-2</v>
       </c>
-      <c r="S54" s="102">
+      <c r="S54" s="101">
         <v>44206</v>
       </c>
       <c r="T54" s="31">
@@ -12699,7 +12701,7 @@
         <v>7.11</v>
       </c>
       <c r="X54" s="31" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Y54" s="31">
         <v>-0.17530000000000001</v>
@@ -12720,7 +12722,7 @@
         <v>84</v>
       </c>
       <c r="AG54" s="31" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AH54" s="31">
         <v>0.13320000000000001</v>
@@ -12741,36 +12743,36 @@
         <v>215.87</v>
       </c>
       <c r="AP54" s="31" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AQ54" s="31">
         <v>-5.2200000000000003E-2</v>
       </c>
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A55" s="102">
+      <c r="A55" s="101">
         <v>44205</v>
       </c>
-      <c r="B55" s="92">
+      <c r="B55" s="91">
         <v>3086.7</v>
       </c>
-      <c r="C55" s="92">
+      <c r="C55" s="91">
         <v>3055.71</v>
       </c>
-      <c r="D55" s="92">
+      <c r="D55" s="91">
         <v>3108.53</v>
       </c>
-      <c r="E55" s="92">
+      <c r="E55" s="91">
         <v>3037.79</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="G55" s="103">
+        <v>306</v>
+      </c>
+      <c r="G55" s="102">
         <v>1.04E-2</v>
       </c>
       <c r="H55" s="31"/>
-      <c r="I55" s="102">
+      <c r="I55" s="101">
         <v>44205</v>
       </c>
       <c r="J55" s="31">
@@ -12786,12 +12788,12 @@
         <v>1.446</v>
       </c>
       <c r="N55" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="O55" s="103">
+        <v>368</v>
+      </c>
+      <c r="O55" s="102">
         <v>-6.7900000000000002E-2</v>
       </c>
-      <c r="S55" s="102">
+      <c r="S55" s="101">
         <v>44205</v>
       </c>
       <c r="T55" s="31">
@@ -12807,12 +12809,12 @@
         <v>8.16</v>
       </c>
       <c r="X55" s="31" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Y55" s="31">
         <v>-1.11E-2</v>
       </c>
-      <c r="AB55" s="102">
+      <c r="AB55" s="101">
         <v>44205</v>
       </c>
       <c r="AC55" s="31">
@@ -12828,12 +12830,12 @@
         <v>82.15</v>
       </c>
       <c r="AG55" s="31" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AH55" s="31">
         <v>-1.44E-2</v>
       </c>
-      <c r="AK55" s="102">
+      <c r="AK55" s="101">
         <v>44205</v>
       </c>
       <c r="AL55" s="31">
@@ -12849,36 +12851,36 @@
         <v>212.2</v>
       </c>
       <c r="AP55" s="31" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AQ55" s="31">
         <v>-6.0699999999999997E-2</v>
       </c>
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A56" s="102">
+      <c r="A56" s="101">
         <v>44204</v>
       </c>
-      <c r="B56" s="92">
+      <c r="B56" s="91">
         <v>3055.05</v>
       </c>
-      <c r="C56" s="92">
+      <c r="C56" s="91">
         <v>3176.42</v>
       </c>
-      <c r="D56" s="92">
+      <c r="D56" s="91">
         <v>3207.99</v>
       </c>
-      <c r="E56" s="92">
+      <c r="E56" s="91">
         <v>3050.24</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="G56" s="103">
+        <v>307</v>
+      </c>
+      <c r="G56" s="102">
         <v>-3.5299999999999998E-2</v>
       </c>
       <c r="H56" s="31"/>
-      <c r="I56" s="102">
+      <c r="I56" s="101">
         <v>44204</v>
       </c>
       <c r="J56" s="31">
@@ -12894,12 +12896,12 @@
         <v>1.5049999999999999</v>
       </c>
       <c r="N56" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="O56" s="103">
+        <v>369</v>
+      </c>
+      <c r="O56" s="102">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="S56" s="102">
+      <c r="S56" s="101">
         <v>44204</v>
       </c>
       <c r="T56" s="31">
@@ -12915,12 +12917,12 @@
         <v>8.74</v>
       </c>
       <c r="X56" s="31" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Y56" s="31">
         <v>-3.4299999999999997E-2</v>
       </c>
-      <c r="AB56" s="102">
+      <c r="AB56" s="101">
         <v>44204</v>
       </c>
       <c r="AC56" s="31">
@@ -12936,12 +12938,12 @@
         <v>82.2</v>
       </c>
       <c r="AG56" s="31" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AH56" s="31">
         <v>8.8700000000000001E-2</v>
       </c>
-      <c r="AK56" s="102">
+      <c r="AK56" s="101">
         <v>44204</v>
       </c>
       <c r="AL56" s="31">
@@ -12957,36 +12959,36 @@
         <v>251.8</v>
       </c>
       <c r="AP56" s="31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AQ56" s="31">
         <v>-5.5899999999999998E-2</v>
       </c>
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A57" s="102">
+      <c r="A57" s="101">
         <v>44203</v>
       </c>
-      <c r="B57" s="92">
+      <c r="B57" s="91">
         <v>3166.94</v>
       </c>
-      <c r="C57" s="92">
+      <c r="C57" s="91">
         <v>3140.25</v>
       </c>
-      <c r="D57" s="92">
+      <c r="D57" s="91">
         <v>3195.25</v>
       </c>
-      <c r="E57" s="92">
+      <c r="E57" s="91">
         <v>3095.35</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="G57" s="103">
+        <v>308</v>
+      </c>
+      <c r="G57" s="102">
         <v>1.17E-2</v>
       </c>
       <c r="H57" s="31"/>
-      <c r="I57" s="102">
+      <c r="I57" s="101">
         <v>44203</v>
       </c>
       <c r="J57" s="31">
@@ -13002,12 +13004,12 @@
         <v>1.5049999999999999</v>
       </c>
       <c r="N57" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="O57" s="103">
+        <v>370</v>
+      </c>
+      <c r="O57" s="102">
         <v>-4.2700000000000002E-2</v>
       </c>
-      <c r="S57" s="102">
+      <c r="S57" s="101">
         <v>44203</v>
       </c>
       <c r="T57" s="31">
@@ -13023,12 +13025,12 @@
         <v>8.7899999999999991</v>
       </c>
       <c r="X57" s="31" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Y57" s="31">
         <v>-1.6899999999999998E-2</v>
       </c>
-      <c r="AB57" s="102">
+      <c r="AB57" s="101">
         <v>44203</v>
       </c>
       <c r="AC57" s="31">
@@ -13044,12 +13046,12 @@
         <v>72.400000000000006</v>
       </c>
       <c r="AG57" s="31" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AH57" s="31">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="AK57" s="102">
+      <c r="AK57" s="101">
         <v>44203</v>
       </c>
       <c r="AL57" s="31">
@@ -13065,36 +13067,36 @@
         <v>226.8</v>
       </c>
       <c r="AP57" s="31" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AQ57" s="31">
         <v>2.0299999999999999E-2</v>
       </c>
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A58" s="102">
+      <c r="A58" s="101">
         <v>44202</v>
       </c>
-      <c r="B58" s="92">
+      <c r="B58" s="91">
         <v>3130.46</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C58" s="91">
         <v>3176.71</v>
       </c>
-      <c r="D58" s="92">
+      <c r="D58" s="91">
         <v>3188</v>
       </c>
-      <c r="E58" s="92">
+      <c r="E58" s="91">
         <v>3089.49</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="G58" s="103">
+        <v>309</v>
+      </c>
+      <c r="G58" s="102">
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="H58" s="31"/>
-      <c r="I58" s="102">
+      <c r="I58" s="101">
         <v>44202</v>
       </c>
       <c r="J58" s="31">
@@ -13110,12 +13112,12 @@
         <v>1.5629999999999999</v>
       </c>
       <c r="N58" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="O58" s="103">
+        <v>371</v>
+      </c>
+      <c r="O58" s="102">
         <v>-3.5299999999999998E-2</v>
       </c>
-      <c r="S58" s="102">
+      <c r="S58" s="101">
         <v>44202</v>
       </c>
       <c r="T58" s="31">
@@ -13131,12 +13133,12 @@
         <v>8.42</v>
       </c>
       <c r="X58" s="31" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Y58" s="31">
         <v>-2.7699999999999999E-2</v>
       </c>
-      <c r="AB58" s="102">
+      <c r="AB58" s="101">
         <v>44202</v>
       </c>
       <c r="AC58" s="31">
@@ -13152,12 +13154,12 @@
         <v>77.95</v>
       </c>
       <c r="AG58" s="31" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AH58" s="31">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="AK58" s="102">
+      <c r="AK58" s="101">
         <v>44202</v>
       </c>
       <c r="AL58" s="31">
@@ -13173,36 +13175,36 @@
         <v>258.2</v>
       </c>
       <c r="AP58" s="31" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AQ58" s="31">
         <v>-0.11840000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A59" s="102">
+      <c r="A59" s="101">
         <v>44201</v>
       </c>
-      <c r="B59" s="92">
+      <c r="B59" s="91">
         <v>3164.28</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C59" s="91">
         <v>3221.79</v>
       </c>
-      <c r="D59" s="92">
+      <c r="D59" s="91">
         <v>3221.94</v>
       </c>
-      <c r="E59" s="92">
+      <c r="E59" s="91">
         <v>3023.95</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="G59" s="103">
+        <v>310</v>
+      </c>
+      <c r="G59" s="102">
         <v>-1.6799999999999999E-2</v>
       </c>
       <c r="H59" s="31"/>
-      <c r="I59" s="102">
+      <c r="I59" s="101">
         <v>44201</v>
       </c>
       <c r="J59" s="31">
@@ -13218,12 +13220,12 @@
         <v>1.4950000000000001</v>
       </c>
       <c r="N59" s="31" t="s">
-        <v>374</v>
-      </c>
-      <c r="O59" s="103">
+        <v>372</v>
+      </c>
+      <c r="O59" s="102">
         <v>-1.1599999999999999E-2</v>
       </c>
-      <c r="S59" s="102">
+      <c r="S59" s="101">
         <v>44201</v>
       </c>
       <c r="T59" s="31">
@@ -13239,12 +13241,12 @@
         <v>9.44</v>
       </c>
       <c r="X59" s="31" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Y59" s="31">
         <v>-3.3700000000000001E-2</v>
       </c>
-      <c r="AB59" s="102">
+      <c r="AB59" s="101">
         <v>44201</v>
       </c>
       <c r="AC59" s="31">
@@ -13260,12 +13262,12 @@
         <v>72.099999999999994</v>
       </c>
       <c r="AG59" s="31" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AH59" s="31">
         <v>9.69E-2</v>
       </c>
-      <c r="AK59" s="102">
+      <c r="AK59" s="101">
         <v>44201</v>
       </c>
       <c r="AL59" s="31">
@@ -13281,36 +13283,36 @@
         <v>276.39999999999998</v>
       </c>
       <c r="AP59" s="31" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="AQ59" s="31">
         <v>9.2999999999999992E-3</v>
       </c>
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A60" s="102">
+      <c r="A60" s="101">
         <v>44200</v>
       </c>
-      <c r="B60" s="92">
+      <c r="B60" s="91">
         <v>3218.27</v>
       </c>
-      <c r="C60" s="92">
+      <c r="C60" s="91">
         <v>3187.17</v>
       </c>
-      <c r="D60" s="92">
+      <c r="D60" s="91">
         <v>3237.23</v>
       </c>
-      <c r="E60" s="92">
+      <c r="E60" s="91">
         <v>3145.28</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="G60" s="103">
+        <v>311</v>
+      </c>
+      <c r="G60" s="102">
         <v>1.67E-2</v>
       </c>
       <c r="H60" s="31"/>
-      <c r="I60" s="102">
+      <c r="I60" s="101">
         <v>44200</v>
       </c>
       <c r="J60" s="31">
@@ -13326,12 +13328,12 @@
         <v>1.66</v>
       </c>
       <c r="N60" s="31" t="s">
-        <v>375</v>
-      </c>
-      <c r="O60" s="103">
+        <v>373</v>
+      </c>
+      <c r="O60" s="102">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="S60" s="102">
+      <c r="S60" s="101">
         <v>44200</v>
       </c>
       <c r="T60" s="31">
@@ -13347,12 +13349,12 @@
         <v>8.9</v>
       </c>
       <c r="X60" s="31" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Y60" s="31">
         <v>0.1003</v>
       </c>
-      <c r="AB60" s="102">
+      <c r="AB60" s="101">
         <v>44200</v>
       </c>
       <c r="AC60" s="31">
@@ -13368,12 +13370,12 @@
         <v>72.05</v>
       </c>
       <c r="AG60" s="31" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AH60" s="31">
         <v>-0.1928</v>
       </c>
-      <c r="AK60" s="102">
+      <c r="AK60" s="101">
         <v>44200</v>
       </c>
       <c r="AL60" s="31">
@@ -13389,36 +13391,36 @@
         <v>295</v>
       </c>
       <c r="AP60" s="31" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AQ60" s="31">
         <v>-2.6599999999999999E-2</v>
       </c>
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A61" s="102">
+      <c r="A61" s="101">
         <v>44199</v>
       </c>
-      <c r="B61" s="92">
+      <c r="B61" s="91">
         <v>3165.34</v>
       </c>
-      <c r="C61" s="92">
+      <c r="C61" s="91">
         <v>2948.69</v>
       </c>
-      <c r="D61" s="92">
+      <c r="D61" s="91">
         <v>3204.24</v>
       </c>
-      <c r="E61" s="92">
+      <c r="E61" s="91">
         <v>2948.64</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="G61" s="103">
+        <v>312</v>
+      </c>
+      <c r="G61" s="102">
         <v>7.3300000000000004E-2</v>
       </c>
       <c r="H61" s="31"/>
-      <c r="I61" s="102">
+      <c r="I61" s="101">
         <v>44199</v>
       </c>
       <c r="J61" s="31">
@@ -13434,12 +13436,12 @@
         <v>1.5529999999999999</v>
       </c>
       <c r="N61" s="31" t="s">
-        <v>376</v>
-      </c>
-      <c r="O61" s="103">
+        <v>374</v>
+      </c>
+      <c r="O61" s="102">
         <v>6.2100000000000002E-2</v>
       </c>
-      <c r="S61" s="102">
+      <c r="S61" s="101">
         <v>44199</v>
       </c>
       <c r="T61" s="31">
@@ -13455,12 +13457,12 @@
         <v>7.7</v>
       </c>
       <c r="X61" s="31" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y61" s="31">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="AB61" s="102">
+      <c r="AB61" s="101">
         <v>44199</v>
       </c>
       <c r="AC61" s="31">
@@ -13476,12 +13478,12 @@
         <v>84.5</v>
       </c>
       <c r="AG61" s="31" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AH61" s="31">
         <v>2.2800000000000001E-2</v>
       </c>
-      <c r="AK61" s="102">
+      <c r="AK61" s="101">
         <v>44199</v>
       </c>
       <c r="AL61" s="31">
@@ -13497,36 +13499,36 @@
         <v>292.52</v>
       </c>
       <c r="AP61" s="31" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AQ61" s="31">
         <v>2.9399999999999999E-2</v>
       </c>
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A62" s="102">
+      <c r="A62" s="101">
         <v>44198</v>
       </c>
-      <c r="B62" s="92">
+      <c r="B62" s="91">
         <v>2949.04</v>
       </c>
-      <c r="C62" s="92">
+      <c r="C62" s="91">
         <v>2888.75</v>
       </c>
-      <c r="D62" s="92">
+      <c r="D62" s="91">
         <v>2976.36</v>
       </c>
-      <c r="E62" s="92">
+      <c r="E62" s="91">
         <v>2869.3</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="G62" s="103">
+        <v>313</v>
+      </c>
+      <c r="G62" s="102">
         <v>1.6E-2</v>
       </c>
       <c r="H62" s="31"/>
-      <c r="I62" s="102">
+      <c r="I62" s="101">
         <v>44198</v>
       </c>
       <c r="J62" s="31">
@@ -13542,12 +13544,12 @@
         <v>1.514</v>
       </c>
       <c r="N62" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="O62" s="103">
+        <v>375</v>
+      </c>
+      <c r="O62" s="102">
         <v>1.9E-2</v>
       </c>
-      <c r="S62" s="102">
+      <c r="S62" s="101">
         <v>44198</v>
       </c>
       <c r="T62" s="31">
@@ -13563,12 +13565,12 @@
         <v>6.1</v>
       </c>
       <c r="X62" s="31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Y62" s="31">
         <v>0.3256</v>
       </c>
-      <c r="AB62" s="102">
+      <c r="AB62" s="101">
         <v>44198</v>
       </c>
       <c r="AC62" s="31">
@@ -13584,12 +13586,12 @@
         <v>71.13</v>
       </c>
       <c r="AG62" s="31" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AH62" s="31">
         <v>0.25440000000000002</v>
       </c>
-      <c r="AK62" s="102">
+      <c r="AK62" s="101">
         <v>44198</v>
       </c>
       <c r="AL62" s="31">
@@ -13605,36 +13607,36 @@
         <v>245.6</v>
       </c>
       <c r="AP62" s="31" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AQ62" s="31">
         <v>0.19500000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A63" s="102">
+      <c r="A63" s="101">
         <v>44197</v>
       </c>
-      <c r="B63" s="92">
+      <c r="B63" s="91">
         <v>2902.52</v>
       </c>
-      <c r="C63" s="92">
+      <c r="C63" s="91">
         <v>2846.2</v>
       </c>
-      <c r="D63" s="92">
+      <c r="D63" s="91">
         <v>3017.15</v>
       </c>
-      <c r="E63" s="92">
+      <c r="E63" s="91">
         <v>2832.04</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="G63" s="103">
+        <v>314</v>
+      </c>
+      <c r="G63" s="102">
         <v>2.06E-2</v>
       </c>
       <c r="H63" s="31"/>
-      <c r="I63" s="102">
+      <c r="I63" s="101">
         <v>44197</v>
       </c>
       <c r="J63" s="31">
@@ -13650,12 +13652,12 @@
         <v>1.534</v>
       </c>
       <c r="N63" s="31" t="s">
-        <v>378</v>
-      </c>
-      <c r="O63" s="103">
+        <v>376</v>
+      </c>
+      <c r="O63" s="102">
         <v>-5.3900000000000003E-2</v>
       </c>
-      <c r="S63" s="102">
+      <c r="S63" s="101">
         <v>44197</v>
       </c>
       <c r="T63" s="31">
@@ -13671,12 +13673,12 @@
         <v>5.81</v>
       </c>
       <c r="X63" s="31" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Y63" s="31">
         <v>-3.5900000000000001E-2</v>
       </c>
-      <c r="AB63" s="102">
+      <c r="AB63" s="101">
         <v>44197</v>
       </c>
       <c r="AC63" s="31">
@@ -13692,12 +13694,12 @@
         <v>66.5</v>
       </c>
       <c r="AG63" s="31" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AH63" s="31">
         <v>-3.04E-2</v>
       </c>
-      <c r="AK63" s="102">
+      <c r="AK63" s="101">
         <v>44197</v>
       </c>
       <c r="AL63" s="31">
@@ -13713,7 +13715,7 @@
         <v>222.81</v>
       </c>
       <c r="AP63" s="31" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AQ63" s="31">
         <v>5.3900000000000003E-2</v>
@@ -13742,17 +13744,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
@@ -13857,11 +13859,11 @@
         <f>F12*(1+G48)</f>
         <v>5457</v>
       </c>
-      <c r="H12" s="107">
+      <c r="H12" s="106">
         <f t="shared" ref="H12:I12" si="1">G12*(1+H48)</f>
         <v>5566.14</v>
       </c>
-      <c r="I12" s="107">
+      <c r="I12" s="106">
         <f t="shared" si="1"/>
         <v>5683.0289400000001</v>
       </c>
@@ -15566,12 +15568,12 @@
         <v>94</v>
       </c>
       <c r="C72" s="34">
-        <f>-C$18/$C$12</f>
+        <f>-C$18/C$12</f>
         <v>2.3321791578241931E-2</v>
       </c>
       <c r="D72" s="34">
-        <f>-D$18/$C$12</f>
-        <v>2.0104992739863731E-2</v>
+        <f>-D$18/D$12</f>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="E72" s="36">
         <f>E$73+$J72</f>
@@ -15636,12 +15638,12 @@
         <v>96</v>
       </c>
       <c r="C74" s="34">
-        <f>-C$18/$C$12</f>
+        <f>-C$18/C$12</f>
         <v>2.3321791578241931E-2</v>
       </c>
       <c r="D74" s="34">
-        <f>-D$18/$C$12</f>
-        <v>2.0104992739863731E-2</v>
+        <f>-D$18/D$12</f>
+        <v>1.7791483809749733E-2</v>
       </c>
       <c r="E74" s="36">
         <f>E$73+$J74</f>
@@ -15720,11 +15722,11 @@
         <v>94</v>
       </c>
       <c r="C77" s="34">
-        <f>-C$19/C$12</f>
+        <f t="shared" ref="C77:D79" si="42">-C$19/C$12</f>
         <v>2.2807997319334299E-2</v>
       </c>
       <c r="D77" s="34">
-        <f>-D$19/D$12</f>
+        <f t="shared" si="42"/>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="E77" s="36">
@@ -15736,15 +15738,15 @@
         <v>1.4235954611947968E-2</v>
       </c>
       <c r="G77" s="36">
-        <f t="shared" ref="G77:I77" ca="1" si="42">G$78+$J77</f>
+        <f t="shared" ref="G77:I77" ca="1" si="43">G$78+$J77</f>
         <v>1.4235954611947968E-2</v>
       </c>
       <c r="H77" s="36">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v>1.4235954611947968E-2</v>
       </c>
       <c r="I77" s="36">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v>1.4235954611947968E-2</v>
       </c>
       <c r="J77" s="36">
@@ -15756,31 +15758,31 @@
         <v>95</v>
       </c>
       <c r="C78" s="34">
-        <f>-C$19/C$12</f>
+        <f t="shared" si="42"/>
         <v>2.2807997319334299E-2</v>
       </c>
       <c r="D78" s="34">
-        <f>-D$19/D$12</f>
+        <f t="shared" si="42"/>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="E78" s="34">
-        <f t="shared" ref="E78:I78" ca="1" si="43">-E$19/E$12</f>
+        <f t="shared" ref="E78:I78" ca="1" si="44">-E$19/E$12</f>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="F78" s="34">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="G78" s="34">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="H78" s="34">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="I78" s="34">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="J78" s="36"/>
@@ -15790,11 +15792,11 @@
         <v>96</v>
       </c>
       <c r="C79" s="34">
-        <f>-C$19/C$12</f>
+        <f t="shared" si="42"/>
         <v>2.2807997319334299E-2</v>
       </c>
       <c r="D79" s="34">
-        <f>-D$19/D$12</f>
+        <f t="shared" si="42"/>
         <v>2.4235954611947969E-2</v>
       </c>
       <c r="E79" s="36">
@@ -15806,15 +15808,15 @@
         <v>3.423595461194797E-2</v>
       </c>
       <c r="G79" s="36">
-        <f t="shared" ref="G79:I79" ca="1" si="44">G$78+$J79</f>
+        <f t="shared" ref="G79:I79" ca="1" si="45">G$78+$J79</f>
         <v>3.423595461194797E-2</v>
       </c>
       <c r="H79" s="36">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v>3.423595461194797E-2</v>
       </c>
       <c r="I79" s="36">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v>3.423595461194797E-2</v>
       </c>
       <c r="J79" s="36">
@@ -15856,15 +15858,15 @@
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="G81" s="39">
-        <f t="shared" ref="G81:I81" ca="1" si="45">OFFSET(G81,MATCH($C$9,$B82:$B84,0),)</f>
+        <f t="shared" ref="G81:I81" ca="1" si="46">OFFSET(G81,MATCH($C$9,$B82:$B84,0),)</f>
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="H81" s="39">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="I81" s="39">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="J81" s="36"/>
@@ -15890,15 +15892,15 @@
         <v>8.0321432807496138E-2</v>
       </c>
       <c r="G82" s="36">
-        <f t="shared" ref="G82:I82" si="46">G$83+$J82</f>
+        <f t="shared" ref="G82:I82" si="47">G$83+$J82</f>
         <v>8.0321432807496138E-2</v>
       </c>
       <c r="H82" s="36">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.0321432807496138E-2</v>
       </c>
       <c r="I82" s="36">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.0321432807496138E-2</v>
       </c>
       <c r="J82" s="36">
@@ -15926,15 +15928,15 @@
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="G83" s="34">
-        <f t="shared" ref="G83:I83" si="47">-SUM($D$20:$D$28)/$D$12</f>
+        <f t="shared" ref="G83:I83" si="48">-SUM($D$20:$D$28)/$D$12</f>
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="H83" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="I83" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>9.0321432807496133E-2</v>
       </c>
       <c r="J83" s="36"/>
@@ -15960,15 +15962,15 @@
         <v>0.10032143280749613</v>
       </c>
       <c r="G84" s="36">
-        <f t="shared" ref="G84:I84" si="48">G$83+$J84</f>
+        <f t="shared" ref="G84:I84" si="49">G$83+$J84</f>
         <v>0.10032143280749613</v>
       </c>
       <c r="H84" s="36">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.10032143280749613</v>
       </c>
       <c r="I84" s="36">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.10032143280749613</v>
       </c>
       <c r="J84" s="36">
@@ -16010,15 +16012,15 @@
         <v>8.8203665137789655E-2</v>
       </c>
       <c r="G86" s="39">
-        <f t="shared" ref="G86:I86" ca="1" si="49">OFFSET(G86,MATCH($C$9,$B87:$B89,0),)</f>
+        <f t="shared" ref="G86:I86" ca="1" si="50">OFFSET(G86,MATCH($C$9,$B87:$B89,0),)</f>
         <v>9.212079344876882E-2</v>
       </c>
       <c r="H86" s="39">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v>9.5287399952282054E-2</v>
       </c>
       <c r="I86" s="39">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v>9.7756483923284163E-2</v>
       </c>
       <c r="J86" s="36"/>
@@ -16044,15 +16046,15 @@
         <v>7.820366513778966E-2</v>
       </c>
       <c r="G87" s="36">
-        <f t="shared" ref="G87:I87" ca="1" si="50">G$88+$J87</f>
+        <f t="shared" ref="G87:I87" ca="1" si="51">G$88+$J87</f>
         <v>8.2120793448768825E-2</v>
       </c>
       <c r="H87" s="36">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v>8.5287399952282059E-2</v>
       </c>
       <c r="I87" s="36">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v>8.7756483923284168E-2</v>
       </c>
       <c r="J87" s="36">
@@ -16080,15 +16082,15 @@
         <v>8.8203665137789655E-2</v>
       </c>
       <c r="G88" s="34">
-        <f t="shared" ref="G88:I88" ca="1" si="51">-G$32/G$12</f>
+        <f t="shared" ref="G88:I88" ca="1" si="52">-G$32/G$12</f>
         <v>9.212079344876882E-2</v>
       </c>
       <c r="H88" s="34">
-        <f t="shared" ca="1" si="51"/>
+        <f t="shared" ca="1" si="52"/>
         <v>9.5287399952282054E-2</v>
       </c>
       <c r="I88" s="34">
-        <f t="shared" ca="1" si="51"/>
+        <f t="shared" ca="1" si="52"/>
         <v>9.7756483923284163E-2</v>
       </c>
       <c r="J88" s="36"/>
@@ -16114,15 +16116,15 @@
         <v>9.820366513778965E-2</v>
       </c>
       <c r="G89" s="36">
-        <f t="shared" ref="G89:I89" ca="1" si="52">G$88+$J89</f>
+        <f t="shared" ref="G89:I89" ca="1" si="53">G$88+$J89</f>
         <v>0.10212079344876882</v>
       </c>
       <c r="H89" s="36">
-        <f t="shared" ca="1" si="52"/>
+        <f t="shared" ca="1" si="53"/>
         <v>0.10528739995228205</v>
       </c>
       <c r="I89" s="36">
-        <f t="shared" ca="1" si="52"/>
+        <f t="shared" ca="1" si="53"/>
         <v>0.10775648392328416</v>
       </c>
       <c r="J89" s="36">
@@ -16164,15 +16166,15 @@
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="G91" s="40">
-        <f t="shared" ref="G91:I91" ca="1" si="53">OFFSET(G$91,MATCH($C$9,$B92:$B94,0),0)</f>
+        <f t="shared" ref="G91:I91" ca="1" si="54">OFFSET(G$91,MATCH($C$9,$B92:$B94,0),0)</f>
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="H91" s="40">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="54"/>
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="I91" s="40">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="54"/>
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="J91" s="36"/>
@@ -16198,15 +16200,15 @@
         <v>6.0327363302099387E-3</v>
       </c>
       <c r="G92" s="36">
-        <f t="shared" ref="G92:I92" si="54">G93+$J$92</f>
+        <f t="shared" ref="G92:I92" si="55">G93+$J$92</f>
         <v>6.0327363302099387E-3</v>
       </c>
       <c r="H92" s="36">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>6.0327363302099387E-3</v>
       </c>
       <c r="I92" s="36">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>6.0327363302099387E-3</v>
       </c>
       <c r="J92" s="36">
@@ -16234,15 +16236,15 @@
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="G93" s="34">
-        <f t="shared" ref="G93:I93" si="55">$D$36/$D$12</f>
+        <f t="shared" ref="G93:I93" si="56">$D$36/$D$12</f>
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="H93" s="34">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="I93" s="34">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>4.0327363302099387E-3</v>
       </c>
       <c r="J93" s="36"/>
@@ -16268,15 +16270,15 @@
         <v>2.0327363302099387E-3</v>
       </c>
       <c r="G94" s="36">
-        <f t="shared" ref="G94:I94" si="56">G$93+$J94</f>
+        <f t="shared" ref="G94:I94" si="57">G$93+$J94</f>
         <v>2.0327363302099387E-3</v>
       </c>
       <c r="H94" s="36">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>2.0327363302099387E-3</v>
       </c>
       <c r="I94" s="36">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>2.0327363302099387E-3</v>
       </c>
       <c r="J94" s="36">
@@ -16318,15 +16320,15 @@
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="G96" s="40">
-        <f t="shared" ref="G96:I96" ca="1" si="57">OFFSET(G$96,MATCH($C$9,$B97:$B99,0),0)</f>
+        <f t="shared" ref="G96:I96" ca="1" si="58">OFFSET(G$96,MATCH($C$9,$B97:$B99,0),0)</f>
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="H96" s="40">
-        <f t="shared" ca="1" si="57"/>
+        <f t="shared" ca="1" si="58"/>
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="I96" s="40">
-        <f t="shared" ca="1" si="57"/>
+        <f t="shared" ca="1" si="58"/>
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="J96" s="36"/>
@@ -16352,15 +16354,15 @@
         <v>8.4376705017198423E-3</v>
       </c>
       <c r="G97" s="34">
-        <f t="shared" ref="G97:I97" si="58">G98+$J$97</f>
+        <f t="shared" ref="G97:I97" si="59">G98+$J$97</f>
         <v>8.4376705017198423E-3</v>
       </c>
       <c r="H97" s="34">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>8.4376705017198423E-3</v>
       </c>
       <c r="I97" s="34">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>8.4376705017198423E-3</v>
       </c>
       <c r="J97" s="36">
@@ -16388,15 +16390,15 @@
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="G98" s="34">
-        <f t="shared" ref="G98:I98" si="59">-$D$37/$D$12</f>
+        <f t="shared" ref="G98:I98" si="60">-$D$37/$D$12</f>
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="H98" s="34">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="I98" s="34">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.0437670501719842E-2</v>
       </c>
       <c r="J98" s="36"/>
@@ -16418,19 +16420,19 @@
         <v>1.2437670501719842E-2</v>
       </c>
       <c r="F99" s="34">
-        <f t="shared" ref="F99:I99" si="60">$E98+$J$99</f>
+        <f t="shared" ref="F99:I99" si="61">$E98+$J$99</f>
         <v>1.2437670501719842E-2</v>
       </c>
       <c r="G99" s="34">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1.2437670501719842E-2</v>
       </c>
       <c r="H99" s="34">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1.2437670501719842E-2</v>
       </c>
       <c r="I99" s="34">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1.2437670501719842E-2</v>
       </c>
       <c r="J99" s="36">
@@ -16472,15 +16474,15 @@
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="G101" s="40">
-        <f t="shared" ref="G101:I101" ca="1" si="61">OFFSET(G$101,MATCH($C$9,$B102:$B104,0),0)</f>
+        <f t="shared" ref="G101:I101" ca="1" si="62">OFFSET(G$101,MATCH($C$9,$B102:$B104,0),0)</f>
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="H101" s="40">
-        <f t="shared" ca="1" si="61"/>
+        <f t="shared" ca="1" si="62"/>
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="I101" s="40">
-        <f t="shared" ca="1" si="61"/>
+        <f t="shared" ca="1" si="62"/>
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="J101" s="36"/>
@@ -16506,15 +16508,15 @@
         <v>3.5814652275333096E-4</v>
       </c>
       <c r="G102" s="34">
-        <f t="shared" ref="G102:I102" si="62">G103+$J102</f>
+        <f t="shared" ref="G102:I102" si="63">G103+$J102</f>
         <v>3.5814652275333096E-4</v>
       </c>
       <c r="H102" s="34">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.5814652275333096E-4</v>
       </c>
       <c r="I102" s="34">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.5814652275333096E-4</v>
       </c>
       <c r="J102" s="36">
@@ -16542,15 +16544,15 @@
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="G103" s="34">
-        <f t="shared" ref="G103:I103" si="63">$D38/$D$12</f>
+        <f t="shared" ref="G103:I103" si="64">$D38/$D$12</f>
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="H103" s="34">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="I103" s="34">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.5814652275333095E-4</v>
       </c>
       <c r="J103" s="36"/>
@@ -16576,15 +16578,15 @@
         <v>-4.1853477246669058E-5</v>
       </c>
       <c r="G104" s="34">
-        <f t="shared" ref="G104:I104" si="64">G$103+$J104</f>
+        <f t="shared" ref="G104:I104" si="65">G$103+$J104</f>
         <v>-4.1853477246669058E-5</v>
       </c>
       <c r="H104" s="34">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-4.1853477246669058E-5</v>
       </c>
       <c r="I104" s="34">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-4.1853477246669058E-5</v>
       </c>
       <c r="J104" s="36">
@@ -16738,13 +16740,13 @@
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
-      <c r="E2" s="113" t="s">
+      <c r="E2" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="41" t="s">
@@ -19614,13 +19616,13 @@
         <v>132</v>
       </c>
       <c r="D1" s="49"/>
-      <c r="E1" s="114" t="s">
+      <c r="E1" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="41" t="s">
@@ -19894,31 +19896,31 @@
       <c r="B14" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="110">
+      <c r="C14" s="109">
         <f>'Profit &amp; loss'!C32</f>
         <v>-368.4</v>
       </c>
-      <c r="D14" s="110">
+      <c r="D14" s="109">
         <f>'Profit &amp; loss'!D32</f>
         <v>-399.6</v>
       </c>
-      <c r="E14" s="110">
+      <c r="E14" s="109">
         <f>E12+E5</f>
         <v>-437.32044448529803</v>
       </c>
-      <c r="F14" s="110">
+      <c r="F14" s="109">
         <f t="shared" ref="F14:I14" ca="1" si="5">F12+F5</f>
         <v>-471.88960848717466</v>
       </c>
-      <c r="G14" s="110">
+      <c r="G14" s="109">
         <f t="shared" ca="1" si="5"/>
         <v>-502.70316984993144</v>
       </c>
-      <c r="H14" s="110">
+      <c r="H14" s="109">
         <f t="shared" ca="1" si="5"/>
         <v>-530.38300837039526</v>
       </c>
-      <c r="I14" s="110">
+      <c r="I14" s="109">
         <f t="shared" ca="1" si="5"/>
         <v>-555.55292720866862</v>
       </c>
@@ -19948,13 +19950,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="114" t="s">
+      <c r="D1" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">

--- a/ComfortDelGro-Equity-Valuation.xlsx
+++ b/ComfortDelGro-Equity-Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChengJing\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE86053-7615-4E0A-B55E-DAD99D5505BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27C44D8-CE24-4986-BA6E-5DEF6D7ABCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{D93AAA56-1308-4026-9D8F-E913B55E5CC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D93AAA56-1308-4026-9D8F-E913B55E5CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Unlevered cash flow" sheetId="14" r:id="rId1"/>
@@ -2202,9 +2202,9 @@
     <numFmt numFmtId="171" formatCode="#\E"/>
     <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="173" formatCode="#,##0_ ;\-#,##0\ "/>
-    <numFmt numFmtId="175" formatCode="#,###.00\x"/>
-    <numFmt numFmtId="176" formatCode="#.##\x"/>
-    <numFmt numFmtId="177" formatCode="#.###\x"/>
+    <numFmt numFmtId="174" formatCode="#,###.00\x"/>
+    <numFmt numFmtId="175" formatCode="#.##\x"/>
+    <numFmt numFmtId="176" formatCode="#.###\x"/>
   </numFmts>
   <fonts count="32" x14ac:knownFonts="1">
     <font>
@@ -2870,7 +2870,7 @@
     <xf numFmtId="169" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2975,13 +2975,13 @@
     <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="173" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="20" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="20" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3011,10 +3011,12 @@
     <xf numFmtId="37" fontId="20" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3023,9 +3025,6 @@
     <xf numFmtId="0" fontId="19" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="20% - Accent1 2" xfId="21" xr:uid="{7F1DC058-3DA4-4945-98D8-2DC0ECB9F210}"/>
@@ -4727,7 +4726,7 @@
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C61" s="117"/>
+      <c r="C61" s="112"/>
       <c r="F61" s="42" t="s">
         <v>569</v>
       </c>
@@ -4893,20 +4892,20 @@
       <c r="B80" s="2">
         <v>4.6951429210283405E-2</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="110">
         <f t="dataTable" ref="C80:G84" dt2D="1" dtr="1" r1="I54" r2="I55" ca="1"/>
         <v>0.87136382120104172</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="110">
         <v>1.075885446946568</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="110">
         <v>1.3562923343417781</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="110">
         <v>1.7644389168197343</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="110">
         <v>2.4133596413566729</v>
       </c>
     </row>
@@ -4915,19 +4914,19 @@
       <c r="B81" s="2">
         <v>4.4451429210283409E-2</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="110">
         <v>0.98077406754290863</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="110">
         <v>1.2210444780641108</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="110">
         <v>1.55957925115278</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="110">
         <v>2.0721551033975731</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="110">
         <v>2.9394196475262482</v>
       </c>
     </row>
@@ -4935,19 +4934,19 @@
       <c r="B82" s="96">
         <v>4.1951429210283407E-2</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="110">
         <v>1.1073189270492059</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="110">
         <v>1.3931470216540573</v>
       </c>
-      <c r="E82" s="116">
+      <c r="E82" s="110">
         <v>1.8091844488115945</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="110">
         <v>2.470650991117223</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="110">
         <v>3.685579827067599</v>
       </c>
     </row>
@@ -4955,19 +4954,19 @@
       <c r="B83" s="96">
         <v>3.9451429210283405E-2</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="110">
         <v>1.2553620176675206</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="110">
         <v>1.6004576602881659</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="110">
         <v>2.122967331919186</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="110">
         <v>3.0070396310439702</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="110">
         <v>4.8264967057991823</v>
       </c>
     </row>
@@ -4975,19 +4974,19 @@
       <c r="B84" s="2">
         <v>3.695142921028341E-2</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="110">
         <v>1.4308860276217881</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="110">
         <v>1.8550059201754288</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="110">
         <v>2.5293229420049621</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="110">
         <v>3.7678545108690278</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="110">
         <v>6.7880795004642955</v>
       </c>
     </row>
@@ -5020,13 +5019,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -5284,17 +5283,17 @@
       <c r="A1" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115" t="s">
+      <c r="C1" s="117"/>
+      <c r="D1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -6757,7 +6756,7 @@
         <v>212</v>
       </c>
       <c r="C18" s="61"/>
-      <c r="D18" s="118">
+      <c r="D18" s="113">
         <f>D16*H8+D17*D7</f>
         <v>4.1951429210283407E-2</v>
       </c>
@@ -6915,51 +6914,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="115" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="I1" s="112" t="s">
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="I1" s="115" t="s">
         <v>315</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="S1" s="112" t="s">
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="S1" s="115" t="s">
         <v>439</v>
       </c>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="AB1" s="112" t="s">
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="115"/>
+      <c r="W1" s="115"/>
+      <c r="X1" s="115"/>
+      <c r="Y1" s="115"/>
+      <c r="AB1" s="115" t="s">
         <v>499</v>
       </c>
-      <c r="AC1" s="112"/>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="112"/>
-      <c r="AG1" s="112"/>
-      <c r="AH1" s="112"/>
-      <c r="AK1" s="112" t="s">
+      <c r="AC1" s="115"/>
+      <c r="AD1" s="115"/>
+      <c r="AE1" s="115"/>
+      <c r="AF1" s="115"/>
+      <c r="AG1" s="115"/>
+      <c r="AH1" s="115"/>
+      <c r="AK1" s="115" t="s">
         <v>232</v>
       </c>
-      <c r="AL1" s="112"/>
-      <c r="AM1" s="112"/>
-      <c r="AN1" s="112"/>
-      <c r="AO1" s="112"/>
-      <c r="AP1" s="112"/>
-      <c r="AQ1" s="112"/>
+      <c r="AL1" s="115"/>
+      <c r="AM1" s="115"/>
+      <c r="AN1" s="115"/>
+      <c r="AO1" s="115"/>
+      <c r="AP1" s="115"/>
+      <c r="AQ1" s="115"/>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
@@ -13744,14 +13743,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
       <c r="G1" s="100"/>
       <c r="H1" s="100"/>
       <c r="I1" s="100"/>
@@ -16740,13 +16739,13 @@
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
-      <c r="E2" s="114" t="s">
+      <c r="E2" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="41" t="s">
@@ -19616,13 +19615,13 @@
         <v>132</v>
       </c>
       <c r="D1" s="49"/>
-      <c r="E1" s="115" t="s">
+      <c r="E1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="41" t="s">
@@ -19950,13 +19949,13 @@
         <v>132</v>
       </c>
       <c r="C1" s="49"/>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
